--- a/Data/FlightPlan/FPL_31AUG26.xlsx
+++ b/Data/FlightPlan/FPL_31AUG26.xlsx
@@ -539,6 +539,9 @@
     <t>14:10</t>
   </si>
   <si>
+    <t>16:01</t>
+  </si>
+  <si>
     <t>16:30</t>
   </si>
   <si>
@@ -674,6 +677,9 @@
     <t>15:24</t>
   </si>
   <si>
+    <t>20:53</t>
+  </si>
+  <si>
     <t>KIX</t>
   </si>
   <si>
@@ -938,7 +944,7 @@
     <t>VN-A607</t>
   </si>
   <si>
-    <t>15:43</t>
+    <t>15:58</t>
   </si>
   <si>
     <t>VN-A629</t>
@@ -971,606 +977,612 @@
     <t>10:06</t>
   </si>
   <si>
+    <t>16:22</t>
+  </si>
+  <si>
+    <t>17:35</t>
+  </si>
+  <si>
+    <t>19:45</t>
+  </si>
+  <si>
+    <t>VN-A632</t>
+  </si>
+  <si>
+    <t>07:05</t>
+  </si>
+  <si>
+    <t>09:10</t>
+  </si>
+  <si>
+    <t>09:07</t>
+  </si>
+  <si>
+    <t>MFM</t>
+  </si>
+  <si>
+    <t>12:15</t>
+  </si>
+  <si>
+    <t>15:04</t>
+  </si>
+  <si>
+    <t>VN-A633</t>
+  </si>
+  <si>
+    <t>KUL</t>
+  </si>
+  <si>
+    <t>14:40</t>
+  </si>
+  <si>
+    <t>14:47</t>
+  </si>
+  <si>
+    <t>SAI</t>
+  </si>
+  <si>
+    <t>18:05</t>
+  </si>
+  <si>
+    <t>19:05</t>
+  </si>
+  <si>
+    <t>01:05</t>
+  </si>
+  <si>
+    <t>VN-A635</t>
+  </si>
+  <si>
+    <t>10:38</t>
+  </si>
+  <si>
+    <t>11:25</t>
+  </si>
+  <si>
+    <t>13:37</t>
+  </si>
+  <si>
+    <t>VN-A636</t>
+  </si>
+  <si>
+    <t>12:54</t>
+  </si>
+  <si>
+    <t>CAN</t>
+  </si>
+  <si>
+    <t>01:10</t>
+  </si>
+  <si>
+    <t>03:05</t>
+  </si>
+  <si>
+    <t>VN-A637</t>
+  </si>
+  <si>
+    <t>07:40</t>
+  </si>
+  <si>
+    <t>07:43</t>
+  </si>
+  <si>
+    <t>11:04</t>
+  </si>
+  <si>
+    <t>14:45</t>
+  </si>
+  <si>
+    <t>20:45</t>
+  </si>
+  <si>
+    <t>21:20</t>
+  </si>
+  <si>
+    <t>VN-A639</t>
+  </si>
+  <si>
+    <t>08:37</t>
+  </si>
+  <si>
+    <t>13:38</t>
+  </si>
+  <si>
+    <t>VTE</t>
+  </si>
+  <si>
+    <t>21:10</t>
+  </si>
+  <si>
+    <t>VN-A640</t>
+  </si>
+  <si>
+    <t>06:50</t>
+  </si>
+  <si>
+    <t>08:52</t>
+  </si>
+  <si>
+    <t>17:15</t>
+  </si>
+  <si>
+    <t>20:15</t>
+  </si>
+  <si>
+    <t>22:45</t>
+  </si>
+  <si>
+    <t>00:45</t>
+  </si>
+  <si>
+    <t>VN-A641</t>
+  </si>
+  <si>
+    <t>11:07</t>
+  </si>
+  <si>
+    <t>23:00</t>
+  </si>
+  <si>
+    <t>VN-A642</t>
+  </si>
+  <si>
+    <t>06:39</t>
+  </si>
+  <si>
+    <t>BMV</t>
+  </si>
+  <si>
+    <t>10:36</t>
+  </si>
+  <si>
+    <t>13:03</t>
+  </si>
+  <si>
+    <t>15:26</t>
+  </si>
+  <si>
+    <t>VN-A643</t>
+  </si>
+  <si>
+    <t>08:14</t>
+  </si>
+  <si>
+    <t>12:53</t>
+  </si>
+  <si>
+    <t>15:41</t>
+  </si>
+  <si>
+    <t>18:55</t>
+  </si>
+  <si>
+    <t>20:40</t>
+  </si>
+  <si>
+    <t>VN-A644</t>
+  </si>
+  <si>
+    <t>10:28</t>
+  </si>
+  <si>
+    <t>13:11</t>
+  </si>
+  <si>
     <t>15:53</t>
   </si>
   <si>
-    <t>17:35</t>
-  </si>
-  <si>
-    <t>19:45</t>
-  </si>
-  <si>
-    <t>VN-A632</t>
-  </si>
-  <si>
-    <t>07:05</t>
-  </si>
-  <si>
-    <t>09:10</t>
-  </si>
-  <si>
-    <t>09:07</t>
-  </si>
-  <si>
-    <t>MFM</t>
-  </si>
-  <si>
-    <t>12:15</t>
-  </si>
-  <si>
-    <t>15:04</t>
-  </si>
-  <si>
-    <t>VN-A633</t>
-  </si>
-  <si>
-    <t>KUL</t>
-  </si>
-  <si>
-    <t>14:40</t>
-  </si>
-  <si>
-    <t>14:47</t>
-  </si>
-  <si>
-    <t>SAI</t>
-  </si>
-  <si>
-    <t>18:05</t>
-  </si>
-  <si>
-    <t>19:05</t>
-  </si>
-  <si>
-    <t>01:05</t>
-  </si>
-  <si>
-    <t>VN-A635</t>
-  </si>
-  <si>
-    <t>10:38</t>
-  </si>
-  <si>
-    <t>11:25</t>
-  </si>
-  <si>
-    <t>13:37</t>
-  </si>
-  <si>
-    <t>VN-A636</t>
-  </si>
-  <si>
-    <t>12:54</t>
-  </si>
-  <si>
-    <t>CAN</t>
-  </si>
-  <si>
-    <t>01:10</t>
-  </si>
-  <si>
-    <t>03:05</t>
-  </si>
-  <si>
-    <t>VN-A637</t>
-  </si>
-  <si>
-    <t>07:40</t>
-  </si>
-  <si>
-    <t>07:43</t>
-  </si>
-  <si>
-    <t>11:04</t>
-  </si>
-  <si>
-    <t>14:45</t>
-  </si>
-  <si>
-    <t>20:45</t>
-  </si>
-  <si>
-    <t>21:20</t>
-  </si>
-  <si>
-    <t>VN-A639</t>
-  </si>
-  <si>
-    <t>08:37</t>
-  </si>
-  <si>
-    <t>13:38</t>
-  </si>
-  <si>
-    <t>18:55</t>
-  </si>
-  <si>
-    <t>20:40</t>
-  </si>
-  <si>
-    <t>VN-A640</t>
-  </si>
-  <si>
-    <t>06:50</t>
-  </si>
-  <si>
-    <t>08:52</t>
-  </si>
-  <si>
-    <t>17:15</t>
-  </si>
-  <si>
-    <t>20:15</t>
-  </si>
-  <si>
-    <t>22:45</t>
-  </si>
-  <si>
-    <t>00:45</t>
-  </si>
-  <si>
-    <t>VN-A641</t>
-  </si>
-  <si>
-    <t>11:07</t>
-  </si>
-  <si>
-    <t>23:00</t>
-  </si>
-  <si>
-    <t>VN-A642</t>
-  </si>
-  <si>
-    <t>06:39</t>
-  </si>
-  <si>
-    <t>BMV</t>
-  </si>
-  <si>
-    <t>10:36</t>
-  </si>
-  <si>
-    <t>13:03</t>
+    <t>06:15</t>
+  </si>
+  <si>
+    <t>VN-A645</t>
+  </si>
+  <si>
+    <t>05:20</t>
+  </si>
+  <si>
+    <t>06:36</t>
+  </si>
+  <si>
+    <t>08:29</t>
+  </si>
+  <si>
+    <t>11:45</t>
+  </si>
+  <si>
+    <t>13:17</t>
+  </si>
+  <si>
+    <t>VN-A646</t>
+  </si>
+  <si>
+    <t>HND</t>
+  </si>
+  <si>
+    <t>02:00</t>
+  </si>
+  <si>
+    <t>06:10</t>
+  </si>
+  <si>
+    <t>VN-A647</t>
+  </si>
+  <si>
+    <t>08:25</t>
+  </si>
+  <si>
+    <t>09:51</t>
+  </si>
+  <si>
+    <t>12:23</t>
+  </si>
+  <si>
+    <t>14:36</t>
+  </si>
+  <si>
+    <t>UIH</t>
+  </si>
+  <si>
+    <t>00:50</t>
+  </si>
+  <si>
+    <t>VN-A649</t>
+  </si>
+  <si>
+    <t>10:19</t>
+  </si>
+  <si>
+    <t>VN-A650</t>
+  </si>
+  <si>
+    <t>09:38</t>
+  </si>
+  <si>
+    <t>11:28</t>
+  </si>
+  <si>
+    <t>13:45</t>
+  </si>
+  <si>
+    <t>13:53</t>
+  </si>
+  <si>
+    <t>PKX</t>
+  </si>
+  <si>
+    <t>VN-A651</t>
+  </si>
+  <si>
+    <t>13:04</t>
+  </si>
+  <si>
+    <t>VN-A653</t>
+  </si>
+  <si>
+    <t>PER</t>
+  </si>
+  <si>
+    <t>16:18</t>
+  </si>
+  <si>
+    <t>22:20</t>
+  </si>
+  <si>
+    <t>VN-A654</t>
+  </si>
+  <si>
+    <t>VN-A655</t>
+  </si>
+  <si>
+    <t>08:35</t>
+  </si>
+  <si>
+    <t>13:21</t>
+  </si>
+  <si>
+    <t>VN-A656</t>
+  </si>
+  <si>
+    <t>12:42</t>
+  </si>
+  <si>
+    <t>01:15</t>
+  </si>
+  <si>
+    <t>02:20</t>
+  </si>
+  <si>
+    <t>04:50</t>
+  </si>
+  <si>
+    <t>VN-A657</t>
+  </si>
+  <si>
+    <t>SIN</t>
+  </si>
+  <si>
+    <t>VN-A658</t>
+  </si>
+  <si>
+    <t>16:45</t>
+  </si>
+  <si>
+    <t>00:20</t>
+  </si>
+  <si>
+    <t>03:55</t>
+  </si>
+  <si>
+    <t>VN-A661</t>
+  </si>
+  <si>
+    <t>15:01</t>
+  </si>
+  <si>
+    <t>21:30</t>
+  </si>
+  <si>
+    <t>VN-A663</t>
+  </si>
+  <si>
+    <t>09:21</t>
+  </si>
+  <si>
+    <t>VN-A666</t>
+  </si>
+  <si>
+    <t>08:09</t>
+  </si>
+  <si>
+    <t>12:03</t>
+  </si>
+  <si>
+    <t>15:48</t>
+  </si>
+  <si>
+    <t>21:05</t>
+  </si>
+  <si>
+    <t>VN-A667</t>
+  </si>
+  <si>
+    <t>06:45</t>
+  </si>
+  <si>
+    <t>08:43</t>
+  </si>
+  <si>
+    <t>15:13</t>
+  </si>
+  <si>
+    <t>23:25</t>
+  </si>
+  <si>
+    <t>FUK</t>
+  </si>
+  <si>
+    <t>02:05</t>
+  </si>
+  <si>
+    <t>VN-A668</t>
+  </si>
+  <si>
+    <t>08:34</t>
+  </si>
+  <si>
+    <t>11:18</t>
+  </si>
+  <si>
+    <t>VN-A669</t>
+  </si>
+  <si>
+    <t>VCL</t>
+  </si>
+  <si>
+    <t>08:19</t>
+  </si>
+  <si>
+    <t>12:34</t>
+  </si>
+  <si>
+    <t>VN-A670</t>
+  </si>
+  <si>
+    <t>07:08</t>
+  </si>
+  <si>
+    <t>08:51</t>
+  </si>
+  <si>
+    <t>10:10</t>
+  </si>
+  <si>
+    <t>14:44</t>
+  </si>
+  <si>
+    <t>01:30</t>
+  </si>
+  <si>
+    <t>02:30</t>
+  </si>
+  <si>
+    <t>04:10</t>
+  </si>
+  <si>
+    <t>VN-A671</t>
+  </si>
+  <si>
+    <t>06:49</t>
+  </si>
+  <si>
+    <t>08:32</t>
+  </si>
+  <si>
+    <t>12:51</t>
+  </si>
+  <si>
+    <t>17:55</t>
+  </si>
+  <si>
+    <t>VN-A673</t>
+  </si>
+  <si>
+    <t>10:01</t>
+  </si>
+  <si>
+    <t>13:10</t>
+  </si>
+  <si>
+    <t>23:45</t>
+  </si>
+  <si>
+    <t>VN-A674</t>
+  </si>
+  <si>
+    <t>13:36</t>
+  </si>
+  <si>
+    <t>00:55</t>
+  </si>
+  <si>
+    <t>VN-A675</t>
+  </si>
+  <si>
+    <t>13:22</t>
+  </si>
+  <si>
+    <t>VN-A676</t>
+  </si>
+  <si>
+    <t>06:05</t>
+  </si>
+  <si>
+    <t>07:37</t>
+  </si>
+  <si>
+    <t>09:41</t>
+  </si>
+  <si>
+    <t>FSZ</t>
+  </si>
+  <si>
+    <t>02:40</t>
+  </si>
+  <si>
+    <t>VN-A677</t>
+  </si>
+  <si>
+    <t>09:39</t>
+  </si>
+  <si>
+    <t>VN-A683</t>
+  </si>
+  <si>
+    <t>VN-A684</t>
+  </si>
+  <si>
+    <t>HKT</t>
+  </si>
+  <si>
+    <t>HKG</t>
+  </si>
+  <si>
+    <t>VN-A685</t>
+  </si>
+  <si>
+    <t>07:31</t>
+  </si>
+  <si>
+    <t>10:23</t>
+  </si>
+  <si>
+    <t>19:35</t>
+  </si>
+  <si>
+    <t>VN-A687</t>
+  </si>
+  <si>
+    <t>06:54</t>
+  </si>
+  <si>
+    <t>09:03</t>
+  </si>
+  <si>
+    <t>17:05</t>
+  </si>
+  <si>
+    <t>18:30</t>
+  </si>
+  <si>
+    <t>VN-A689</t>
+  </si>
+  <si>
+    <t>11:48</t>
+  </si>
+  <si>
+    <t>13:49</t>
+  </si>
+  <si>
+    <t>21:40</t>
+  </si>
+  <si>
+    <t>VN-A693</t>
+  </si>
+  <si>
+    <t>VN-A697</t>
+  </si>
+  <si>
+    <t>04:05</t>
+  </si>
+  <si>
+    <t>VN-A698</t>
+  </si>
+  <si>
+    <t>05:05</t>
+  </si>
+  <si>
+    <t>06:29</t>
+  </si>
+  <si>
+    <t>08:39</t>
+  </si>
+  <si>
+    <t>12:22</t>
+  </si>
+  <si>
+    <t>17:53</t>
+  </si>
+  <si>
+    <t>VN-A699</t>
+  </si>
+  <si>
+    <t>14:14</t>
+  </si>
+  <si>
+    <t>VN-A811</t>
+  </si>
+  <si>
+    <t>NQZ</t>
+  </si>
+  <si>
+    <t>08:15</t>
+  </si>
+  <si>
+    <t>VN-A812</t>
+  </si>
+  <si>
+    <t>OVB</t>
+  </si>
+  <si>
+    <t>VN-A814</t>
+  </si>
+  <si>
+    <t>UFA</t>
   </si>
   <si>
     <t>15:21</t>
   </si>
   <si>
-    <t>VN-A643</t>
-  </si>
-  <si>
-    <t>08:14</t>
-  </si>
-  <si>
-    <t>12:53</t>
-  </si>
-  <si>
-    <t>15:41</t>
-  </si>
-  <si>
-    <t>VTE</t>
-  </si>
-  <si>
-    <t>21:10</t>
-  </si>
-  <si>
-    <t>VN-A644</t>
-  </si>
-  <si>
-    <t>10:28</t>
-  </si>
-  <si>
-    <t>13:11</t>
-  </si>
-  <si>
-    <t>06:15</t>
-  </si>
-  <si>
-    <t>VN-A645</t>
-  </si>
-  <si>
-    <t>05:20</t>
-  </si>
-  <si>
-    <t>06:36</t>
-  </si>
-  <si>
-    <t>08:29</t>
-  </si>
-  <si>
-    <t>11:45</t>
-  </si>
-  <si>
-    <t>13:17</t>
-  </si>
-  <si>
-    <t>VN-A646</t>
-  </si>
-  <si>
-    <t>HND</t>
-  </si>
-  <si>
-    <t>02:00</t>
-  </si>
-  <si>
-    <t>06:10</t>
-  </si>
-  <si>
-    <t>VN-A647</t>
-  </si>
-  <si>
-    <t>08:25</t>
-  </si>
-  <si>
-    <t>09:51</t>
-  </si>
-  <si>
-    <t>12:23</t>
-  </si>
-  <si>
-    <t>14:36</t>
-  </si>
-  <si>
-    <t>UIH</t>
-  </si>
-  <si>
-    <t>00:50</t>
-  </si>
-  <si>
-    <t>VN-A649</t>
-  </si>
-  <si>
-    <t>10:19</t>
-  </si>
-  <si>
-    <t>VN-A650</t>
-  </si>
-  <si>
-    <t>09:38</t>
-  </si>
-  <si>
-    <t>11:28</t>
-  </si>
-  <si>
-    <t>13:45</t>
-  </si>
-  <si>
-    <t>13:53</t>
-  </si>
-  <si>
-    <t>PKX</t>
-  </si>
-  <si>
-    <t>VN-A651</t>
-  </si>
-  <si>
-    <t>13:04</t>
-  </si>
-  <si>
-    <t>VN-A653</t>
-  </si>
-  <si>
-    <t>PER</t>
-  </si>
-  <si>
-    <t>16:18</t>
-  </si>
-  <si>
-    <t>22:20</t>
-  </si>
-  <si>
-    <t>VN-A654</t>
-  </si>
-  <si>
-    <t>VN-A655</t>
-  </si>
-  <si>
-    <t>08:35</t>
-  </si>
-  <si>
-    <t>13:21</t>
-  </si>
-  <si>
-    <t>VN-A656</t>
-  </si>
-  <si>
-    <t>12:42</t>
-  </si>
-  <si>
-    <t>01:15</t>
-  </si>
-  <si>
-    <t>02:20</t>
-  </si>
-  <si>
-    <t>04:50</t>
-  </si>
-  <si>
-    <t>VN-A657</t>
-  </si>
-  <si>
-    <t>SIN</t>
-  </si>
-  <si>
-    <t>VN-A658</t>
-  </si>
-  <si>
-    <t>16:45</t>
-  </si>
-  <si>
-    <t>00:20</t>
-  </si>
-  <si>
-    <t>03:55</t>
-  </si>
-  <si>
-    <t>VN-A661</t>
-  </si>
-  <si>
-    <t>15:01</t>
-  </si>
-  <si>
-    <t>21:30</t>
-  </si>
-  <si>
-    <t>VN-A663</t>
-  </si>
-  <si>
-    <t>09:21</t>
-  </si>
-  <si>
-    <t>VN-A666</t>
-  </si>
-  <si>
-    <t>08:09</t>
-  </si>
-  <si>
-    <t>12:03</t>
-  </si>
-  <si>
-    <t>15:48</t>
-  </si>
-  <si>
-    <t>21:05</t>
-  </si>
-  <si>
-    <t>VN-A667</t>
-  </si>
-  <si>
-    <t>06:45</t>
-  </si>
-  <si>
-    <t>08:43</t>
-  </si>
-  <si>
-    <t>15:13</t>
-  </si>
-  <si>
-    <t>23:25</t>
-  </si>
-  <si>
-    <t>FUK</t>
-  </si>
-  <si>
-    <t>02:05</t>
-  </si>
-  <si>
-    <t>VN-A668</t>
-  </si>
-  <si>
-    <t>08:34</t>
-  </si>
-  <si>
-    <t>11:18</t>
-  </si>
-  <si>
-    <t>VN-A669</t>
-  </si>
-  <si>
-    <t>VCL</t>
-  </si>
-  <si>
-    <t>08:19</t>
-  </si>
-  <si>
-    <t>12:34</t>
-  </si>
-  <si>
-    <t>VN-A670</t>
-  </si>
-  <si>
-    <t>07:08</t>
-  </si>
-  <si>
-    <t>08:51</t>
-  </si>
-  <si>
-    <t>10:10</t>
-  </si>
-  <si>
-    <t>14:44</t>
-  </si>
-  <si>
-    <t>01:30</t>
-  </si>
-  <si>
-    <t>02:30</t>
-  </si>
-  <si>
-    <t>04:10</t>
-  </si>
-  <si>
-    <t>VN-A671</t>
-  </si>
-  <si>
-    <t>06:49</t>
-  </si>
-  <si>
-    <t>08:32</t>
-  </si>
-  <si>
-    <t>12:51</t>
-  </si>
-  <si>
-    <t>17:55</t>
-  </si>
-  <si>
-    <t>VN-A673</t>
-  </si>
-  <si>
-    <t>10:01</t>
-  </si>
-  <si>
-    <t>13:10</t>
-  </si>
-  <si>
-    <t>23:45</t>
-  </si>
-  <si>
-    <t>VN-A674</t>
-  </si>
-  <si>
-    <t>13:36</t>
-  </si>
-  <si>
-    <t>00:55</t>
-  </si>
-  <si>
-    <t>VN-A675</t>
-  </si>
-  <si>
-    <t>13:22</t>
-  </si>
-  <si>
-    <t>VN-A676</t>
-  </si>
-  <si>
-    <t>06:05</t>
-  </si>
-  <si>
-    <t>07:37</t>
-  </si>
-  <si>
-    <t>09:41</t>
-  </si>
-  <si>
-    <t>FSZ</t>
-  </si>
-  <si>
-    <t>02:40</t>
-  </si>
-  <si>
-    <t>VN-A677</t>
-  </si>
-  <si>
-    <t>09:39</t>
-  </si>
-  <si>
-    <t>VN-A683</t>
-  </si>
-  <si>
-    <t>VN-A684</t>
-  </si>
-  <si>
-    <t>HKT</t>
-  </si>
-  <si>
-    <t>HKG</t>
-  </si>
-  <si>
-    <t>VN-A685</t>
-  </si>
-  <si>
-    <t>07:31</t>
-  </si>
-  <si>
-    <t>10:23</t>
-  </si>
-  <si>
-    <t>19:35</t>
-  </si>
-  <si>
-    <t>VN-A687</t>
-  </si>
-  <si>
-    <t>06:54</t>
-  </si>
-  <si>
-    <t>09:03</t>
-  </si>
-  <si>
-    <t>17:05</t>
-  </si>
-  <si>
-    <t>18:30</t>
-  </si>
-  <si>
-    <t>VN-A689</t>
-  </si>
-  <si>
-    <t>11:48</t>
-  </si>
-  <si>
-    <t>13:49</t>
-  </si>
-  <si>
-    <t>21:40</t>
-  </si>
-  <si>
-    <t>VN-A693</t>
-  </si>
-  <si>
-    <t>VN-A697</t>
-  </si>
-  <si>
-    <t>04:05</t>
-  </si>
-  <si>
-    <t>VN-A698</t>
-  </si>
-  <si>
-    <t>05:05</t>
-  </si>
-  <si>
-    <t>06:29</t>
-  </si>
-  <si>
-    <t>08:39</t>
-  </si>
-  <si>
-    <t>12:22</t>
-  </si>
-  <si>
-    <t>17:53</t>
-  </si>
-  <si>
-    <t>VN-A699</t>
-  </si>
-  <si>
-    <t>14:14</t>
-  </si>
-  <si>
-    <t>VN-A811</t>
-  </si>
-  <si>
-    <t>NQZ</t>
-  </si>
-  <si>
-    <t>08:15</t>
-  </si>
-  <si>
-    <t>VN-A812</t>
-  </si>
-  <si>
-    <t>OVB</t>
-  </si>
-  <si>
-    <t>VN-A814</t>
-  </si>
-  <si>
-    <t>UFA</t>
-  </si>
-  <si>
     <t>VN-A815</t>
   </si>
   <si>
@@ -1610,7 +1622,7 @@
     <t>Total Record(s): 406</t>
   </si>
   <si>
-    <t xml:space="preserve">Generated on  Aug 31, 2026 14:18</t>
+    <t xml:space="preserve">Generated on  Aug 31, 2026 14:28</t>
   </si>
   <si>
     <t>Page 1 of 1</t>
@@ -4425,7 +4437,9 @@
       </c>
       <c r="K80" s="7"/>
       <c r="L80" s="7"/>
-      <c r="M80" s="7"/>
+      <c t="s" r="M80" s="7">
+        <v>176</v>
+      </c>
     </row>
     <row r="81" ht="14.25" customHeight="1">
       <c t="s" r="A81" s="6">
@@ -4451,7 +4465,7 @@
         <v>52</v>
       </c>
       <c t="s" r="I81" s="7">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c t="s" r="J81" s="7">
         <v>129</v>
@@ -4487,7 +4501,7 @@
         <v>160</v>
       </c>
       <c t="s" r="J82" s="7">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="K82" s="7"/>
       <c r="L82" s="7"/>
@@ -4517,10 +4531,10 @@
         <v>52</v>
       </c>
       <c t="s" r="I83" s="7">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c t="s" r="J83" s="7">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="K83" s="7"/>
       <c r="L83" s="7"/>
@@ -4553,7 +4567,7 @@
       </c>
       <c r="D85" s="7"/>
       <c t="s" r="E85" s="7">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F85" s="7">
         <v>321</v>
@@ -4565,15 +4579,15 @@
         <v>17</v>
       </c>
       <c t="s" r="I85" s="7">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c t="s" r="J85" s="7">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="K85" s="7"/>
       <c r="L85" s="7"/>
       <c t="s" r="M85" s="7">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="86" ht="14.25" customHeight="1">
@@ -4588,7 +4602,7 @@
       </c>
       <c r="D86" s="7"/>
       <c t="s" r="E86" s="7">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F86" s="7">
         <v>321</v>
@@ -4597,18 +4611,18 @@
         <v>17</v>
       </c>
       <c t="s" r="H86" s="8">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c t="s" r="I86" s="7">
         <v>115</v>
       </c>
       <c t="s" r="J86" s="7">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="K86" s="7"/>
       <c r="L86" s="7"/>
       <c t="s" r="M86" s="7">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="87" ht="14.25" customHeight="1">
@@ -4623,13 +4637,13 @@
       </c>
       <c r="D87" s="7"/>
       <c t="s" r="E87" s="7">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F87" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G87" s="8">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c t="s" r="H87" s="8">
         <v>17</v>
@@ -4643,7 +4657,7 @@
       <c r="K87" s="7"/>
       <c r="L87" s="7"/>
       <c t="s" r="M87" s="7">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="88" ht="14.25" customHeight="1">
@@ -4658,7 +4672,7 @@
       </c>
       <c r="D88" s="7"/>
       <c t="s" r="E88" s="7">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F88" s="7">
         <v>321</v>
@@ -4670,10 +4684,10 @@
         <v>52</v>
       </c>
       <c t="s" r="I88" s="7">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c t="s" r="J88" s="7">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="K88" s="7"/>
       <c r="L88" s="7"/>
@@ -4706,7 +4720,7 @@
       </c>
       <c r="D90" s="7"/>
       <c t="s" r="E90" s="7">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F90" s="7">
         <v>321</v>
@@ -4726,7 +4740,7 @@
       <c r="K90" s="7"/>
       <c r="L90" s="7"/>
       <c t="s" r="M90" s="7">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="91" ht="14.25" customHeight="1">
@@ -4741,7 +4755,7 @@
       </c>
       <c r="D91" s="7"/>
       <c t="s" r="E91" s="7">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F91" s="7">
         <v>321</v>
@@ -4756,12 +4770,12 @@
         <v>94</v>
       </c>
       <c t="s" r="J91" s="7">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="K91" s="7"/>
       <c r="L91" s="7"/>
       <c t="s" r="M91" s="7">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="92" ht="14.25" customHeight="1">
@@ -4776,7 +4790,7 @@
       </c>
       <c r="D92" s="7"/>
       <c t="s" r="E92" s="7">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F92" s="7">
         <v>321</v>
@@ -4785,7 +4799,7 @@
         <v>46</v>
       </c>
       <c t="s" r="H92" s="8">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c t="s" r="I92" s="7">
         <v>48</v>
@@ -4809,19 +4823,19 @@
       </c>
       <c r="D93" s="7"/>
       <c t="s" r="E93" s="7">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F93" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G93" s="8">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c t="s" r="H93" s="8">
         <v>46</v>
       </c>
       <c t="s" r="I93" s="7">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c t="s" r="J93" s="7">
         <v>54</v>
@@ -4857,7 +4871,7 @@
       </c>
       <c r="D95" s="7"/>
       <c t="s" r="E95" s="7">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F95" s="7">
         <v>321</v>
@@ -4872,12 +4886,12 @@
         <v>44</v>
       </c>
       <c t="s" r="J95" s="7">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="K95" s="7"/>
       <c r="L95" s="7"/>
       <c t="s" r="M95" s="7">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="96" ht="14.25" customHeight="1">
@@ -4892,7 +4906,7 @@
       </c>
       <c r="D96" s="7"/>
       <c t="s" r="E96" s="7">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F96" s="7">
         <v>321</v>
@@ -4907,12 +4921,12 @@
         <v>114</v>
       </c>
       <c t="s" r="J96" s="7">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="K96" s="7"/>
       <c r="L96" s="7"/>
       <c t="s" r="M96" s="7">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="97" ht="14.25" customHeight="1">
@@ -4927,7 +4941,7 @@
       </c>
       <c r="D97" s="7"/>
       <c t="s" r="E97" s="7">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F97" s="7">
         <v>321</v>
@@ -4947,7 +4961,7 @@
       <c r="K97" s="7"/>
       <c r="L97" s="7"/>
       <c t="s" r="M97" s="7">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="98" ht="14.25" customHeight="1">
@@ -4962,7 +4976,7 @@
       </c>
       <c r="D98" s="7"/>
       <c t="s" r="E98" s="7">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F98" s="7">
         <v>321</v>
@@ -4995,7 +5009,7 @@
       </c>
       <c r="D99" s="7"/>
       <c t="s" r="E99" s="7">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F99" s="7">
         <v>321</v>
@@ -5007,10 +5021,10 @@
         <v>46</v>
       </c>
       <c t="s" r="I99" s="7">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c t="s" r="J99" s="7">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="K99" s="7"/>
       <c r="L99" s="7"/>
@@ -5028,7 +5042,7 @@
       </c>
       <c r="D100" s="7"/>
       <c t="s" r="E100" s="7">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F100" s="7">
         <v>321</v>
@@ -5037,13 +5051,13 @@
         <v>46</v>
       </c>
       <c t="s" r="H100" s="8">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c t="s" r="I100" s="7">
         <v>39</v>
       </c>
       <c t="s" r="J100" s="7">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="K100" s="7"/>
       <c r="L100" s="7"/>
@@ -5061,19 +5075,19 @@
       </c>
       <c r="D101" s="7"/>
       <c t="s" r="E101" s="7">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F101" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G101" s="8">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c t="s" r="H101" s="8">
         <v>46</v>
       </c>
       <c t="s" r="I101" s="7">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c t="s" r="J101" s="7">
         <v>121</v>
@@ -5109,7 +5123,7 @@
       </c>
       <c r="D103" s="7"/>
       <c t="s" r="E103" s="7">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F103" s="7">
         <v>321</v>
@@ -5121,7 +5135,7 @@
         <v>52</v>
       </c>
       <c t="s" r="I103" s="7">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c t="s" r="J103" s="7">
         <v>143</v>
@@ -5129,7 +5143,7 @@
       <c r="K103" s="7"/>
       <c r="L103" s="7"/>
       <c t="s" r="M103" s="7">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="104" ht="14.25" customHeight="1">
@@ -5144,7 +5158,7 @@
       </c>
       <c r="D104" s="7"/>
       <c t="s" r="E104" s="7">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F104" s="7">
         <v>321</v>
@@ -5156,7 +5170,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I104" s="7">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c t="s" r="J104" s="7">
         <v>144</v>
@@ -5164,7 +5178,7 @@
       <c r="K104" s="7"/>
       <c r="L104" s="7"/>
       <c t="s" r="M104" s="7">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="105" ht="15" customHeight="1">
@@ -5179,7 +5193,7 @@
       </c>
       <c r="D105" s="7"/>
       <c t="s" r="E105" s="7">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F105" s="7">
         <v>321</v>
@@ -5199,7 +5213,7 @@
       <c r="K105" s="7"/>
       <c r="L105" s="7"/>
       <c t="s" r="M105" s="7">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="106" ht="14.25" customHeight="1">
@@ -5214,7 +5228,7 @@
       </c>
       <c r="D106" s="7"/>
       <c t="s" r="E106" s="7">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F106" s="7">
         <v>321</v>
@@ -5234,7 +5248,7 @@
       <c r="K106" s="7"/>
       <c r="L106" s="7"/>
       <c t="s" r="M106" s="7">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="107" ht="14.25" customHeight="1">
@@ -5249,7 +5263,7 @@
       </c>
       <c r="D107" s="7"/>
       <c t="s" r="E107" s="7">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F107" s="7">
         <v>321</v>
@@ -5264,11 +5278,13 @@
         <v>64</v>
       </c>
       <c t="s" r="J107" s="7">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="K107" s="7"/>
       <c r="L107" s="7"/>
-      <c r="M107" s="7"/>
+      <c t="s" r="M107" s="7">
+        <v>97</v>
+      </c>
     </row>
     <row r="108" ht="14.25" customHeight="1">
       <c t="s" r="A108" s="6">
@@ -5282,7 +5298,7 @@
       </c>
       <c r="D108" s="7"/>
       <c t="s" r="E108" s="7">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F108" s="7">
         <v>321</v>
@@ -5294,7 +5310,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I108" s="7">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c t="s" r="J108" s="7">
         <v>24</v>
@@ -5315,7 +5331,7 @@
       </c>
       <c r="D109" s="7"/>
       <c t="s" r="E109" s="7">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F109" s="7">
         <v>321</v>
@@ -5327,10 +5343,10 @@
         <v>66</v>
       </c>
       <c t="s" r="I109" s="7">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c t="s" r="J109" s="7">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="K109" s="7"/>
       <c r="L109" s="7"/>
@@ -5348,7 +5364,7 @@
       </c>
       <c r="D110" s="7"/>
       <c t="s" r="E110" s="7">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F110" s="7">
         <v>321</v>
@@ -5360,10 +5376,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I110" s="7">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c t="s" r="J110" s="7">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="K110" s="7"/>
       <c r="L110" s="7"/>
@@ -5396,7 +5412,7 @@
       </c>
       <c r="D112" s="7"/>
       <c t="s" r="E112" s="7">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F112" s="7">
         <v>321</v>
@@ -5411,12 +5427,12 @@
         <v>166</v>
       </c>
       <c t="s" r="J112" s="7">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="K112" s="7"/>
       <c r="L112" s="7"/>
       <c t="s" r="M112" s="7">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="113" ht="14.25" customHeight="1">
@@ -5431,7 +5447,7 @@
       </c>
       <c r="D113" s="7"/>
       <c t="s" r="E113" s="7">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F113" s="7">
         <v>321</v>
@@ -5443,14 +5459,16 @@
         <v>17</v>
       </c>
       <c t="s" r="I113" s="7">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c t="s" r="J113" s="7">
         <v>99</v>
       </c>
       <c r="K113" s="7"/>
       <c r="L113" s="7"/>
-      <c r="M113" s="7"/>
+      <c t="s" r="M113" s="7">
+        <v>222</v>
+      </c>
     </row>
     <row r="114" ht="14.25" customHeight="1">
       <c t="s" r="A114" s="6">
@@ -5464,7 +5482,7 @@
       </c>
       <c r="D114" s="7"/>
       <c t="s" r="E114" s="7">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F114" s="7">
         <v>321</v>
@@ -5473,13 +5491,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H114" s="8">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c t="s" r="I114" s="7">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c t="s" r="J114" s="7">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="K114" s="7"/>
       <c r="L114" s="7"/>
@@ -5512,7 +5530,7 @@
       </c>
       <c r="D116" s="7"/>
       <c t="s" r="E116" s="7">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="F116" s="7">
         <v>321</v>
@@ -5521,18 +5539,18 @@
         <v>46</v>
       </c>
       <c t="s" r="H116" s="8">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c t="s" r="I116" s="7">
         <v>102</v>
       </c>
       <c t="s" r="J116" s="7">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="K116" s="7"/>
       <c r="L116" s="7"/>
       <c t="s" r="M116" s="7">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="117" ht="14.25" customHeight="1">
@@ -5547,19 +5565,19 @@
       </c>
       <c r="D117" s="7"/>
       <c t="s" r="E117" s="7">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="F117" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G117" s="8">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c t="s" r="H117" s="8">
         <v>46</v>
       </c>
       <c t="s" r="I117" s="7">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c t="s" r="J117" s="7">
         <v>18</v>
@@ -5567,7 +5585,7 @@
       <c r="K117" s="7"/>
       <c r="L117" s="7"/>
       <c t="s" r="M117" s="7">
-        <v>227</v>
+        <v>229</v>
       </c>
     </row>
     <row r="118" ht="14.25" customHeight="1">
@@ -5582,7 +5600,7 @@
       </c>
       <c r="D118" s="7"/>
       <c t="s" r="E118" s="7">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="F118" s="7">
         <v>321</v>
@@ -5594,15 +5612,15 @@
         <v>169</v>
       </c>
       <c t="s" r="I118" s="7">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c t="s" r="J118" s="7">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="K118" s="7"/>
       <c r="L118" s="7"/>
       <c t="s" r="M118" s="7">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="119" ht="14.25" customHeight="1">
@@ -5617,7 +5635,7 @@
       </c>
       <c r="D119" s="7"/>
       <c t="s" r="E119" s="7">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="F119" s="7">
         <v>321</v>
@@ -5637,7 +5655,7 @@
       <c r="K119" s="7"/>
       <c r="L119" s="7"/>
       <c t="s" r="M119" s="7">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="120" ht="15" customHeight="1">
@@ -5652,7 +5670,7 @@
       </c>
       <c r="D120" s="7"/>
       <c t="s" r="E120" s="7">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="F120" s="7">
         <v>321</v>
@@ -5667,7 +5685,7 @@
         <v>97</v>
       </c>
       <c t="s" r="J120" s="7">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="K120" s="7"/>
       <c r="L120" s="7"/>
@@ -5685,7 +5703,7 @@
       </c>
       <c r="D121" s="7"/>
       <c t="s" r="E121" s="7">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="F121" s="7">
         <v>321</v>
@@ -5700,7 +5718,7 @@
         <v>159</v>
       </c>
       <c t="s" r="J121" s="7">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="K121" s="7"/>
       <c r="L121" s="7"/>
@@ -5718,7 +5736,7 @@
       </c>
       <c r="D122" s="7"/>
       <c t="s" r="E122" s="7">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="F122" s="7">
         <v>321</v>
@@ -5727,13 +5745,13 @@
         <v>46</v>
       </c>
       <c t="s" r="H122" s="8">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c t="s" r="I122" s="7">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c t="s" r="J122" s="7">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="K122" s="7"/>
       <c r="L122" s="7"/>
@@ -5751,22 +5769,22 @@
       </c>
       <c r="D123" s="7"/>
       <c t="s" r="E123" s="7">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="F123" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G123" s="8">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c t="s" r="H123" s="8">
         <v>46</v>
       </c>
       <c t="s" r="I123" s="7">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c t="s" r="J123" s="7">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="K123" s="7"/>
       <c r="L123" s="7"/>
@@ -5799,7 +5817,7 @@
       </c>
       <c r="D125" s="7"/>
       <c t="s" r="E125" s="7">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="F125" s="7">
         <v>321</v>
@@ -5811,7 +5829,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I125" s="7">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c t="s" r="J125" s="7">
         <v>88</v>
@@ -5819,7 +5837,7 @@
       <c r="K125" s="7"/>
       <c r="L125" s="7"/>
       <c t="s" r="M125" s="7">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="126" ht="14.25" customHeight="1">
@@ -5834,7 +5852,7 @@
       </c>
       <c r="D126" s="7"/>
       <c t="s" r="E126" s="7">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="F126" s="7">
         <v>321</v>
@@ -5846,7 +5864,7 @@
         <v>66</v>
       </c>
       <c t="s" r="I126" s="7">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c t="s" r="J126" s="7">
         <v>149</v>
@@ -5854,7 +5872,7 @@
       <c r="K126" s="7"/>
       <c r="L126" s="7"/>
       <c t="s" r="M126" s="7">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="127" ht="14.25" customHeight="1">
@@ -5869,7 +5887,7 @@
       </c>
       <c r="D127" s="7"/>
       <c t="s" r="E127" s="7">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="F127" s="7">
         <v>321</v>
@@ -5884,12 +5902,12 @@
         <v>34</v>
       </c>
       <c t="s" r="J127" s="7">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="K127" s="7"/>
       <c r="L127" s="7"/>
       <c t="s" r="M127" s="7">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="128" ht="14.25" customHeight="1">
@@ -5904,7 +5922,7 @@
       </c>
       <c r="D128" s="7"/>
       <c t="s" r="E128" s="7">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="F128" s="7">
         <v>321</v>
@@ -5913,10 +5931,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H128" s="8">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c t="s" r="I128" s="7">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c t="s" r="J128" s="7">
         <v>141</v>
@@ -5937,22 +5955,22 @@
       </c>
       <c r="D129" s="7"/>
       <c t="s" r="E129" s="7">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="F129" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G129" s="8">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c t="s" r="H129" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I129" s="7">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c t="s" r="J129" s="7">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="K129" s="7"/>
       <c r="L129" s="7"/>
@@ -5981,33 +5999,33 @@
         <v>7615</v>
       </c>
       <c t="s" r="C131" s="7">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="D131" s="7"/>
       <c t="s" r="E131" s="7">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="F131" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G131" s="8">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c t="s" r="H131" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I131" s="7">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c t="s" r="J131" s="7">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c t="s" r="K131" s="7">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="L131" s="7"/>
       <c t="s" r="M131" s="7">
-        <v>255</v>
+        <v>257</v>
       </c>
     </row>
     <row r="132" ht="14.25" customHeight="1">
@@ -6018,11 +6036,11 @@
         <v>7615</v>
       </c>
       <c t="s" r="C132" s="7">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="D132" s="7"/>
       <c t="s" r="E132" s="7">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="F132" s="7">
         <v>321</v>
@@ -6037,14 +6055,14 @@
         <v>144</v>
       </c>
       <c t="s" r="J132" s="7">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c t="s" r="K132" s="7">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="L132" s="7"/>
       <c t="s" r="M132" s="7">
-        <v>258</v>
+        <v>260</v>
       </c>
     </row>
     <row r="133" ht="14.25" customHeight="1">
@@ -6059,7 +6077,7 @@
       </c>
       <c r="D133" s="7"/>
       <c t="s" r="E133" s="7">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="F133" s="7">
         <v>321</v>
@@ -6071,17 +6089,17 @@
         <v>17</v>
       </c>
       <c t="s" r="I133" s="7">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c t="s" r="J133" s="7">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c t="s" r="K133" s="7">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="L133" s="7"/>
       <c t="s" r="M133" s="7">
-        <v>261</v>
+        <v>263</v>
       </c>
     </row>
     <row r="134" ht="14.25" customHeight="1">
@@ -6111,13 +6129,13 @@
       </c>
       <c r="D135" s="7"/>
       <c t="s" r="E135" s="7">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="F135" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G135" s="8">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c t="s" r="H135" s="8">
         <v>17</v>
@@ -6126,7 +6144,7 @@
         <v>146</v>
       </c>
       <c t="s" r="J135" s="7">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="K135" s="7"/>
       <c r="L135" s="7"/>
@@ -6146,7 +6164,7 @@
       </c>
       <c r="D136" s="7"/>
       <c t="s" r="E136" s="7">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="F136" s="7">
         <v>321</v>
@@ -6155,18 +6173,18 @@
         <v>17</v>
       </c>
       <c t="s" r="H136" s="8">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c t="s" r="I136" s="7">
         <v>20</v>
       </c>
       <c t="s" r="J136" s="7">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="K136" s="7"/>
       <c r="L136" s="7"/>
       <c t="s" r="M136" s="7">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="137" ht="14.25" customHeight="1">
@@ -6181,13 +6199,13 @@
       </c>
       <c r="D137" s="7"/>
       <c t="s" r="E137" s="7">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="F137" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G137" s="8">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c t="s" r="H137" s="8">
         <v>17</v>
@@ -6196,7 +6214,7 @@
         <v>23</v>
       </c>
       <c t="s" r="J137" s="7">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="K137" s="7"/>
       <c r="L137" s="7"/>
@@ -6214,7 +6232,7 @@
       </c>
       <c r="D138" s="7"/>
       <c t="s" r="E138" s="7">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="F138" s="7">
         <v>321</v>
@@ -6226,7 +6244,7 @@
         <v>42</v>
       </c>
       <c t="s" r="I138" s="7">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c t="s" r="J138" s="7">
         <v>166</v>
@@ -6262,13 +6280,13 @@
       </c>
       <c r="D140" s="7"/>
       <c t="s" r="E140" s="7">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="F140" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G140" s="8">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c t="s" r="H140" s="8">
         <v>17</v>
@@ -6297,7 +6315,7 @@
       </c>
       <c r="D141" s="7"/>
       <c t="s" r="E141" s="7">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="F141" s="7">
         <v>321</v>
@@ -6309,15 +6327,15 @@
         <v>66</v>
       </c>
       <c t="s" r="I141" s="7">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c t="s" r="J141" s="7">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="K141" s="7"/>
       <c r="L141" s="7"/>
       <c t="s" r="M141" s="7">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="142" ht="14.25" customHeight="1">
@@ -6332,7 +6350,7 @@
       </c>
       <c r="D142" s="7"/>
       <c t="s" r="E142" s="7">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="F142" s="7">
         <v>321</v>
@@ -6365,7 +6383,7 @@
       </c>
       <c r="D143" s="7"/>
       <c t="s" r="E143" s="7">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="F143" s="7">
         <v>321</v>
@@ -6380,7 +6398,7 @@
         <v>23</v>
       </c>
       <c t="s" r="J143" s="7">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="K143" s="7"/>
       <c r="L143" s="7"/>
@@ -6398,7 +6416,7 @@
       </c>
       <c r="D144" s="7"/>
       <c t="s" r="E144" s="7">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="F144" s="7">
         <v>321</v>
@@ -6410,7 +6428,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I144" s="7">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c t="s" r="J144" s="7">
         <v>50</v>
@@ -6431,7 +6449,7 @@
       </c>
       <c r="D145" s="7"/>
       <c t="s" r="E145" s="7">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="F145" s="7">
         <v>321</v>
@@ -6440,10 +6458,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H145" s="8">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c t="s" r="I145" s="7">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c t="s" r="J145" s="7">
         <v>28</v>
@@ -6479,7 +6497,7 @@
       </c>
       <c r="D147" s="7"/>
       <c t="s" r="E147" s="7">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="F147" s="7">
         <v>321</v>
@@ -6494,12 +6512,12 @@
         <v>144</v>
       </c>
       <c t="s" r="J147" s="7">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="K147" s="7"/>
       <c r="L147" s="7"/>
       <c t="s" r="M147" s="7">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="148" ht="14.25" customHeight="1">
@@ -6514,7 +6532,7 @@
       </c>
       <c r="D148" s="7"/>
       <c t="s" r="E148" s="7">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="F148" s="7">
         <v>321</v>
@@ -6529,12 +6547,12 @@
         <v>156</v>
       </c>
       <c t="s" r="J148" s="7">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="K148" s="7"/>
       <c r="L148" s="7"/>
       <c t="s" r="M148" s="7">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="149" ht="14.25" customHeight="1">
@@ -6549,7 +6567,7 @@
       </c>
       <c r="D149" s="7"/>
       <c t="s" r="E149" s="7">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="F149" s="7">
         <v>321</v>
@@ -6561,7 +6579,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I149" s="7">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c t="s" r="J149" s="7">
         <v>139</v>
@@ -6569,7 +6587,7 @@
       <c r="K149" s="7"/>
       <c r="L149" s="7"/>
       <c t="s" r="M149" s="7">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
     <row r="150" ht="15" customHeight="1">
@@ -6584,7 +6602,7 @@
       </c>
       <c r="D150" s="7"/>
       <c t="s" r="E150" s="7">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="F150" s="7">
         <v>321</v>
@@ -6596,10 +6614,10 @@
         <v>46</v>
       </c>
       <c t="s" r="I150" s="7">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c t="s" r="J150" s="7">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="K150" s="7"/>
       <c r="L150" s="7"/>
@@ -6617,7 +6635,7 @@
       </c>
       <c r="D151" s="7"/>
       <c t="s" r="E151" s="7">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="F151" s="7">
         <v>321</v>
@@ -6626,13 +6644,13 @@
         <v>46</v>
       </c>
       <c t="s" r="H151" s="8">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c t="s" r="I151" s="7">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c t="s" r="J151" s="7">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="K151" s="7"/>
       <c r="L151" s="7"/>
@@ -6650,22 +6668,22 @@
       </c>
       <c r="D152" s="7"/>
       <c t="s" r="E152" s="7">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="F152" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G152" s="8">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c t="s" r="H152" s="8">
         <v>46</v>
       </c>
       <c t="s" r="I152" s="7">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c t="s" r="J152" s="7">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="K152" s="7"/>
       <c r="L152" s="7"/>
@@ -6698,7 +6716,7 @@
       </c>
       <c r="D154" s="7"/>
       <c t="s" r="E154" s="7">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="F154" s="7">
         <v>321</v>
@@ -6710,10 +6728,10 @@
         <v>46</v>
       </c>
       <c t="s" r="I154" s="7">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c t="s" r="J154" s="7">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="K154" s="7"/>
       <c r="L154" s="7"/>
@@ -6733,7 +6751,7 @@
       </c>
       <c r="D155" s="7"/>
       <c t="s" r="E155" s="7">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="F155" s="7">
         <v>321</v>
@@ -6745,15 +6763,15 @@
         <v>52</v>
       </c>
       <c t="s" r="I155" s="7">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c t="s" r="J155" s="7">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="K155" s="7"/>
       <c r="L155" s="7"/>
       <c t="s" r="M155" s="7">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="156" ht="14.25" customHeight="1">
@@ -6768,7 +6786,7 @@
       </c>
       <c r="D156" s="7"/>
       <c t="s" r="E156" s="7">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="F156" s="7">
         <v>321</v>
@@ -6777,18 +6795,18 @@
         <v>52</v>
       </c>
       <c t="s" r="H156" s="8">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c t="s" r="I156" s="7">
         <v>174</v>
       </c>
       <c t="s" r="J156" s="7">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="K156" s="7"/>
       <c r="L156" s="7"/>
       <c t="s" r="M156" s="7">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="157" ht="14.25" customHeight="1">
@@ -6803,22 +6821,22 @@
       </c>
       <c r="D157" s="7"/>
       <c t="s" r="E157" s="7">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="F157" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G157" s="8">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c t="s" r="H157" s="8">
         <v>109</v>
       </c>
       <c t="s" r="I157" s="7">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c t="s" r="J157" s="7">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="K157" s="7"/>
       <c r="L157" s="7"/>
@@ -6836,7 +6854,7 @@
       </c>
       <c r="D158" s="7"/>
       <c t="s" r="E158" s="7">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="F158" s="7">
         <v>321</v>
@@ -6845,13 +6863,13 @@
         <v>109</v>
       </c>
       <c t="s" r="H158" s="8">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c t="s" r="I158" s="7">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c t="s" r="J158" s="7">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="K158" s="7"/>
       <c r="L158" s="7"/>
@@ -6869,13 +6887,13 @@
       </c>
       <c r="D159" s="7"/>
       <c t="s" r="E159" s="7">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="F159" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G159" s="8">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c t="s" r="H159" s="8">
         <v>17</v>
@@ -6884,7 +6902,7 @@
         <v>99</v>
       </c>
       <c t="s" r="J159" s="7">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="K159" s="7"/>
       <c r="L159" s="7"/>
@@ -6917,7 +6935,7 @@
       </c>
       <c r="D161" s="7"/>
       <c t="s" r="E161" s="7">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="F161" s="7">
         <v>321</v>
@@ -6929,7 +6947,7 @@
         <v>125</v>
       </c>
       <c t="s" r="I161" s="7">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c t="s" r="J161" s="7">
         <v>34</v>
@@ -6937,7 +6955,7 @@
       <c r="K161" s="7"/>
       <c r="L161" s="7"/>
       <c t="s" r="M161" s="7">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="162" ht="14.25" customHeight="1">
@@ -6952,7 +6970,7 @@
       </c>
       <c r="D162" s="7"/>
       <c t="s" r="E162" s="7">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="F162" s="7">
         <v>321</v>
@@ -6967,12 +6985,12 @@
         <v>20</v>
       </c>
       <c t="s" r="J162" s="7">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="K162" s="7"/>
       <c r="L162" s="7"/>
       <c t="s" r="M162" s="7">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="163" ht="14.25" customHeight="1">
@@ -6987,7 +7005,7 @@
       </c>
       <c r="D163" s="7"/>
       <c t="s" r="E163" s="7">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="F163" s="7">
         <v>321</v>
@@ -6999,10 +7017,10 @@
         <v>30</v>
       </c>
       <c t="s" r="I163" s="7">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c t="s" r="J163" s="7">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="K163" s="7"/>
       <c r="L163" s="7"/>
@@ -7035,7 +7053,7 @@
       </c>
       <c r="D165" s="7"/>
       <c t="s" r="E165" s="7">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="F165" s="7">
         <v>321</v>
@@ -7050,7 +7068,7 @@
         <v>114</v>
       </c>
       <c t="s" r="J165" s="7">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c t="s" r="K165" s="7">
         <v>144</v>
@@ -7072,7 +7090,7 @@
       </c>
       <c r="D166" s="7"/>
       <c t="s" r="E166" s="7">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="F166" s="7">
         <v>321</v>
@@ -7092,7 +7110,7 @@
       <c r="K166" s="7"/>
       <c r="L166" s="7"/>
       <c t="s" r="M166" s="7">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="167" ht="14.25" customHeight="1">
@@ -7107,7 +7125,7 @@
       </c>
       <c r="D167" s="7"/>
       <c t="s" r="E167" s="7">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="F167" s="7">
         <v>321</v>
@@ -7119,10 +7137,10 @@
         <v>46</v>
       </c>
       <c t="s" r="I167" s="7">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c t="s" r="J167" s="7">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="K167" s="7"/>
       <c r="L167" s="7"/>
@@ -7140,7 +7158,7 @@
       </c>
       <c r="D168" s="7"/>
       <c t="s" r="E168" s="7">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="F168" s="7">
         <v>321</v>
@@ -7149,13 +7167,13 @@
         <v>46</v>
       </c>
       <c t="s" r="H168" s="8">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c t="s" r="I168" s="7">
         <v>120</v>
       </c>
       <c t="s" r="J168" s="7">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="K168" s="7"/>
       <c r="L168" s="7"/>
@@ -7173,22 +7191,22 @@
       </c>
       <c r="D169" s="7"/>
       <c t="s" r="E169" s="7">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="F169" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G169" s="8">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c t="s" r="H169" s="8">
         <v>46</v>
       </c>
       <c t="s" r="I169" s="7">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c t="s" r="J169" s="7">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="K169" s="7"/>
       <c r="L169" s="7"/>
@@ -7221,7 +7239,7 @@
       </c>
       <c r="D171" s="7"/>
       <c t="s" r="E171" s="7">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="F171" s="7">
         <v>321</v>
@@ -7233,7 +7251,7 @@
         <v>46</v>
       </c>
       <c t="s" r="I171" s="7">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c t="s" r="J171" s="7">
         <v>36</v>
@@ -7241,7 +7259,7 @@
       <c r="K171" s="7"/>
       <c r="L171" s="7"/>
       <c t="s" r="M171" s="7">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="172" ht="14.25" customHeight="1">
@@ -7256,7 +7274,7 @@
       </c>
       <c r="D172" s="7"/>
       <c t="s" r="E172" s="7">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="F172" s="7">
         <v>321</v>
@@ -7265,10 +7283,10 @@
         <v>46</v>
       </c>
       <c t="s" r="H172" s="8">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c t="s" r="I172" s="7">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c t="s" r="J172" s="7">
         <v>161</v>
@@ -7289,22 +7307,22 @@
       </c>
       <c r="D173" s="7"/>
       <c t="s" r="E173" s="7">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="F173" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G173" s="8">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c t="s" r="H173" s="8">
         <v>46</v>
       </c>
       <c t="s" r="I173" s="7">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c t="s" r="J173" s="7">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="K173" s="7"/>
       <c r="L173" s="7"/>
@@ -7337,7 +7355,7 @@
       </c>
       <c r="D175" s="7"/>
       <c t="s" r="E175" s="7">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="F175" s="7">
         <v>321</v>
@@ -7349,7 +7367,7 @@
         <v>46</v>
       </c>
       <c t="s" r="I175" s="7">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c t="s" r="J175" s="7">
         <v>138</v>
@@ -7372,7 +7390,7 @@
       </c>
       <c r="D176" s="7"/>
       <c t="s" r="E176" s="7">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="F176" s="7">
         <v>321</v>
@@ -7392,7 +7410,7 @@
       <c r="K176" s="7"/>
       <c r="L176" s="7"/>
       <c t="s" r="M176" s="7">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="177" ht="14.25" customHeight="1">
@@ -7407,7 +7425,7 @@
       </c>
       <c r="D177" s="7"/>
       <c t="s" r="E177" s="7">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="F177" s="7">
         <v>321</v>
@@ -7440,7 +7458,7 @@
       </c>
       <c r="D178" s="7"/>
       <c t="s" r="E178" s="7">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="F178" s="7">
         <v>321</v>
@@ -7452,7 +7470,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I178" s="7">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c t="s" r="J178" s="7">
         <v>166</v>
@@ -7488,7 +7506,7 @@
       </c>
       <c r="D180" s="7"/>
       <c t="s" r="E180" s="7">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="F180" s="7">
         <v>321</v>
@@ -7500,7 +7518,7 @@
         <v>31</v>
       </c>
       <c t="s" r="I180" s="7">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c t="s" r="J180" s="7">
         <v>167</v>
@@ -7508,7 +7526,7 @@
       <c r="K180" s="7"/>
       <c r="L180" s="7"/>
       <c t="s" r="M180" s="7">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="181" ht="14.25" customHeight="1">
@@ -7523,7 +7541,7 @@
       </c>
       <c r="D181" s="7"/>
       <c t="s" r="E181" s="7">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="F181" s="7">
         <v>321</v>
@@ -7535,7 +7553,7 @@
         <v>52</v>
       </c>
       <c t="s" r="I181" s="7">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c t="s" r="J181" s="7">
         <v>172</v>
@@ -7543,7 +7561,7 @@
       <c r="K181" s="7"/>
       <c r="L181" s="7"/>
       <c t="s" r="M181" s="7">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="182" ht="14.25" customHeight="1">
@@ -7558,7 +7576,7 @@
       </c>
       <c r="D182" s="7"/>
       <c t="s" r="E182" s="7">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="F182" s="7">
         <v>321</v>
@@ -7578,7 +7596,7 @@
       <c r="K182" s="7"/>
       <c r="L182" s="7"/>
       <c t="s" r="M182" s="7">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="183" ht="14.25" customHeight="1">
@@ -7593,7 +7611,7 @@
       </c>
       <c r="D183" s="7"/>
       <c t="s" r="E183" s="7">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="F183" s="7">
         <v>321</v>
@@ -7626,7 +7644,7 @@
       </c>
       <c r="D184" s="7"/>
       <c t="s" r="E184" s="7">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="F184" s="7">
         <v>321</v>
@@ -7638,7 +7656,7 @@
         <v>46</v>
       </c>
       <c t="s" r="I184" s="7">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c t="s" r="J184" s="7">
         <v>23</v>
@@ -7659,7 +7677,7 @@
       </c>
       <c r="D185" s="7"/>
       <c t="s" r="E185" s="7">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="F185" s="7">
         <v>321</v>
@@ -7671,10 +7689,10 @@
         <v>52</v>
       </c>
       <c t="s" r="I185" s="7">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c t="s" r="J185" s="7">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="K185" s="7"/>
       <c r="L185" s="7"/>
@@ -7692,7 +7710,7 @@
       </c>
       <c r="D186" s="7"/>
       <c t="s" r="E186" s="7">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="F186" s="7">
         <v>321</v>
@@ -7704,7 +7722,7 @@
         <v>46</v>
       </c>
       <c t="s" r="I186" s="7">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c t="s" r="J186" s="7">
         <v>43</v>
@@ -7740,7 +7758,7 @@
       </c>
       <c r="D188" s="7"/>
       <c t="s" r="E188" s="7">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="F188" s="7">
         <v>321</v>
@@ -7752,15 +7770,15 @@
         <v>66</v>
       </c>
       <c t="s" r="I188" s="7">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c t="s" r="J188" s="7">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="K188" s="7"/>
       <c r="L188" s="7"/>
       <c t="s" r="M188" s="7">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="189" ht="14.25" customHeight="1">
@@ -7775,7 +7793,7 @@
       </c>
       <c r="D189" s="7"/>
       <c t="s" r="E189" s="7">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="F189" s="7">
         <v>321</v>
@@ -7787,15 +7805,15 @@
         <v>17</v>
       </c>
       <c t="s" r="I189" s="7">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c t="s" r="J189" s="7">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="K189" s="7"/>
       <c r="L189" s="7"/>
       <c t="s" r="M189" s="7">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="190" ht="15" customHeight="1">
@@ -7810,7 +7828,7 @@
       </c>
       <c r="D190" s="7"/>
       <c t="s" r="E190" s="7">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="F190" s="7">
         <v>321</v>
@@ -7830,7 +7848,7 @@
       <c r="K190" s="7"/>
       <c r="L190" s="7"/>
       <c t="s" r="M190" s="7">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="191" ht="14.25" customHeight="1">
@@ -7845,7 +7863,7 @@
       </c>
       <c r="D191" s="7"/>
       <c t="s" r="E191" s="7">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="F191" s="7">
         <v>321</v>
@@ -7865,7 +7883,7 @@
       <c r="K191" s="7"/>
       <c r="L191" s="7"/>
       <c t="s" r="M191" s="7">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="192" ht="14.25" customHeight="1">
@@ -7880,7 +7898,7 @@
       </c>
       <c r="D192" s="7"/>
       <c t="s" r="E192" s="7">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="F192" s="7">
         <v>321</v>
@@ -7892,10 +7910,10 @@
         <v>46</v>
       </c>
       <c t="s" r="I192" s="7">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c t="s" r="J192" s="7">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="K192" s="7"/>
       <c r="L192" s="7"/>
@@ -7928,7 +7946,7 @@
       </c>
       <c r="D194" s="7"/>
       <c t="s" r="E194" s="7">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="F194" s="7">
         <v>321</v>
@@ -7940,7 +7958,7 @@
         <v>169</v>
       </c>
       <c t="s" r="I194" s="7">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c t="s" r="J194" s="7">
         <v>154</v>
@@ -7948,7 +7966,7 @@
       <c r="K194" s="7"/>
       <c r="L194" s="7"/>
       <c t="s" r="M194" s="7">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="195" ht="15" customHeight="1">
@@ -7963,7 +7981,7 @@
       </c>
       <c r="D195" s="7"/>
       <c t="s" r="E195" s="7">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="F195" s="7">
         <v>321</v>
@@ -7978,12 +7996,12 @@
         <v>166</v>
       </c>
       <c t="s" r="J195" s="7">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="K195" s="7"/>
       <c r="L195" s="7"/>
       <c t="s" r="M195" s="7">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="196" ht="14.25" customHeight="1">
@@ -7998,7 +8016,7 @@
       </c>
       <c r="D196" s="7"/>
       <c t="s" r="E196" s="7">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="F196" s="7">
         <v>321</v>
@@ -8007,18 +8025,18 @@
         <v>52</v>
       </c>
       <c t="s" r="H196" s="8">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c t="s" r="I196" s="7">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c t="s" r="J196" s="7">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="K196" s="7"/>
       <c r="L196" s="7"/>
       <c t="s" r="M196" s="7">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="197" ht="14.25" customHeight="1">
@@ -8033,13 +8051,13 @@
       </c>
       <c r="D197" s="7"/>
       <c t="s" r="E197" s="7">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="F197" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G197" s="8">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c t="s" r="H197" s="8">
         <v>52</v>
@@ -8066,7 +8084,7 @@
       </c>
       <c r="D198" s="7"/>
       <c t="s" r="E198" s="7">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="F198" s="7">
         <v>321</v>
@@ -8075,13 +8093,13 @@
         <v>52</v>
       </c>
       <c t="s" r="H198" s="8">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c t="s" r="I198" s="7">
         <v>129</v>
       </c>
       <c t="s" r="J198" s="7">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="K198" s="7"/>
       <c r="L198" s="7"/>
@@ -8099,13 +8117,13 @@
       </c>
       <c r="D199" s="7"/>
       <c t="s" r="E199" s="7">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="F199" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G199" s="8">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c t="s" r="H199" s="8">
         <v>52</v>
@@ -8147,7 +8165,7 @@
       </c>
       <c r="D201" s="7"/>
       <c t="s" r="E201" s="7">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="F201" s="7">
         <v>321</v>
@@ -8156,18 +8174,18 @@
         <v>17</v>
       </c>
       <c t="s" r="H201" s="8">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c t="s" r="I201" s="7">
         <v>113</v>
       </c>
       <c t="s" r="J201" s="7">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="K201" s="7"/>
       <c r="L201" s="7"/>
       <c t="s" r="M201" s="7">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="202" ht="14.25" customHeight="1">
@@ -8182,13 +8200,13 @@
       </c>
       <c r="D202" s="7"/>
       <c t="s" r="E202" s="7">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="F202" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G202" s="8">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c t="s" r="H202" s="8">
         <v>17</v>
@@ -8197,12 +8215,12 @@
         <v>34</v>
       </c>
       <c t="s" r="J202" s="7">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="K202" s="7"/>
       <c r="L202" s="7"/>
       <c t="s" r="M202" s="7">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="203" ht="14.25" customHeight="1">
@@ -8217,7 +8235,7 @@
       </c>
       <c r="D203" s="7"/>
       <c t="s" r="E203" s="7">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="F203" s="7">
         <v>321</v>
@@ -8226,13 +8244,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H203" s="8">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c t="s" r="I203" s="7">
         <v>97</v>
       </c>
       <c t="s" r="J203" s="7">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="K203" s="7"/>
       <c r="L203" s="7"/>
@@ -8250,22 +8268,22 @@
       </c>
       <c r="D204" s="7"/>
       <c t="s" r="E204" s="7">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="F204" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G204" s="8">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c t="s" r="H204" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I204" s="7">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c t="s" r="J204" s="7">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="K204" s="7"/>
       <c r="L204" s="7"/>
@@ -8283,7 +8301,7 @@
       </c>
       <c r="D205" s="7"/>
       <c t="s" r="E205" s="7">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="F205" s="7">
         <v>321</v>
@@ -8295,7 +8313,7 @@
         <v>30</v>
       </c>
       <c t="s" r="I205" s="7">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c t="s" r="J205" s="7">
         <v>56</v>
@@ -8331,7 +8349,7 @@
       </c>
       <c r="D207" s="7"/>
       <c t="s" r="E207" s="7">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="F207" s="7">
         <v>321</v>
@@ -8351,7 +8369,7 @@
       <c r="K207" s="7"/>
       <c r="L207" s="7"/>
       <c t="s" r="M207" s="7">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="208" ht="14.25" customHeight="1">
@@ -8366,7 +8384,7 @@
       </c>
       <c r="D208" s="7"/>
       <c t="s" r="E208" s="7">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="F208" s="7">
         <v>321</v>
@@ -8378,7 +8396,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I208" s="7">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c t="s" r="J208" s="7">
         <v>20</v>
@@ -8386,7 +8404,7 @@
       <c r="K208" s="7"/>
       <c r="L208" s="7"/>
       <c t="s" r="M208" s="7">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="209" ht="14.25" customHeight="1">
@@ -8401,7 +8419,7 @@
       </c>
       <c r="D209" s="7"/>
       <c t="s" r="E209" s="7">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="F209" s="7">
         <v>321</v>
@@ -8413,10 +8431,10 @@
         <v>31</v>
       </c>
       <c t="s" r="I209" s="7">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c t="s" r="J209" s="7">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="K209" s="7"/>
       <c r="L209" s="7"/>
@@ -8434,7 +8452,7 @@
       </c>
       <c r="D210" s="7"/>
       <c t="s" r="E210" s="7">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="F210" s="7">
         <v>321</v>
@@ -8449,7 +8467,7 @@
         <v>39</v>
       </c>
       <c t="s" r="J210" s="7">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="K210" s="7"/>
       <c r="L210" s="7"/>
@@ -8482,7 +8500,7 @@
       </c>
       <c r="D212" s="7"/>
       <c t="s" r="E212" s="7">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="F212" s="7">
         <v>321</v>
@@ -8517,7 +8535,7 @@
       </c>
       <c r="D213" s="7"/>
       <c t="s" r="E213" s="7">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="F213" s="7">
         <v>321</v>
@@ -8529,15 +8547,15 @@
         <v>119</v>
       </c>
       <c t="s" r="I213" s="7">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c t="s" r="J213" s="7">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="K213" s="7"/>
       <c r="L213" s="7"/>
       <c t="s" r="M213" s="7">
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="214" ht="14.25" customHeight="1">
@@ -8552,7 +8570,7 @@
       </c>
       <c r="D214" s="7"/>
       <c t="s" r="E214" s="7">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="F214" s="7">
         <v>321</v>
@@ -8564,7 +8582,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I214" s="7">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c t="s" r="J214" s="7">
         <v>151</v>
@@ -8572,7 +8590,7 @@
       <c r="K214" s="7"/>
       <c r="L214" s="7"/>
       <c t="s" r="M214" s="7">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="215" ht="15" customHeight="1">
@@ -8587,7 +8605,7 @@
       </c>
       <c r="D215" s="7"/>
       <c t="s" r="E215" s="7">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="F215" s="7">
         <v>321</v>
@@ -8596,13 +8614,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H215" s="8">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c t="s" r="I215" s="7">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c t="s" r="J215" s="7">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="K215" s="7"/>
       <c r="L215" s="7"/>
@@ -8620,19 +8638,19 @@
       </c>
       <c r="D216" s="7"/>
       <c t="s" r="E216" s="7">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="F216" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G216" s="8">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c t="s" r="H216" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I216" s="7">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c t="s" r="J216" s="7">
         <v>40</v>
@@ -8653,7 +8671,7 @@
       </c>
       <c r="D217" s="7"/>
       <c t="s" r="E217" s="7">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="F217" s="7">
         <v>321</v>
@@ -8662,13 +8680,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H217" s="8">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c t="s" r="I217" s="7">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c t="s" r="J217" s="7">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="K217" s="7"/>
       <c r="L217" s="7"/>
@@ -8686,22 +8704,22 @@
       </c>
       <c r="D218" s="7"/>
       <c t="s" r="E218" s="7">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="F218" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G218" s="8">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c t="s" r="H218" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I218" s="7">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c t="s" r="J218" s="7">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="K218" s="7"/>
       <c r="L218" s="7"/>
@@ -8734,7 +8752,7 @@
       </c>
       <c r="D220" s="7"/>
       <c t="s" r="E220" s="7">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="F220" s="7">
         <v>321</v>
@@ -8749,12 +8767,12 @@
         <v>44</v>
       </c>
       <c t="s" r="J220" s="7">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="K220" s="7"/>
       <c r="L220" s="7"/>
       <c t="s" r="M220" s="7">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="221" ht="14.25" customHeight="1">
@@ -8769,7 +8787,7 @@
       </c>
       <c r="D221" s="7"/>
       <c t="s" r="E221" s="7">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="F221" s="7">
         <v>321</v>
@@ -8789,7 +8807,7 @@
       <c r="K221" s="7"/>
       <c r="L221" s="7"/>
       <c t="s" r="M221" s="7">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="222" ht="14.25" customHeight="1">
@@ -8804,7 +8822,7 @@
       </c>
       <c r="D222" s="7"/>
       <c t="s" r="E222" s="7">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="F222" s="7">
         <v>321</v>
@@ -8824,7 +8842,7 @@
       <c r="K222" s="7"/>
       <c r="L222" s="7"/>
       <c t="s" r="M222" s="7">
-        <v>351</v>
+        <v>353</v>
       </c>
     </row>
     <row r="223" ht="14.25" customHeight="1">
@@ -8839,7 +8857,7 @@
       </c>
       <c r="D223" s="7"/>
       <c t="s" r="E223" s="7">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="F223" s="7">
         <v>321</v>
@@ -8854,7 +8872,7 @@
         <v>75</v>
       </c>
       <c t="s" r="J223" s="7">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="K223" s="7"/>
       <c r="L223" s="7"/>
@@ -8872,7 +8890,7 @@
       </c>
       <c r="D224" s="7"/>
       <c t="s" r="E224" s="7">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="F224" s="7">
         <v>321</v>
@@ -8887,7 +8905,7 @@
         <v>48</v>
       </c>
       <c t="s" r="J224" s="7">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="K224" s="7"/>
       <c r="L224" s="7"/>
@@ -8905,7 +8923,7 @@
       </c>
       <c r="D225" s="7"/>
       <c t="s" r="E225" s="7">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="F225" s="7">
         <v>321</v>
@@ -8917,7 +8935,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I225" s="7">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c t="s" r="J225" s="7">
         <v>110</v>
@@ -8953,7 +8971,7 @@
       </c>
       <c r="D227" s="7"/>
       <c t="s" r="E227" s="7">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="F227" s="7">
         <v>321</v>
@@ -8968,12 +8986,12 @@
         <v>32</v>
       </c>
       <c t="s" r="J227" s="7">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="K227" s="7"/>
       <c r="L227" s="7"/>
       <c t="s" r="M227" s="7">
-        <v>355</v>
+        <v>357</v>
       </c>
     </row>
     <row r="228" ht="14.25" customHeight="1">
@@ -8988,7 +9006,7 @@
       </c>
       <c r="D228" s="7"/>
       <c t="s" r="E228" s="7">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="F228" s="7">
         <v>321</v>
@@ -8997,7 +9015,7 @@
         <v>46</v>
       </c>
       <c t="s" r="H228" s="8">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c t="s" r="I228" s="7">
         <v>89</v>
@@ -9008,7 +9026,7 @@
       <c r="K228" s="7"/>
       <c r="L228" s="7"/>
       <c t="s" r="M228" s="7">
-        <v>356</v>
+        <v>358</v>
       </c>
     </row>
     <row r="229" ht="14.25" customHeight="1">
@@ -9023,13 +9041,13 @@
       </c>
       <c r="D229" s="7"/>
       <c t="s" r="E229" s="7">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="F229" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G229" s="8">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c t="s" r="H229" s="8">
         <v>46</v>
@@ -9043,7 +9061,7 @@
       <c r="K229" s="7"/>
       <c r="L229" s="7"/>
       <c t="s" r="M229" s="7">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="230" ht="15" customHeight="1">
@@ -9051,14 +9069,14 @@
         <v>13</v>
       </c>
       <c r="B230" s="7">
-        <v>331</v>
+        <v>1831</v>
       </c>
       <c t="s" r="C230" s="7">
         <v>14</v>
       </c>
       <c r="D230" s="7"/>
       <c t="s" r="E230" s="7">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="F230" s="7">
         <v>321</v>
@@ -9067,13 +9085,13 @@
         <v>46</v>
       </c>
       <c t="s" r="H230" s="8">
-        <v>31</v>
+        <v>359</v>
       </c>
       <c t="s" r="I230" s="7">
-        <v>86</v>
+        <v>190</v>
       </c>
       <c t="s" r="J230" s="7">
-        <v>232</v>
+        <v>300</v>
       </c>
       <c r="K230" s="7"/>
       <c r="L230" s="7"/>
@@ -9084,63 +9102,45 @@
         <v>13</v>
       </c>
       <c r="B231" s="7">
-        <v>328</v>
+        <v>1832</v>
       </c>
       <c t="s" r="C231" s="7">
         <v>14</v>
       </c>
       <c r="D231" s="7"/>
       <c t="s" r="E231" s="7">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="F231" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G231" s="8">
-        <v>31</v>
+        <v>359</v>
       </c>
       <c t="s" r="H231" s="8">
         <v>46</v>
       </c>
       <c t="s" r="I231" s="7">
-        <v>357</v>
+        <v>281</v>
       </c>
       <c t="s" r="J231" s="7">
-        <v>120</v>
+        <v>360</v>
       </c>
       <c r="K231" s="7"/>
       <c r="L231" s="7"/>
       <c r="M231" s="7"/>
     </row>
     <row r="232" ht="14.25" customHeight="1">
-      <c t="s" r="A232" s="6">
-        <v>13</v>
-      </c>
-      <c r="B232" s="7">
-        <v>646</v>
-      </c>
-      <c t="s" r="C232" s="7">
-        <v>14</v>
-      </c>
+      <c r="A232" s="6"/>
+      <c r="B232" s="7"/>
+      <c r="C232" s="7"/>
       <c r="D232" s="7"/>
-      <c t="s" r="E232" s="7">
-        <v>354</v>
-      </c>
-      <c r="F232" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G232" s="8">
-        <v>46</v>
-      </c>
-      <c t="s" r="H232" s="8">
-        <v>52</v>
-      </c>
-      <c t="s" r="I232" s="7">
-        <v>358</v>
-      </c>
-      <c t="s" r="J232" s="7">
-        <v>177</v>
-      </c>
+      <c r="E232" s="7"/>
+      <c r="F232" s="7"/>
+      <c r="G232" s="8"/>
+      <c r="H232" s="8"/>
+      <c r="I232" s="7"/>
+      <c r="J232" s="7"/>
       <c r="K232" s="7"/>
       <c r="L232" s="7"/>
       <c r="M232" s="7"/>
@@ -9150,62 +9150,84 @@
         <v>13</v>
       </c>
       <c r="B233" s="7">
-        <v>1649</v>
+        <v>1242</v>
       </c>
       <c t="s" r="C233" s="7">
         <v>14</v>
       </c>
       <c r="D233" s="7"/>
       <c t="s" r="E233" s="7">
-        <v>354</v>
+        <v>361</v>
       </c>
       <c r="F233" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G233" s="8">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c t="s" r="H233" s="8">
-        <v>46</v>
+        <v>104</v>
       </c>
       <c t="s" r="I233" s="7">
-        <v>178</v>
+        <v>362</v>
       </c>
       <c t="s" r="J233" s="7">
-        <v>162</v>
+        <v>144</v>
       </c>
       <c r="K233" s="7"/>
       <c r="L233" s="7"/>
-      <c r="M233" s="7"/>
+      <c t="s" r="M233" s="7">
+        <v>363</v>
+      </c>
     </row>
     <row r="234" ht="14.25" customHeight="1">
-      <c r="A234" s="6"/>
-      <c r="B234" s="7"/>
-      <c r="C234" s="7"/>
+      <c t="s" r="A234" s="6">
+        <v>13</v>
+      </c>
+      <c r="B234" s="7">
+        <v>1241</v>
+      </c>
+      <c t="s" r="C234" s="7">
+        <v>14</v>
+      </c>
       <c r="D234" s="7"/>
-      <c r="E234" s="7"/>
-      <c r="F234" s="7"/>
-      <c r="G234" s="8"/>
-      <c r="H234" s="8"/>
-      <c r="I234" s="7"/>
-      <c r="J234" s="7"/>
+      <c t="s" r="E234" s="7">
+        <v>361</v>
+      </c>
+      <c r="F234" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G234" s="8">
+        <v>104</v>
+      </c>
+      <c t="s" r="H234" s="8">
+        <v>46</v>
+      </c>
+      <c t="s" r="I234" s="7">
+        <v>59</v>
+      </c>
+      <c t="s" r="J234" s="7">
+        <v>172</v>
+      </c>
       <c r="K234" s="7"/>
       <c r="L234" s="7"/>
-      <c r="M234" s="7"/>
+      <c t="s" r="M234" s="7">
+        <v>277</v>
+      </c>
     </row>
     <row r="235" ht="15" customHeight="1">
       <c t="s" r="A235" s="6">
         <v>13</v>
       </c>
       <c r="B235" s="7">
-        <v>1242</v>
+        <v>807</v>
       </c>
       <c t="s" r="C235" s="7">
         <v>14</v>
       </c>
       <c r="D235" s="7"/>
       <c t="s" r="E235" s="7">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="F235" s="7">
         <v>321</v>
@@ -9214,18 +9236,18 @@
         <v>46</v>
       </c>
       <c t="s" r="H235" s="8">
-        <v>104</v>
+        <v>37</v>
       </c>
       <c t="s" r="I235" s="7">
-        <v>360</v>
+        <v>271</v>
       </c>
       <c t="s" r="J235" s="7">
-        <v>144</v>
+        <v>353</v>
       </c>
       <c r="K235" s="7"/>
       <c r="L235" s="7"/>
       <c t="s" r="M235" s="7">
-        <v>361</v>
+        <v>247</v>
       </c>
     </row>
     <row r="236" ht="14.25" customHeight="1">
@@ -9233,49 +9255,47 @@
         <v>13</v>
       </c>
       <c r="B236" s="7">
-        <v>1241</v>
+        <v>800</v>
       </c>
       <c t="s" r="C236" s="7">
         <v>14</v>
       </c>
       <c r="D236" s="7"/>
       <c t="s" r="E236" s="7">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="F236" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G236" s="8">
-        <v>104</v>
+        <v>37</v>
       </c>
       <c t="s" r="H236" s="8">
         <v>46</v>
       </c>
       <c t="s" r="I236" s="7">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c t="s" r="J236" s="7">
-        <v>172</v>
+        <v>364</v>
       </c>
       <c r="K236" s="7"/>
       <c r="L236" s="7"/>
-      <c t="s" r="M236" s="7">
-        <v>275</v>
-      </c>
+      <c r="M236" s="7"/>
     </row>
     <row r="237" ht="14.25" customHeight="1">
       <c t="s" r="A237" s="6">
         <v>13</v>
       </c>
       <c r="B237" s="7">
-        <v>807</v>
+        <v>1282</v>
       </c>
       <c t="s" r="C237" s="7">
         <v>14</v>
       </c>
       <c r="D237" s="7"/>
       <c t="s" r="E237" s="7">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="F237" s="7">
         <v>321</v>
@@ -9284,82 +9304,62 @@
         <v>46</v>
       </c>
       <c t="s" r="H237" s="8">
-        <v>37</v>
+        <v>169</v>
       </c>
       <c t="s" r="I237" s="7">
-        <v>269</v>
+        <v>365</v>
       </c>
       <c t="s" r="J237" s="7">
-        <v>351</v>
+        <v>218</v>
       </c>
       <c r="K237" s="7"/>
       <c r="L237" s="7"/>
-      <c t="s" r="M237" s="7">
-        <v>245</v>
-      </c>
+      <c r="M237" s="7"/>
     </row>
     <row r="238" ht="14.25" customHeight="1">
       <c t="s" r="A238" s="6">
         <v>13</v>
       </c>
       <c r="B238" s="7">
-        <v>800</v>
+        <v>1283</v>
       </c>
       <c t="s" r="C238" s="7">
         <v>14</v>
       </c>
       <c r="D238" s="7"/>
       <c t="s" r="E238" s="7">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="F238" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G238" s="8">
-        <v>37</v>
+        <v>169</v>
       </c>
       <c t="s" r="H238" s="8">
         <v>46</v>
       </c>
       <c t="s" r="I238" s="7">
-        <v>38</v>
+        <v>366</v>
       </c>
       <c t="s" r="J238" s="7">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="K238" s="7"/>
       <c r="L238" s="7"/>
       <c r="M238" s="7"/>
     </row>
     <row r="239" ht="14.25" customHeight="1">
-      <c t="s" r="A239" s="6">
-        <v>13</v>
-      </c>
-      <c r="B239" s="7">
-        <v>1282</v>
-      </c>
-      <c t="s" r="C239" s="7">
-        <v>14</v>
-      </c>
+      <c r="A239" s="6"/>
+      <c r="B239" s="7"/>
+      <c r="C239" s="7"/>
       <c r="D239" s="7"/>
-      <c t="s" r="E239" s="7">
-        <v>359</v>
-      </c>
-      <c r="F239" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G239" s="8">
-        <v>46</v>
-      </c>
-      <c t="s" r="H239" s="8">
-        <v>169</v>
-      </c>
-      <c t="s" r="I239" s="7">
-        <v>363</v>
-      </c>
-      <c t="s" r="J239" s="7">
-        <v>217</v>
-      </c>
+      <c r="E239" s="7"/>
+      <c r="F239" s="7"/>
+      <c r="G239" s="8"/>
+      <c r="H239" s="8"/>
+      <c r="I239" s="7"/>
+      <c r="J239" s="7"/>
       <c r="K239" s="7"/>
       <c r="L239" s="7"/>
       <c r="M239" s="7"/>
@@ -9369,97 +9369,117 @@
         <v>13</v>
       </c>
       <c r="B240" s="7">
-        <v>1283</v>
+        <v>272</v>
       </c>
       <c t="s" r="C240" s="7">
         <v>14</v>
       </c>
       <c r="D240" s="7"/>
       <c t="s" r="E240" s="7">
-        <v>359</v>
+        <v>368</v>
       </c>
       <c r="F240" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G240" s="8">
+        <v>46</v>
+      </c>
+      <c t="s" r="H240" s="8">
         <v>169</v>
       </c>
-      <c t="s" r="H240" s="8">
-        <v>46</v>
-      </c>
       <c t="s" r="I240" s="7">
-        <v>364</v>
+        <v>167</v>
       </c>
       <c t="s" r="J240" s="7">
-        <v>365</v>
+        <v>91</v>
       </c>
       <c r="K240" s="7"/>
       <c r="L240" s="7"/>
-      <c r="M240" s="7"/>
+      <c t="s" r="M240" s="7">
+        <v>369</v>
+      </c>
     </row>
     <row r="241" ht="14.25" customHeight="1">
-      <c r="A241" s="6"/>
-      <c r="B241" s="7"/>
-      <c r="C241" s="7"/>
+      <c t="s" r="A241" s="6">
+        <v>13</v>
+      </c>
+      <c r="B241" s="7">
+        <v>7078</v>
+      </c>
+      <c t="s" r="C241" s="7">
+        <v>14</v>
+      </c>
       <c r="D241" s="7"/>
-      <c r="E241" s="7"/>
-      <c r="F241" s="7"/>
-      <c r="G241" s="8"/>
-      <c r="H241" s="8"/>
-      <c r="I241" s="7"/>
-      <c r="J241" s="7"/>
+      <c t="s" r="E241" s="7">
+        <v>368</v>
+      </c>
+      <c r="F241" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G241" s="8">
+        <v>169</v>
+      </c>
+      <c t="s" r="H241" s="8">
+        <v>329</v>
+      </c>
+      <c t="s" r="I241" s="7">
+        <v>136</v>
+      </c>
+      <c t="s" r="J241" s="7">
+        <v>272</v>
+      </c>
       <c r="K241" s="7"/>
       <c r="L241" s="7"/>
-      <c r="M241" s="7"/>
+      <c t="s" r="M241" s="7">
+        <v>189</v>
+      </c>
     </row>
     <row r="242" ht="14.25" customHeight="1">
       <c t="s" r="A242" s="6">
         <v>13</v>
       </c>
       <c r="B242" s="7">
-        <v>272</v>
+        <v>7079</v>
       </c>
       <c t="s" r="C242" s="7">
         <v>14</v>
       </c>
       <c r="D242" s="7"/>
       <c t="s" r="E242" s="7">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="F242" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G242" s="8">
-        <v>46</v>
+        <v>329</v>
       </c>
       <c t="s" r="H242" s="8">
         <v>169</v>
       </c>
       <c t="s" r="I242" s="7">
-        <v>167</v>
+        <v>67</v>
       </c>
       <c t="s" r="J242" s="7">
-        <v>91</v>
+        <v>193</v>
       </c>
       <c r="K242" s="7"/>
       <c r="L242" s="7"/>
-      <c t="s" r="M242" s="7">
-        <v>367</v>
-      </c>
+      <c r="M242" s="7"/>
     </row>
     <row r="243" ht="14.25" customHeight="1">
       <c t="s" r="A243" s="6">
         <v>13</v>
       </c>
       <c r="B243" s="7">
-        <v>7078</v>
+        <v>273</v>
       </c>
       <c t="s" r="C243" s="7">
         <v>14</v>
       </c>
       <c r="D243" s="7"/>
       <c t="s" r="E243" s="7">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="F243" s="7">
         <v>321</v>
@@ -9468,82 +9488,62 @@
         <v>169</v>
       </c>
       <c t="s" r="H243" s="8">
-        <v>327</v>
+        <v>46</v>
       </c>
       <c t="s" r="I243" s="7">
-        <v>136</v>
+        <v>68</v>
       </c>
       <c t="s" r="J243" s="7">
-        <v>270</v>
+        <v>207</v>
       </c>
       <c r="K243" s="7"/>
       <c r="L243" s="7"/>
-      <c t="s" r="M243" s="7">
-        <v>188</v>
-      </c>
+      <c r="M243" s="7"/>
     </row>
     <row r="244" ht="14.25" customHeight="1">
       <c t="s" r="A244" s="6">
         <v>13</v>
       </c>
       <c r="B244" s="7">
-        <v>7079</v>
+        <v>168</v>
       </c>
       <c t="s" r="C244" s="7">
         <v>14</v>
       </c>
       <c r="D244" s="7"/>
       <c t="s" r="E244" s="7">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="F244" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G244" s="8">
-        <v>327</v>
+        <v>46</v>
       </c>
       <c t="s" r="H244" s="8">
-        <v>169</v>
+        <v>17</v>
       </c>
       <c t="s" r="I244" s="7">
-        <v>67</v>
+        <v>370</v>
       </c>
       <c t="s" r="J244" s="7">
-        <v>192</v>
+        <v>347</v>
       </c>
       <c r="K244" s="7"/>
       <c r="L244" s="7"/>
       <c r="M244" s="7"/>
     </row>
     <row r="245" ht="15" customHeight="1">
-      <c t="s" r="A245" s="6">
-        <v>13</v>
-      </c>
-      <c r="B245" s="7">
-        <v>273</v>
-      </c>
-      <c t="s" r="C245" s="7">
-        <v>14</v>
-      </c>
+      <c r="A245" s="6"/>
+      <c r="B245" s="7"/>
+      <c r="C245" s="7"/>
       <c r="D245" s="7"/>
-      <c t="s" r="E245" s="7">
-        <v>366</v>
-      </c>
-      <c r="F245" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G245" s="8">
-        <v>169</v>
-      </c>
-      <c t="s" r="H245" s="8">
-        <v>46</v>
-      </c>
-      <c t="s" r="I245" s="7">
-        <v>68</v>
-      </c>
-      <c t="s" r="J245" s="7">
-        <v>206</v>
-      </c>
+      <c r="E245" s="7"/>
+      <c r="F245" s="7"/>
+      <c r="G245" s="8"/>
+      <c r="H245" s="8"/>
+      <c r="I245" s="7"/>
+      <c r="J245" s="7"/>
       <c r="K245" s="7"/>
       <c r="L245" s="7"/>
       <c r="M245" s="7"/>
@@ -9553,14 +9553,14 @@
         <v>13</v>
       </c>
       <c r="B246" s="7">
-        <v>168</v>
+        <v>224</v>
       </c>
       <c t="s" r="C246" s="7">
         <v>14</v>
       </c>
       <c r="D246" s="7"/>
       <c t="s" r="E246" s="7">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="F246" s="7">
         <v>321</v>
@@ -9569,66 +9569,88 @@
         <v>46</v>
       </c>
       <c t="s" r="H246" s="8">
-        <v>17</v>
+        <v>109</v>
       </c>
       <c t="s" r="I246" s="7">
-        <v>368</v>
+        <v>112</v>
       </c>
       <c t="s" r="J246" s="7">
-        <v>345</v>
+        <v>362</v>
       </c>
       <c r="K246" s="7"/>
       <c r="L246" s="7"/>
-      <c r="M246" s="7"/>
+      <c t="s" r="M246" s="7">
+        <v>372</v>
+      </c>
     </row>
     <row r="247" ht="14.25" customHeight="1">
-      <c r="A247" s="6"/>
-      <c r="B247" s="7"/>
-      <c r="C247" s="7"/>
+      <c t="s" r="A247" s="6">
+        <v>13</v>
+      </c>
+      <c r="B247" s="7">
+        <v>741</v>
+      </c>
+      <c t="s" r="C247" s="7">
+        <v>14</v>
+      </c>
       <c r="D247" s="7"/>
-      <c r="E247" s="7"/>
-      <c r="F247" s="7"/>
-      <c r="G247" s="8"/>
-      <c r="H247" s="8"/>
-      <c r="I247" s="7"/>
-      <c r="J247" s="7"/>
+      <c t="s" r="E247" s="7">
+        <v>371</v>
+      </c>
+      <c r="F247" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G247" s="8">
+        <v>109</v>
+      </c>
+      <c t="s" r="H247" s="8">
+        <v>373</v>
+      </c>
+      <c t="s" r="I247" s="7">
+        <v>154</v>
+      </c>
+      <c t="s" r="J247" s="7">
+        <v>83</v>
+      </c>
       <c r="K247" s="7"/>
       <c r="L247" s="7"/>
-      <c r="M247" s="7"/>
+      <c t="s" r="M247" s="7">
+        <v>83</v>
+      </c>
     </row>
     <row r="248" ht="14.25" customHeight="1">
       <c t="s" r="A248" s="6">
         <v>13</v>
       </c>
       <c r="B248" s="7">
-        <v>224</v>
+        <v>740</v>
       </c>
       <c t="s" r="C248" s="7">
         <v>14</v>
       </c>
       <c r="D248" s="7"/>
       <c t="s" r="E248" s="7">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="F248" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G248" s="8">
-        <v>46</v>
+        <v>373</v>
       </c>
       <c t="s" r="H248" s="8">
         <v>109</v>
       </c>
       <c t="s" r="I248" s="7">
-        <v>112</v>
+        <v>259</v>
       </c>
       <c t="s" r="J248" s="7">
-        <v>360</v>
+        <v>60</v>
       </c>
       <c r="K248" s="7"/>
       <c r="L248" s="7"/>
       <c t="s" r="M248" s="7">
-        <v>370</v>
+        <v>374</v>
       </c>
     </row>
     <row r="249" ht="14.25" customHeight="1">
@@ -9636,14 +9658,14 @@
         <v>13</v>
       </c>
       <c r="B249" s="7">
-        <v>741</v>
+        <v>227</v>
       </c>
       <c t="s" r="C249" s="7">
         <v>14</v>
       </c>
       <c r="D249" s="7"/>
       <c t="s" r="E249" s="7">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="F249" s="7">
         <v>321</v>
@@ -9652,18 +9674,18 @@
         <v>109</v>
       </c>
       <c t="s" r="H249" s="8">
-        <v>371</v>
+        <v>46</v>
       </c>
       <c t="s" r="I249" s="7">
-        <v>154</v>
+        <v>33</v>
       </c>
       <c t="s" r="J249" s="7">
-        <v>83</v>
+        <v>127</v>
       </c>
       <c r="K249" s="7"/>
       <c r="L249" s="7"/>
       <c t="s" r="M249" s="7">
-        <v>83</v>
+        <v>375</v>
       </c>
     </row>
     <row r="250" ht="15" customHeight="1">
@@ -9671,34 +9693,34 @@
         <v>13</v>
       </c>
       <c r="B250" s="7">
-        <v>740</v>
+        <v>308</v>
       </c>
       <c t="s" r="C250" s="7">
         <v>14</v>
       </c>
       <c r="D250" s="7"/>
       <c t="s" r="E250" s="7">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="F250" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G250" s="8">
-        <v>371</v>
+        <v>46</v>
       </c>
       <c t="s" r="H250" s="8">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c t="s" r="I250" s="7">
-        <v>257</v>
+        <v>139</v>
       </c>
       <c t="s" r="J250" s="7">
-        <v>60</v>
+        <v>106</v>
       </c>
       <c r="K250" s="7"/>
       <c r="L250" s="7"/>
       <c t="s" r="M250" s="7">
-        <v>372</v>
+        <v>376</v>
       </c>
     </row>
     <row r="251" ht="14.25" customHeight="1">
@@ -9706,49 +9728,47 @@
         <v>13</v>
       </c>
       <c r="B251" s="7">
-        <v>227</v>
+        <v>307</v>
       </c>
       <c t="s" r="C251" s="7">
         <v>14</v>
       </c>
       <c r="D251" s="7"/>
       <c t="s" r="E251" s="7">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="F251" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G251" s="8">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c t="s" r="H251" s="8">
         <v>46</v>
       </c>
       <c t="s" r="I251" s="7">
-        <v>33</v>
+        <v>108</v>
       </c>
       <c t="s" r="J251" s="7">
-        <v>127</v>
+        <v>323</v>
       </c>
       <c r="K251" s="7"/>
       <c r="L251" s="7"/>
-      <c t="s" r="M251" s="7">
-        <v>373</v>
-      </c>
+      <c r="M251" s="7"/>
     </row>
     <row r="252" ht="14.25" customHeight="1">
       <c t="s" r="A252" s="6">
         <v>13</v>
       </c>
       <c r="B252" s="7">
-        <v>308</v>
+        <v>248</v>
       </c>
       <c t="s" r="C252" s="7">
         <v>14</v>
       </c>
       <c r="D252" s="7"/>
       <c t="s" r="E252" s="7">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="F252" s="7">
         <v>321</v>
@@ -9757,82 +9777,62 @@
         <v>46</v>
       </c>
       <c t="s" r="H252" s="8">
-        <v>119</v>
+        <v>104</v>
       </c>
       <c t="s" r="I252" s="7">
-        <v>139</v>
+        <v>129</v>
       </c>
       <c t="s" r="J252" s="7">
-        <v>106</v>
+        <v>365</v>
       </c>
       <c r="K252" s="7"/>
       <c r="L252" s="7"/>
-      <c t="s" r="M252" s="7">
-        <v>374</v>
-      </c>
+      <c r="M252" s="7"/>
     </row>
     <row r="253" ht="14.25" customHeight="1">
       <c t="s" r="A253" s="6">
         <v>13</v>
       </c>
       <c r="B253" s="7">
-        <v>307</v>
+        <v>249</v>
       </c>
       <c t="s" r="C253" s="7">
         <v>14</v>
       </c>
       <c r="D253" s="7"/>
       <c t="s" r="E253" s="7">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="F253" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G253" s="8">
-        <v>119</v>
+        <v>104</v>
       </c>
       <c t="s" r="H253" s="8">
         <v>46</v>
       </c>
       <c t="s" r="I253" s="7">
-        <v>108</v>
+        <v>354</v>
       </c>
       <c t="s" r="J253" s="7">
-        <v>321</v>
+        <v>366</v>
       </c>
       <c r="K253" s="7"/>
       <c r="L253" s="7"/>
       <c r="M253" s="7"/>
     </row>
     <row r="254" ht="14.25" customHeight="1">
-      <c t="s" r="A254" s="6">
-        <v>13</v>
-      </c>
-      <c r="B254" s="7">
-        <v>248</v>
-      </c>
-      <c t="s" r="C254" s="7">
-        <v>14</v>
-      </c>
+      <c r="A254" s="6"/>
+      <c r="B254" s="7"/>
+      <c r="C254" s="7"/>
       <c r="D254" s="7"/>
-      <c t="s" r="E254" s="7">
-        <v>369</v>
-      </c>
-      <c r="F254" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G254" s="8">
-        <v>46</v>
-      </c>
-      <c t="s" r="H254" s="8">
-        <v>104</v>
-      </c>
-      <c t="s" r="I254" s="7">
-        <v>129</v>
-      </c>
-      <c t="s" r="J254" s="7">
-        <v>363</v>
-      </c>
+      <c r="E254" s="7"/>
+      <c r="F254" s="7"/>
+      <c r="G254" s="8"/>
+      <c r="H254" s="8"/>
+      <c r="I254" s="7"/>
+      <c r="J254" s="7"/>
       <c r="K254" s="7"/>
       <c r="L254" s="7"/>
       <c r="M254" s="7"/>
@@ -9842,62 +9842,84 @@
         <v>13</v>
       </c>
       <c r="B255" s="7">
-        <v>249</v>
+        <v>260</v>
       </c>
       <c t="s" r="C255" s="7">
         <v>14</v>
       </c>
       <c r="D255" s="7"/>
       <c t="s" r="E255" s="7">
-        <v>369</v>
+        <v>377</v>
       </c>
       <c r="F255" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G255" s="8">
-        <v>104</v>
+        <v>46</v>
       </c>
       <c t="s" r="H255" s="8">
-        <v>46</v>
+        <v>205</v>
       </c>
       <c t="s" r="I255" s="7">
-        <v>352</v>
+        <v>54</v>
       </c>
       <c t="s" r="J255" s="7">
-        <v>364</v>
+        <v>114</v>
       </c>
       <c r="K255" s="7"/>
       <c r="L255" s="7"/>
-      <c r="M255" s="7"/>
+      <c t="s" r="M255" s="7">
+        <v>378</v>
+      </c>
     </row>
     <row r="256" ht="14.25" customHeight="1">
-      <c r="A256" s="6"/>
-      <c r="B256" s="7"/>
-      <c r="C256" s="7"/>
+      <c t="s" r="A256" s="6">
+        <v>13</v>
+      </c>
+      <c r="B256" s="7">
+        <v>261</v>
+      </c>
+      <c t="s" r="C256" s="7">
+        <v>14</v>
+      </c>
       <c r="D256" s="7"/>
-      <c r="E256" s="7"/>
-      <c r="F256" s="7"/>
-      <c r="G256" s="8"/>
-      <c r="H256" s="8"/>
-      <c r="I256" s="7"/>
-      <c r="J256" s="7"/>
+      <c t="s" r="E256" s="7">
+        <v>377</v>
+      </c>
+      <c r="F256" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G256" s="8">
+        <v>205</v>
+      </c>
+      <c t="s" r="H256" s="8">
+        <v>46</v>
+      </c>
+      <c t="s" r="I256" s="7">
+        <v>126</v>
+      </c>
+      <c t="s" r="J256" s="7">
+        <v>200</v>
+      </c>
       <c r="K256" s="7"/>
       <c r="L256" s="7"/>
-      <c r="M256" s="7"/>
+      <c t="s" r="M256" s="7">
+        <v>89</v>
+      </c>
     </row>
     <row r="257" ht="14.25" customHeight="1">
       <c t="s" r="A257" s="6">
         <v>13</v>
       </c>
       <c r="B257" s="7">
-        <v>260</v>
+        <v>803</v>
       </c>
       <c t="s" r="C257" s="7">
         <v>14</v>
       </c>
       <c r="D257" s="7"/>
       <c t="s" r="E257" s="7">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="F257" s="7">
         <v>321</v>
@@ -9906,18 +9928,18 @@
         <v>46</v>
       </c>
       <c t="s" r="H257" s="8">
-        <v>204</v>
+        <v>37</v>
       </c>
       <c t="s" r="I257" s="7">
-        <v>54</v>
+        <v>147</v>
       </c>
       <c t="s" r="J257" s="7">
-        <v>114</v>
+        <v>294</v>
       </c>
       <c r="K257" s="7"/>
       <c r="L257" s="7"/>
       <c t="s" r="M257" s="7">
-        <v>376</v>
+        <v>379</v>
       </c>
     </row>
     <row r="258" ht="14.25" customHeight="1">
@@ -9925,34 +9947,34 @@
         <v>13</v>
       </c>
       <c r="B258" s="7">
-        <v>261</v>
+        <v>804</v>
       </c>
       <c t="s" r="C258" s="7">
         <v>14</v>
       </c>
       <c r="D258" s="7"/>
       <c t="s" r="E258" s="7">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="F258" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G258" s="8">
-        <v>204</v>
+        <v>37</v>
       </c>
       <c t="s" r="H258" s="8">
         <v>46</v>
       </c>
       <c t="s" r="I258" s="7">
-        <v>126</v>
+        <v>202</v>
       </c>
       <c t="s" r="J258" s="7">
-        <v>199</v>
+        <v>289</v>
       </c>
       <c r="K258" s="7"/>
       <c r="L258" s="7"/>
       <c t="s" r="M258" s="7">
-        <v>89</v>
+        <v>380</v>
       </c>
     </row>
     <row r="259" ht="14.25" customHeight="1">
@@ -9960,14 +9982,14 @@
         <v>13</v>
       </c>
       <c r="B259" s="7">
-        <v>803</v>
+        <v>331</v>
       </c>
       <c t="s" r="C259" s="7">
         <v>14</v>
       </c>
       <c r="D259" s="7"/>
       <c t="s" r="E259" s="7">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="F259" s="7">
         <v>321</v>
@@ -9976,68 +9998,64 @@
         <v>46</v>
       </c>
       <c t="s" r="H259" s="8">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c t="s" r="I259" s="7">
-        <v>147</v>
+        <v>86</v>
       </c>
       <c t="s" r="J259" s="7">
-        <v>292</v>
+        <v>234</v>
       </c>
       <c r="K259" s="7"/>
       <c r="L259" s="7"/>
-      <c t="s" r="M259" s="7">
-        <v>377</v>
-      </c>
+      <c r="M259" s="7"/>
     </row>
     <row r="260" ht="15" customHeight="1">
       <c t="s" r="A260" s="6">
         <v>13</v>
       </c>
       <c r="B260" s="7">
-        <v>804</v>
+        <v>328</v>
       </c>
       <c t="s" r="C260" s="7">
         <v>14</v>
       </c>
       <c r="D260" s="7"/>
       <c t="s" r="E260" s="7">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="F260" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G260" s="8">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c t="s" r="H260" s="8">
         <v>46</v>
       </c>
       <c t="s" r="I260" s="7">
-        <v>201</v>
+        <v>381</v>
       </c>
       <c t="s" r="J260" s="7">
-        <v>287</v>
+        <v>120</v>
       </c>
       <c r="K260" s="7"/>
       <c r="L260" s="7"/>
-      <c t="s" r="M260" s="7">
-        <v>378</v>
-      </c>
+      <c r="M260" s="7"/>
     </row>
     <row r="261" ht="14.25" customHeight="1">
       <c t="s" r="A261" s="6">
         <v>13</v>
       </c>
       <c r="B261" s="7">
-        <v>1831</v>
+        <v>646</v>
       </c>
       <c t="s" r="C261" s="7">
         <v>14</v>
       </c>
       <c r="D261" s="7"/>
       <c t="s" r="E261" s="7">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="F261" s="7">
         <v>321</v>
@@ -10046,13 +10064,13 @@
         <v>46</v>
       </c>
       <c t="s" r="H261" s="8">
-        <v>379</v>
+        <v>52</v>
       </c>
       <c t="s" r="I261" s="7">
-        <v>189</v>
+        <v>382</v>
       </c>
       <c t="s" r="J261" s="7">
-        <v>298</v>
+        <v>178</v>
       </c>
       <c r="K261" s="7"/>
       <c r="L261" s="7"/>
@@ -10063,29 +10081,29 @@
         <v>13</v>
       </c>
       <c r="B262" s="7">
-        <v>1832</v>
+        <v>1649</v>
       </c>
       <c t="s" r="C262" s="7">
         <v>14</v>
       </c>
       <c r="D262" s="7"/>
       <c t="s" r="E262" s="7">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="F262" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G262" s="8">
-        <v>379</v>
+        <v>52</v>
       </c>
       <c t="s" r="H262" s="8">
         <v>46</v>
       </c>
       <c t="s" r="I262" s="7">
-        <v>279</v>
+        <v>179</v>
       </c>
       <c t="s" r="J262" s="7">
-        <v>380</v>
+        <v>162</v>
       </c>
       <c r="K262" s="7"/>
       <c r="L262" s="7"/>
@@ -10118,7 +10136,7 @@
       </c>
       <c r="D264" s="7"/>
       <c t="s" r="E264" s="7">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="F264" s="7">
         <v>321</v>
@@ -10138,7 +10156,7 @@
       <c r="K264" s="7"/>
       <c r="L264" s="7"/>
       <c t="s" r="M264" s="7">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
     <row r="265" ht="15" customHeight="1">
@@ -10153,7 +10171,7 @@
       </c>
       <c r="D265" s="7"/>
       <c t="s" r="E265" s="7">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="F265" s="7">
         <v>321</v>
@@ -10173,7 +10191,7 @@
       <c r="K265" s="7"/>
       <c r="L265" s="7"/>
       <c t="s" r="M265" s="7">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
     <row r="266" ht="14.25" customHeight="1">
@@ -10188,7 +10206,7 @@
       </c>
       <c r="D266" s="7"/>
       <c t="s" r="E266" s="7">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="F266" s="7">
         <v>321</v>
@@ -10208,7 +10226,7 @@
       <c r="K266" s="7"/>
       <c r="L266" s="7"/>
       <c t="s" r="M266" s="7">
-        <v>320</v>
+        <v>386</v>
       </c>
     </row>
     <row r="267" ht="14.25" customHeight="1">
@@ -10223,7 +10241,7 @@
       </c>
       <c r="D267" s="7"/>
       <c t="s" r="E267" s="7">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="F267" s="7">
         <v>321</v>
@@ -10238,7 +10256,7 @@
         <v>152</v>
       </c>
       <c t="s" r="J267" s="7">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="K267" s="7"/>
       <c r="L267" s="7"/>
@@ -10256,7 +10274,7 @@
       </c>
       <c r="D268" s="7"/>
       <c t="s" r="E268" s="7">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="F268" s="7">
         <v>321</v>
@@ -10268,10 +10286,10 @@
         <v>169</v>
       </c>
       <c t="s" r="I268" s="7">
-        <v>357</v>
+        <v>381</v>
       </c>
       <c t="s" r="J268" s="7">
-        <v>358</v>
+        <v>382</v>
       </c>
       <c r="K268" s="7"/>
       <c r="L268" s="7"/>
@@ -10289,7 +10307,7 @@
       </c>
       <c r="D269" s="7"/>
       <c t="s" r="E269" s="7">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="F269" s="7">
         <v>321</v>
@@ -10304,7 +10322,7 @@
         <v>162</v>
       </c>
       <c t="s" r="J269" s="7">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="K269" s="7"/>
       <c r="L269" s="7"/>
@@ -10337,7 +10355,7 @@
       </c>
       <c r="D271" s="7"/>
       <c t="s" r="E271" s="7">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="F271" s="7">
         <v>321</v>
@@ -10349,7 +10367,7 @@
         <v>52</v>
       </c>
       <c t="s" r="I271" s="7">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c t="s" r="J271" s="7">
         <v>102</v>
@@ -10357,7 +10375,7 @@
       <c r="K271" s="7"/>
       <c r="L271" s="7"/>
       <c t="s" r="M271" s="7">
-        <v>387</v>
+        <v>390</v>
       </c>
     </row>
     <row r="272" ht="14.25" customHeight="1">
@@ -10372,7 +10390,7 @@
       </c>
       <c r="D272" s="7"/>
       <c t="s" r="E272" s="7">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="F272" s="7">
         <v>321</v>
@@ -10392,7 +10410,7 @@
       <c r="K272" s="7"/>
       <c r="L272" s="7"/>
       <c t="s" r="M272" s="7">
-        <v>388</v>
+        <v>391</v>
       </c>
     </row>
     <row r="273" ht="14.25" customHeight="1">
@@ -10407,7 +10425,7 @@
       </c>
       <c r="D273" s="7"/>
       <c t="s" r="E273" s="7">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="F273" s="7">
         <v>321</v>
@@ -10442,7 +10460,7 @@
       </c>
       <c r="D274" s="7"/>
       <c t="s" r="E274" s="7">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="F274" s="7">
         <v>321</v>
@@ -10460,11 +10478,11 @@
         <v>47</v>
       </c>
       <c t="s" r="K274" s="7">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="L274" s="7"/>
       <c t="s" r="M274" s="7">
-        <v>390</v>
+        <v>393</v>
       </c>
     </row>
     <row r="275" ht="15" customHeight="1">
@@ -10479,7 +10497,7 @@
       </c>
       <c r="D275" s="7"/>
       <c t="s" r="E275" s="7">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="F275" s="7">
         <v>321</v>
@@ -10494,12 +10512,12 @@
         <v>127</v>
       </c>
       <c t="s" r="J275" s="7">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="K275" s="7"/>
       <c r="L275" s="7"/>
       <c t="s" r="M275" s="7">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="276" ht="14.25" customHeight="1">
@@ -10514,7 +10532,7 @@
       </c>
       <c r="D276" s="7"/>
       <c t="s" r="E276" s="7">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="F276" s="7">
         <v>321</v>
@@ -10526,7 +10544,7 @@
         <v>46</v>
       </c>
       <c t="s" r="I276" s="7">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c t="s" r="J276" s="7">
         <v>108</v>
@@ -10547,7 +10565,7 @@
       </c>
       <c r="D277" s="7"/>
       <c t="s" r="E277" s="7">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="F277" s="7">
         <v>321</v>
@@ -10580,7 +10598,7 @@
       </c>
       <c r="D278" s="7"/>
       <c t="s" r="E278" s="7">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="F278" s="7">
         <v>321</v>
@@ -10595,7 +10613,7 @@
         <v>121</v>
       </c>
       <c t="s" r="J278" s="7">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="K278" s="7"/>
       <c r="L278" s="7"/>
@@ -10628,7 +10646,7 @@
       </c>
       <c r="D280" s="7"/>
       <c t="s" r="E280" s="7">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="F280" s="7">
         <v>321</v>
@@ -10640,10 +10658,10 @@
         <v>158</v>
       </c>
       <c t="s" r="I280" s="7">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c t="s" r="J280" s="7">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="K280" s="7"/>
       <c r="L280" s="7"/>
@@ -10663,7 +10681,7 @@
       </c>
       <c r="D281" s="7"/>
       <c t="s" r="E281" s="7">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="F281" s="7">
         <v>321</v>
@@ -10678,12 +10696,12 @@
         <v>157</v>
       </c>
       <c t="s" r="J281" s="7">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="K281" s="7"/>
       <c r="L281" s="7"/>
       <c t="s" r="M281" s="7">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="282" ht="14.25" customHeight="1">
@@ -10698,7 +10716,7 @@
       </c>
       <c r="D282" s="7"/>
       <c t="s" r="E282" s="7">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="F282" s="7">
         <v>321</v>
@@ -10707,13 +10725,13 @@
         <v>46</v>
       </c>
       <c t="s" r="H282" s="8">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c t="s" r="I282" s="7">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c t="s" r="J282" s="7">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="K282" s="7"/>
       <c r="L282" s="7"/>
@@ -10731,22 +10749,22 @@
       </c>
       <c r="D283" s="7"/>
       <c t="s" r="E283" s="7">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="F283" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G283" s="8">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c t="s" r="H283" s="8">
         <v>46</v>
       </c>
       <c t="s" r="I283" s="7">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c t="s" r="J283" s="7">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="K283" s="7"/>
       <c r="L283" s="7"/>
@@ -10779,7 +10797,7 @@
       </c>
       <c r="D285" s="7"/>
       <c t="s" r="E285" s="7">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="F285" s="7">
         <v>321</v>
@@ -10791,15 +10809,15 @@
         <v>52</v>
       </c>
       <c t="s" r="I285" s="7">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c t="s" r="J285" s="7">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="K285" s="7"/>
       <c r="L285" s="7"/>
       <c t="s" r="M285" s="7">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="286" ht="14.25" customHeight="1">
@@ -10814,7 +10832,7 @@
       </c>
       <c r="D286" s="7"/>
       <c t="s" r="E286" s="7">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="F286" s="7">
         <v>321</v>
@@ -10826,7 +10844,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I286" s="7">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c t="s" r="J286" s="7">
         <v>135</v>
@@ -10834,7 +10852,7 @@
       <c r="K286" s="7"/>
       <c r="L286" s="7"/>
       <c t="s" r="M286" s="7">
-        <v>397</v>
+        <v>400</v>
       </c>
     </row>
     <row r="287" ht="14.25" customHeight="1">
@@ -10849,7 +10867,7 @@
       </c>
       <c r="D287" s="7"/>
       <c t="s" r="E287" s="7">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="F287" s="7">
         <v>321</v>
@@ -10858,18 +10876,18 @@
         <v>17</v>
       </c>
       <c t="s" r="H287" s="8">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c t="s" r="I287" s="7">
         <v>156</v>
       </c>
       <c t="s" r="J287" s="7">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="K287" s="7"/>
       <c r="L287" s="7"/>
       <c t="s" r="M287" s="7">
-        <v>398</v>
+        <v>401</v>
       </c>
     </row>
     <row r="288" ht="14.25" customHeight="1">
@@ -10884,19 +10902,19 @@
       </c>
       <c r="D288" s="7"/>
       <c t="s" r="E288" s="7">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="F288" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G288" s="8">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c t="s" r="H288" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I288" s="7">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c t="s" r="J288" s="7">
         <v>151</v>
@@ -10904,7 +10922,7 @@
       <c r="K288" s="7"/>
       <c r="L288" s="7"/>
       <c t="s" r="M288" s="7">
-        <v>399</v>
+        <v>402</v>
       </c>
     </row>
     <row r="289" ht="14.25" customHeight="1">
@@ -10919,7 +10937,7 @@
       </c>
       <c r="D289" s="7"/>
       <c t="s" r="E289" s="7">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="F289" s="7">
         <v>321</v>
@@ -10928,13 +10946,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H289" s="8">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c t="s" r="I289" s="7">
         <v>106</v>
       </c>
       <c t="s" r="J289" s="7">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="K289" s="7"/>
       <c r="L289" s="7"/>
@@ -10952,13 +10970,13 @@
       </c>
       <c r="D290" s="7"/>
       <c t="s" r="E290" s="7">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="F290" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G290" s="8">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c t="s" r="H290" s="8">
         <v>17</v>
@@ -10985,7 +11003,7 @@
       </c>
       <c r="D291" s="7"/>
       <c t="s" r="E291" s="7">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="F291" s="7">
         <v>321</v>
@@ -11000,7 +11018,7 @@
         <v>41</v>
       </c>
       <c t="s" r="J291" s="7">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="K291" s="7"/>
       <c r="L291" s="7"/>
@@ -11018,7 +11036,7 @@
       </c>
       <c r="D292" s="7"/>
       <c t="s" r="E292" s="7">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="F292" s="7">
         <v>321</v>
@@ -11030,10 +11048,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I292" s="7">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c t="s" r="J292" s="7">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="K292" s="7"/>
       <c r="L292" s="7"/>
@@ -11066,7 +11084,7 @@
       </c>
       <c r="D294" s="7"/>
       <c t="s" r="E294" s="7">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="F294" s="7">
         <v>321</v>
@@ -11086,7 +11104,7 @@
       <c r="K294" s="7"/>
       <c r="L294" s="7"/>
       <c t="s" r="M294" s="7">
-        <v>403</v>
+        <v>406</v>
       </c>
     </row>
     <row r="295" ht="15" customHeight="1">
@@ -11101,7 +11119,7 @@
       </c>
       <c r="D295" s="7"/>
       <c t="s" r="E295" s="7">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="F295" s="7">
         <v>321</v>
@@ -11151,7 +11169,7 @@
       </c>
       <c r="D297" s="7"/>
       <c t="s" r="E297" s="7">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="F297" s="7">
         <v>320</v>
@@ -11160,18 +11178,18 @@
         <v>46</v>
       </c>
       <c t="s" r="H297" s="8">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c t="s" r="I297" s="7">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c t="s" r="J297" s="7">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="K297" s="7"/>
       <c r="L297" s="7"/>
       <c t="s" r="M297" s="7">
-        <v>405</v>
+        <v>408</v>
       </c>
     </row>
     <row r="298" ht="14.25" customHeight="1">
@@ -11186,19 +11204,19 @@
       </c>
       <c r="D298" s="7"/>
       <c t="s" r="E298" s="7">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="F298" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G298" s="8">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c t="s" r="H298" s="8">
         <v>46</v>
       </c>
       <c t="s" r="I298" s="7">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c t="s" r="J298" s="7">
         <v>33</v>
@@ -11206,7 +11224,7 @@
       <c r="K298" s="7"/>
       <c r="L298" s="7"/>
       <c t="s" r="M298" s="7">
-        <v>406</v>
+        <v>409</v>
       </c>
     </row>
     <row r="299" ht="14.25" customHeight="1">
@@ -11221,7 +11239,7 @@
       </c>
       <c r="D299" s="7"/>
       <c t="s" r="E299" s="7">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="F299" s="7">
         <v>320</v>
@@ -11233,15 +11251,15 @@
         <v>104</v>
       </c>
       <c t="s" r="I299" s="7">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c t="s" r="J299" s="7">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="K299" s="7"/>
       <c r="L299" s="7"/>
       <c t="s" r="M299" s="7">
-        <v>408</v>
+        <v>411</v>
       </c>
     </row>
     <row r="300" ht="15" customHeight="1">
@@ -11256,7 +11274,7 @@
       </c>
       <c r="D300" s="7"/>
       <c t="s" r="E300" s="7">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="F300" s="7">
         <v>320</v>
@@ -11271,7 +11289,7 @@
         <v>139</v>
       </c>
       <c t="s" r="J300" s="7">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="K300" s="7"/>
       <c r="L300" s="7"/>
@@ -11289,7 +11307,7 @@
       </c>
       <c r="D301" s="7"/>
       <c t="s" r="E301" s="7">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="F301" s="7">
         <v>320</v>
@@ -11298,13 +11316,13 @@
         <v>46</v>
       </c>
       <c t="s" r="H301" s="8">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c t="s" r="I301" s="7">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c t="s" r="J301" s="7">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="K301" s="7"/>
       <c r="L301" s="7"/>
@@ -11322,19 +11340,19 @@
       </c>
       <c r="D302" s="7"/>
       <c t="s" r="E302" s="7">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="F302" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G302" s="8">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c t="s" r="H302" s="8">
         <v>46</v>
       </c>
       <c t="s" r="I302" s="7">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c t="s" r="J302" s="7">
         <v>112</v>
@@ -11370,7 +11388,7 @@
       </c>
       <c r="D304" s="7"/>
       <c t="s" r="E304" s="7">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="F304" s="7">
         <v>321</v>
@@ -11379,7 +11397,7 @@
         <v>46</v>
       </c>
       <c t="s" r="H304" s="8">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c t="s" r="I304" s="7">
         <v>18</v>
@@ -11390,7 +11408,7 @@
       <c r="K304" s="7"/>
       <c r="L304" s="7"/>
       <c t="s" r="M304" s="7">
-        <v>411</v>
+        <v>414</v>
       </c>
     </row>
     <row r="305" ht="15" customHeight="1">
@@ -11405,13 +11423,13 @@
       </c>
       <c r="D305" s="7"/>
       <c t="s" r="E305" s="7">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="F305" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G305" s="8">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c t="s" r="H305" s="8">
         <v>46</v>
@@ -11420,12 +11438,12 @@
         <v>72</v>
       </c>
       <c t="s" r="J305" s="7">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="K305" s="7"/>
       <c r="L305" s="7"/>
       <c t="s" r="M305" s="7">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="306" ht="14.25" customHeight="1">
@@ -11440,7 +11458,7 @@
       </c>
       <c r="D306" s="7"/>
       <c t="s" r="E306" s="7">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="F306" s="7">
         <v>321</v>
@@ -11477,7 +11495,7 @@
       </c>
       <c r="D307" s="7"/>
       <c t="s" r="E307" s="7">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="F307" s="7">
         <v>321</v>
@@ -11489,17 +11507,17 @@
         <v>46</v>
       </c>
       <c t="s" r="I307" s="7">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c t="s" r="J307" s="7">
         <v>24</v>
       </c>
       <c t="s" r="K307" s="7">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="L307" s="7"/>
       <c t="s" r="M307" s="7">
-        <v>261</v>
+        <v>263</v>
       </c>
     </row>
     <row r="308" ht="14.25" customHeight="1">
@@ -11529,19 +11547,19 @@
       </c>
       <c r="D309" s="7"/>
       <c t="s" r="E309" s="7">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="F309" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G309" s="8">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c t="s" r="H309" s="8">
         <v>46</v>
       </c>
       <c t="s" r="I309" s="7">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c t="s" r="J309" s="7">
         <v>108</v>
@@ -11549,7 +11567,7 @@
       <c r="K309" s="7"/>
       <c r="L309" s="7"/>
       <c t="s" r="M309" s="7">
-        <v>414</v>
+        <v>417</v>
       </c>
     </row>
     <row r="310" ht="15" customHeight="1">
@@ -11564,7 +11582,7 @@
       </c>
       <c r="D310" s="7"/>
       <c t="s" r="E310" s="7">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="F310" s="7">
         <v>321</v>
@@ -11576,10 +11594,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I310" s="7">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c t="s" r="J310" s="7">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="K310" s="7"/>
       <c r="L310" s="7"/>
@@ -11597,7 +11615,7 @@
       </c>
       <c r="D311" s="7"/>
       <c t="s" r="E311" s="7">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="F311" s="7">
         <v>321</v>
@@ -11609,10 +11627,10 @@
         <v>46</v>
       </c>
       <c t="s" r="I311" s="7">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c t="s" r="J311" s="7">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="K311" s="7"/>
       <c r="L311" s="7"/>
@@ -11630,7 +11648,7 @@
       </c>
       <c r="D312" s="7"/>
       <c t="s" r="E312" s="7">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="F312" s="7">
         <v>321</v>
@@ -11639,10 +11657,10 @@
         <v>46</v>
       </c>
       <c t="s" r="H312" s="8">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c t="s" r="I312" s="7">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c t="s" r="J312" s="7">
         <v>57</v>
@@ -11678,22 +11696,22 @@
       </c>
       <c r="D314" s="7"/>
       <c t="s" r="E314" s="7">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="F314" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G314" s="8">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c t="s" r="H314" s="8">
         <v>52</v>
       </c>
       <c t="s" r="I314" s="7">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c t="s" r="J314" s="7">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="K314" s="7"/>
       <c r="L314" s="7"/>
@@ -11726,7 +11744,7 @@
       </c>
       <c r="D316" s="7"/>
       <c t="s" r="E316" s="7">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="F316" s="7">
         <v>320</v>
@@ -11738,10 +11756,10 @@
         <v>37</v>
       </c>
       <c t="s" r="I316" s="7">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c t="s" r="J316" s="7">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="K316" s="7"/>
       <c r="L316" s="7"/>
@@ -11761,7 +11779,7 @@
       </c>
       <c r="D317" s="7"/>
       <c t="s" r="E317" s="7">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="F317" s="7">
         <v>320</v>
@@ -11773,7 +11791,7 @@
         <v>46</v>
       </c>
       <c t="s" r="I317" s="7">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c t="s" r="J317" s="7">
         <v>127</v>
@@ -11781,7 +11799,7 @@
       <c r="K317" s="7"/>
       <c r="L317" s="7"/>
       <c t="s" r="M317" s="7">
-        <v>419</v>
+        <v>422</v>
       </c>
     </row>
     <row r="318" ht="14.25" customHeight="1">
@@ -11796,7 +11814,7 @@
       </c>
       <c r="D318" s="7"/>
       <c t="s" r="E318" s="7">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="F318" s="7">
         <v>320</v>
@@ -11808,7 +11826,7 @@
         <v>37</v>
       </c>
       <c t="s" r="I318" s="7">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c t="s" r="J318" s="7">
         <v>40</v>
@@ -11829,7 +11847,7 @@
       </c>
       <c r="D319" s="7"/>
       <c t="s" r="E319" s="7">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="F319" s="7">
         <v>320</v>
@@ -11841,7 +11859,7 @@
         <v>46</v>
       </c>
       <c t="s" r="I319" s="7">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c t="s" r="J319" s="7">
         <v>121</v>
@@ -11877,7 +11895,7 @@
       </c>
       <c r="D321" s="7"/>
       <c t="s" r="E321" s="7">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="F321" s="7">
         <v>320</v>
@@ -11886,7 +11904,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H321" s="8">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c t="s" r="I321" s="7">
         <v>89</v>
@@ -11897,7 +11915,7 @@
       <c r="K321" s="7"/>
       <c r="L321" s="7"/>
       <c t="s" r="M321" s="7">
-        <v>421</v>
+        <v>424</v>
       </c>
     </row>
     <row r="322" ht="14.25" customHeight="1">
@@ -11912,13 +11930,13 @@
       </c>
       <c r="D322" s="7"/>
       <c t="s" r="E322" s="7">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="F322" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G322" s="8">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c t="s" r="H322" s="8">
         <v>17</v>
@@ -11947,7 +11965,7 @@
       </c>
       <c r="D323" s="7"/>
       <c t="s" r="E323" s="7">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="F323" s="7">
         <v>320</v>
@@ -11962,7 +11980,7 @@
         <v>75</v>
       </c>
       <c t="s" r="J323" s="7">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="K323" s="7"/>
       <c r="L323" s="7"/>
@@ -11980,7 +11998,7 @@
       </c>
       <c r="D324" s="7"/>
       <c t="s" r="E324" s="7">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="F324" s="7">
         <v>320</v>
@@ -11992,10 +12010,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I324" s="7">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c t="s" r="J324" s="7">
-        <v>357</v>
+        <v>381</v>
       </c>
       <c r="K324" s="7"/>
       <c r="L324" s="7"/>
@@ -12013,7 +12031,7 @@
       </c>
       <c r="D325" s="7"/>
       <c t="s" r="E325" s="7">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="F325" s="7">
         <v>320</v>
@@ -12022,13 +12040,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H325" s="8">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c t="s" r="I325" s="7">
         <v>50</v>
       </c>
       <c t="s" r="J325" s="7">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="K325" s="7"/>
       <c r="L325" s="7"/>
@@ -12046,22 +12064,22 @@
       </c>
       <c r="D326" s="7"/>
       <c t="s" r="E326" s="7">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="F326" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G326" s="8">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c t="s" r="H326" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I326" s="7">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c t="s" r="J326" s="7">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="K326" s="7"/>
       <c r="L326" s="7"/>
@@ -12094,7 +12112,7 @@
       </c>
       <c r="D328" s="7"/>
       <c t="s" r="E328" s="7">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="F328" s="7">
         <v>321</v>
@@ -12109,7 +12127,7 @@
         <v>44</v>
       </c>
       <c t="s" r="J328" s="7">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="K328" s="7"/>
       <c r="L328" s="7"/>
@@ -12129,7 +12147,7 @@
       </c>
       <c r="D329" s="7"/>
       <c t="s" r="E329" s="7">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="F329" s="7">
         <v>321</v>
@@ -12144,7 +12162,7 @@
         <v>28</v>
       </c>
       <c t="s" r="J329" s="7">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="K329" s="7"/>
       <c r="L329" s="7"/>
@@ -12164,7 +12182,7 @@
       </c>
       <c r="D330" s="7"/>
       <c t="s" r="E330" s="7">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="F330" s="7">
         <v>321</v>
@@ -12173,7 +12191,7 @@
         <v>46</v>
       </c>
       <c t="s" r="H330" s="8">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c t="s" r="I330" s="7">
         <v>33</v>
@@ -12199,13 +12217,13 @@
       </c>
       <c r="D331" s="7"/>
       <c t="s" r="E331" s="7">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="F331" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G331" s="8">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c t="s" r="H331" s="8">
         <v>46</v>
@@ -12214,7 +12232,7 @@
         <v>65</v>
       </c>
       <c t="s" r="J331" s="7">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="K331" s="7"/>
       <c r="L331" s="7"/>
@@ -12247,7 +12265,7 @@
       </c>
       <c r="D333" s="7"/>
       <c t="s" r="E333" s="7">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="F333" s="7">
         <v>320</v>
@@ -12256,7 +12274,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H333" s="8">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c t="s" r="I333" s="7">
         <v>56</v>
@@ -12282,19 +12300,19 @@
       </c>
       <c r="D334" s="7"/>
       <c t="s" r="E334" s="7">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="F334" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G334" s="8">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c t="s" r="H334" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I334" s="7">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c t="s" r="J334" s="7">
         <v>170</v>
@@ -12302,7 +12320,7 @@
       <c r="K334" s="7"/>
       <c r="L334" s="7"/>
       <c t="s" r="M334" s="7">
-        <v>283</v>
+        <v>285</v>
       </c>
     </row>
     <row r="335" ht="15" customHeight="1">
@@ -12317,7 +12335,7 @@
       </c>
       <c r="D335" s="7"/>
       <c t="s" r="E335" s="7">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="F335" s="7">
         <v>320</v>
@@ -12329,7 +12347,7 @@
         <v>31</v>
       </c>
       <c t="s" r="I335" s="7">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c t="s" r="J335" s="7">
         <v>150</v>
@@ -12352,7 +12370,7 @@
       </c>
       <c r="D336" s="7"/>
       <c t="s" r="E336" s="7">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="F336" s="7">
         <v>320</v>
@@ -12367,7 +12385,7 @@
         <v>35</v>
       </c>
       <c t="s" r="J336" s="7">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="K336" s="7"/>
       <c r="L336" s="7"/>
@@ -12385,7 +12403,7 @@
       </c>
       <c r="D337" s="7"/>
       <c t="s" r="E337" s="7">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="F337" s="7">
         <v>320</v>
@@ -12394,13 +12412,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H337" s="8">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c t="s" r="I337" s="7">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c t="s" r="J337" s="7">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="K337" s="7"/>
       <c r="L337" s="7"/>
@@ -12418,22 +12436,22 @@
       </c>
       <c r="D338" s="7"/>
       <c t="s" r="E338" s="7">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="F338" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G338" s="8">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c t="s" r="H338" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I338" s="7">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c t="s" r="J338" s="7">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="K338" s="7"/>
       <c r="L338" s="7"/>
@@ -12466,7 +12484,7 @@
       </c>
       <c r="D340" s="7"/>
       <c t="s" r="E340" s="7">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="F340" s="7">
         <v>321</v>
@@ -12478,7 +12496,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I340" s="7">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c t="s" r="J340" s="7">
         <v>72</v>
@@ -12486,7 +12504,7 @@
       <c r="K340" s="7"/>
       <c r="L340" s="7"/>
       <c t="s" r="M340" s="7">
-        <v>432</v>
+        <v>435</v>
       </c>
     </row>
     <row r="341" ht="14.25" customHeight="1">
@@ -12501,7 +12519,7 @@
       </c>
       <c r="D341" s="7"/>
       <c t="s" r="E341" s="7">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="F341" s="7">
         <v>321</v>
@@ -12510,13 +12528,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H341" s="8">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c t="s" r="I341" s="7">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c t="s" r="J341" s="7">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="K341" s="7"/>
       <c r="L341" s="7"/>
@@ -12534,22 +12552,22 @@
       </c>
       <c r="D342" s="7"/>
       <c t="s" r="E342" s="7">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="F342" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G342" s="8">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c t="s" r="H342" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I342" s="7">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c t="s" r="J342" s="7">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="K342" s="7"/>
       <c r="L342" s="7"/>
@@ -12582,7 +12600,7 @@
       </c>
       <c r="D344" s="7"/>
       <c t="s" r="E344" s="7">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="F344" s="7">
         <v>320</v>
@@ -12594,7 +12612,7 @@
         <v>52</v>
       </c>
       <c t="s" r="I344" s="7">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c t="s" r="J344" s="7">
         <v>144</v>
@@ -12602,7 +12620,7 @@
       <c r="K344" s="7"/>
       <c r="L344" s="7"/>
       <c t="s" r="M344" s="7">
-        <v>435</v>
+        <v>438</v>
       </c>
     </row>
     <row r="345" ht="15" customHeight="1">
@@ -12632,7 +12650,7 @@
       </c>
       <c r="D346" s="7"/>
       <c t="s" r="E346" s="7">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="F346" s="7">
         <v>320</v>
@@ -12644,7 +12662,7 @@
         <v>46</v>
       </c>
       <c t="s" r="I346" s="7">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c t="s" r="J346" s="7">
         <v>114</v>
@@ -12652,7 +12670,7 @@
       <c r="K346" s="7"/>
       <c r="L346" s="7"/>
       <c t="s" r="M346" s="7">
-        <v>437</v>
+        <v>440</v>
       </c>
     </row>
     <row r="347" ht="14.25" customHeight="1">
@@ -12667,7 +12685,7 @@
       </c>
       <c r="D347" s="7"/>
       <c t="s" r="E347" s="7">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="F347" s="7">
         <v>320</v>
@@ -12679,7 +12697,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I347" s="7">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c t="s" r="J347" s="7">
         <v>149</v>
@@ -12687,7 +12705,7 @@
       <c r="K347" s="7"/>
       <c r="L347" s="7"/>
       <c t="s" r="M347" s="7">
-        <v>438</v>
+        <v>441</v>
       </c>
     </row>
     <row r="348" ht="14.25" customHeight="1">
@@ -12702,7 +12720,7 @@
       </c>
       <c r="D348" s="7"/>
       <c t="s" r="E348" s="7">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="F348" s="7">
         <v>320</v>
@@ -12711,10 +12729,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H348" s="8">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c t="s" r="I348" s="7">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c t="s" r="J348" s="7">
         <v>65</v>
@@ -12722,7 +12740,7 @@
       <c r="K348" s="7"/>
       <c r="L348" s="7"/>
       <c t="s" r="M348" s="7">
-        <v>439</v>
+        <v>442</v>
       </c>
     </row>
     <row r="349" ht="14.25" customHeight="1">
@@ -12737,13 +12755,13 @@
       </c>
       <c r="D349" s="7"/>
       <c t="s" r="E349" s="7">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="F349" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G349" s="8">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c t="s" r="H349" s="8">
         <v>17</v>
@@ -12752,7 +12770,7 @@
         <v>67</v>
       </c>
       <c t="s" r="J349" s="7">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="K349" s="7"/>
       <c r="L349" s="7"/>
@@ -12770,7 +12788,7 @@
       </c>
       <c r="D350" s="7"/>
       <c t="s" r="E350" s="7">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="F350" s="7">
         <v>320</v>
@@ -12803,7 +12821,7 @@
       </c>
       <c r="D351" s="7"/>
       <c t="s" r="E351" s="7">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="F351" s="7">
         <v>320</v>
@@ -12815,7 +12833,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I351" s="7">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c t="s" r="J351" s="7">
         <v>69</v>
@@ -12851,7 +12869,7 @@
       </c>
       <c r="D353" s="7"/>
       <c t="s" r="E353" s="7">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="F353" s="7">
         <v>321</v>
@@ -12860,18 +12878,18 @@
         <v>17</v>
       </c>
       <c t="s" r="H353" s="8">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c t="s" r="I353" s="7">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c t="s" r="J353" s="7">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="K353" s="7"/>
       <c r="L353" s="7"/>
       <c t="s" r="M353" s="7">
-        <v>443</v>
+        <v>446</v>
       </c>
     </row>
     <row r="354" ht="14.25" customHeight="1">
@@ -12886,13 +12904,13 @@
       </c>
       <c r="D354" s="7"/>
       <c t="s" r="E354" s="7">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="F354" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G354" s="8">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c t="s" r="H354" s="8">
         <v>17</v>
@@ -12901,7 +12919,7 @@
         <v>18</v>
       </c>
       <c t="s" r="J354" s="7">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="K354" s="7"/>
       <c r="L354" s="7"/>
@@ -12921,7 +12939,7 @@
       </c>
       <c r="D355" s="7"/>
       <c t="s" r="E355" s="7">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="F355" s="7">
         <v>321</v>
@@ -12936,12 +12954,12 @@
         <v>127</v>
       </c>
       <c t="s" r="J355" s="7">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="K355" s="7"/>
       <c r="L355" s="7"/>
       <c t="s" r="M355" s="7">
-        <v>444</v>
+        <v>447</v>
       </c>
     </row>
     <row r="356" ht="14.25" customHeight="1">
@@ -12956,7 +12974,7 @@
       </c>
       <c r="D356" s="7"/>
       <c t="s" r="E356" s="7">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="F356" s="7">
         <v>321</v>
@@ -12989,7 +13007,7 @@
       </c>
       <c r="D357" s="7"/>
       <c t="s" r="E357" s="7">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="F357" s="7">
         <v>321</v>
@@ -13001,10 +13019,10 @@
         <v>93</v>
       </c>
       <c t="s" r="I357" s="7">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c t="s" r="J357" s="7">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="K357" s="7"/>
       <c r="L357" s="7"/>
@@ -13022,7 +13040,7 @@
       </c>
       <c r="D358" s="7"/>
       <c t="s" r="E358" s="7">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="F358" s="7">
         <v>321</v>
@@ -13037,7 +13055,7 @@
         <v>77</v>
       </c>
       <c t="s" r="J358" s="7">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="K358" s="7"/>
       <c r="L358" s="7"/>
@@ -13055,7 +13073,7 @@
       </c>
       <c r="D359" s="7"/>
       <c t="s" r="E359" s="7">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="F359" s="7">
         <v>321</v>
@@ -13064,10 +13082,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H359" s="8">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c t="s" r="I359" s="7">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c t="s" r="J359" s="7">
         <v>166</v>
@@ -13103,7 +13121,7 @@
       </c>
       <c r="D361" s="7"/>
       <c t="s" r="E361" s="7">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="F361" s="7">
         <v>320</v>
@@ -13115,15 +13133,15 @@
         <v>31</v>
       </c>
       <c t="s" r="I361" s="7">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c t="s" r="J361" s="7">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="K361" s="7"/>
       <c r="L361" s="7"/>
       <c t="s" r="M361" s="7">
-        <v>449</v>
+        <v>452</v>
       </c>
     </row>
     <row r="362" ht="14.25" customHeight="1">
@@ -13138,7 +13156,7 @@
       </c>
       <c r="D362" s="7"/>
       <c t="s" r="E362" s="7">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="F362" s="7">
         <v>320</v>
@@ -13150,7 +13168,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I362" s="7">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c t="s" r="J362" s="7">
         <v>147</v>
@@ -13158,7 +13176,7 @@
       <c r="K362" s="7"/>
       <c r="L362" s="7"/>
       <c t="s" r="M362" s="7">
-        <v>450</v>
+        <v>453</v>
       </c>
     </row>
     <row r="363" ht="14.25" customHeight="1">
@@ -13173,7 +13191,7 @@
       </c>
       <c r="D363" s="7"/>
       <c t="s" r="E363" s="7">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="F363" s="7">
         <v>320</v>
@@ -13185,7 +13203,7 @@
         <v>66</v>
       </c>
       <c t="s" r="I363" s="7">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c t="s" r="J363" s="7">
         <v>72</v>
@@ -13193,7 +13211,7 @@
       <c r="K363" s="7"/>
       <c r="L363" s="7"/>
       <c t="s" r="M363" s="7">
-        <v>408</v>
+        <v>411</v>
       </c>
     </row>
     <row r="364" ht="14.25" customHeight="1">
@@ -13208,7 +13226,7 @@
       </c>
       <c r="D364" s="7"/>
       <c t="s" r="E364" s="7">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="F364" s="7">
         <v>320</v>
@@ -13241,7 +13259,7 @@
       </c>
       <c r="D365" s="7"/>
       <c t="s" r="E365" s="7">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="F365" s="7">
         <v>320</v>
@@ -13253,10 +13271,10 @@
         <v>66</v>
       </c>
       <c t="s" r="I365" s="7">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c t="s" r="J365" s="7">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="K365" s="7"/>
       <c r="L365" s="7"/>
@@ -13274,7 +13292,7 @@
       </c>
       <c r="D366" s="7"/>
       <c t="s" r="E366" s="7">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="F366" s="7">
         <v>320</v>
@@ -13286,10 +13304,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I366" s="7">
-        <v>358</v>
+        <v>382</v>
       </c>
       <c t="s" r="J366" s="7">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="K366" s="7"/>
       <c r="L366" s="7"/>
@@ -13322,7 +13340,7 @@
       </c>
       <c r="D368" s="7"/>
       <c t="s" r="E368" s="7">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="F368" s="7">
         <v>320</v>
@@ -13331,10 +13349,10 @@
         <v>46</v>
       </c>
       <c t="s" r="H368" s="8">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c t="s" r="I368" s="7">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c t="s" r="J368" s="7">
         <v>102</v>
@@ -13342,7 +13360,7 @@
       <c r="K368" s="7"/>
       <c r="L368" s="7"/>
       <c t="s" r="M368" s="7">
-        <v>370</v>
+        <v>372</v>
       </c>
     </row>
     <row r="369" ht="14.25" customHeight="1">
@@ -13357,13 +13375,13 @@
       </c>
       <c r="D369" s="7"/>
       <c t="s" r="E369" s="7">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="F369" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G369" s="8">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c t="s" r="H369" s="8">
         <v>46</v>
@@ -13377,7 +13395,7 @@
       <c r="K369" s="7"/>
       <c r="L369" s="7"/>
       <c t="s" r="M369" s="7">
-        <v>453</v>
+        <v>456</v>
       </c>
     </row>
     <row r="370" ht="15" customHeight="1">
@@ -13392,7 +13410,7 @@
       </c>
       <c r="D370" s="7"/>
       <c t="s" r="E370" s="7">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="F370" s="7">
         <v>320</v>
@@ -13401,7 +13419,7 @@
         <v>46</v>
       </c>
       <c t="s" r="H370" s="8">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c t="s" r="I370" s="7">
         <v>59</v>
@@ -13427,13 +13445,13 @@
       </c>
       <c r="D371" s="7"/>
       <c t="s" r="E371" s="7">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="F371" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G371" s="8">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c t="s" r="H371" s="8">
         <v>46</v>
@@ -13447,7 +13465,7 @@
       <c r="K371" s="7"/>
       <c r="L371" s="7"/>
       <c t="s" r="M371" s="7">
-        <v>454</v>
+        <v>457</v>
       </c>
     </row>
     <row r="372" ht="14.25" customHeight="1">
@@ -13462,7 +13480,7 @@
       </c>
       <c r="D372" s="7"/>
       <c t="s" r="E372" s="7">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="F372" s="7">
         <v>320</v>
@@ -13471,13 +13489,13 @@
         <v>46</v>
       </c>
       <c t="s" r="H372" s="8">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c t="s" r="I372" s="7">
         <v>106</v>
       </c>
       <c t="s" r="J372" s="7">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="K372" s="7"/>
       <c r="L372" s="7"/>
@@ -13495,19 +13513,19 @@
       </c>
       <c r="D373" s="7"/>
       <c t="s" r="E373" s="7">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="F373" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G373" s="8">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c t="s" r="H373" s="8">
         <v>46</v>
       </c>
       <c t="s" r="I373" s="7">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c t="s" r="J373" s="7">
         <v>159</v>
@@ -13528,7 +13546,7 @@
       </c>
       <c r="D374" s="7"/>
       <c t="s" r="E374" s="7">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="F374" s="7">
         <v>320</v>
@@ -13540,7 +13558,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I374" s="7">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c t="s" r="J374" s="7">
         <v>110</v>
@@ -13576,7 +13594,7 @@
       </c>
       <c r="D376" s="7"/>
       <c t="s" r="E376" s="7">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="F376" s="7">
         <v>321</v>
@@ -13585,18 +13603,18 @@
         <v>46</v>
       </c>
       <c t="s" r="H376" s="8">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c t="s" r="I376" s="7">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c t="s" r="J376" s="7">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="K376" s="7"/>
       <c r="L376" s="7"/>
       <c t="s" r="M376" s="7">
-        <v>456</v>
+        <v>459</v>
       </c>
     </row>
     <row r="377" ht="14.25" customHeight="1">
@@ -13611,13 +13629,13 @@
       </c>
       <c r="D377" s="7"/>
       <c t="s" r="E377" s="7">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="F377" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G377" s="8">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c t="s" r="H377" s="8">
         <v>46</v>
@@ -13631,7 +13649,7 @@
       <c r="K377" s="7"/>
       <c r="L377" s="7"/>
       <c t="s" r="M377" s="7">
-        <v>457</v>
+        <v>460</v>
       </c>
     </row>
     <row r="378" ht="14.25" customHeight="1">
@@ -13646,7 +13664,7 @@
       </c>
       <c r="D378" s="7"/>
       <c t="s" r="E378" s="7">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="F378" s="7">
         <v>321</v>
@@ -13655,10 +13673,10 @@
         <v>46</v>
       </c>
       <c t="s" r="H378" s="8">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c t="s" r="I378" s="7">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c t="s" r="J378" s="7">
         <v>151</v>
@@ -13666,7 +13684,7 @@
       <c r="K378" s="7"/>
       <c r="L378" s="7"/>
       <c t="s" r="M378" s="7">
-        <v>459</v>
+        <v>462</v>
       </c>
     </row>
     <row r="379" ht="14.25" customHeight="1">
@@ -13681,19 +13699,19 @@
       </c>
       <c r="D379" s="7"/>
       <c t="s" r="E379" s="7">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="F379" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G379" s="8">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c t="s" r="H379" s="8">
         <v>46</v>
       </c>
       <c t="s" r="I379" s="7">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c t="s" r="J379" s="7">
         <v>23</v>
@@ -13714,7 +13732,7 @@
       </c>
       <c r="D380" s="7"/>
       <c t="s" r="E380" s="7">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="F380" s="7">
         <v>321</v>
@@ -13723,13 +13741,13 @@
         <v>46</v>
       </c>
       <c t="s" r="H380" s="8">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c t="s" r="I380" s="7">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c t="s" r="J380" s="7">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="K380" s="7"/>
       <c r="L380" s="7"/>
@@ -13747,22 +13765,22 @@
       </c>
       <c r="D381" s="7"/>
       <c t="s" r="E381" s="7">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="F381" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G381" s="8">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c t="s" r="H381" s="8">
         <v>46</v>
       </c>
       <c t="s" r="I381" s="7">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c t="s" r="J381" s="7">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="K381" s="7"/>
       <c r="L381" s="7"/>
@@ -13795,7 +13813,7 @@
       </c>
       <c r="D383" s="7"/>
       <c t="s" r="E383" s="7">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="F383" s="7">
         <v>320</v>
@@ -13804,18 +13822,18 @@
         <v>46</v>
       </c>
       <c t="s" r="H383" s="8">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c t="s" r="I383" s="7">
         <v>70</v>
       </c>
       <c t="s" r="J383" s="7">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="K383" s="7"/>
       <c r="L383" s="7"/>
       <c t="s" r="M383" s="7">
-        <v>464</v>
+        <v>467</v>
       </c>
     </row>
     <row r="384" ht="14.25" customHeight="1">
@@ -13830,27 +13848,27 @@
       </c>
       <c r="D384" s="7"/>
       <c t="s" r="E384" s="7">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="F384" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G384" s="8">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c t="s" r="H384" s="8">
         <v>46</v>
       </c>
       <c t="s" r="I384" s="7">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c t="s" r="J384" s="7">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="K384" s="7"/>
       <c r="L384" s="7"/>
       <c t="s" r="M384" s="7">
-        <v>465</v>
+        <v>468</v>
       </c>
     </row>
     <row r="385" ht="15" customHeight="1">
@@ -13865,7 +13883,7 @@
       </c>
       <c r="D385" s="7"/>
       <c t="s" r="E385" s="7">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="F385" s="7">
         <v>320</v>
@@ -13880,12 +13898,12 @@
         <v>144</v>
       </c>
       <c t="s" r="J385" s="7">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="K385" s="7"/>
       <c r="L385" s="7"/>
       <c t="s" r="M385" s="7">
-        <v>283</v>
+        <v>285</v>
       </c>
     </row>
     <row r="386" ht="14.25" customHeight="1">
@@ -13900,7 +13918,7 @@
       </c>
       <c r="D386" s="7"/>
       <c t="s" r="E386" s="7">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="F386" s="7">
         <v>320</v>
@@ -13912,7 +13930,7 @@
         <v>46</v>
       </c>
       <c t="s" r="I386" s="7">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c t="s" r="J386" s="7">
         <v>62</v>
@@ -13920,7 +13938,7 @@
       <c r="K386" s="7"/>
       <c r="L386" s="7"/>
       <c t="s" r="M386" s="7">
-        <v>466</v>
+        <v>469</v>
       </c>
     </row>
     <row r="387" ht="14.25" customHeight="1">
@@ -13935,7 +13953,7 @@
       </c>
       <c r="D387" s="7"/>
       <c t="s" r="E387" s="7">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="F387" s="7">
         <v>320</v>
@@ -13950,7 +13968,7 @@
         <v>35</v>
       </c>
       <c t="s" r="J387" s="7">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="K387" s="7"/>
       <c r="L387" s="7"/>
@@ -13968,7 +13986,7 @@
       </c>
       <c r="D388" s="7"/>
       <c t="s" r="E388" s="7">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="F388" s="7">
         <v>320</v>
@@ -14001,7 +14019,7 @@
       </c>
       <c r="D389" s="7"/>
       <c t="s" r="E389" s="7">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="F389" s="7">
         <v>320</v>
@@ -14010,13 +14028,13 @@
         <v>46</v>
       </c>
       <c t="s" r="H389" s="8">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c t="s" r="I389" s="7">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c t="s" r="J389" s="7">
-        <v>357</v>
+        <v>381</v>
       </c>
       <c r="K389" s="7"/>
       <c r="L389" s="7"/>
@@ -14034,13 +14052,13 @@
       </c>
       <c r="D390" s="7"/>
       <c t="s" r="E390" s="7">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="F390" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G390" s="8">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c t="s" r="H390" s="8">
         <v>46</v>
@@ -14067,7 +14085,7 @@
       </c>
       <c r="D391" s="7"/>
       <c t="s" r="E391" s="7">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="F391" s="7">
         <v>320</v>
@@ -14079,10 +14097,10 @@
         <v>52</v>
       </c>
       <c t="s" r="I391" s="7">
-        <v>380</v>
+        <v>360</v>
       </c>
       <c t="s" r="J391" s="7">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="K391" s="7"/>
       <c r="L391" s="7"/>
@@ -14100,7 +14118,7 @@
       </c>
       <c r="D392" s="7"/>
       <c t="s" r="E392" s="7">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="F392" s="7">
         <v>320</v>
@@ -14112,10 +14130,10 @@
         <v>46</v>
       </c>
       <c t="s" r="I392" s="7">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c t="s" r="J392" s="7">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="K392" s="7"/>
       <c r="L392" s="7"/>
@@ -14148,7 +14166,7 @@
       </c>
       <c r="D394" s="7"/>
       <c t="s" r="E394" s="7">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="F394" s="7">
         <v>321</v>
@@ -14163,12 +14181,12 @@
         <v>143</v>
       </c>
       <c t="s" r="J394" s="7">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="K394" s="7"/>
       <c r="L394" s="7"/>
       <c t="s" r="M394" s="7">
-        <v>469</v>
+        <v>472</v>
       </c>
     </row>
     <row r="395" ht="15" customHeight="1">
@@ -14183,7 +14201,7 @@
       </c>
       <c r="D395" s="7"/>
       <c t="s" r="E395" s="7">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="F395" s="7">
         <v>321</v>
@@ -14192,10 +14210,10 @@
         <v>52</v>
       </c>
       <c t="s" r="H395" s="8">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c t="s" r="I395" s="7">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c t="s" r="J395" s="7">
         <v>141</v>
@@ -14203,7 +14221,7 @@
       <c r="K395" s="7"/>
       <c r="L395" s="7"/>
       <c t="s" r="M395" s="7">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="396" ht="14.25" customHeight="1">
@@ -14218,19 +14236,19 @@
       </c>
       <c r="D396" s="7"/>
       <c t="s" r="E396" s="7">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="F396" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G396" s="8">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c t="s" r="H396" s="8">
         <v>46</v>
       </c>
       <c t="s" r="I396" s="7">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c t="s" r="J396" s="7">
         <v>24</v>
@@ -14251,7 +14269,7 @@
       </c>
       <c r="D397" s="7"/>
       <c t="s" r="E397" s="7">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="F397" s="7">
         <v>321</v>
@@ -14263,10 +14281,10 @@
         <v>52</v>
       </c>
       <c t="s" r="I397" s="7">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c t="s" r="J397" s="7">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="K397" s="7"/>
       <c r="L397" s="7"/>
@@ -14284,7 +14302,7 @@
       </c>
       <c r="D398" s="7"/>
       <c t="s" r="E398" s="7">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="F398" s="7">
         <v>321</v>
@@ -14296,10 +14314,10 @@
         <v>42</v>
       </c>
       <c t="s" r="I398" s="7">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c t="s" r="J398" s="7">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="K398" s="7"/>
       <c r="L398" s="7"/>
@@ -14332,7 +14350,7 @@
       </c>
       <c r="D400" s="7"/>
       <c t="s" r="E400" s="7">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="F400" s="7">
         <v>321</v>
@@ -14352,7 +14370,7 @@
       <c r="K400" s="7"/>
       <c r="L400" s="7"/>
       <c t="s" r="M400" s="7">
-        <v>473</v>
+        <v>476</v>
       </c>
     </row>
     <row r="401" ht="14.25" customHeight="1">
@@ -14367,7 +14385,7 @@
       </c>
       <c r="D401" s="7"/>
       <c t="s" r="E401" s="7">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="F401" s="7">
         <v>321</v>
@@ -14382,7 +14400,7 @@
         <v>152</v>
       </c>
       <c t="s" r="J401" s="7">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="K401" s="7"/>
       <c r="L401" s="7"/>
@@ -14400,7 +14418,7 @@
       </c>
       <c r="D402" s="7"/>
       <c t="s" r="E402" s="7">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="F402" s="7">
         <v>321</v>
@@ -14412,10 +14430,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I402" s="7">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c t="s" r="J402" s="7">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="K402" s="7"/>
       <c r="L402" s="7"/>
@@ -14433,7 +14451,7 @@
       </c>
       <c r="D403" s="7"/>
       <c t="s" r="E403" s="7">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="F403" s="7">
         <v>321</v>
@@ -14445,10 +14463,10 @@
         <v>46</v>
       </c>
       <c t="s" r="I403" s="7">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c t="s" r="J403" s="7">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="K403" s="7"/>
       <c r="L403" s="7"/>
@@ -14481,7 +14499,7 @@
       </c>
       <c r="D405" s="7"/>
       <c t="s" r="E405" s="7">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="F405" s="7">
         <v>320</v>
@@ -14493,15 +14511,15 @@
         <v>17</v>
       </c>
       <c t="s" r="I405" s="7">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c t="s" r="J405" s="7">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="K405" s="7"/>
       <c r="L405" s="7"/>
       <c t="s" r="M405" s="7">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="406" ht="14.25" customHeight="1">
@@ -14516,7 +14534,7 @@
       </c>
       <c r="D406" s="7"/>
       <c t="s" r="E406" s="7">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="F406" s="7">
         <v>320</v>
@@ -14528,7 +14546,7 @@
         <v>46</v>
       </c>
       <c t="s" r="I406" s="7">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c t="s" r="J406" s="7">
         <v>47</v>
@@ -14536,7 +14554,7 @@
       <c r="K406" s="7"/>
       <c r="L406" s="7"/>
       <c t="s" r="M406" s="7">
-        <v>476</v>
+        <v>479</v>
       </c>
     </row>
     <row r="407" ht="14.25" customHeight="1">
@@ -14551,7 +14569,7 @@
       </c>
       <c r="D407" s="7"/>
       <c t="s" r="E407" s="7">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="F407" s="7">
         <v>320</v>
@@ -14563,10 +14581,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I407" s="7">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c t="s" r="J407" s="7">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="K407" s="7"/>
       <c r="L407" s="7"/>
@@ -14584,7 +14602,7 @@
       </c>
       <c r="D408" s="7"/>
       <c t="s" r="E408" s="7">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="F408" s="7">
         <v>320</v>
@@ -14599,7 +14617,7 @@
         <v>24</v>
       </c>
       <c t="s" r="J408" s="7">
-        <v>380</v>
+        <v>360</v>
       </c>
       <c r="K408" s="7"/>
       <c r="L408" s="7"/>
@@ -14632,7 +14650,7 @@
       </c>
       <c r="D410" s="7"/>
       <c t="s" r="E410" s="7">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="F410" s="7">
         <v>320</v>
@@ -14641,18 +14659,18 @@
         <v>17</v>
       </c>
       <c t="s" r="H410" s="8">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c t="s" r="I410" s="7">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c t="s" r="J410" s="7">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="K410" s="7"/>
       <c r="L410" s="7"/>
       <c t="s" r="M410" s="7">
-        <v>479</v>
+        <v>482</v>
       </c>
     </row>
     <row r="411" ht="14.25" customHeight="1">
@@ -14667,13 +14685,13 @@
       </c>
       <c r="D411" s="7"/>
       <c t="s" r="E411" s="7">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="F411" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G411" s="8">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c t="s" r="H411" s="8">
         <v>17</v>
@@ -14687,7 +14705,7 @@
       <c r="K411" s="7"/>
       <c r="L411" s="7"/>
       <c t="s" r="M411" s="7">
-        <v>480</v>
+        <v>483</v>
       </c>
     </row>
     <row r="412" ht="14.25" customHeight="1">
@@ -14702,7 +14720,7 @@
       </c>
       <c r="D412" s="7"/>
       <c t="s" r="E412" s="7">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="F412" s="7">
         <v>320</v>
@@ -14717,7 +14735,7 @@
         <v>89</v>
       </c>
       <c t="s" r="J412" s="7">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="K412" s="7"/>
       <c r="L412" s="7"/>
@@ -14737,7 +14755,7 @@
       </c>
       <c r="D413" s="7"/>
       <c t="s" r="E413" s="7">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="F413" s="7">
         <v>320</v>
@@ -14749,15 +14767,15 @@
         <v>17</v>
       </c>
       <c t="s" r="I413" s="7">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c t="s" r="J413" s="7">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="K413" s="7"/>
       <c r="L413" s="7"/>
       <c t="s" r="M413" s="7">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="414" ht="14.25" customHeight="1">
@@ -14772,7 +14790,7 @@
       </c>
       <c r="D414" s="7"/>
       <c t="s" r="E414" s="7">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="F414" s="7">
         <v>320</v>
@@ -14784,7 +14802,7 @@
         <v>31</v>
       </c>
       <c t="s" r="I414" s="7">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c t="s" r="J414" s="7">
         <v>159</v>
@@ -14805,7 +14823,7 @@
       </c>
       <c r="D415" s="7"/>
       <c t="s" r="E415" s="7">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="F415" s="7">
         <v>320</v>
@@ -14817,7 +14835,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I415" s="7">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c t="s" r="J415" s="7">
         <v>121</v>
@@ -14838,7 +14856,7 @@
       </c>
       <c r="D416" s="7"/>
       <c t="s" r="E416" s="7">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="F416" s="7">
         <v>320</v>
@@ -14847,10 +14865,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H416" s="8">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c t="s" r="I416" s="7">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c t="s" r="J416" s="7">
         <v>18</v>
@@ -14886,7 +14904,7 @@
       </c>
       <c r="D418" s="7"/>
       <c t="s" r="E418" s="7">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="F418" s="7">
         <v>321</v>
@@ -14898,15 +14916,15 @@
         <v>66</v>
       </c>
       <c t="s" r="I418" s="7">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c t="s" r="J418" s="7">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="K418" s="7"/>
       <c r="L418" s="7"/>
       <c t="s" r="M418" s="7">
-        <v>484</v>
+        <v>487</v>
       </c>
     </row>
     <row r="419" ht="14.25" customHeight="1">
@@ -14921,7 +14939,7 @@
       </c>
       <c r="D419" s="7"/>
       <c t="s" r="E419" s="7">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="F419" s="7">
         <v>321</v>
@@ -14933,7 +14951,7 @@
         <v>169</v>
       </c>
       <c t="s" r="I419" s="7">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c t="s" r="J419" s="7">
         <v>136</v>
@@ -14956,7 +14974,7 @@
       </c>
       <c r="D420" s="7"/>
       <c t="s" r="E420" s="7">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="F420" s="7">
         <v>321</v>
@@ -14971,12 +14989,12 @@
         <v>138</v>
       </c>
       <c t="s" r="J420" s="7">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="K420" s="7"/>
       <c r="L420" s="7"/>
       <c t="s" r="M420" s="7">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="421" ht="14.25" customHeight="1">
@@ -15006,7 +15024,7 @@
       </c>
       <c r="D422" s="7"/>
       <c t="s" r="E422" s="7">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="F422" s="7">
         <v>321</v>
@@ -15015,13 +15033,13 @@
         <v>46</v>
       </c>
       <c t="s" r="H422" s="8">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c t="s" r="I422" s="7">
         <v>56</v>
       </c>
       <c t="s" r="J422" s="7">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="K422" s="7"/>
       <c r="L422" s="7"/>
@@ -15041,13 +15059,13 @@
       </c>
       <c r="D423" s="7"/>
       <c t="s" r="E423" s="7">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="F423" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G423" s="8">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c t="s" r="H423" s="8">
         <v>52</v>
@@ -15056,12 +15074,12 @@
         <v>147</v>
       </c>
       <c t="s" r="J423" s="7">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="K423" s="7"/>
       <c r="L423" s="7"/>
       <c t="s" r="M423" s="7">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
     <row r="424" ht="14.25" customHeight="1">
@@ -15076,7 +15094,7 @@
       </c>
       <c r="D424" s="7"/>
       <c t="s" r="E424" s="7">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="F424" s="7">
         <v>321</v>
@@ -15085,7 +15103,7 @@
         <v>52</v>
       </c>
       <c t="s" r="H424" s="8">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c t="s" r="I424" s="7">
         <v>139</v>
@@ -15095,7 +15113,9 @@
       </c>
       <c r="K424" s="7"/>
       <c r="L424" s="7"/>
-      <c r="M424" s="7"/>
+      <c t="s" r="M424" s="7">
+        <v>234</v>
+      </c>
     </row>
     <row r="425" ht="15" customHeight="1">
       <c t="s" r="A425" s="6">
@@ -15109,22 +15129,22 @@
       </c>
       <c r="D425" s="7"/>
       <c t="s" r="E425" s="7">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="F425" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G425" s="8">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c t="s" r="H425" s="8">
         <v>52</v>
       </c>
       <c t="s" r="I425" s="7">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c t="s" r="J425" s="7">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="K425" s="7"/>
       <c r="L425" s="7"/>
@@ -15157,7 +15177,7 @@
       </c>
       <c r="D427" s="7"/>
       <c t="s" r="E427" s="7">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="F427" s="7">
         <v>321</v>
@@ -15166,7 +15186,7 @@
         <v>46</v>
       </c>
       <c t="s" r="H427" s="8">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c t="s" r="I427" s="7">
         <v>144</v>
@@ -15192,27 +15212,27 @@
       </c>
       <c r="D428" s="7"/>
       <c t="s" r="E428" s="7">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="F428" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G428" s="8">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c t="s" r="H428" s="8">
         <v>46</v>
       </c>
       <c t="s" r="I428" s="7">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c t="s" r="J428" s="7">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="K428" s="7"/>
       <c r="L428" s="7"/>
       <c t="s" r="M428" s="7">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="429" ht="14.25" customHeight="1">
@@ -15227,7 +15247,7 @@
       </c>
       <c r="D429" s="7"/>
       <c t="s" r="E429" s="7">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="F429" s="7">
         <v>321</v>
@@ -15236,10 +15256,10 @@
         <v>46</v>
       </c>
       <c t="s" r="H429" s="8">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c t="s" r="I429" s="7">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c t="s" r="J429" s="7">
         <v>159</v>
@@ -15260,22 +15280,22 @@
       </c>
       <c r="D430" s="7"/>
       <c t="s" r="E430" s="7">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="F430" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G430" s="8">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c t="s" r="H430" s="8">
         <v>46</v>
       </c>
       <c t="s" r="I430" s="7">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c t="s" r="J430" s="7">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="K430" s="7"/>
       <c r="L430" s="7"/>
@@ -15308,7 +15328,7 @@
       </c>
       <c r="D432" s="7"/>
       <c t="s" r="E432" s="7">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="F432" s="7">
         <v>321</v>
@@ -15320,15 +15340,15 @@
         <v>104</v>
       </c>
       <c t="s" r="I432" s="7">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c t="s" r="J432" s="7">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="K432" s="7"/>
       <c r="L432" s="7"/>
       <c t="s" r="M432" s="7">
-        <v>490</v>
+        <v>493</v>
       </c>
     </row>
     <row r="433" ht="14.25" customHeight="1">
@@ -15343,7 +15363,7 @@
       </c>
       <c r="D433" s="7"/>
       <c t="s" r="E433" s="7">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="F433" s="7">
         <v>321</v>
@@ -15358,12 +15378,12 @@
         <v>114</v>
       </c>
       <c t="s" r="J433" s="7">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="K433" s="7"/>
       <c r="L433" s="7"/>
       <c t="s" r="M433" s="7">
-        <v>491</v>
+        <v>494</v>
       </c>
     </row>
     <row r="434" ht="14.25" customHeight="1">
@@ -15378,7 +15398,7 @@
       </c>
       <c r="D434" s="7"/>
       <c t="s" r="E434" s="7">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="F434" s="7">
         <v>321</v>
@@ -15390,10 +15410,10 @@
         <v>109</v>
       </c>
       <c t="s" r="I434" s="7">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c t="s" r="J434" s="7">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="K434" s="7"/>
       <c r="L434" s="7"/>
@@ -15413,7 +15433,7 @@
       </c>
       <c r="D435" s="7"/>
       <c t="s" r="E435" s="7">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="F435" s="7">
         <v>321</v>
@@ -15425,7 +15445,7 @@
         <v>46</v>
       </c>
       <c t="s" r="I435" s="7">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c t="s" r="J435" s="7">
         <v>118</v>
@@ -15448,7 +15468,7 @@
       </c>
       <c r="D436" s="7"/>
       <c t="s" r="E436" s="7">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="F436" s="7">
         <v>321</v>
@@ -15457,13 +15477,13 @@
         <v>46</v>
       </c>
       <c t="s" r="H436" s="8">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c t="s" r="I436" s="7">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c t="s" r="J436" s="7">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="K436" s="7"/>
       <c r="L436" s="7"/>
@@ -15481,22 +15501,22 @@
       </c>
       <c r="D437" s="7"/>
       <c t="s" r="E437" s="7">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="F437" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G437" s="8">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c t="s" r="H437" s="8">
         <v>46</v>
       </c>
       <c t="s" r="I437" s="7">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c t="s" r="J437" s="7">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="K437" s="7"/>
       <c r="L437" s="7"/>
@@ -15529,7 +15549,7 @@
       </c>
       <c r="D439" s="7"/>
       <c t="s" r="E439" s="7">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="F439" s="7">
         <v>321</v>
@@ -15544,12 +15564,12 @@
         <v>44</v>
       </c>
       <c t="s" r="J439" s="7">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="K439" s="7"/>
       <c r="L439" s="7"/>
       <c t="s" r="M439" s="7">
-        <v>494</v>
+        <v>497</v>
       </c>
     </row>
     <row r="440" ht="15" customHeight="1">
@@ -15564,7 +15584,7 @@
       </c>
       <c r="D440" s="7"/>
       <c t="s" r="E440" s="7">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="F440" s="7">
         <v>321</v>
@@ -15584,7 +15604,7 @@
       <c r="K440" s="7"/>
       <c r="L440" s="7"/>
       <c t="s" r="M440" s="7">
-        <v>495</v>
+        <v>498</v>
       </c>
     </row>
     <row r="441" ht="14.25" customHeight="1">
@@ -15599,7 +15619,7 @@
       </c>
       <c r="D441" s="7"/>
       <c t="s" r="E441" s="7">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="F441" s="7">
         <v>321</v>
@@ -15614,12 +15634,12 @@
         <v>156</v>
       </c>
       <c t="s" r="J441" s="7">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="K441" s="7"/>
       <c r="L441" s="7"/>
       <c t="s" r="M441" s="7">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="442" ht="14.25" customHeight="1">
@@ -15634,7 +15654,7 @@
       </c>
       <c r="D442" s="7"/>
       <c t="s" r="E442" s="7">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="F442" s="7">
         <v>321</v>
@@ -15649,7 +15669,7 @@
         <v>136</v>
       </c>
       <c t="s" r="J442" s="7">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="K442" s="7"/>
       <c r="L442" s="7"/>
@@ -15669,7 +15689,7 @@
       </c>
       <c r="D443" s="7"/>
       <c t="s" r="E443" s="7">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="F443" s="7">
         <v>321</v>
@@ -15681,10 +15701,10 @@
         <v>52</v>
       </c>
       <c t="s" r="I443" s="7">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c t="s" r="J443" s="7">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="K443" s="7"/>
       <c r="L443" s="7"/>
@@ -15702,7 +15722,7 @@
       </c>
       <c r="D444" s="7"/>
       <c t="s" r="E444" s="7">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="F444" s="7">
         <v>321</v>
@@ -15714,10 +15734,10 @@
         <v>46</v>
       </c>
       <c t="s" r="I444" s="7">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c t="s" r="J444" s="7">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="K444" s="7"/>
       <c r="L444" s="7"/>
@@ -15750,7 +15770,7 @@
       </c>
       <c r="D446" s="7"/>
       <c t="s" r="E446" s="7">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="F446" s="7">
         <v>320</v>
@@ -15770,7 +15790,7 @@
       <c r="K446" s="7"/>
       <c r="L446" s="7"/>
       <c t="s" r="M446" s="7">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="447" ht="14.25" customHeight="1">
@@ -15785,7 +15805,7 @@
       </c>
       <c r="D447" s="7"/>
       <c t="s" r="E447" s="7">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="F447" s="7">
         <v>320</v>
@@ -15805,7 +15825,7 @@
       <c r="K447" s="7"/>
       <c r="L447" s="7"/>
       <c t="s" r="M447" s="7">
-        <v>499</v>
+        <v>502</v>
       </c>
     </row>
     <row r="448" ht="14.25" customHeight="1">
@@ -15820,7 +15840,7 @@
       </c>
       <c r="D448" s="7"/>
       <c t="s" r="E448" s="7">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="F448" s="7">
         <v>320</v>
@@ -15832,7 +15852,7 @@
         <v>93</v>
       </c>
       <c t="s" r="I448" s="7">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c t="s" r="J448" s="7">
         <v>19</v>
@@ -15840,7 +15860,7 @@
       <c r="K448" s="7"/>
       <c r="L448" s="7"/>
       <c t="s" r="M448" s="7">
-        <v>500</v>
+        <v>503</v>
       </c>
     </row>
     <row r="449" ht="14.25" customHeight="1">
@@ -15855,7 +15875,7 @@
       </c>
       <c r="D449" s="7"/>
       <c t="s" r="E449" s="7">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="F449" s="7">
         <v>320</v>
@@ -15888,7 +15908,7 @@
       </c>
       <c r="D450" s="7"/>
       <c t="s" r="E450" s="7">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="F450" s="7">
         <v>320</v>
@@ -15900,10 +15920,10 @@
         <v>46</v>
       </c>
       <c t="s" r="I450" s="7">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c t="s" r="J450" s="7">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="K450" s="7"/>
       <c r="L450" s="7"/>
@@ -15921,7 +15941,7 @@
       </c>
       <c r="D451" s="7"/>
       <c t="s" r="E451" s="7">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="F451" s="7">
         <v>320</v>
@@ -15936,7 +15956,7 @@
         <v>100</v>
       </c>
       <c t="s" r="J451" s="7">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="K451" s="7"/>
       <c r="L451" s="7"/>
@@ -15969,13 +15989,13 @@
       </c>
       <c r="D453" s="7"/>
       <c t="s" r="E453" s="7">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="F453" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G453" s="8">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c t="s" r="H453" s="8">
         <v>46</v>
@@ -16004,7 +16024,7 @@
       </c>
       <c r="D454" s="7"/>
       <c t="s" r="E454" s="7">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="F454" s="7">
         <v>321</v>
@@ -16016,7 +16036,7 @@
         <v>31</v>
       </c>
       <c t="s" r="I454" s="7">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c t="s" r="J454" s="7">
         <v>95</v>
@@ -16037,7 +16057,7 @@
       </c>
       <c r="D455" s="7"/>
       <c t="s" r="E455" s="7">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="F455" s="7">
         <v>321</v>
@@ -16049,10 +16069,10 @@
         <v>46</v>
       </c>
       <c t="s" r="I455" s="7">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c t="s" r="J455" s="7">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="K455" s="7"/>
       <c r="L455" s="7"/>
@@ -16070,7 +16090,7 @@
       </c>
       <c r="D456" s="7"/>
       <c t="s" r="E456" s="7">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="F456" s="7">
         <v>321</v>
@@ -16082,10 +16102,10 @@
         <v>119</v>
       </c>
       <c t="s" r="I456" s="7">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c t="s" r="J456" s="7">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="K456" s="7"/>
       <c r="L456" s="7"/>
@@ -16103,7 +16123,7 @@
       </c>
       <c r="D457" s="7"/>
       <c t="s" r="E457" s="7">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="F457" s="7">
         <v>321</v>
@@ -16151,7 +16171,7 @@
       </c>
       <c r="D459" s="7"/>
       <c t="s" r="E459" s="7">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="F459" s="7">
         <v>321</v>
@@ -16163,15 +16183,15 @@
         <v>31</v>
       </c>
       <c t="s" r="I459" s="7">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c t="s" r="J459" s="7">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="K459" s="7"/>
       <c r="L459" s="7"/>
       <c t="s" r="M459" s="7">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="460" ht="15" customHeight="1">
@@ -16186,7 +16206,7 @@
       </c>
       <c r="D460" s="7"/>
       <c t="s" r="E460" s="7">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="F460" s="7">
         <v>321</v>
@@ -16201,7 +16221,7 @@
         <v>39</v>
       </c>
       <c t="s" r="J460" s="7">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="K460" s="7"/>
       <c r="L460" s="7"/>
@@ -16234,7 +16254,7 @@
       </c>
       <c r="D462" s="7"/>
       <c t="s" r="E462" s="7">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="F462" s="7">
         <v>321</v>
@@ -16246,7 +16266,7 @@
         <v>52</v>
       </c>
       <c t="s" r="I462" s="7">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c t="s" r="J462" s="7">
         <v>164</v>
@@ -16254,7 +16274,7 @@
       <c r="K462" s="7"/>
       <c r="L462" s="7"/>
       <c t="s" r="M462" s="7">
-        <v>507</v>
+        <v>510</v>
       </c>
     </row>
     <row r="463" ht="14.25" customHeight="1">
@@ -16269,7 +16289,7 @@
       </c>
       <c r="D463" s="7"/>
       <c t="s" r="E463" s="7">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="F463" s="7">
         <v>321</v>
@@ -16281,7 +16301,7 @@
         <v>46</v>
       </c>
       <c t="s" r="I463" s="7">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c t="s" r="J463" s="7">
         <v>114</v>
@@ -16289,7 +16309,7 @@
       <c r="K463" s="7"/>
       <c r="L463" s="7"/>
       <c t="s" r="M463" s="7">
-        <v>508</v>
+        <v>511</v>
       </c>
     </row>
     <row r="464" ht="14.25" customHeight="1">
@@ -16304,7 +16324,7 @@
       </c>
       <c r="D464" s="7"/>
       <c t="s" r="E464" s="7">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="F464" s="7">
         <v>321</v>
@@ -16316,10 +16336,10 @@
         <v>31</v>
       </c>
       <c t="s" r="I464" s="7">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c t="s" r="J464" s="7">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="K464" s="7"/>
       <c r="L464" s="7"/>
@@ -16339,7 +16359,7 @@
       </c>
       <c r="D465" s="7"/>
       <c t="s" r="E465" s="7">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="F465" s="7">
         <v>321</v>
@@ -16354,12 +16374,12 @@
         <v>170</v>
       </c>
       <c t="s" r="J465" s="7">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="K465" s="7"/>
       <c r="L465" s="7"/>
       <c t="s" r="M465" s="7">
-        <v>509</v>
+        <v>512</v>
       </c>
     </row>
     <row r="466" ht="14.25" customHeight="1">
@@ -16374,7 +16394,7 @@
       </c>
       <c r="D466" s="7"/>
       <c t="s" r="E466" s="7">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="F466" s="7">
         <v>321</v>
@@ -16394,7 +16414,7 @@
       <c r="K466" s="7"/>
       <c r="L466" s="7"/>
       <c t="s" r="M466" s="7">
-        <v>510</v>
+        <v>513</v>
       </c>
     </row>
     <row r="467" ht="14.25" customHeight="1">
@@ -16409,7 +16429,7 @@
       </c>
       <c r="D467" s="7"/>
       <c t="s" r="E467" s="7">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="F467" s="7">
         <v>321</v>
@@ -16457,7 +16477,7 @@
       </c>
       <c r="D469" s="7"/>
       <c t="s" r="E469" s="7">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="F469" s="7">
         <v>320</v>
@@ -16479,7 +16499,7 @@
       </c>
       <c r="L469" s="7"/>
       <c t="s" r="M469" s="7">
-        <v>464</v>
+        <v>467</v>
       </c>
     </row>
     <row r="470" ht="15" customHeight="1">
@@ -16494,7 +16514,7 @@
       </c>
       <c r="D470" s="7"/>
       <c t="s" r="E470" s="7">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="F470" s="7">
         <v>320</v>
@@ -16503,7 +16523,7 @@
         <v>46</v>
       </c>
       <c t="s" r="H470" s="8">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c t="s" r="I470" s="7">
         <v>138</v>
@@ -16514,7 +16534,7 @@
       <c r="K470" s="7"/>
       <c r="L470" s="7"/>
       <c t="s" r="M470" s="7">
-        <v>512</v>
+        <v>515</v>
       </c>
     </row>
     <row r="471" ht="14.25" customHeight="1">
@@ -16529,22 +16549,22 @@
       </c>
       <c r="D471" s="7"/>
       <c t="s" r="E471" s="7">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="F471" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G471" s="8">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c t="s" r="H471" s="8">
         <v>46</v>
       </c>
       <c t="s" r="I471" s="7">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c t="s" r="J471" s="7">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="K471" s="7"/>
       <c r="L471" s="7"/>
@@ -16562,7 +16582,7 @@
       </c>
       <c r="D472" s="7"/>
       <c t="s" r="E472" s="7">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="F472" s="7">
         <v>320</v>
@@ -16571,7 +16591,7 @@
         <v>46</v>
       </c>
       <c t="s" r="H472" s="8">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c t="s" r="I472" s="7">
         <v>152</v>
@@ -16595,13 +16615,13 @@
       </c>
       <c r="D473" s="7"/>
       <c t="s" r="E473" s="7">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="F473" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G473" s="8">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c t="s" r="H473" s="8">
         <v>46</v>
@@ -16610,7 +16630,7 @@
         <v>129</v>
       </c>
       <c t="s" r="J473" s="7">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="K473" s="7"/>
       <c r="L473" s="7"/>
@@ -16643,7 +16663,7 @@
       </c>
       <c r="D475" s="7"/>
       <c t="s" r="E475" s="7">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="F475" s="7">
         <v>330</v>
@@ -16652,13 +16672,13 @@
         <v>52</v>
       </c>
       <c t="s" r="H475" s="8">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c t="s" r="I475" s="7">
         <v>118</v>
       </c>
       <c t="s" r="J475" s="7">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="K475" s="7"/>
       <c r="L475" s="7"/>
@@ -16676,22 +16696,22 @@
       </c>
       <c r="D476" s="7"/>
       <c t="s" r="E476" s="7">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="F476" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G476" s="8">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c t="s" r="H476" s="8">
         <v>52</v>
       </c>
       <c t="s" r="I476" s="7">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c t="s" r="J476" s="7">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="K476" s="7"/>
       <c r="L476" s="7"/>
@@ -16724,7 +16744,7 @@
       </c>
       <c r="D478" s="7"/>
       <c t="s" r="E478" s="7">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="F478" s="7">
         <v>330</v>
@@ -16736,10 +16756,10 @@
         <v>66</v>
       </c>
       <c t="s" r="I478" s="7">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c t="s" r="J478" s="7">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="K478" s="7"/>
       <c r="L478" s="7"/>
@@ -16757,7 +16777,7 @@
       </c>
       <c r="D479" s="7"/>
       <c t="s" r="E479" s="7">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="F479" s="7">
         <v>330</v>
@@ -16766,13 +16786,13 @@
         <v>66</v>
       </c>
       <c t="s" r="H479" s="8">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c t="s" r="I479" s="7">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c t="s" r="J479" s="7">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="K479" s="7"/>
       <c r="L479" s="7"/>
@@ -16805,7 +16825,7 @@
       </c>
       <c r="D481" s="7"/>
       <c t="s" r="E481" s="7">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="F481" s="7">
         <v>330</v>
@@ -16814,7 +16834,7 @@
         <v>66</v>
       </c>
       <c t="s" r="H481" s="8">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c t="s" r="I481" s="7">
         <v>28</v>
@@ -16825,7 +16845,7 @@
       <c r="K481" s="7"/>
       <c r="L481" s="7"/>
       <c t="s" r="M481" s="7">
-        <v>374</v>
+        <v>523</v>
       </c>
     </row>
     <row r="482" ht="14.25" customHeight="1">
@@ -16840,22 +16860,22 @@
       </c>
       <c r="D482" s="7"/>
       <c t="s" r="E482" s="7">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="F482" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G482" s="8">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c t="s" r="H482" s="8">
         <v>66</v>
       </c>
       <c t="s" r="I482" s="7">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c t="s" r="J482" s="7">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="K482" s="7"/>
       <c r="L482" s="7"/>
@@ -16888,7 +16908,7 @@
       </c>
       <c r="D484" s="7"/>
       <c t="s" r="E484" s="7">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="F484" s="7">
         <v>330</v>
@@ -16900,17 +16920,17 @@
         <v>46</v>
       </c>
       <c t="s" r="I484" s="7">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c t="s" r="J484" s="7">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c t="s" r="K484" s="7">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="L484" s="7"/>
       <c t="s" r="M484" s="7">
-        <v>521</v>
+        <v>525</v>
       </c>
     </row>
     <row r="485" ht="15" customHeight="1">
@@ -16925,7 +16945,7 @@
       </c>
       <c r="D485" s="7"/>
       <c t="s" r="E485" s="7">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="F485" s="7">
         <v>330</v>
@@ -16934,7 +16954,7 @@
         <v>46</v>
       </c>
       <c t="s" r="H485" s="8">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c t="s" r="I485" s="7">
         <v>60</v>
@@ -16945,7 +16965,7 @@
       <c r="K485" s="7"/>
       <c r="L485" s="7"/>
       <c t="s" r="M485" s="7">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="486" ht="14.25" customHeight="1">
@@ -16960,19 +16980,19 @@
       </c>
       <c r="D486" s="7"/>
       <c t="s" r="E486" s="7">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="F486" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G486" s="8">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c t="s" r="H486" s="8">
         <v>46</v>
       </c>
       <c t="s" r="I486" s="7">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c t="s" r="J486" s="7">
         <v>112</v>
@@ -17004,11 +17024,11 @@
         <v>5805</v>
       </c>
       <c t="s" r="C488" s="7">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="D488" s="7"/>
       <c t="s" r="E488" s="7">
-        <v>524</v>
+        <v>528</v>
       </c>
       <c r="F488" s="7">
         <v>330</v>
@@ -17017,18 +17037,18 @@
         <v>66</v>
       </c>
       <c t="s" r="H488" s="8">
-        <v>525</v>
+        <v>529</v>
       </c>
       <c t="s" r="I488" s="7">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c t="s" r="J488" s="7">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="K488" s="7"/>
       <c r="L488" s="7"/>
       <c t="s" r="M488" s="7">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="489" ht="14.25" customHeight="1">
@@ -17039,26 +17059,26 @@
         <v>5806</v>
       </c>
       <c t="s" r="C489" s="7">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="D489" s="7"/>
       <c t="s" r="E489" s="7">
-        <v>524</v>
+        <v>528</v>
       </c>
       <c r="F489" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G489" s="8">
-        <v>525</v>
+        <v>529</v>
       </c>
       <c t="s" r="H489" s="8">
         <v>66</v>
       </c>
       <c t="s" r="I489" s="7">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c t="s" r="J489" s="7">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="K489" s="7"/>
       <c r="L489" s="7"/>
@@ -17091,27 +17111,27 @@
       </c>
       <c r="D491" s="7"/>
       <c t="s" r="E491" s="7">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="F491" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G491" s="8">
-        <v>527</v>
+        <v>531</v>
       </c>
       <c t="s" r="H491" s="8">
         <v>46</v>
       </c>
       <c t="s" r="I491" s="7">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c t="s" r="J491" s="7">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="K491" s="7"/>
       <c r="L491" s="7"/>
       <c t="s" r="M491" s="7">
-        <v>528</v>
+        <v>532</v>
       </c>
     </row>
     <row r="492" ht="14.25" customHeight="1">
@@ -17126,7 +17146,7 @@
       </c>
       <c r="D492" s="7"/>
       <c t="s" r="E492" s="7">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="F492" s="7">
         <v>330</v>
@@ -17138,7 +17158,7 @@
         <v>52</v>
       </c>
       <c t="s" r="I492" s="7">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c t="s" r="J492" s="7">
         <v>48</v>
@@ -17174,7 +17194,7 @@
       </c>
       <c r="D494" s="7"/>
       <c t="s" r="E494" s="7">
-        <v>529</v>
+        <v>533</v>
       </c>
       <c r="F494" s="7">
         <v>330</v>
@@ -17183,7 +17203,7 @@
         <v>46</v>
       </c>
       <c t="s" r="H494" s="8">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c t="s" r="I494" s="7">
         <v>33</v>
@@ -17194,7 +17214,7 @@
       <c r="K494" s="7"/>
       <c r="L494" s="7"/>
       <c t="s" r="M494" s="7">
-        <v>531</v>
+        <v>535</v>
       </c>
     </row>
     <row r="495" ht="15" customHeight="1">
@@ -17209,13 +17229,13 @@
       </c>
       <c r="D495" s="7"/>
       <c t="s" r="E495" s="7">
-        <v>529</v>
+        <v>533</v>
       </c>
       <c r="F495" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G495" s="8">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c t="s" r="H495" s="8">
         <v>46</v>
@@ -17224,7 +17244,7 @@
         <v>27</v>
       </c>
       <c t="s" r="J495" s="7">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="K495" s="7"/>
       <c r="L495" s="7"/>
@@ -17232,7 +17252,7 @@
     </row>
     <row r="496" ht="15.75" customHeight="1">
       <c t="s" r="A496" s="9">
-        <v>532</v>
+        <v>536</v>
       </c>
       <c r="B496" s="9"/>
       <c r="C496" s="9"/>
@@ -17252,7 +17272,7 @@
     <row r="497" ht="65.25" customHeight="1"/>
     <row r="498" ht="16.5" customHeight="1">
       <c t="s" r="A498" s="10">
-        <v>533</v>
+        <v>537</v>
       </c>
       <c r="B498" s="10"/>
       <c r="C498" s="10"/>
@@ -17265,7 +17285,7 @@
       <c r="J498" s="10"/>
       <c r="K498" s="10"/>
       <c t="s" r="L498" s="11">
-        <v>534</v>
+        <v>538</v>
       </c>
       <c r="M498" s="11"/>
       <c r="N498" s="11"/>

--- a/Data/FlightPlan/FPL_31AUG26.xlsx
+++ b/Data/FlightPlan/FPL_31AUG26.xlsx
@@ -371,9 +371,6 @@
     <t>VII</t>
   </si>
   <si>
-    <t>21:46</t>
-  </si>
-  <si>
     <t>22:40</t>
   </si>
   <si>
@@ -413,582 +410,594 @@
     <t>01:00</t>
   </si>
   <si>
+    <t>01:24</t>
+  </si>
+  <si>
+    <t>02:15</t>
+  </si>
+  <si>
+    <t>05:25</t>
+  </si>
+  <si>
+    <t>VN-A524</t>
+  </si>
+  <si>
+    <t>CGK</t>
+  </si>
+  <si>
+    <t>08:40</t>
+  </si>
+  <si>
+    <t>13:00</t>
+  </si>
+  <si>
+    <t>12:57</t>
+  </si>
+  <si>
+    <t>18:15</t>
+  </si>
+  <si>
+    <t>19:20</t>
+  </si>
+  <si>
+    <t>BOM</t>
+  </si>
+  <si>
+    <t>23:40</t>
+  </si>
+  <si>
+    <t>VN-A526</t>
+  </si>
+  <si>
+    <t>VVO</t>
+  </si>
+  <si>
+    <t>09:45</t>
+  </si>
+  <si>
+    <t>12:25</t>
+  </si>
+  <si>
+    <t>12:08</t>
+  </si>
+  <si>
+    <t>12:55</t>
+  </si>
+  <si>
+    <t>14:15</t>
+  </si>
+  <si>
+    <t>14:27</t>
+  </si>
+  <si>
+    <t>16:55</t>
+  </si>
+  <si>
+    <t>18:31</t>
+  </si>
+  <si>
+    <t>VN-A529</t>
+  </si>
+  <si>
+    <t>07:00</t>
+  </si>
+  <si>
+    <t>08:50</t>
+  </si>
+  <si>
+    <t>09:08</t>
+  </si>
+  <si>
+    <t>09:25</t>
+  </si>
+  <si>
+    <t>11:15</t>
+  </si>
+  <si>
+    <t>11:31</t>
+  </si>
+  <si>
+    <t>11:50</t>
+  </si>
+  <si>
+    <t>13:55</t>
+  </si>
+  <si>
+    <t>14:30</t>
+  </si>
+  <si>
+    <t>16:35</t>
+  </si>
+  <si>
+    <t>VN-A532</t>
+  </si>
+  <si>
+    <t>07:20</t>
+  </si>
+  <si>
+    <t>09:31</t>
+  </si>
+  <si>
+    <t>10:30</t>
+  </si>
+  <si>
+    <t>12:40</t>
+  </si>
+  <si>
+    <t>KHH</t>
+  </si>
+  <si>
+    <t>18:12</t>
+  </si>
+  <si>
+    <t>18:50</t>
+  </si>
+  <si>
+    <t>20:35</t>
+  </si>
+  <si>
+    <t>20:37</t>
+  </si>
+  <si>
+    <t>22:35</t>
+  </si>
+  <si>
+    <t>23:55</t>
+  </si>
+  <si>
+    <t>VN-A534</t>
+  </si>
+  <si>
+    <t>06:20</t>
+  </si>
+  <si>
+    <t>07:21</t>
+  </si>
+  <si>
+    <t>07:55</t>
+  </si>
+  <si>
+    <t>09:00</t>
+  </si>
+  <si>
+    <t>09:13</t>
+  </si>
+  <si>
+    <t>HPH</t>
+  </si>
+  <si>
+    <t>10:50</t>
+  </si>
+  <si>
+    <t>11:09</t>
+  </si>
+  <si>
+    <t>11:20</t>
+  </si>
+  <si>
+    <t>12:35</t>
+  </si>
+  <si>
+    <t>13:20</t>
+  </si>
+  <si>
+    <t>14:10</t>
+  </si>
+  <si>
+    <t>15:49</t>
+  </si>
+  <si>
+    <t>16:30</t>
+  </si>
+  <si>
+    <t>18:30</t>
+  </si>
+  <si>
+    <t>22:00</t>
+  </si>
+  <si>
+    <t>22:03</t>
+  </si>
+  <si>
+    <t>22:30</t>
+  </si>
+  <si>
+    <t>23:50</t>
+  </si>
+  <si>
+    <t>VN-A535</t>
+  </si>
+  <si>
+    <t>06:25</t>
+  </si>
+  <si>
+    <t>08:55</t>
+  </si>
+  <si>
+    <t>08:47</t>
+  </si>
+  <si>
+    <t>PXU</t>
+  </si>
+  <si>
+    <t>11:55</t>
+  </si>
+  <si>
+    <t>11:51</t>
+  </si>
+  <si>
+    <t>14:11</t>
+  </si>
+  <si>
+    <t>15:05</t>
+  </si>
+  <si>
+    <t>16:25</t>
+  </si>
+  <si>
+    <t>16:42</t>
+  </si>
+  <si>
+    <t>VN-A536</t>
+  </si>
+  <si>
+    <t>13:09</t>
+  </si>
+  <si>
+    <t>16:50</t>
+  </si>
+  <si>
+    <t>17:10</t>
+  </si>
+  <si>
+    <t>DEL</t>
+  </si>
+  <si>
+    <t>23:01</t>
+  </si>
+  <si>
+    <t>00:05</t>
+  </si>
+  <si>
+    <t>VN-A539</t>
+  </si>
+  <si>
+    <t>07:35</t>
+  </si>
+  <si>
+    <t>07:24</t>
+  </si>
+  <si>
+    <t>10:15</t>
+  </si>
+  <si>
+    <t>10:17</t>
+  </si>
+  <si>
+    <t>13:50</t>
+  </si>
+  <si>
+    <t>16:08</t>
+  </si>
+  <si>
+    <t>16:05</t>
+  </si>
+  <si>
+    <t>17:53</t>
+  </si>
+  <si>
+    <t>HUI</t>
+  </si>
+  <si>
+    <t>21:25</t>
+  </si>
+  <si>
+    <t>21:16</t>
+  </si>
+  <si>
+    <t>21:55</t>
+  </si>
+  <si>
+    <t>23:20</t>
+  </si>
+  <si>
+    <t>VN-A542</t>
+  </si>
+  <si>
+    <t>05:40</t>
+  </si>
+  <si>
+    <t>07:29</t>
+  </si>
+  <si>
+    <t>07:30</t>
+  </si>
+  <si>
+    <t>09:27</t>
+  </si>
+  <si>
+    <t>11:14</t>
+  </si>
+  <si>
+    <t>13:16</t>
+  </si>
+  <si>
+    <t>16:15</t>
+  </si>
+  <si>
+    <t>16:31</t>
+  </si>
+  <si>
+    <t>19:43</t>
+  </si>
+  <si>
+    <t>VN-A543</t>
+  </si>
+  <si>
+    <t>15:30</t>
+  </si>
+  <si>
+    <t>15:24</t>
+  </si>
+  <si>
+    <t>KIX</t>
+  </si>
+  <si>
+    <t>01:20</t>
+  </si>
+  <si>
+    <t>07:50</t>
+  </si>
+  <si>
+    <t>VN-A544</t>
+  </si>
+  <si>
+    <t>07:51</t>
+  </si>
+  <si>
+    <t>08:20</t>
+  </si>
+  <si>
+    <t>09:40</t>
+  </si>
+  <si>
+    <t>10:05</t>
+  </si>
+  <si>
+    <t>12:05</t>
+  </si>
+  <si>
+    <t>12:24</t>
+  </si>
+  <si>
+    <t>15:16</t>
+  </si>
+  <si>
+    <t>18:16</t>
+  </si>
+  <si>
+    <t>20:50</t>
+  </si>
+  <si>
+    <t>MNL</t>
+  </si>
+  <si>
+    <t>22:25</t>
+  </si>
+  <si>
+    <t>02:10</t>
+  </si>
+  <si>
+    <t>03:00</t>
+  </si>
+  <si>
+    <t>04:35</t>
+  </si>
+  <si>
+    <t>VN-A546</t>
+  </si>
+  <si>
+    <t>06:55</t>
+  </si>
+  <si>
+    <t>08:59</t>
+  </si>
+  <si>
+    <t>10:00</t>
+  </si>
+  <si>
+    <t>11:59</t>
+  </si>
+  <si>
+    <t>14:20</t>
+  </si>
+  <si>
+    <t>14:50</t>
+  </si>
+  <si>
+    <t>TBB</t>
+  </si>
+  <si>
+    <t>15:10</t>
+  </si>
+  <si>
+    <t>17:00</t>
+  </si>
+  <si>
+    <t>17:30</t>
+  </si>
+  <si>
+    <t>19:15</t>
+  </si>
+  <si>
+    <t>19:19</t>
+  </si>
+  <si>
+    <t>22:45</t>
+  </si>
+  <si>
+    <t>00:55</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>VN-A549</t>
+  </si>
+  <si>
+    <t>BQS</t>
+  </si>
+  <si>
+    <t>04:40</t>
+  </si>
+  <si>
+    <t>05:15</t>
+  </si>
+  <si>
+    <t>08:36</t>
+  </si>
+  <si>
+    <t>10:35</t>
+  </si>
+  <si>
+    <t>09:15</t>
+  </si>
+  <si>
+    <t>11:24</t>
+  </si>
+  <si>
+    <t>20:10</t>
+  </si>
+  <si>
+    <t>19:30</t>
+  </si>
+  <si>
+    <t>21:19</t>
+  </si>
+  <si>
+    <t>VN-A551</t>
+  </si>
+  <si>
+    <t>NGO</t>
+  </si>
+  <si>
+    <t>12:50</t>
+  </si>
+  <si>
+    <t>RMQ</t>
+  </si>
+  <si>
+    <t>19:50</t>
+  </si>
+  <si>
+    <t>20:02</t>
+  </si>
+  <si>
+    <t>01:40</t>
+  </si>
+  <si>
+    <t>VN-A552</t>
+  </si>
+  <si>
+    <t>13:15</t>
+  </si>
+  <si>
+    <t>15:00</t>
+  </si>
+  <si>
+    <t>15:19</t>
+  </si>
+  <si>
+    <t>18:11</t>
+  </si>
+  <si>
+    <t>20:03</t>
+  </si>
+  <si>
+    <t>19:55</t>
+  </si>
+  <si>
+    <t>22:09</t>
+  </si>
+  <si>
+    <t>VN-A553</t>
+  </si>
+  <si>
+    <t>09:55</t>
+  </si>
+  <si>
+    <t>09:57</t>
+  </si>
+  <si>
+    <t>11:30</t>
+  </si>
+  <si>
+    <t>12:01</t>
+  </si>
+  <si>
+    <t>14:49</t>
+  </si>
+  <si>
+    <t>AMD</t>
+  </si>
+  <si>
+    <t>19:10</t>
+  </si>
+  <si>
+    <t>22:50</t>
+  </si>
+  <si>
+    <t>22:43</t>
+  </si>
+  <si>
+    <t>06:30</t>
+  </si>
+  <si>
+    <t>VN-A554</t>
+  </si>
+  <si>
+    <t>10:45</t>
+  </si>
+  <si>
+    <t>12:27</t>
+  </si>
+  <si>
+    <t>VCA</t>
+  </si>
+  <si>
+    <t>14:54</t>
+  </si>
+  <si>
+    <t>15:20</t>
+  </si>
+  <si>
+    <t>17:29</t>
+  </si>
+  <si>
+    <t>19:52</t>
+  </si>
+  <si>
+    <t>22:15</t>
+  </si>
+  <si>
+    <t>22:59</t>
+  </si>
+  <si>
+    <t>VN-A575</t>
+  </si>
+  <si>
+    <t>09:35</t>
+  </si>
+  <si>
+    <t>12:45</t>
+  </si>
+  <si>
+    <t>16:40</t>
+  </si>
+  <si>
     <t>01:10</t>
   </si>
   <si>
-    <t>02:15</t>
-  </si>
-  <si>
-    <t>05:25</t>
-  </si>
-  <si>
-    <t>VN-A524</t>
-  </si>
-  <si>
-    <t>CGK</t>
-  </si>
-  <si>
-    <t>08:40</t>
-  </si>
-  <si>
-    <t>13:00</t>
-  </si>
-  <si>
-    <t>12:57</t>
-  </si>
-  <si>
-    <t>18:15</t>
-  </si>
-  <si>
-    <t>19:20</t>
-  </si>
-  <si>
-    <t>BOM</t>
-  </si>
-  <si>
-    <t>23:40</t>
-  </si>
-  <si>
-    <t>VN-A526</t>
-  </si>
-  <si>
-    <t>VVO</t>
-  </si>
-  <si>
-    <t>09:45</t>
-  </si>
-  <si>
-    <t>12:25</t>
-  </si>
-  <si>
-    <t>12:08</t>
-  </si>
-  <si>
-    <t>12:55</t>
-  </si>
-  <si>
-    <t>14:15</t>
-  </si>
-  <si>
-    <t>14:27</t>
-  </si>
-  <si>
-    <t>16:55</t>
-  </si>
-  <si>
-    <t>18:31</t>
-  </si>
-  <si>
-    <t>VN-A529</t>
-  </si>
-  <si>
-    <t>07:00</t>
-  </si>
-  <si>
-    <t>08:50</t>
-  </si>
-  <si>
-    <t>09:08</t>
-  </si>
-  <si>
-    <t>09:25</t>
-  </si>
-  <si>
-    <t>11:15</t>
-  </si>
-  <si>
-    <t>11:31</t>
-  </si>
-  <si>
-    <t>11:50</t>
-  </si>
-  <si>
-    <t>13:55</t>
-  </si>
-  <si>
-    <t>14:30</t>
-  </si>
-  <si>
-    <t>16:35</t>
-  </si>
-  <si>
-    <t>VN-A532</t>
-  </si>
-  <si>
-    <t>07:20</t>
-  </si>
-  <si>
-    <t>09:31</t>
-  </si>
-  <si>
-    <t>10:30</t>
-  </si>
-  <si>
-    <t>12:40</t>
-  </si>
-  <si>
-    <t>KHH</t>
-  </si>
-  <si>
-    <t>18:12</t>
-  </si>
-  <si>
-    <t>18:50</t>
-  </si>
-  <si>
-    <t>20:35</t>
-  </si>
-  <si>
-    <t>20:37</t>
-  </si>
-  <si>
-    <t>22:35</t>
-  </si>
-  <si>
-    <t>23:55</t>
-  </si>
-  <si>
-    <t>VN-A534</t>
-  </si>
-  <si>
-    <t>06:20</t>
-  </si>
-  <si>
-    <t>07:21</t>
-  </si>
-  <si>
-    <t>07:55</t>
-  </si>
-  <si>
-    <t>09:00</t>
-  </si>
-  <si>
-    <t>09:13</t>
-  </si>
-  <si>
-    <t>HPH</t>
-  </si>
-  <si>
-    <t>10:50</t>
-  </si>
-  <si>
-    <t>11:09</t>
-  </si>
-  <si>
-    <t>11:20</t>
-  </si>
-  <si>
-    <t>12:35</t>
-  </si>
-  <si>
-    <t>13:20</t>
-  </si>
-  <si>
-    <t>14:10</t>
-  </si>
-  <si>
-    <t>15:49</t>
-  </si>
-  <si>
-    <t>16:30</t>
-  </si>
-  <si>
-    <t>18:30</t>
-  </si>
-  <si>
-    <t>22:00</t>
-  </si>
-  <si>
-    <t>22:30</t>
-  </si>
-  <si>
-    <t>23:50</t>
-  </si>
-  <si>
-    <t>VN-A535</t>
-  </si>
-  <si>
-    <t>06:25</t>
-  </si>
-  <si>
-    <t>08:55</t>
-  </si>
-  <si>
-    <t>08:47</t>
-  </si>
-  <si>
-    <t>PXU</t>
-  </si>
-  <si>
-    <t>11:55</t>
-  </si>
-  <si>
-    <t>11:51</t>
-  </si>
-  <si>
-    <t>14:11</t>
-  </si>
-  <si>
-    <t>15:05</t>
-  </si>
-  <si>
-    <t>16:25</t>
-  </si>
-  <si>
-    <t>16:42</t>
-  </si>
-  <si>
-    <t>VN-A536</t>
-  </si>
-  <si>
-    <t>13:09</t>
-  </si>
-  <si>
-    <t>16:50</t>
-  </si>
-  <si>
-    <t>17:10</t>
-  </si>
-  <si>
-    <t>DEL</t>
-  </si>
-  <si>
-    <t>23:01</t>
-  </si>
-  <si>
-    <t>00:05</t>
-  </si>
-  <si>
-    <t>VN-A539</t>
-  </si>
-  <si>
-    <t>07:35</t>
-  </si>
-  <si>
-    <t>07:24</t>
-  </si>
-  <si>
-    <t>10:15</t>
-  </si>
-  <si>
-    <t>10:17</t>
-  </si>
-  <si>
-    <t>13:50</t>
-  </si>
-  <si>
-    <t>16:08</t>
-  </si>
-  <si>
-    <t>16:05</t>
-  </si>
-  <si>
-    <t>17:53</t>
-  </si>
-  <si>
-    <t>HUI</t>
-  </si>
-  <si>
-    <t>21:25</t>
-  </si>
-  <si>
-    <t>21:16</t>
-  </si>
-  <si>
-    <t>21:55</t>
-  </si>
-  <si>
-    <t>23:20</t>
-  </si>
-  <si>
-    <t>VN-A542</t>
-  </si>
-  <si>
-    <t>05:40</t>
-  </si>
-  <si>
-    <t>07:29</t>
-  </si>
-  <si>
-    <t>07:30</t>
-  </si>
-  <si>
-    <t>09:27</t>
-  </si>
-  <si>
-    <t>11:14</t>
-  </si>
-  <si>
-    <t>13:16</t>
-  </si>
-  <si>
-    <t>16:15</t>
-  </si>
-  <si>
-    <t>16:31</t>
-  </si>
-  <si>
-    <t>19:43</t>
-  </si>
-  <si>
-    <t>VN-A543</t>
-  </si>
-  <si>
-    <t>15:30</t>
-  </si>
-  <si>
-    <t>15:24</t>
-  </si>
-  <si>
-    <t>KIX</t>
-  </si>
-  <si>
-    <t>01:20</t>
-  </si>
-  <si>
-    <t>07:50</t>
-  </si>
-  <si>
-    <t>VN-A544</t>
-  </si>
-  <si>
-    <t>07:51</t>
-  </si>
-  <si>
-    <t>08:20</t>
-  </si>
-  <si>
-    <t>09:40</t>
-  </si>
-  <si>
-    <t>10:05</t>
-  </si>
-  <si>
-    <t>12:05</t>
-  </si>
-  <si>
-    <t>12:24</t>
-  </si>
-  <si>
-    <t>15:16</t>
-  </si>
-  <si>
-    <t>18:16</t>
-  </si>
-  <si>
-    <t>20:50</t>
-  </si>
-  <si>
-    <t>MNL</t>
-  </si>
-  <si>
-    <t>22:25</t>
-  </si>
-  <si>
-    <t>02:10</t>
-  </si>
-  <si>
-    <t>03:00</t>
-  </si>
-  <si>
-    <t>04:35</t>
-  </si>
-  <si>
-    <t>VN-A546</t>
-  </si>
-  <si>
-    <t>06:55</t>
-  </si>
-  <si>
-    <t>08:59</t>
-  </si>
-  <si>
-    <t>10:00</t>
-  </si>
-  <si>
-    <t>11:59</t>
-  </si>
-  <si>
-    <t>14:20</t>
-  </si>
-  <si>
-    <t>14:50</t>
-  </si>
-  <si>
-    <t>TBB</t>
-  </si>
-  <si>
-    <t>15:10</t>
-  </si>
-  <si>
-    <t>17:00</t>
-  </si>
-  <si>
-    <t>17:30</t>
-  </si>
-  <si>
-    <t>19:15</t>
-  </si>
-  <si>
-    <t>19:19</t>
-  </si>
-  <si>
-    <t>22:45</t>
-  </si>
-  <si>
-    <t>00:55</t>
-  </si>
-  <si>
-    <t>C</t>
-  </si>
-  <si>
-    <t>VN-A549</t>
-  </si>
-  <si>
-    <t>BQS</t>
-  </si>
-  <si>
-    <t>04:40</t>
-  </si>
-  <si>
-    <t>05:15</t>
-  </si>
-  <si>
-    <t>08:36</t>
-  </si>
-  <si>
-    <t>10:35</t>
-  </si>
-  <si>
-    <t>09:15</t>
-  </si>
-  <si>
-    <t>11:24</t>
-  </si>
-  <si>
-    <t>20:10</t>
-  </si>
-  <si>
-    <t>19:30</t>
-  </si>
-  <si>
-    <t>21:19</t>
-  </si>
-  <si>
-    <t>VN-A551</t>
-  </si>
-  <si>
-    <t>NGO</t>
-  </si>
-  <si>
-    <t>12:50</t>
-  </si>
-  <si>
-    <t>RMQ</t>
-  </si>
-  <si>
-    <t>19:50</t>
-  </si>
-  <si>
-    <t>20:02</t>
-  </si>
-  <si>
-    <t>01:40</t>
-  </si>
-  <si>
-    <t>VN-A552</t>
-  </si>
-  <si>
-    <t>13:15</t>
-  </si>
-  <si>
-    <t>15:00</t>
-  </si>
-  <si>
-    <t>15:19</t>
-  </si>
-  <si>
-    <t>18:11</t>
-  </si>
-  <si>
-    <t>20:03</t>
-  </si>
-  <si>
-    <t>19:55</t>
-  </si>
-  <si>
-    <t>VN-A553</t>
-  </si>
-  <si>
-    <t>09:55</t>
-  </si>
-  <si>
-    <t>09:57</t>
-  </si>
-  <si>
-    <t>11:30</t>
-  </si>
-  <si>
-    <t>12:01</t>
-  </si>
-  <si>
-    <t>14:49</t>
-  </si>
-  <si>
-    <t>AMD</t>
-  </si>
-  <si>
-    <t>19:10</t>
-  </si>
-  <si>
-    <t>22:50</t>
-  </si>
-  <si>
-    <t>22:43</t>
-  </si>
-  <si>
-    <t>06:30</t>
-  </si>
-  <si>
-    <t>VN-A554</t>
-  </si>
-  <si>
-    <t>10:45</t>
-  </si>
-  <si>
-    <t>12:27</t>
-  </si>
-  <si>
-    <t>VCA</t>
-  </si>
-  <si>
-    <t>14:54</t>
-  </si>
-  <si>
-    <t>15:20</t>
-  </si>
-  <si>
-    <t>17:29</t>
-  </si>
-  <si>
-    <t>19:52</t>
-  </si>
-  <si>
-    <t>22:15</t>
-  </si>
-  <si>
-    <t>VN-A575</t>
-  </si>
-  <si>
-    <t>09:35</t>
-  </si>
-  <si>
-    <t>12:45</t>
-  </si>
-  <si>
-    <t>16:40</t>
-  </si>
-  <si>
     <t>VN-A578</t>
   </si>
   <si>
@@ -1004,6 +1013,9 @@
     <t>BLR</t>
   </si>
   <si>
+    <t>23:16</t>
+  </si>
+  <si>
     <t>23:35</t>
   </si>
   <si>
@@ -1055,6 +1067,9 @@
     <t>21:50</t>
   </si>
   <si>
+    <t>23:19</t>
+  </si>
+  <si>
     <t>VN-A630</t>
   </si>
   <si>
@@ -1106,6 +1121,9 @@
     <t>20:48</t>
   </si>
   <si>
+    <t>22:46</t>
+  </si>
+  <si>
     <t>VN-A633</t>
   </si>
   <si>
@@ -1235,9 +1253,6 @@
     <t>20:15</t>
   </si>
   <si>
-    <t>22:17</t>
-  </si>
-  <si>
     <t>00:45</t>
   </si>
   <si>
@@ -1274,6 +1289,9 @@
     <t>20:14</t>
   </si>
   <si>
+    <t>22:53</t>
+  </si>
+  <si>
     <t>VN-A643</t>
   </si>
   <si>
@@ -1292,6 +1310,9 @@
     <t>20:12</t>
   </si>
   <si>
+    <t>22:02</t>
+  </si>
+  <si>
     <t>VN-A644</t>
   </si>
   <si>
@@ -1337,6 +1358,9 @@
     <t>20:52</t>
   </si>
   <si>
+    <t>23:54</t>
+  </si>
+  <si>
     <t>VN-A646</t>
   </si>
   <si>
@@ -1373,7 +1397,7 @@
     <t>19:22</t>
   </si>
   <si>
-    <t>22:09</t>
+    <t>21:59</t>
   </si>
   <si>
     <t>00:50</t>
@@ -1427,6 +1451,9 @@
     <t>22:20</t>
   </si>
   <si>
+    <t>22:44</t>
+  </si>
+  <si>
     <t>VN-A654</t>
   </si>
   <si>
@@ -1442,6 +1469,9 @@
     <t>13:21</t>
   </si>
   <si>
+    <t>22:18</t>
+  </si>
+  <si>
     <t>VN-A656</t>
   </si>
   <si>
@@ -1484,6 +1514,9 @@
     <t>21:40</t>
   </si>
   <si>
+    <t>23:57</t>
+  </si>
+  <si>
     <t>FSZ</t>
   </si>
   <si>
@@ -1541,6 +1574,9 @@
     <t>23:25</t>
   </si>
   <si>
+    <t>00:02</t>
+  </si>
+  <si>
     <t>FUK</t>
   </si>
   <si>
@@ -1559,6 +1595,9 @@
     <t>20:21</t>
   </si>
   <si>
+    <t>23:14</t>
+  </si>
+  <si>
     <t>VN-A669</t>
   </si>
   <si>
@@ -1577,6 +1616,9 @@
     <t>18:52</t>
   </si>
   <si>
+    <t>22:31</t>
+  </si>
+  <si>
     <t>VN-A670</t>
   </si>
   <si>
@@ -1640,6 +1682,9 @@
     <t>20:33</t>
   </si>
   <si>
+    <t>22:34</t>
+  </si>
+  <si>
     <t>VN-A673</t>
   </si>
   <si>
@@ -1655,6 +1700,9 @@
     <t>19:09</t>
   </si>
   <si>
+    <t>21:51</t>
+  </si>
+  <si>
     <t>23:45</t>
   </si>
   <si>
@@ -1670,6 +1718,9 @@
     <t>01:15</t>
   </si>
   <si>
+    <t>01:27</t>
+  </si>
+  <si>
     <t>02:20</t>
   </si>
   <si>
@@ -1775,12 +1826,18 @@
     <t>21:42</t>
   </si>
   <si>
+    <t>00:12</t>
+  </si>
+  <si>
     <t>VN-A693</t>
   </si>
   <si>
     <t>19:57</t>
   </si>
   <si>
+    <t>22:16</t>
+  </si>
+  <si>
     <t>VN-A697</t>
   </si>
   <si>
@@ -1844,7 +1901,7 @@
     <t>15:14</t>
   </si>
   <si>
-    <t>04:27</t>
+    <t>04:26</t>
   </si>
   <si>
     <t>VN-A815</t>
@@ -1859,12 +1916,18 @@
     <t>23:30</t>
   </si>
   <si>
+    <t>05:34</t>
+  </si>
+  <si>
     <t>VN-A816</t>
   </si>
   <si>
     <t>KZN</t>
   </si>
   <si>
+    <t>06:56</t>
+  </si>
+  <si>
     <t>VN-A817</t>
   </si>
   <si>
@@ -1886,10 +1949,13 @@
     <t>23:08</t>
   </si>
   <si>
+    <t>05:55</t>
+  </si>
+  <si>
     <t>Total Record(s): 406</t>
   </si>
   <si>
-    <t xml:space="preserve">Generated on  Aug 31, 2026 20:27</t>
+    <t xml:space="preserve">Generated on  Aug 31, 2026 22:21</t>
   </si>
   <si>
     <t>Page 1 of 1</t>
@@ -3683,7 +3749,7 @@
       <c r="K46" s="7"/>
       <c r="L46" s="7"/>
       <c t="s" r="M46" s="7">
-        <v>120</v>
+        <v>108</v>
       </c>
     </row>
     <row r="47" ht="14.25" customHeight="1">
@@ -3710,7 +3776,7 @@
         <v>50</v>
       </c>
       <c t="s" r="I47" s="7">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c t="s" r="J47" s="7">
         <v>29</v>
@@ -3746,7 +3812,7 @@
       </c>
       <c r="D49" s="7"/>
       <c t="s" r="E49" s="7">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F49" s="7">
         <v>321</v>
@@ -3758,7 +3824,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I49" s="7">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c t="s" r="J49" s="7">
         <v>61</v>
@@ -3766,7 +3832,7 @@
       <c r="K49" s="7"/>
       <c r="L49" s="7"/>
       <c t="s" r="M49" s="7">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="50" ht="15" customHeight="1">
@@ -3781,7 +3847,7 @@
       </c>
       <c r="D50" s="7"/>
       <c t="s" r="E50" s="7">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F50" s="7">
         <v>321</v>
@@ -3793,15 +3859,15 @@
         <v>50</v>
       </c>
       <c t="s" r="I50" s="7">
+        <v>124</v>
+      </c>
+      <c t="s" r="J50" s="7">
         <v>125</v>
-      </c>
-      <c t="s" r="J50" s="7">
-        <v>126</v>
       </c>
       <c r="K50" s="7"/>
       <c r="L50" s="7"/>
       <c t="s" r="M50" s="7">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="51" ht="14.25" customHeight="1">
@@ -3816,7 +3882,7 @@
       </c>
       <c r="D51" s="7"/>
       <c t="s" r="E51" s="7">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F51" s="7">
         <v>321</v>
@@ -3831,12 +3897,12 @@
         <v>19</v>
       </c>
       <c t="s" r="J51" s="7">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="K51" s="7"/>
       <c r="L51" s="7"/>
       <c t="s" r="M51" s="7">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="52" ht="14.25" customHeight="1">
@@ -3851,7 +3917,7 @@
       </c>
       <c r="D52" s="7"/>
       <c t="s" r="E52" s="7">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F52" s="7">
         <v>321</v>
@@ -3871,7 +3937,7 @@
       <c r="K52" s="7"/>
       <c r="L52" s="7"/>
       <c t="s" r="M52" s="7">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="53" ht="14.25" customHeight="1">
@@ -3886,7 +3952,7 @@
       </c>
       <c r="D53" s="7"/>
       <c t="s" r="E53" s="7">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F53" s="7">
         <v>321</v>
@@ -3895,18 +3961,18 @@
         <v>50</v>
       </c>
       <c t="s" r="H53" s="8">
+        <v>130</v>
+      </c>
+      <c t="s" r="I53" s="7">
         <v>131</v>
       </c>
-      <c t="s" r="I53" s="7">
+      <c t="s" r="J53" s="7">
         <v>132</v>
-      </c>
-      <c t="s" r="J53" s="7">
-        <v>133</v>
       </c>
       <c r="K53" s="7"/>
       <c r="L53" s="7"/>
       <c t="s" r="M53" s="7">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="54" ht="14.25" customHeight="1">
@@ -3921,22 +3987,22 @@
       </c>
       <c r="D54" s="7"/>
       <c t="s" r="E54" s="7">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F54" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G54" s="8">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c t="s" r="H54" s="8">
         <v>50</v>
       </c>
       <c t="s" r="I54" s="7">
+        <v>134</v>
+      </c>
+      <c t="s" r="J54" s="7">
         <v>135</v>
-      </c>
-      <c t="s" r="J54" s="7">
-        <v>136</v>
       </c>
       <c r="K54" s="7"/>
       <c r="L54" s="7"/>
@@ -3969,7 +4035,7 @@
       </c>
       <c r="D56" s="7"/>
       <c t="s" r="E56" s="7">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F56" s="7">
         <v>321</v>
@@ -3978,18 +4044,18 @@
         <v>17</v>
       </c>
       <c t="s" r="H56" s="8">
+        <v>137</v>
+      </c>
+      <c t="s" r="I56" s="7">
         <v>138</v>
       </c>
-      <c t="s" r="I56" s="7">
+      <c t="s" r="J56" s="7">
         <v>139</v>
-      </c>
-      <c t="s" r="J56" s="7">
-        <v>140</v>
       </c>
       <c r="K56" s="7"/>
       <c r="L56" s="7"/>
       <c t="s" r="M56" s="7">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="57" ht="14.25" customHeight="1">
@@ -4004,13 +4070,13 @@
       </c>
       <c r="D57" s="7"/>
       <c t="s" r="E57" s="7">
+        <v>136</v>
+      </c>
+      <c r="F57" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G57" s="8">
         <v>137</v>
-      </c>
-      <c r="F57" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G57" s="8">
-        <v>138</v>
       </c>
       <c t="s" r="H57" s="8">
         <v>17</v>
@@ -4019,12 +4085,12 @@
         <v>102</v>
       </c>
       <c t="s" r="J57" s="7">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="K57" s="7"/>
       <c r="L57" s="7"/>
       <c t="s" r="M57" s="7">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="58" ht="14.25" customHeight="1">
@@ -4039,7 +4105,7 @@
       </c>
       <c r="D58" s="7"/>
       <c t="s" r="E58" s="7">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F58" s="7">
         <v>321</v>
@@ -4048,13 +4114,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H58" s="8">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c t="s" r="I58" s="7">
         <v>107</v>
       </c>
       <c t="s" r="J58" s="7">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="K58" s="7"/>
       <c r="L58" s="7"/>
@@ -4074,13 +4140,13 @@
       </c>
       <c r="D59" s="7"/>
       <c t="s" r="E59" s="7">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F59" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G59" s="8">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c t="s" r="H59" s="8">
         <v>17</v>
@@ -4122,27 +4188,27 @@
       </c>
       <c r="D61" s="7"/>
       <c t="s" r="E61" s="7">
+        <v>145</v>
+      </c>
+      <c r="F61" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G61" s="8">
         <v>146</v>
-      </c>
-      <c r="F61" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G61" s="8">
-        <v>147</v>
       </c>
       <c t="s" r="H61" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I61" s="7">
+        <v>147</v>
+      </c>
+      <c t="s" r="J61" s="7">
         <v>148</v>
-      </c>
-      <c t="s" r="J61" s="7">
-        <v>149</v>
       </c>
       <c r="K61" s="7"/>
       <c r="L61" s="7"/>
       <c t="s" r="M61" s="7">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="62" ht="14.25" customHeight="1">
@@ -4157,7 +4223,7 @@
       </c>
       <c r="D62" s="7"/>
       <c t="s" r="E62" s="7">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F62" s="7">
         <v>321</v>
@@ -4169,15 +4235,15 @@
         <v>57</v>
       </c>
       <c t="s" r="I62" s="7">
+        <v>150</v>
+      </c>
+      <c t="s" r="J62" s="7">
         <v>151</v>
-      </c>
-      <c t="s" r="J62" s="7">
-        <v>152</v>
       </c>
       <c r="K62" s="7"/>
       <c r="L62" s="7"/>
       <c t="s" r="M62" s="7">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="63" ht="14.25" customHeight="1">
@@ -4192,7 +4258,7 @@
       </c>
       <c r="D63" s="7"/>
       <c t="s" r="E63" s="7">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F63" s="7">
         <v>321</v>
@@ -4204,15 +4270,15 @@
         <v>17</v>
       </c>
       <c t="s" r="I63" s="7">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c t="s" r="J63" s="7">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="K63" s="7"/>
       <c r="L63" s="7"/>
       <c t="s" r="M63" s="7">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="64" ht="14.25" customHeight="1">
@@ -4242,7 +4308,7 @@
       </c>
       <c r="D65" s="7"/>
       <c t="s" r="E65" s="7">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F65" s="7">
         <v>321</v>
@@ -4254,15 +4320,15 @@
         <v>72</v>
       </c>
       <c t="s" r="I65" s="7">
+        <v>156</v>
+      </c>
+      <c t="s" r="J65" s="7">
         <v>157</v>
-      </c>
-      <c t="s" r="J65" s="7">
-        <v>158</v>
       </c>
       <c r="K65" s="7"/>
       <c r="L65" s="7"/>
       <c t="s" r="M65" s="7">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="66" ht="14.25" customHeight="1">
@@ -4277,7 +4343,7 @@
       </c>
       <c r="D66" s="7"/>
       <c t="s" r="E66" s="7">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F66" s="7">
         <v>321</v>
@@ -4289,15 +4355,15 @@
         <v>17</v>
       </c>
       <c t="s" r="I66" s="7">
+        <v>159</v>
+      </c>
+      <c t="s" r="J66" s="7">
         <v>160</v>
-      </c>
-      <c t="s" r="J66" s="7">
-        <v>161</v>
       </c>
       <c r="K66" s="7"/>
       <c r="L66" s="7"/>
       <c t="s" r="M66" s="7">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="67" ht="14.25" customHeight="1">
@@ -4312,7 +4378,7 @@
       </c>
       <c r="D67" s="7"/>
       <c t="s" r="E67" s="7">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F67" s="7">
         <v>321</v>
@@ -4324,10 +4390,10 @@
         <v>33</v>
       </c>
       <c t="s" r="I67" s="7">
+        <v>162</v>
+      </c>
+      <c t="s" r="J67" s="7">
         <v>163</v>
-      </c>
-      <c t="s" r="J67" s="7">
-        <v>164</v>
       </c>
       <c r="K67" s="7"/>
       <c r="L67" s="7"/>
@@ -4347,7 +4413,7 @@
       </c>
       <c r="D68" s="7"/>
       <c t="s" r="E68" s="7">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F68" s="7">
         <v>321</v>
@@ -4359,10 +4425,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I68" s="7">
+        <v>164</v>
+      </c>
+      <c t="s" r="J68" s="7">
         <v>165</v>
-      </c>
-      <c t="s" r="J68" s="7">
-        <v>166</v>
       </c>
       <c r="K68" s="7"/>
       <c r="L68" s="7"/>
@@ -4397,7 +4463,7 @@
       </c>
       <c r="D70" s="7"/>
       <c t="s" r="E70" s="7">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="F70" s="7">
         <v>321</v>
@@ -4409,7 +4475,7 @@
         <v>50</v>
       </c>
       <c t="s" r="I70" s="7">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c t="s" r="J70" s="7">
         <v>18</v>
@@ -4417,7 +4483,7 @@
       <c r="K70" s="7"/>
       <c r="L70" s="7"/>
       <c t="s" r="M70" s="7">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="71" ht="14.25" customHeight="1">
@@ -4432,7 +4498,7 @@
       </c>
       <c r="D71" s="7"/>
       <c t="s" r="E71" s="7">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="F71" s="7">
         <v>321</v>
@@ -4444,15 +4510,15 @@
         <v>17</v>
       </c>
       <c t="s" r="I71" s="7">
+        <v>169</v>
+      </c>
+      <c t="s" r="J71" s="7">
         <v>170</v>
-      </c>
-      <c t="s" r="J71" s="7">
-        <v>171</v>
       </c>
       <c r="K71" s="7"/>
       <c r="L71" s="7"/>
       <c t="s" r="M71" s="7">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="72" ht="14.25" customHeight="1">
@@ -4467,7 +4533,7 @@
       </c>
       <c r="D72" s="7"/>
       <c t="s" r="E72" s="7">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="F72" s="7">
         <v>321</v>
@@ -4476,7 +4542,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H72" s="8">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c t="s" r="I72" s="7">
         <v>37</v>
@@ -4487,7 +4553,7 @@
       <c r="K72" s="7"/>
       <c r="L72" s="7"/>
       <c t="s" r="M72" s="7">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="73" ht="14.25" customHeight="1">
@@ -4502,27 +4568,27 @@
       </c>
       <c r="D73" s="7"/>
       <c t="s" r="E73" s="7">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="F73" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G73" s="8">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c t="s" r="H73" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I73" s="7">
+        <v>173</v>
+      </c>
+      <c t="s" r="J73" s="7">
         <v>174</v>
-      </c>
-      <c t="s" r="J73" s="7">
-        <v>175</v>
       </c>
       <c r="K73" s="7"/>
       <c r="L73" s="7"/>
       <c t="s" r="M73" s="7">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="74" ht="14.25" customHeight="1">
@@ -4537,7 +4603,7 @@
       </c>
       <c r="D74" s="7"/>
       <c t="s" r="E74" s="7">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="F74" s="7">
         <v>321</v>
@@ -4549,10 +4615,10 @@
         <v>57</v>
       </c>
       <c t="s" r="I74" s="7">
+        <v>176</v>
+      </c>
+      <c t="s" r="J74" s="7">
         <v>177</v>
-      </c>
-      <c t="s" r="J74" s="7">
-        <v>178</v>
       </c>
       <c r="K74" s="7"/>
       <c r="L74" s="7"/>
@@ -4585,7 +4651,7 @@
       </c>
       <c r="D76" s="7"/>
       <c t="s" r="E76" s="7">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F76" s="7">
         <v>321</v>
@@ -4597,15 +4663,15 @@
         <v>72</v>
       </c>
       <c t="s" r="I76" s="7">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c t="s" r="J76" s="7">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="K76" s="7"/>
       <c r="L76" s="7"/>
       <c t="s" r="M76" s="7">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="77" ht="14.25" customHeight="1">
@@ -4620,7 +4686,7 @@
       </c>
       <c r="D77" s="7"/>
       <c t="s" r="E77" s="7">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F77" s="7">
         <v>321</v>
@@ -4632,15 +4698,15 @@
         <v>57</v>
       </c>
       <c t="s" r="I77" s="7">
+        <v>181</v>
+      </c>
+      <c t="s" r="J77" s="7">
         <v>182</v>
-      </c>
-      <c t="s" r="J77" s="7">
-        <v>183</v>
       </c>
       <c r="K77" s="7"/>
       <c r="L77" s="7"/>
       <c t="s" r="M77" s="7">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="78" ht="14.25" customHeight="1">
@@ -4655,7 +4721,7 @@
       </c>
       <c r="D78" s="7"/>
       <c t="s" r="E78" s="7">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F78" s="7">
         <v>321</v>
@@ -4664,18 +4730,18 @@
         <v>57</v>
       </c>
       <c t="s" r="H78" s="8">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c t="s" r="I78" s="7">
         <v>18</v>
       </c>
       <c t="s" r="J78" s="7">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="K78" s="7"/>
       <c r="L78" s="7"/>
       <c t="s" r="M78" s="7">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="79" ht="14.25" customHeight="1">
@@ -4690,27 +4756,27 @@
       </c>
       <c r="D79" s="7"/>
       <c t="s" r="E79" s="7">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F79" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G79" s="8">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c t="s" r="H79" s="8">
         <v>57</v>
       </c>
       <c t="s" r="I79" s="7">
+        <v>187</v>
+      </c>
+      <c t="s" r="J79" s="7">
         <v>188</v>
-      </c>
-      <c t="s" r="J79" s="7">
-        <v>189</v>
       </c>
       <c r="K79" s="7"/>
       <c r="L79" s="7"/>
       <c t="s" r="M79" s="7">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="80" ht="15" customHeight="1">
@@ -4725,7 +4791,7 @@
       </c>
       <c r="D80" s="7"/>
       <c t="s" r="E80" s="7">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F80" s="7">
         <v>321</v>
@@ -4737,7 +4803,7 @@
         <v>33</v>
       </c>
       <c t="s" r="I80" s="7">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c t="s" r="J80" s="7">
         <v>82</v>
@@ -4745,7 +4811,7 @@
       <c r="K80" s="7"/>
       <c r="L80" s="7"/>
       <c t="s" r="M80" s="7">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="81" ht="14.25" customHeight="1">
@@ -4760,7 +4826,7 @@
       </c>
       <c r="D81" s="7"/>
       <c t="s" r="E81" s="7">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F81" s="7">
         <v>321</v>
@@ -4772,15 +4838,15 @@
         <v>57</v>
       </c>
       <c t="s" r="I81" s="7">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c t="s" r="J81" s="7">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="K81" s="7"/>
       <c r="L81" s="7"/>
       <c t="s" r="M81" s="7">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="82" ht="14.25" customHeight="1">
@@ -4795,7 +4861,7 @@
       </c>
       <c r="D82" s="7"/>
       <c t="s" r="E82" s="7">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F82" s="7">
         <v>321</v>
@@ -4807,14 +4873,16 @@
         <v>50</v>
       </c>
       <c t="s" r="I82" s="7">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c t="s" r="J82" s="7">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="K82" s="7"/>
       <c r="L82" s="7"/>
-      <c r="M82" s="7"/>
+      <c t="s" r="M82" s="7">
+        <v>195</v>
+      </c>
     </row>
     <row r="83" ht="14.25" customHeight="1">
       <c t="s" r="A83" s="6">
@@ -4828,7 +4896,7 @@
       </c>
       <c r="D83" s="7"/>
       <c t="s" r="E83" s="7">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F83" s="7">
         <v>321</v>
@@ -4923,7 +4991,7 @@
         <v>202</v>
       </c>
       <c t="s" r="I86" s="7">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c t="s" r="J86" s="7">
         <v>203</v>
@@ -5043,10 +5111,10 @@
         <v>90</v>
       </c>
       <c t="s" r="I90" s="7">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c t="s" r="J90" s="7">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="K90" s="7"/>
       <c r="L90" s="7"/>
@@ -5231,7 +5299,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I96" s="7">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c t="s" r="J96" s="7">
         <v>219</v>
@@ -5266,7 +5334,7 @@
         <v>50</v>
       </c>
       <c t="s" r="I97" s="7">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c t="s" r="J97" s="7">
         <v>20</v>
@@ -5304,7 +5372,7 @@
         <v>37</v>
       </c>
       <c t="s" r="J98" s="7">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="K98" s="7"/>
       <c r="L98" s="7"/>
@@ -5371,7 +5439,7 @@
         <v>225</v>
       </c>
       <c t="s" r="I100" s="7">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c t="s" r="J100" s="7">
         <v>226</v>
@@ -5413,7 +5481,9 @@
       </c>
       <c r="K101" s="7"/>
       <c r="L101" s="7"/>
-      <c r="M101" s="7"/>
+      <c t="s" r="M101" s="7">
+        <v>229</v>
+      </c>
     </row>
     <row r="102" ht="14.25" customHeight="1">
       <c r="A102" s="6"/>
@@ -5457,7 +5527,7 @@
         <v>231</v>
       </c>
       <c t="s" r="J103" s="7">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="K103" s="7"/>
       <c r="L103" s="7"/>
@@ -5492,7 +5562,7 @@
         <v>233</v>
       </c>
       <c t="s" r="J104" s="7">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="K104" s="7"/>
       <c r="L104" s="7"/>
@@ -5524,7 +5594,7 @@
         <v>225</v>
       </c>
       <c t="s" r="I105" s="7">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c t="s" r="J105" s="7">
         <v>65</v>
@@ -5559,7 +5629,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I106" s="7">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c t="s" r="J106" s="7">
         <v>36</v>
@@ -5679,7 +5749,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I110" s="7">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c t="s" r="J110" s="7">
         <v>241</v>
@@ -5714,7 +5784,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I111" s="7">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c t="s" r="J111" s="7">
         <v>107</v>
@@ -5722,7 +5792,7 @@
       <c r="K111" s="7"/>
       <c r="L111" s="7"/>
       <c t="s" r="M111" s="7">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="112" ht="14.25" customHeight="1">
@@ -5864,7 +5934,7 @@
         <v>50</v>
       </c>
       <c t="s" r="H116" s="8">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c t="s" r="I116" s="7">
         <v>250</v>
@@ -5896,13 +5966,13 @@
         <v>321</v>
       </c>
       <c t="s" r="G117" s="8">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c t="s" r="H117" s="8">
         <v>50</v>
       </c>
       <c t="s" r="I117" s="7">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c t="s" r="J117" s="7">
         <v>37</v>
@@ -5940,7 +6010,7 @@
         <v>105</v>
       </c>
       <c t="s" r="J118" s="7">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="K118" s="7"/>
       <c r="L118" s="7"/>
@@ -5972,7 +6042,7 @@
         <v>50</v>
       </c>
       <c t="s" r="I119" s="7">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c t="s" r="J119" s="7">
         <v>255</v>
@@ -6126,7 +6196,7 @@
         <v>264</v>
       </c>
       <c t="s" r="J124" s="7">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="K124" s="7"/>
       <c r="L124" s="7"/>
@@ -6196,7 +6266,7 @@
         <v>269</v>
       </c>
       <c t="s" r="J126" s="7">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="K126" s="7"/>
       <c r="L126" s="7"/>
@@ -6348,7 +6418,7 @@
         <v>72</v>
       </c>
       <c t="s" r="I131" s="7">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c t="s" r="J131" s="7">
         <v>282</v>
@@ -6385,7 +6455,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I132" s="7">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c t="s" r="J132" s="7">
         <v>285</v>
@@ -6437,7 +6507,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I134" s="7">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c t="s" r="J134" s="7">
         <v>290</v>
@@ -6445,7 +6515,7 @@
       <c r="K134" s="7"/>
       <c r="L134" s="7"/>
       <c t="s" r="M134" s="7">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="135" ht="15" customHeight="1">
@@ -6545,7 +6615,7 @@
         <v>294</v>
       </c>
       <c t="s" r="J137" s="7">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="K137" s="7"/>
       <c r="L137" s="7"/>
@@ -6660,7 +6730,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I141" s="7">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c t="s" r="J141" s="7">
         <v>93</v>
@@ -6698,7 +6768,7 @@
         <v>23</v>
       </c>
       <c t="s" r="J142" s="7">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c t="s" r="K142" s="7">
         <v>75</v>
@@ -6738,11 +6808,11 @@
         <v>54</v>
       </c>
       <c t="s" r="K143" s="7">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="L143" s="7"/>
       <c t="s" r="M143" s="7">
-        <v>195</v>
+        <v>302</v>
       </c>
     </row>
     <row r="144" ht="14.25" customHeight="1">
@@ -6805,7 +6875,7 @@
       </c>
       <c r="D146" s="7"/>
       <c t="s" r="E146" s="7">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F146" s="7">
         <v>321</v>
@@ -6817,15 +6887,15 @@
         <v>33</v>
       </c>
       <c t="s" r="I146" s="7">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c t="s" r="J146" s="7">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="K146" s="7"/>
       <c r="L146" s="7"/>
       <c t="s" r="M146" s="7">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="147" ht="14.25" customHeight="1">
@@ -6840,7 +6910,7 @@
       </c>
       <c r="D147" s="7"/>
       <c t="s" r="E147" s="7">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F147" s="7">
         <v>321</v>
@@ -6852,15 +6922,15 @@
         <v>50</v>
       </c>
       <c t="s" r="I147" s="7">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c t="s" r="J147" s="7">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K147" s="7"/>
       <c r="L147" s="7"/>
       <c t="s" r="M147" s="7">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="148" ht="14.25" customHeight="1">
@@ -6875,7 +6945,7 @@
       </c>
       <c r="D148" s="7"/>
       <c t="s" r="E148" s="7">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F148" s="7">
         <v>321</v>
@@ -6890,12 +6960,12 @@
         <v>251</v>
       </c>
       <c t="s" r="J148" s="7">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="K148" s="7"/>
       <c r="L148" s="7"/>
       <c t="s" r="M148" s="7">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="149" ht="14.25" customHeight="1">
@@ -6910,7 +6980,7 @@
       </c>
       <c r="D149" s="7"/>
       <c t="s" r="E149" s="7">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F149" s="7">
         <v>321</v>
@@ -6945,7 +7015,7 @@
       </c>
       <c r="D150" s="7"/>
       <c t="s" r="E150" s="7">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F150" s="7">
         <v>321</v>
@@ -6954,18 +7024,18 @@
         <v>50</v>
       </c>
       <c t="s" r="H150" s="8">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c t="s" r="I150" s="7">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c t="s" r="J150" s="7">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="K150" s="7"/>
       <c r="L150" s="7"/>
       <c t="s" r="M150" s="7">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="151" ht="14.25" customHeight="1">
@@ -6980,13 +7050,13 @@
       </c>
       <c r="D151" s="7"/>
       <c t="s" r="E151" s="7">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F151" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G151" s="8">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c t="s" r="H151" s="8">
         <v>50</v>
@@ -6995,7 +7065,7 @@
         <v>197</v>
       </c>
       <c t="s" r="J151" s="7">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="K151" s="7"/>
       <c r="L151" s="7"/>
@@ -7028,7 +7098,7 @@
       </c>
       <c r="D153" s="7"/>
       <c t="s" r="E153" s="7">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="F153" s="7">
         <v>321</v>
@@ -7063,7 +7133,7 @@
       </c>
       <c r="D154" s="7"/>
       <c t="s" r="E154" s="7">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="F154" s="7">
         <v>321</v>
@@ -7075,7 +7145,7 @@
         <v>57</v>
       </c>
       <c t="s" r="I154" s="7">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c t="s" r="J154" s="7">
         <v>251</v>
@@ -7083,7 +7153,7 @@
       <c r="K154" s="7"/>
       <c r="L154" s="7"/>
       <c t="s" r="M154" s="7">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="155" ht="15" customHeight="1">
@@ -7098,7 +7168,7 @@
       </c>
       <c r="D155" s="7"/>
       <c t="s" r="E155" s="7">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="F155" s="7">
         <v>321</v>
@@ -7107,10 +7177,10 @@
         <v>57</v>
       </c>
       <c t="s" r="H155" s="8">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c t="s" r="I155" s="7">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c t="s" r="J155" s="7">
         <v>267</v>
@@ -7118,7 +7188,7 @@
       <c r="K155" s="7"/>
       <c r="L155" s="7"/>
       <c t="s" r="M155" s="7">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="156" ht="14.25" customHeight="1">
@@ -7133,19 +7203,19 @@
       </c>
       <c r="D156" s="7"/>
       <c t="s" r="E156" s="7">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="F156" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G156" s="8">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c t="s" r="H156" s="8">
         <v>119</v>
       </c>
       <c t="s" r="I156" s="7">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c t="s" r="J156" s="7">
         <v>212</v>
@@ -7153,7 +7223,7 @@
       <c r="K156" s="7"/>
       <c r="L156" s="7"/>
       <c t="s" r="M156" s="7">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="157" ht="14.25" customHeight="1">
@@ -7168,7 +7238,7 @@
       </c>
       <c r="D157" s="7"/>
       <c t="s" r="E157" s="7">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="F157" s="7">
         <v>321</v>
@@ -7177,7 +7247,7 @@
         <v>119</v>
       </c>
       <c t="s" r="H157" s="8">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c t="s" r="I157" s="7">
         <v>94</v>
@@ -7188,7 +7258,7 @@
       <c r="K157" s="7"/>
       <c r="L157" s="7"/>
       <c t="s" r="M157" s="7">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="158" ht="14.25" customHeight="1">
@@ -7203,13 +7273,13 @@
       </c>
       <c r="D158" s="7"/>
       <c t="s" r="E158" s="7">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="F158" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G158" s="8">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c t="s" r="H158" s="8">
         <v>17</v>
@@ -7218,11 +7288,13 @@
         <v>107</v>
       </c>
       <c t="s" r="J158" s="7">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="K158" s="7"/>
       <c r="L158" s="7"/>
-      <c r="M158" s="7"/>
+      <c t="s" r="M158" s="7">
+        <v>323</v>
+      </c>
     </row>
     <row r="159" ht="14.25" customHeight="1">
       <c r="A159" s="6"/>
@@ -7251,7 +7323,7 @@
       </c>
       <c r="D160" s="7"/>
       <c t="s" r="E160" s="7">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="F160" s="7">
         <v>321</v>
@@ -7260,10 +7332,10 @@
         <v>50</v>
       </c>
       <c t="s" r="H160" s="8">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c t="s" r="I160" s="7">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c t="s" r="J160" s="7">
         <v>36</v>
@@ -7271,7 +7343,7 @@
       <c r="K160" s="7"/>
       <c r="L160" s="7"/>
       <c t="s" r="M160" s="7">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="161" ht="14.25" customHeight="1">
@@ -7286,13 +7358,13 @@
       </c>
       <c r="D161" s="7"/>
       <c t="s" r="E161" s="7">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="F161" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G161" s="8">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c t="s" r="H161" s="8">
         <v>50</v>
@@ -7301,7 +7373,7 @@
         <v>20</v>
       </c>
       <c t="s" r="J161" s="7">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="K161" s="7"/>
       <c r="L161" s="7"/>
@@ -7321,7 +7393,7 @@
       </c>
       <c r="D162" s="7"/>
       <c t="s" r="E162" s="7">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="F162" s="7">
         <v>321</v>
@@ -7338,9 +7410,13 @@
       <c t="s" r="J162" s="7">
         <v>262</v>
       </c>
-      <c r="K162" s="7"/>
+      <c t="s" r="K162" s="7">
+        <v>328</v>
+      </c>
       <c r="L162" s="7"/>
-      <c r="M162" s="7"/>
+      <c t="s" r="M162" s="7">
+        <v>30</v>
+      </c>
     </row>
     <row r="163" ht="14.25" customHeight="1">
       <c r="A163" s="6"/>
@@ -7369,7 +7445,7 @@
       </c>
       <c r="D164" s="7"/>
       <c t="s" r="E164" s="7">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="F164" s="7">
         <v>321</v>
@@ -7381,17 +7457,17 @@
         <v>50</v>
       </c>
       <c t="s" r="I164" s="7">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c t="s" r="J164" s="7">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c t="s" r="K164" s="7">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="L164" s="7"/>
       <c t="s" r="M164" s="7">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="165" ht="15" customHeight="1">
@@ -7406,7 +7482,7 @@
       </c>
       <c r="D165" s="7"/>
       <c t="s" r="E165" s="7">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="F165" s="7">
         <v>321</v>
@@ -7415,10 +7491,10 @@
         <v>50</v>
       </c>
       <c t="s" r="H165" s="8">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c t="s" r="I165" s="7">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c t="s" r="J165" s="7">
         <v>82</v>
@@ -7426,7 +7502,7 @@
       <c r="K165" s="7"/>
       <c r="L165" s="7"/>
       <c t="s" r="M165" s="7">
-        <v>328</v>
+        <v>331</v>
       </c>
     </row>
     <row r="166" ht="14.25" customHeight="1">
@@ -7441,13 +7517,13 @@
       </c>
       <c r="D166" s="7"/>
       <c t="s" r="E166" s="7">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="F166" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G166" s="8">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c t="s" r="H166" s="8">
         <v>50</v>
@@ -7456,7 +7532,7 @@
         <v>207</v>
       </c>
       <c t="s" r="J166" s="7">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="K166" s="7"/>
       <c r="L166" s="7"/>
@@ -7476,7 +7552,7 @@
       </c>
       <c r="D167" s="7"/>
       <c t="s" r="E167" s="7">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="F167" s="7">
         <v>321</v>
@@ -7485,18 +7561,18 @@
         <v>50</v>
       </c>
       <c t="s" r="H167" s="8">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c t="s" r="I167" s="7">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c t="s" r="J167" s="7">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="K167" s="7"/>
       <c r="L167" s="7"/>
       <c t="s" r="M167" s="7">
-        <v>145</v>
+        <v>334</v>
       </c>
     </row>
     <row r="168" ht="14.25" customHeight="1">
@@ -7511,22 +7587,22 @@
       </c>
       <c r="D168" s="7"/>
       <c t="s" r="E168" s="7">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="F168" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G168" s="8">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c t="s" r="H168" s="8">
         <v>50</v>
       </c>
       <c t="s" r="I168" s="7">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c t="s" r="J168" s="7">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="K168" s="7"/>
       <c r="L168" s="7"/>
@@ -7559,7 +7635,7 @@
       </c>
       <c r="D170" s="7"/>
       <c t="s" r="E170" s="7">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="F170" s="7">
         <v>321</v>
@@ -7571,7 +7647,7 @@
         <v>50</v>
       </c>
       <c t="s" r="I170" s="7">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c t="s" r="J170" s="7">
         <v>38</v>
@@ -7594,7 +7670,7 @@
       </c>
       <c r="D171" s="7"/>
       <c t="s" r="E171" s="7">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="F171" s="7">
         <v>321</v>
@@ -7603,13 +7679,13 @@
         <v>50</v>
       </c>
       <c t="s" r="H171" s="8">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c t="s" r="I171" s="7">
         <v>41</v>
       </c>
       <c t="s" r="J171" s="7">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="K171" s="7"/>
       <c r="L171" s="7"/>
@@ -7629,13 +7705,13 @@
       </c>
       <c r="D172" s="7"/>
       <c t="s" r="E172" s="7">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="F172" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G172" s="8">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c t="s" r="H172" s="8">
         <v>50</v>
@@ -7679,7 +7755,7 @@
       </c>
       <c r="D174" s="7"/>
       <c t="s" r="E174" s="7">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="F174" s="7">
         <v>321</v>
@@ -7694,12 +7770,12 @@
         <v>200</v>
       </c>
       <c t="s" r="J174" s="7">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="K174" s="7"/>
       <c r="L174" s="7"/>
       <c t="s" r="M174" s="7">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="175" ht="15" customHeight="1">
@@ -7714,7 +7790,7 @@
       </c>
       <c r="D175" s="7"/>
       <c t="s" r="E175" s="7">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="F175" s="7">
         <v>321</v>
@@ -7734,7 +7810,7 @@
       <c r="K175" s="7"/>
       <c r="L175" s="7"/>
       <c t="s" r="M175" s="7">
-        <v>337</v>
+        <v>341</v>
       </c>
     </row>
     <row r="176" ht="14.25" customHeight="1">
@@ -7749,7 +7825,7 @@
       </c>
       <c r="D176" s="7"/>
       <c t="s" r="E176" s="7">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="F176" s="7">
         <v>321</v>
@@ -7769,7 +7845,7 @@
       <c r="K176" s="7"/>
       <c r="L176" s="7"/>
       <c t="s" r="M176" s="7">
-        <v>338</v>
+        <v>342</v>
       </c>
     </row>
     <row r="177" ht="14.25" customHeight="1">
@@ -7784,7 +7860,7 @@
       </c>
       <c r="D177" s="7"/>
       <c t="s" r="E177" s="7">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="F177" s="7">
         <v>321</v>
@@ -7796,10 +7872,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I177" s="7">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c t="s" r="J177" s="7">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="K177" s="7"/>
       <c r="L177" s="7"/>
@@ -7832,7 +7908,7 @@
       </c>
       <c r="D179" s="7"/>
       <c t="s" r="E179" s="7">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="F179" s="7">
         <v>321</v>
@@ -7844,15 +7920,15 @@
         <v>33</v>
       </c>
       <c t="s" r="I179" s="7">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c t="s" r="J179" s="7">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="K179" s="7"/>
       <c r="L179" s="7"/>
       <c t="s" r="M179" s="7">
-        <v>341</v>
+        <v>345</v>
       </c>
     </row>
     <row r="180" ht="15" customHeight="1">
@@ -7867,7 +7943,7 @@
       </c>
       <c r="D180" s="7"/>
       <c t="s" r="E180" s="7">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="F180" s="7">
         <v>321</v>
@@ -7879,15 +7955,15 @@
         <v>57</v>
       </c>
       <c t="s" r="I180" s="7">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c t="s" r="J180" s="7">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="K180" s="7"/>
       <c r="L180" s="7"/>
       <c t="s" r="M180" s="7">
-        <v>342</v>
+        <v>346</v>
       </c>
     </row>
     <row r="181" ht="14.25" customHeight="1">
@@ -7902,7 +7978,7 @@
       </c>
       <c r="D181" s="7"/>
       <c t="s" r="E181" s="7">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="F181" s="7">
         <v>321</v>
@@ -7914,7 +7990,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I181" s="7">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c t="s" r="J181" s="7">
         <v>102</v>
@@ -7922,7 +7998,7 @@
       <c r="K181" s="7"/>
       <c r="L181" s="7"/>
       <c t="s" r="M181" s="7">
-        <v>343</v>
+        <v>347</v>
       </c>
     </row>
     <row r="182" ht="14.25" customHeight="1">
@@ -7937,7 +8013,7 @@
       </c>
       <c r="D182" s="7"/>
       <c t="s" r="E182" s="7">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="F182" s="7">
         <v>321</v>
@@ -7957,7 +8033,7 @@
       <c r="K182" s="7"/>
       <c r="L182" s="7"/>
       <c t="s" r="M182" s="7">
-        <v>344</v>
+        <v>348</v>
       </c>
     </row>
     <row r="183" ht="14.25" customHeight="1">
@@ -7972,7 +8048,7 @@
       </c>
       <c r="D183" s="7"/>
       <c t="s" r="E183" s="7">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="F183" s="7">
         <v>321</v>
@@ -7984,7 +8060,7 @@
         <v>50</v>
       </c>
       <c t="s" r="I183" s="7">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c t="s" r="J183" s="7">
         <v>23</v>
@@ -7992,7 +8068,7 @@
       <c r="K183" s="7"/>
       <c r="L183" s="7"/>
       <c t="s" r="M183" s="7">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="184" ht="14.25" customHeight="1">
@@ -8007,7 +8083,7 @@
       </c>
       <c r="D184" s="7"/>
       <c t="s" r="E184" s="7">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="F184" s="7">
         <v>321</v>
@@ -8019,17 +8095,17 @@
         <v>57</v>
       </c>
       <c t="s" r="I184" s="7">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c t="s" r="J184" s="7">
         <v>301</v>
       </c>
       <c t="s" r="K184" s="7">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="L184" s="7"/>
       <c t="s" r="M184" s="7">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="185" ht="15" customHeight="1">
@@ -8044,7 +8120,7 @@
       </c>
       <c r="D185" s="7"/>
       <c t="s" r="E185" s="7">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="F185" s="7">
         <v>321</v>
@@ -8056,14 +8132,16 @@
         <v>50</v>
       </c>
       <c t="s" r="I185" s="7">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c t="s" r="J185" s="7">
         <v>47</v>
       </c>
       <c r="K185" s="7"/>
       <c r="L185" s="7"/>
-      <c r="M185" s="7"/>
+      <c t="s" r="M185" s="7">
+        <v>352</v>
+      </c>
     </row>
     <row r="186" ht="14.25" customHeight="1">
       <c r="A186" s="6"/>
@@ -8092,7 +8170,7 @@
       </c>
       <c r="D187" s="7"/>
       <c t="s" r="E187" s="7">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="F187" s="7">
         <v>321</v>
@@ -8104,7 +8182,7 @@
         <v>72</v>
       </c>
       <c t="s" r="I187" s="7">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c t="s" r="J187" s="7">
         <v>217</v>
@@ -8127,7 +8205,7 @@
       </c>
       <c r="D188" s="7"/>
       <c t="s" r="E188" s="7">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="F188" s="7">
         <v>321</v>
@@ -8139,15 +8217,15 @@
         <v>17</v>
       </c>
       <c t="s" r="I188" s="7">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c t="s" r="J188" s="7">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="K188" s="7"/>
       <c r="L188" s="7"/>
       <c t="s" r="M188" s="7">
-        <v>351</v>
+        <v>356</v>
       </c>
     </row>
     <row r="189" ht="14.25" customHeight="1">
@@ -8162,7 +8240,7 @@
       </c>
       <c r="D189" s="7"/>
       <c t="s" r="E189" s="7">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="F189" s="7">
         <v>321</v>
@@ -8177,7 +8255,7 @@
         <v>35</v>
       </c>
       <c t="s" r="J189" s="7">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="K189" s="7"/>
       <c r="L189" s="7"/>
@@ -8197,7 +8275,7 @@
       </c>
       <c r="D190" s="7"/>
       <c t="s" r="E190" s="7">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="F190" s="7">
         <v>321</v>
@@ -8217,7 +8295,7 @@
       <c r="K190" s="7"/>
       <c r="L190" s="7"/>
       <c t="s" r="M190" s="7">
-        <v>352</v>
+        <v>357</v>
       </c>
     </row>
     <row r="191" ht="14.25" customHeight="1">
@@ -8232,7 +8310,7 @@
       </c>
       <c r="D191" s="7"/>
       <c t="s" r="E191" s="7">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="F191" s="7">
         <v>321</v>
@@ -8244,15 +8322,15 @@
         <v>50</v>
       </c>
       <c t="s" r="I191" s="7">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c t="s" r="J191" s="7">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="K191" s="7"/>
       <c r="L191" s="7"/>
       <c t="s" r="M191" s="7">
-        <v>355</v>
+        <v>360</v>
       </c>
     </row>
     <row r="192" ht="14.25" customHeight="1">
@@ -8282,7 +8360,7 @@
       </c>
       <c r="D193" s="7"/>
       <c t="s" r="E193" s="7">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="F193" s="7">
         <v>321</v>
@@ -8291,18 +8369,18 @@
         <v>57</v>
       </c>
       <c t="s" r="H193" s="8">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c t="s" r="I193" s="7">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c t="s" r="J193" s="7">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="K193" s="7"/>
       <c r="L193" s="7"/>
       <c t="s" r="M193" s="7">
-        <v>357</v>
+        <v>362</v>
       </c>
     </row>
     <row r="194" ht="14.25" customHeight="1">
@@ -8317,27 +8395,27 @@
       </c>
       <c r="D194" s="7"/>
       <c t="s" r="E194" s="7">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="F194" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G194" s="8">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c t="s" r="H194" s="8">
         <v>57</v>
       </c>
       <c t="s" r="I194" s="7">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c t="s" r="J194" s="7">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="K194" s="7"/>
       <c r="L194" s="7"/>
       <c t="s" r="M194" s="7">
-        <v>359</v>
+        <v>364</v>
       </c>
     </row>
     <row r="195" ht="15" customHeight="1">
@@ -8352,7 +8430,7 @@
       </c>
       <c r="D195" s="7"/>
       <c t="s" r="E195" s="7">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="F195" s="7">
         <v>321</v>
@@ -8361,10 +8439,10 @@
         <v>57</v>
       </c>
       <c t="s" r="H195" s="8">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c t="s" r="I195" s="7">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c t="s" r="J195" s="7">
         <v>267</v>
@@ -8372,7 +8450,7 @@
       <c r="K195" s="7"/>
       <c r="L195" s="7"/>
       <c t="s" r="M195" s="7">
-        <v>362</v>
+        <v>367</v>
       </c>
     </row>
     <row r="196" ht="14.25" customHeight="1">
@@ -8387,13 +8465,13 @@
       </c>
       <c r="D196" s="7"/>
       <c t="s" r="E196" s="7">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="F196" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G196" s="8">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c t="s" r="H196" s="8">
         <v>57</v>
@@ -8402,12 +8480,12 @@
         <v>103</v>
       </c>
       <c t="s" r="J196" s="7">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="K196" s="7"/>
       <c r="L196" s="7"/>
       <c t="s" r="M196" s="7">
-        <v>363</v>
+        <v>368</v>
       </c>
     </row>
     <row r="197" ht="14.25" customHeight="1">
@@ -8422,7 +8500,7 @@
       </c>
       <c r="D197" s="7"/>
       <c t="s" r="E197" s="7">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="F197" s="7">
         <v>321</v>
@@ -8431,10 +8509,10 @@
         <v>57</v>
       </c>
       <c t="s" r="H197" s="8">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c t="s" r="I197" s="7">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c t="s" r="J197" s="7">
         <v>255</v>
@@ -8442,7 +8520,7 @@
       <c r="K197" s="7"/>
       <c r="L197" s="7"/>
       <c t="s" r="M197" s="7">
-        <v>364</v>
+        <v>369</v>
       </c>
     </row>
     <row r="198" ht="14.25" customHeight="1">
@@ -8457,13 +8535,13 @@
       </c>
       <c r="D198" s="7"/>
       <c t="s" r="E198" s="7">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="F198" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G198" s="8">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c t="s" r="H198" s="8">
         <v>57</v>
@@ -8472,11 +8550,13 @@
         <v>228</v>
       </c>
       <c t="s" r="J198" s="7">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="K198" s="7"/>
       <c r="L198" s="7"/>
-      <c r="M198" s="7"/>
+      <c t="s" r="M198" s="7">
+        <v>370</v>
+      </c>
     </row>
     <row r="199" ht="14.25" customHeight="1">
       <c r="A199" s="6"/>
@@ -8505,7 +8585,7 @@
       </c>
       <c r="D200" s="7"/>
       <c t="s" r="E200" s="7">
-        <v>365</v>
+        <v>371</v>
       </c>
       <c r="F200" s="7">
         <v>321</v>
@@ -8514,18 +8594,18 @@
         <v>17</v>
       </c>
       <c t="s" r="H200" s="8">
-        <v>366</v>
+        <v>372</v>
       </c>
       <c t="s" r="I200" s="7">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c t="s" r="J200" s="7">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K200" s="7"/>
       <c r="L200" s="7"/>
       <c t="s" r="M200" s="7">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="201" ht="14.25" customHeight="1">
@@ -8540,13 +8620,13 @@
       </c>
       <c r="D201" s="7"/>
       <c t="s" r="E201" s="7">
-        <v>365</v>
+        <v>371</v>
       </c>
       <c r="F201" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G201" s="8">
-        <v>366</v>
+        <v>372</v>
       </c>
       <c t="s" r="H201" s="8">
         <v>17</v>
@@ -8555,12 +8635,12 @@
         <v>36</v>
       </c>
       <c t="s" r="J201" s="7">
-        <v>367</v>
+        <v>373</v>
       </c>
       <c r="K201" s="7"/>
       <c r="L201" s="7"/>
       <c t="s" r="M201" s="7">
-        <v>368</v>
+        <v>374</v>
       </c>
     </row>
     <row r="202" ht="14.25" customHeight="1">
@@ -8575,7 +8655,7 @@
       </c>
       <c r="D202" s="7"/>
       <c t="s" r="E202" s="7">
-        <v>365</v>
+        <v>371</v>
       </c>
       <c r="F202" s="7">
         <v>321</v>
@@ -8584,18 +8664,18 @@
         <v>17</v>
       </c>
       <c t="s" r="H202" s="8">
-        <v>369</v>
+        <v>375</v>
       </c>
       <c t="s" r="I202" s="7">
         <v>105</v>
       </c>
       <c t="s" r="J202" s="7">
-        <v>370</v>
+        <v>376</v>
       </c>
       <c r="K202" s="7"/>
       <c r="L202" s="7"/>
       <c t="s" r="M202" s="7">
-        <v>371</v>
+        <v>377</v>
       </c>
     </row>
     <row r="203" ht="14.25" customHeight="1">
@@ -8610,19 +8690,19 @@
       </c>
       <c r="D203" s="7"/>
       <c t="s" r="E203" s="7">
-        <v>365</v>
+        <v>371</v>
       </c>
       <c r="F203" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G203" s="8">
-        <v>369</v>
+        <v>375</v>
       </c>
       <c t="s" r="H203" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I203" s="7">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c t="s" r="J203" s="7">
         <v>255</v>
@@ -8630,7 +8710,7 @@
       <c r="K203" s="7"/>
       <c r="L203" s="7"/>
       <c t="s" r="M203" s="7">
-        <v>372</v>
+        <v>378</v>
       </c>
     </row>
     <row r="204" ht="14.25" customHeight="1">
@@ -8645,7 +8725,7 @@
       </c>
       <c r="D204" s="7"/>
       <c t="s" r="E204" s="7">
-        <v>365</v>
+        <v>371</v>
       </c>
       <c r="F204" s="7">
         <v>321</v>
@@ -8657,7 +8737,7 @@
         <v>32</v>
       </c>
       <c t="s" r="I204" s="7">
-        <v>373</v>
+        <v>379</v>
       </c>
       <c t="s" r="J204" s="7">
         <v>61</v>
@@ -8693,7 +8773,7 @@
       </c>
       <c r="D206" s="7"/>
       <c t="s" r="E206" s="7">
-        <v>374</v>
+        <v>380</v>
       </c>
       <c r="F206" s="7">
         <v>321</v>
@@ -8708,12 +8788,12 @@
         <v>91</v>
       </c>
       <c t="s" r="J206" s="7">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="K206" s="7"/>
       <c r="L206" s="7"/>
       <c t="s" r="M206" s="7">
-        <v>375</v>
+        <v>381</v>
       </c>
     </row>
     <row r="207" ht="14.25" customHeight="1">
@@ -8728,7 +8808,7 @@
       </c>
       <c r="D207" s="7"/>
       <c t="s" r="E207" s="7">
-        <v>374</v>
+        <v>380</v>
       </c>
       <c r="F207" s="7">
         <v>321</v>
@@ -8740,7 +8820,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I207" s="7">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c t="s" r="J207" s="7">
         <v>20</v>
@@ -8748,7 +8828,7 @@
       <c r="K207" s="7"/>
       <c r="L207" s="7"/>
       <c t="s" r="M207" s="7">
-        <v>377</v>
+        <v>383</v>
       </c>
     </row>
     <row r="208" ht="14.25" customHeight="1">
@@ -8763,7 +8843,7 @@
       </c>
       <c r="D208" s="7"/>
       <c t="s" r="E208" s="7">
-        <v>374</v>
+        <v>380</v>
       </c>
       <c r="F208" s="7">
         <v>321</v>
@@ -8783,7 +8863,7 @@
       <c r="K208" s="7"/>
       <c r="L208" s="7"/>
       <c t="s" r="M208" s="7">
-        <v>378</v>
+        <v>384</v>
       </c>
     </row>
     <row r="209" ht="14.25" customHeight="1">
@@ -8798,7 +8878,7 @@
       </c>
       <c r="D209" s="7"/>
       <c t="s" r="E209" s="7">
-        <v>374</v>
+        <v>380</v>
       </c>
       <c r="F209" s="7">
         <v>321</v>
@@ -8818,7 +8898,7 @@
       <c r="K209" s="7"/>
       <c r="L209" s="7"/>
       <c t="s" r="M209" s="7">
-        <v>379</v>
+        <v>385</v>
       </c>
     </row>
     <row r="210" ht="15" customHeight="1">
@@ -8848,7 +8928,7 @@
       </c>
       <c r="D211" s="7"/>
       <c t="s" r="E211" s="7">
-        <v>380</v>
+        <v>386</v>
       </c>
       <c r="F211" s="7">
         <v>321</v>
@@ -8860,7 +8940,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I211" s="7">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c t="s" r="J211" s="7">
         <v>65</v>
@@ -8883,7 +8963,7 @@
       </c>
       <c r="D212" s="7"/>
       <c t="s" r="E212" s="7">
-        <v>380</v>
+        <v>386</v>
       </c>
       <c r="F212" s="7">
         <v>321</v>
@@ -8895,15 +8975,15 @@
         <v>225</v>
       </c>
       <c t="s" r="I212" s="7">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c t="s" r="J212" s="7">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="K212" s="7"/>
       <c r="L212" s="7"/>
       <c t="s" r="M212" s="7">
-        <v>381</v>
+        <v>387</v>
       </c>
     </row>
     <row r="213" ht="14.25" customHeight="1">
@@ -8918,7 +8998,7 @@
       </c>
       <c r="D213" s="7"/>
       <c t="s" r="E213" s="7">
-        <v>380</v>
+        <v>386</v>
       </c>
       <c r="F213" s="7">
         <v>321</v>
@@ -8933,7 +9013,7 @@
         <v>296</v>
       </c>
       <c t="s" r="J213" s="7">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="K213" s="7"/>
       <c r="L213" s="7"/>
@@ -8953,7 +9033,7 @@
       </c>
       <c r="D214" s="7"/>
       <c t="s" r="E214" s="7">
-        <v>380</v>
+        <v>386</v>
       </c>
       <c r="F214" s="7">
         <v>321</v>
@@ -8968,12 +9048,12 @@
         <v>206</v>
       </c>
       <c t="s" r="J214" s="7">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="K214" s="7"/>
       <c r="L214" s="7"/>
       <c t="s" r="M214" s="7">
-        <v>382</v>
+        <v>388</v>
       </c>
     </row>
     <row r="215" ht="15" customHeight="1">
@@ -8988,7 +9068,7 @@
       </c>
       <c r="D215" s="7"/>
       <c t="s" r="E215" s="7">
-        <v>380</v>
+        <v>386</v>
       </c>
       <c r="F215" s="7">
         <v>321</v>
@@ -9008,7 +9088,7 @@
       <c r="K215" s="7"/>
       <c r="L215" s="7"/>
       <c t="s" r="M215" s="7">
-        <v>383</v>
+        <v>389</v>
       </c>
     </row>
     <row r="216" ht="14.25" customHeight="1">
@@ -9023,7 +9103,7 @@
       </c>
       <c r="D216" s="7"/>
       <c t="s" r="E216" s="7">
-        <v>380</v>
+        <v>386</v>
       </c>
       <c r="F216" s="7">
         <v>321</v>
@@ -9032,13 +9112,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H216" s="8">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c t="s" r="I216" s="7">
         <v>196</v>
       </c>
       <c t="s" r="J216" s="7">
-        <v>134</v>
+        <v>328</v>
       </c>
       <c r="K216" s="7"/>
       <c r="L216" s="7"/>
@@ -9056,13 +9136,13 @@
       </c>
       <c r="D217" s="7"/>
       <c t="s" r="E217" s="7">
-        <v>380</v>
+        <v>386</v>
       </c>
       <c r="F217" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G217" s="8">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c t="s" r="H217" s="8">
         <v>17</v>
@@ -9071,7 +9151,7 @@
         <v>258</v>
       </c>
       <c t="s" r="J217" s="7">
-        <v>385</v>
+        <v>391</v>
       </c>
       <c r="K217" s="7"/>
       <c r="L217" s="7"/>
@@ -9104,7 +9184,7 @@
       </c>
       <c r="D219" s="7"/>
       <c t="s" r="E219" s="7">
-        <v>386</v>
+        <v>392</v>
       </c>
       <c r="F219" s="7">
         <v>321</v>
@@ -9119,12 +9199,12 @@
         <v>48</v>
       </c>
       <c t="s" r="J219" s="7">
-        <v>387</v>
+        <v>393</v>
       </c>
       <c r="K219" s="7"/>
       <c r="L219" s="7"/>
       <c t="s" r="M219" s="7">
-        <v>388</v>
+        <v>394</v>
       </c>
     </row>
     <row r="220" ht="15" customHeight="1">
@@ -9139,7 +9219,7 @@
       </c>
       <c r="D220" s="7"/>
       <c t="s" r="E220" s="7">
-        <v>386</v>
+        <v>392</v>
       </c>
       <c r="F220" s="7">
         <v>321</v>
@@ -9151,15 +9231,15 @@
         <v>17</v>
       </c>
       <c t="s" r="I220" s="7">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c t="s" r="J220" s="7">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="K220" s="7"/>
       <c r="L220" s="7"/>
       <c t="s" r="M220" s="7">
-        <v>389</v>
+        <v>395</v>
       </c>
     </row>
     <row r="221" ht="14.25" customHeight="1">
@@ -9174,7 +9254,7 @@
       </c>
       <c r="D221" s="7"/>
       <c t="s" r="E221" s="7">
-        <v>386</v>
+        <v>392</v>
       </c>
       <c r="F221" s="7">
         <v>321</v>
@@ -9189,12 +9269,12 @@
         <v>51</v>
       </c>
       <c t="s" r="J221" s="7">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="K221" s="7"/>
       <c r="L221" s="7"/>
       <c t="s" r="M221" s="7">
-        <v>390</v>
+        <v>396</v>
       </c>
     </row>
     <row r="222" ht="14.25" customHeight="1">
@@ -9209,7 +9289,7 @@
       </c>
       <c r="D222" s="7"/>
       <c t="s" r="E222" s="7">
-        <v>386</v>
+        <v>392</v>
       </c>
       <c r="F222" s="7">
         <v>321</v>
@@ -9224,12 +9304,12 @@
         <v>82</v>
       </c>
       <c t="s" r="J222" s="7">
-        <v>370</v>
+        <v>376</v>
       </c>
       <c r="K222" s="7"/>
       <c r="L222" s="7"/>
       <c t="s" r="M222" s="7">
-        <v>391</v>
+        <v>397</v>
       </c>
     </row>
     <row r="223" ht="14.25" customHeight="1">
@@ -9244,7 +9324,7 @@
       </c>
       <c r="D223" s="7"/>
       <c t="s" r="E223" s="7">
-        <v>386</v>
+        <v>392</v>
       </c>
       <c r="F223" s="7">
         <v>321</v>
@@ -9259,12 +9339,12 @@
         <v>52</v>
       </c>
       <c t="s" r="J223" s="7">
-        <v>392</v>
+        <v>398</v>
       </c>
       <c r="K223" s="7"/>
       <c r="L223" s="7"/>
       <c t="s" r="M223" s="7">
-        <v>393</v>
+        <v>399</v>
       </c>
     </row>
     <row r="224" ht="14.25" customHeight="1">
@@ -9279,7 +9359,7 @@
       </c>
       <c r="D224" s="7"/>
       <c t="s" r="E224" s="7">
-        <v>386</v>
+        <v>392</v>
       </c>
       <c r="F224" s="7">
         <v>321</v>
@@ -9291,14 +9371,16 @@
         <v>17</v>
       </c>
       <c t="s" r="I224" s="7">
-        <v>394</v>
+        <v>400</v>
       </c>
       <c t="s" r="J224" s="7">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="K224" s="7"/>
       <c r="L224" s="7"/>
-      <c r="M224" s="7"/>
+      <c t="s" r="M224" s="7">
+        <v>312</v>
+      </c>
     </row>
     <row r="225" ht="15" customHeight="1">
       <c r="A225" s="6"/>
@@ -9327,7 +9409,7 @@
       </c>
       <c r="D226" s="7"/>
       <c t="s" r="E226" s="7">
-        <v>395</v>
+        <v>401</v>
       </c>
       <c r="F226" s="7">
         <v>321</v>
@@ -9347,7 +9429,7 @@
       <c r="K226" s="7"/>
       <c r="L226" s="7"/>
       <c t="s" r="M226" s="7">
-        <v>396</v>
+        <v>402</v>
       </c>
     </row>
     <row r="227" ht="14.25" customHeight="1">
@@ -9362,7 +9444,7 @@
       </c>
       <c r="D227" s="7"/>
       <c t="s" r="E227" s="7">
-        <v>395</v>
+        <v>401</v>
       </c>
       <c r="F227" s="7">
         <v>321</v>
@@ -9371,7 +9453,7 @@
         <v>50</v>
       </c>
       <c t="s" r="H227" s="8">
-        <v>366</v>
+        <v>372</v>
       </c>
       <c t="s" r="I227" s="7">
         <v>97</v>
@@ -9382,7 +9464,7 @@
       <c r="K227" s="7"/>
       <c r="L227" s="7"/>
       <c t="s" r="M227" s="7">
-        <v>397</v>
+        <v>403</v>
       </c>
     </row>
     <row r="228" ht="14.25" customHeight="1">
@@ -9397,27 +9479,27 @@
       </c>
       <c r="D228" s="7"/>
       <c t="s" r="E228" s="7">
-        <v>395</v>
+        <v>401</v>
       </c>
       <c r="F228" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G228" s="8">
-        <v>366</v>
+        <v>372</v>
       </c>
       <c t="s" r="H228" s="8">
         <v>50</v>
       </c>
       <c t="s" r="I228" s="7">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c t="s" r="J228" s="7">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="K228" s="7"/>
       <c r="L228" s="7"/>
       <c t="s" r="M228" s="7">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="229" ht="14.25" customHeight="1">
@@ -9432,7 +9514,7 @@
       </c>
       <c r="D229" s="7"/>
       <c t="s" r="E229" s="7">
-        <v>395</v>
+        <v>401</v>
       </c>
       <c r="F229" s="7">
         <v>321</v>
@@ -9441,18 +9523,18 @@
         <v>50</v>
       </c>
       <c t="s" r="H229" s="8">
-        <v>398</v>
+        <v>404</v>
       </c>
       <c t="s" r="I229" s="7">
         <v>207</v>
       </c>
       <c t="s" r="J229" s="7">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="K229" s="7"/>
       <c r="L229" s="7"/>
       <c t="s" r="M229" s="7">
-        <v>399</v>
+        <v>405</v>
       </c>
     </row>
     <row r="230" ht="15" customHeight="1">
@@ -9467,27 +9549,27 @@
       </c>
       <c r="D230" s="7"/>
       <c t="s" r="E230" s="7">
-        <v>395</v>
+        <v>401</v>
       </c>
       <c r="F230" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G230" s="8">
-        <v>398</v>
+        <v>404</v>
       </c>
       <c t="s" r="H230" s="8">
         <v>50</v>
       </c>
       <c t="s" r="I230" s="7">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c t="s" r="J230" s="7">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="K230" s="7"/>
       <c r="L230" s="7"/>
       <c t="s" r="M230" s="7">
-        <v>401</v>
+        <v>407</v>
       </c>
     </row>
     <row r="231" ht="14.25" customHeight="1">
@@ -9517,7 +9599,7 @@
       </c>
       <c r="D232" s="7"/>
       <c t="s" r="E232" s="7">
-        <v>402</v>
+        <v>408</v>
       </c>
       <c r="F232" s="7">
         <v>321</v>
@@ -9529,15 +9611,15 @@
         <v>113</v>
       </c>
       <c t="s" r="I232" s="7">
-        <v>403</v>
+        <v>409</v>
       </c>
       <c t="s" r="J232" s="7">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="K232" s="7"/>
       <c r="L232" s="7"/>
       <c t="s" r="M232" s="7">
-        <v>404</v>
+        <v>410</v>
       </c>
     </row>
     <row r="233" ht="14.25" customHeight="1">
@@ -9552,7 +9634,7 @@
       </c>
       <c r="D233" s="7"/>
       <c t="s" r="E233" s="7">
-        <v>402</v>
+        <v>408</v>
       </c>
       <c r="F233" s="7">
         <v>321</v>
@@ -9567,12 +9649,12 @@
         <v>64</v>
       </c>
       <c t="s" r="J233" s="7">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="K233" s="7"/>
       <c r="L233" s="7"/>
       <c t="s" r="M233" s="7">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="234" ht="14.25" customHeight="1">
@@ -9587,7 +9669,7 @@
       </c>
       <c r="D234" s="7"/>
       <c t="s" r="E234" s="7">
-        <v>402</v>
+        <v>408</v>
       </c>
       <c r="F234" s="7">
         <v>321</v>
@@ -9602,7 +9684,7 @@
         <v>296</v>
       </c>
       <c t="s" r="J234" s="7">
-        <v>390</v>
+        <v>396</v>
       </c>
       <c r="K234" s="7"/>
       <c r="L234" s="7"/>
@@ -9622,7 +9704,7 @@
       </c>
       <c r="D235" s="7"/>
       <c t="s" r="E235" s="7">
-        <v>402</v>
+        <v>408</v>
       </c>
       <c r="F235" s="7">
         <v>321</v>
@@ -9637,12 +9719,12 @@
         <v>40</v>
       </c>
       <c t="s" r="J235" s="7">
-        <v>405</v>
+        <v>411</v>
       </c>
       <c r="K235" s="7"/>
       <c r="L235" s="7"/>
       <c t="s" r="M235" s="7">
-        <v>406</v>
+        <v>412</v>
       </c>
     </row>
     <row r="236" ht="14.25" customHeight="1">
@@ -9657,7 +9739,7 @@
       </c>
       <c r="D236" s="7"/>
       <c t="s" r="E236" s="7">
-        <v>402</v>
+        <v>408</v>
       </c>
       <c r="F236" s="7">
         <v>321</v>
@@ -9666,18 +9748,18 @@
         <v>50</v>
       </c>
       <c t="s" r="H236" s="8">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c t="s" r="I236" s="7">
-        <v>407</v>
+        <v>413</v>
       </c>
       <c t="s" r="J236" s="7">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="K236" s="7"/>
       <c r="L236" s="7"/>
       <c t="s" r="M236" s="7">
-        <v>408</v>
+        <v>322</v>
       </c>
     </row>
     <row r="237" ht="14.25" customHeight="1">
@@ -9692,13 +9774,13 @@
       </c>
       <c r="D237" s="7"/>
       <c t="s" r="E237" s="7">
-        <v>402</v>
+        <v>408</v>
       </c>
       <c r="F237" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G237" s="8">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c t="s" r="H237" s="8">
         <v>50</v>
@@ -9707,7 +9789,7 @@
         <v>274</v>
       </c>
       <c t="s" r="J237" s="7">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="K237" s="7"/>
       <c r="L237" s="7"/>
@@ -9740,7 +9822,7 @@
       </c>
       <c r="D239" s="7"/>
       <c t="s" r="E239" s="7">
-        <v>410</v>
+        <v>415</v>
       </c>
       <c r="F239" s="7">
         <v>321</v>
@@ -9749,10 +9831,10 @@
         <v>50</v>
       </c>
       <c t="s" r="H239" s="8">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c t="s" r="I239" s="7">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c t="s" r="J239" s="7">
         <v>99</v>
@@ -9760,7 +9842,7 @@
       <c r="K239" s="7"/>
       <c r="L239" s="7"/>
       <c t="s" r="M239" s="7">
-        <v>411</v>
+        <v>416</v>
       </c>
     </row>
     <row r="240" ht="15" customHeight="1">
@@ -9775,19 +9857,19 @@
       </c>
       <c r="D240" s="7"/>
       <c t="s" r="E240" s="7">
-        <v>410</v>
+        <v>415</v>
       </c>
       <c r="F240" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G240" s="8">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c t="s" r="H240" s="8">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c t="s" r="I240" s="7">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c t="s" r="J240" s="7">
         <v>297</v>
@@ -9810,16 +9892,16 @@
       </c>
       <c r="D241" s="7"/>
       <c t="s" r="E241" s="7">
-        <v>410</v>
+        <v>415</v>
       </c>
       <c r="F241" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G241" s="8">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c t="s" r="H241" s="8">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c t="s" r="I241" s="7">
         <v>73</v>
@@ -9845,13 +9927,13 @@
       </c>
       <c r="D242" s="7"/>
       <c t="s" r="E242" s="7">
-        <v>410</v>
+        <v>415</v>
       </c>
       <c r="F242" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G242" s="8">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c t="s" r="H242" s="8">
         <v>50</v>
@@ -9865,7 +9947,7 @@
       <c r="K242" s="7"/>
       <c r="L242" s="7"/>
       <c t="s" r="M242" s="7">
-        <v>412</v>
+        <v>417</v>
       </c>
     </row>
     <row r="243" ht="14.25" customHeight="1">
@@ -9880,7 +9962,7 @@
       </c>
       <c r="D243" s="7"/>
       <c t="s" r="E243" s="7">
-        <v>410</v>
+        <v>415</v>
       </c>
       <c r="F243" s="7">
         <v>321</v>
@@ -9892,10 +9974,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I243" s="7">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c t="s" r="J243" s="7">
-        <v>134</v>
+        <v>328</v>
       </c>
       <c r="K243" s="7"/>
       <c r="L243" s="7"/>
@@ -9928,7 +10010,7 @@
       </c>
       <c r="D245" s="7"/>
       <c t="s" r="E245" s="7">
-        <v>414</v>
+        <v>419</v>
       </c>
       <c r="F245" s="7">
         <v>321</v>
@@ -9940,15 +10022,15 @@
         <v>119</v>
       </c>
       <c t="s" r="I245" s="7">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c t="s" r="J245" s="7">
-        <v>403</v>
+        <v>409</v>
       </c>
       <c r="K245" s="7"/>
       <c r="L245" s="7"/>
       <c t="s" r="M245" s="7">
-        <v>415</v>
+        <v>420</v>
       </c>
     </row>
     <row r="246" ht="14.25" customHeight="1">
@@ -9963,7 +10045,7 @@
       </c>
       <c r="D246" s="7"/>
       <c t="s" r="E246" s="7">
-        <v>414</v>
+        <v>419</v>
       </c>
       <c r="F246" s="7">
         <v>321</v>
@@ -9972,10 +10054,10 @@
         <v>119</v>
       </c>
       <c t="s" r="H246" s="8">
-        <v>416</v>
+        <v>421</v>
       </c>
       <c t="s" r="I246" s="7">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c t="s" r="J246" s="7">
         <v>91</v>
@@ -9998,13 +10080,13 @@
       </c>
       <c r="D247" s="7"/>
       <c t="s" r="E247" s="7">
-        <v>414</v>
+        <v>419</v>
       </c>
       <c r="F247" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G247" s="8">
-        <v>416</v>
+        <v>421</v>
       </c>
       <c t="s" r="H247" s="8">
         <v>119</v>
@@ -10018,7 +10100,7 @@
       <c r="K247" s="7"/>
       <c r="L247" s="7"/>
       <c t="s" r="M247" s="7">
-        <v>417</v>
+        <v>422</v>
       </c>
     </row>
     <row r="248" ht="14.25" customHeight="1">
@@ -10033,7 +10115,7 @@
       </c>
       <c r="D248" s="7"/>
       <c t="s" r="E248" s="7">
-        <v>414</v>
+        <v>419</v>
       </c>
       <c r="F248" s="7">
         <v>321</v>
@@ -10048,12 +10130,12 @@
         <v>35</v>
       </c>
       <c t="s" r="J248" s="7">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="K248" s="7"/>
       <c r="L248" s="7"/>
       <c t="s" r="M248" s="7">
-        <v>418</v>
+        <v>423</v>
       </c>
     </row>
     <row r="249" ht="14.25" customHeight="1">
@@ -10068,7 +10150,7 @@
       </c>
       <c r="D249" s="7"/>
       <c t="s" r="E249" s="7">
-        <v>414</v>
+        <v>419</v>
       </c>
       <c r="F249" s="7">
         <v>321</v>
@@ -10080,7 +10162,7 @@
         <v>225</v>
       </c>
       <c t="s" r="I249" s="7">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c t="s" r="J249" s="7">
         <v>115</v>
@@ -10088,7 +10170,7 @@
       <c r="K249" s="7"/>
       <c r="L249" s="7"/>
       <c t="s" r="M249" s="7">
-        <v>419</v>
+        <v>424</v>
       </c>
     </row>
     <row r="250" ht="15" customHeight="1">
@@ -10103,7 +10185,7 @@
       </c>
       <c r="D250" s="7"/>
       <c t="s" r="E250" s="7">
-        <v>414</v>
+        <v>419</v>
       </c>
       <c r="F250" s="7">
         <v>321</v>
@@ -10118,12 +10200,12 @@
         <v>117</v>
       </c>
       <c t="s" r="J250" s="7">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="K250" s="7"/>
       <c r="L250" s="7"/>
       <c t="s" r="M250" s="7">
-        <v>406</v>
+        <v>412</v>
       </c>
     </row>
     <row r="251" ht="14.25" customHeight="1">
@@ -10138,7 +10220,7 @@
       </c>
       <c r="D251" s="7"/>
       <c t="s" r="E251" s="7">
-        <v>414</v>
+        <v>419</v>
       </c>
       <c r="F251" s="7">
         <v>321</v>
@@ -10150,15 +10232,15 @@
         <v>113</v>
       </c>
       <c t="s" r="I251" s="7">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c t="s" r="J251" s="7">
-        <v>407</v>
+        <v>413</v>
       </c>
       <c r="K251" s="7"/>
       <c r="L251" s="7"/>
       <c t="s" r="M251" s="7">
-        <v>420</v>
+        <v>425</v>
       </c>
     </row>
     <row r="252" ht="14.25" customHeight="1">
@@ -10173,7 +10255,7 @@
       </c>
       <c r="D252" s="7"/>
       <c t="s" r="E252" s="7">
-        <v>414</v>
+        <v>419</v>
       </c>
       <c r="F252" s="7">
         <v>321</v>
@@ -10185,14 +10267,16 @@
         <v>50</v>
       </c>
       <c t="s" r="I252" s="7">
-        <v>392</v>
+        <v>398</v>
       </c>
       <c t="s" r="J252" s="7">
         <v>274</v>
       </c>
       <c r="K252" s="7"/>
       <c r="L252" s="7"/>
-      <c r="M252" s="7"/>
+      <c t="s" r="M252" s="7">
+        <v>426</v>
+      </c>
     </row>
     <row r="253" ht="14.25" customHeight="1">
       <c r="A253" s="6"/>
@@ -10221,7 +10305,7 @@
       </c>
       <c r="D254" s="7"/>
       <c t="s" r="E254" s="7">
-        <v>421</v>
+        <v>427</v>
       </c>
       <c r="F254" s="7">
         <v>321</v>
@@ -10230,18 +10314,18 @@
         <v>50</v>
       </c>
       <c t="s" r="H254" s="8">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c t="s" r="I254" s="7">
         <v>59</v>
       </c>
       <c t="s" r="J254" s="7">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="K254" s="7"/>
       <c r="L254" s="7"/>
       <c t="s" r="M254" s="7">
-        <v>422</v>
+        <v>428</v>
       </c>
     </row>
     <row r="255" ht="15" customHeight="1">
@@ -10256,19 +10340,19 @@
       </c>
       <c r="D255" s="7"/>
       <c t="s" r="E255" s="7">
-        <v>421</v>
+        <v>427</v>
       </c>
       <c r="F255" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G255" s="8">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c t="s" r="H255" s="8">
         <v>50</v>
       </c>
       <c t="s" r="I255" s="7">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c t="s" r="J255" s="7">
         <v>219</v>
@@ -10291,7 +10375,7 @@
       </c>
       <c r="D256" s="7"/>
       <c t="s" r="E256" s="7">
-        <v>421</v>
+        <v>427</v>
       </c>
       <c r="F256" s="7">
         <v>321</v>
@@ -10303,15 +10387,15 @@
         <v>39</v>
       </c>
       <c t="s" r="I256" s="7">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c t="s" r="J256" s="7">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="K256" s="7"/>
       <c r="L256" s="7"/>
       <c t="s" r="M256" s="7">
-        <v>423</v>
+        <v>429</v>
       </c>
     </row>
     <row r="257" ht="14.25" customHeight="1">
@@ -10326,7 +10410,7 @@
       </c>
       <c r="D257" s="7"/>
       <c t="s" r="E257" s="7">
-        <v>421</v>
+        <v>427</v>
       </c>
       <c r="F257" s="7">
         <v>321</v>
@@ -10341,7 +10425,7 @@
         <v>221</v>
       </c>
       <c t="s" r="J257" s="7">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="K257" s="7"/>
       <c r="L257" s="7"/>
@@ -10361,7 +10445,7 @@
       </c>
       <c r="D258" s="7"/>
       <c t="s" r="E258" s="7">
-        <v>421</v>
+        <v>427</v>
       </c>
       <c r="F258" s="7">
         <v>321</v>
@@ -10373,10 +10457,10 @@
         <v>33</v>
       </c>
       <c t="s" r="I258" s="7">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c t="s" r="J258" s="7">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="K258" s="7"/>
       <c r="L258" s="7"/>
@@ -10396,7 +10480,7 @@
       </c>
       <c r="D259" s="7"/>
       <c t="s" r="E259" s="7">
-        <v>421</v>
+        <v>427</v>
       </c>
       <c r="F259" s="7">
         <v>321</v>
@@ -10408,15 +10492,15 @@
         <v>50</v>
       </c>
       <c t="s" r="I259" s="7">
-        <v>425</v>
+        <v>431</v>
       </c>
       <c t="s" r="J259" s="7">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="K259" s="7"/>
       <c r="L259" s="7"/>
       <c t="s" r="M259" s="7">
-        <v>426</v>
+        <v>432</v>
       </c>
     </row>
     <row r="260" ht="15" customHeight="1">
@@ -10431,7 +10515,7 @@
       </c>
       <c r="D260" s="7"/>
       <c t="s" r="E260" s="7">
-        <v>421</v>
+        <v>427</v>
       </c>
       <c r="F260" s="7">
         <v>321</v>
@@ -10443,14 +10527,16 @@
         <v>57</v>
       </c>
       <c t="s" r="I260" s="7">
-        <v>393</v>
+        <v>399</v>
       </c>
       <c t="s" r="J260" s="7">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="K260" s="7"/>
       <c r="L260" s="7"/>
-      <c r="M260" s="7"/>
+      <c t="s" r="M260" s="7">
+        <v>433</v>
+      </c>
     </row>
     <row r="261" ht="14.25" customHeight="1">
       <c t="s" r="A261" s="6">
@@ -10464,7 +10550,7 @@
       </c>
       <c r="D261" s="7"/>
       <c t="s" r="E261" s="7">
-        <v>421</v>
+        <v>427</v>
       </c>
       <c r="F261" s="7">
         <v>321</v>
@@ -10479,7 +10565,7 @@
         <v>196</v>
       </c>
       <c t="s" r="J261" s="7">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K261" s="7"/>
       <c r="L261" s="7"/>
@@ -10512,7 +10598,7 @@
       </c>
       <c r="D263" s="7"/>
       <c t="s" r="E263" s="7">
-        <v>427</v>
+        <v>434</v>
       </c>
       <c r="F263" s="7">
         <v>321</v>
@@ -10521,7 +10607,7 @@
         <v>46</v>
       </c>
       <c t="s" r="H263" s="8">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c t="s" r="I263" s="7">
         <v>34</v>
@@ -10532,7 +10618,7 @@
       <c r="K263" s="7"/>
       <c r="L263" s="7"/>
       <c t="s" r="M263" s="7">
-        <v>428</v>
+        <v>435</v>
       </c>
     </row>
     <row r="264" ht="14.25" customHeight="1">
@@ -10547,27 +10633,27 @@
       </c>
       <c r="D264" s="7"/>
       <c t="s" r="E264" s="7">
-        <v>427</v>
+        <v>434</v>
       </c>
       <c r="F264" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G264" s="8">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c t="s" r="H264" s="8">
         <v>33</v>
       </c>
       <c t="s" r="I264" s="7">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c t="s" r="J264" s="7">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="K264" s="7"/>
       <c r="L264" s="7"/>
       <c t="s" r="M264" s="7">
-        <v>429</v>
+        <v>436</v>
       </c>
     </row>
     <row r="265" ht="15" customHeight="1">
@@ -10582,7 +10668,7 @@
       </c>
       <c r="D265" s="7"/>
       <c t="s" r="E265" s="7">
-        <v>427</v>
+        <v>434</v>
       </c>
       <c r="F265" s="7">
         <v>321</v>
@@ -10591,10 +10677,10 @@
         <v>33</v>
       </c>
       <c t="s" r="H265" s="8">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c t="s" r="I265" s="7">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c t="s" r="J265" s="7">
         <v>73</v>
@@ -10602,7 +10688,7 @@
       <c r="K265" s="7"/>
       <c r="L265" s="7"/>
       <c t="s" r="M265" s="7">
-        <v>430</v>
+        <v>437</v>
       </c>
     </row>
     <row r="266" ht="14.25" customHeight="1">
@@ -10617,27 +10703,27 @@
       </c>
       <c r="D266" s="7"/>
       <c t="s" r="E266" s="7">
-        <v>427</v>
+        <v>434</v>
       </c>
       <c r="F266" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G266" s="8">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c t="s" r="H266" s="8">
         <v>101</v>
       </c>
       <c t="s" r="I266" s="7">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c t="s" r="J266" s="7">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="K266" s="7"/>
       <c r="L266" s="7"/>
       <c t="s" r="M266" s="7">
-        <v>431</v>
+        <v>438</v>
       </c>
     </row>
     <row r="267" ht="14.25" customHeight="1">
@@ -10652,7 +10738,7 @@
       </c>
       <c r="D267" s="7"/>
       <c t="s" r="E267" s="7">
-        <v>427</v>
+        <v>434</v>
       </c>
       <c r="F267" s="7">
         <v>321</v>
@@ -10661,18 +10747,18 @@
         <v>101</v>
       </c>
       <c t="s" r="H267" s="8">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c t="s" r="I267" s="7">
-        <v>425</v>
+        <v>431</v>
       </c>
       <c t="s" r="J267" s="7">
-        <v>393</v>
+        <v>399</v>
       </c>
       <c r="K267" s="7"/>
       <c r="L267" s="7"/>
       <c t="s" r="M267" s="7">
-        <v>432</v>
+        <v>439</v>
       </c>
     </row>
     <row r="268" ht="14.25" customHeight="1">
@@ -10687,22 +10773,22 @@
       </c>
       <c r="D268" s="7"/>
       <c t="s" r="E268" s="7">
-        <v>427</v>
+        <v>434</v>
       </c>
       <c r="F268" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G268" s="8">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c t="s" r="H268" s="8">
         <v>46</v>
       </c>
       <c t="s" r="I268" s="7">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c t="s" r="J268" s="7">
-        <v>433</v>
+        <v>440</v>
       </c>
       <c r="K268" s="7"/>
       <c r="L268" s="7"/>
@@ -10735,7 +10821,7 @@
       </c>
       <c r="D270" s="7"/>
       <c t="s" r="E270" s="7">
-        <v>434</v>
+        <v>441</v>
       </c>
       <c r="F270" s="7">
         <v>321</v>
@@ -10747,7 +10833,7 @@
         <v>57</v>
       </c>
       <c t="s" r="I270" s="7">
-        <v>435</v>
+        <v>442</v>
       </c>
       <c t="s" r="J270" s="7">
         <v>111</v>
@@ -10755,7 +10841,7 @@
       <c r="K270" s="7"/>
       <c r="L270" s="7"/>
       <c t="s" r="M270" s="7">
-        <v>436</v>
+        <v>443</v>
       </c>
     </row>
     <row r="271" ht="14.25" customHeight="1">
@@ -10770,7 +10856,7 @@
       </c>
       <c r="D271" s="7"/>
       <c t="s" r="E271" s="7">
-        <v>434</v>
+        <v>441</v>
       </c>
       <c r="F271" s="7">
         <v>321</v>
@@ -10790,7 +10876,7 @@
       <c r="K271" s="7"/>
       <c r="L271" s="7"/>
       <c t="s" r="M271" s="7">
-        <v>437</v>
+        <v>444</v>
       </c>
     </row>
     <row r="272" ht="14.25" customHeight="1">
@@ -10805,7 +10891,7 @@
       </c>
       <c r="D272" s="7"/>
       <c t="s" r="E272" s="7">
-        <v>434</v>
+        <v>441</v>
       </c>
       <c r="F272" s="7">
         <v>321</v>
@@ -10840,7 +10926,7 @@
       </c>
       <c r="D273" s="7"/>
       <c t="s" r="E273" s="7">
-        <v>434</v>
+        <v>441</v>
       </c>
       <c r="F273" s="7">
         <v>321</v>
@@ -10858,11 +10944,11 @@
         <v>51</v>
       </c>
       <c t="s" r="K273" s="7">
-        <v>438</v>
+        <v>445</v>
       </c>
       <c r="L273" s="7"/>
       <c t="s" r="M273" s="7">
-        <v>439</v>
+        <v>446</v>
       </c>
     </row>
     <row r="274" ht="14.25" customHeight="1">
@@ -10877,7 +10963,7 @@
       </c>
       <c r="D274" s="7"/>
       <c t="s" r="E274" s="7">
-        <v>434</v>
+        <v>441</v>
       </c>
       <c r="F274" s="7">
         <v>321</v>
@@ -10889,7 +10975,7 @@
         <v>57</v>
       </c>
       <c t="s" r="I274" s="7">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c t="s" r="J274" s="7">
         <v>266</v>
@@ -10897,7 +10983,7 @@
       <c r="K274" s="7"/>
       <c r="L274" s="7"/>
       <c t="s" r="M274" s="7">
-        <v>440</v>
+        <v>447</v>
       </c>
     </row>
     <row r="275" ht="15" customHeight="1">
@@ -10912,7 +10998,7 @@
       </c>
       <c r="D275" s="7"/>
       <c t="s" r="E275" s="7">
-        <v>434</v>
+        <v>441</v>
       </c>
       <c r="F275" s="7">
         <v>321</v>
@@ -10947,7 +11033,7 @@
       </c>
       <c r="D276" s="7"/>
       <c t="s" r="E276" s="7">
-        <v>434</v>
+        <v>441</v>
       </c>
       <c r="F276" s="7">
         <v>321</v>
@@ -10967,7 +11053,7 @@
       <c r="K276" s="7"/>
       <c r="L276" s="7"/>
       <c t="s" r="M276" s="7">
-        <v>441</v>
+        <v>448</v>
       </c>
     </row>
     <row r="277" ht="14.25" customHeight="1">
@@ -10982,7 +11068,7 @@
       </c>
       <c r="D277" s="7"/>
       <c t="s" r="E277" s="7">
-        <v>434</v>
+        <v>441</v>
       </c>
       <c r="F277" s="7">
         <v>321</v>
@@ -10997,11 +11083,13 @@
         <v>226</v>
       </c>
       <c t="s" r="J277" s="7">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="K277" s="7"/>
       <c r="L277" s="7"/>
-      <c r="M277" s="7"/>
+      <c t="s" r="M277" s="7">
+        <v>449</v>
+      </c>
     </row>
     <row r="278" ht="14.25" customHeight="1">
       <c r="A278" s="6"/>
@@ -11030,7 +11118,7 @@
       </c>
       <c r="D279" s="7"/>
       <c t="s" r="E279" s="7">
-        <v>442</v>
+        <v>450</v>
       </c>
       <c r="F279" s="7">
         <v>321</v>
@@ -11039,13 +11127,13 @@
         <v>50</v>
       </c>
       <c t="s" r="H279" s="8">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c t="s" r="I279" s="7">
         <v>233</v>
       </c>
       <c t="s" r="J279" s="7">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="K279" s="7"/>
       <c r="L279" s="7"/>
@@ -11065,19 +11153,19 @@
       </c>
       <c r="D280" s="7"/>
       <c t="s" r="E280" s="7">
-        <v>442</v>
+        <v>450</v>
       </c>
       <c r="F280" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G280" s="8">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c t="s" r="H280" s="8">
         <v>50</v>
       </c>
       <c t="s" r="I280" s="7">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c t="s" r="J280" s="7">
         <v>267</v>
@@ -11100,7 +11188,7 @@
       </c>
       <c r="D281" s="7"/>
       <c t="s" r="E281" s="7">
-        <v>442</v>
+        <v>450</v>
       </c>
       <c r="F281" s="7">
         <v>321</v>
@@ -11109,18 +11197,18 @@
         <v>50</v>
       </c>
       <c t="s" r="H281" s="8">
-        <v>443</v>
+        <v>451</v>
       </c>
       <c t="s" r="I281" s="7">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c t="s" r="J281" s="7">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="K281" s="7"/>
       <c r="L281" s="7"/>
       <c t="s" r="M281" s="7">
-        <v>444</v>
+        <v>452</v>
       </c>
     </row>
     <row r="282" ht="14.25" customHeight="1">
@@ -11135,22 +11223,22 @@
       </c>
       <c r="D282" s="7"/>
       <c t="s" r="E282" s="7">
-        <v>442</v>
+        <v>450</v>
       </c>
       <c r="F282" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G282" s="8">
-        <v>443</v>
+        <v>451</v>
       </c>
       <c t="s" r="H282" s="8">
         <v>50</v>
       </c>
       <c t="s" r="I282" s="7">
-        <v>445</v>
+        <v>453</v>
       </c>
       <c t="s" r="J282" s="7">
-        <v>446</v>
+        <v>454</v>
       </c>
       <c r="K282" s="7"/>
       <c r="L282" s="7"/>
@@ -11183,7 +11271,7 @@
       </c>
       <c r="D284" s="7"/>
       <c t="s" r="E284" s="7">
-        <v>447</v>
+        <v>455</v>
       </c>
       <c r="F284" s="7">
         <v>321</v>
@@ -11195,7 +11283,7 @@
         <v>57</v>
       </c>
       <c t="s" r="I284" s="7">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c t="s" r="J284" s="7">
         <v>245</v>
@@ -11218,7 +11306,7 @@
       </c>
       <c r="D285" s="7"/>
       <c t="s" r="E285" s="7">
-        <v>447</v>
+        <v>455</v>
       </c>
       <c r="F285" s="7">
         <v>321</v>
@@ -11230,15 +11318,15 @@
         <v>17</v>
       </c>
       <c t="s" r="I285" s="7">
-        <v>448</v>
+        <v>456</v>
       </c>
       <c t="s" r="J285" s="7">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="K285" s="7"/>
       <c r="L285" s="7"/>
       <c t="s" r="M285" s="7">
-        <v>449</v>
+        <v>457</v>
       </c>
     </row>
     <row r="286" ht="14.25" customHeight="1">
@@ -11253,7 +11341,7 @@
       </c>
       <c r="D286" s="7"/>
       <c t="s" r="E286" s="7">
-        <v>447</v>
+        <v>455</v>
       </c>
       <c r="F286" s="7">
         <v>321</v>
@@ -11262,18 +11350,18 @@
         <v>17</v>
       </c>
       <c t="s" r="H286" s="8">
-        <v>416</v>
+        <v>421</v>
       </c>
       <c t="s" r="I286" s="7">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c t="s" r="J286" s="7">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="K286" s="7"/>
       <c r="L286" s="7"/>
       <c t="s" r="M286" s="7">
-        <v>450</v>
+        <v>458</v>
       </c>
     </row>
     <row r="287" ht="14.25" customHeight="1">
@@ -11288,27 +11376,27 @@
       </c>
       <c r="D287" s="7"/>
       <c t="s" r="E287" s="7">
-        <v>447</v>
+        <v>455</v>
       </c>
       <c r="F287" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G287" s="8">
-        <v>416</v>
+        <v>421</v>
       </c>
       <c t="s" r="H287" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I287" s="7">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c t="s" r="J287" s="7">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="K287" s="7"/>
       <c r="L287" s="7"/>
       <c t="s" r="M287" s="7">
-        <v>451</v>
+        <v>459</v>
       </c>
     </row>
     <row r="288" ht="14.25" customHeight="1">
@@ -11323,7 +11411,7 @@
       </c>
       <c r="D288" s="7"/>
       <c t="s" r="E288" s="7">
-        <v>447</v>
+        <v>455</v>
       </c>
       <c r="F288" s="7">
         <v>321</v>
@@ -11332,18 +11420,18 @@
         <v>17</v>
       </c>
       <c t="s" r="H288" s="8">
-        <v>452</v>
+        <v>460</v>
       </c>
       <c t="s" r="I288" s="7">
         <v>115</v>
       </c>
       <c t="s" r="J288" s="7">
-        <v>405</v>
+        <v>411</v>
       </c>
       <c r="K288" s="7"/>
       <c r="L288" s="7"/>
       <c t="s" r="M288" s="7">
-        <v>378</v>
+        <v>384</v>
       </c>
     </row>
     <row r="289" ht="14.25" customHeight="1">
@@ -11358,13 +11446,13 @@
       </c>
       <c r="D289" s="7"/>
       <c t="s" r="E289" s="7">
-        <v>447</v>
+        <v>455</v>
       </c>
       <c r="F289" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G289" s="8">
-        <v>452</v>
+        <v>460</v>
       </c>
       <c t="s" r="H289" s="8">
         <v>17</v>
@@ -11378,7 +11466,7 @@
       <c r="K289" s="7"/>
       <c r="L289" s="7"/>
       <c t="s" r="M289" s="7">
-        <v>453</v>
+        <v>461</v>
       </c>
     </row>
     <row r="290" ht="15" customHeight="1">
@@ -11393,7 +11481,7 @@
       </c>
       <c r="D290" s="7"/>
       <c t="s" r="E290" s="7">
-        <v>447</v>
+        <v>455</v>
       </c>
       <c r="F290" s="7">
         <v>321</v>
@@ -11408,12 +11496,12 @@
         <v>44</v>
       </c>
       <c t="s" r="J290" s="7">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="K290" s="7"/>
       <c r="L290" s="7"/>
       <c t="s" r="M290" s="7">
-        <v>454</v>
+        <v>462</v>
       </c>
     </row>
     <row r="291" ht="14.25" customHeight="1">
@@ -11428,7 +11516,7 @@
       </c>
       <c r="D291" s="7"/>
       <c t="s" r="E291" s="7">
-        <v>447</v>
+        <v>455</v>
       </c>
       <c r="F291" s="7">
         <v>321</v>
@@ -11440,10 +11528,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I291" s="7">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c t="s" r="J291" s="7">
-        <v>455</v>
+        <v>463</v>
       </c>
       <c r="K291" s="7"/>
       <c r="L291" s="7"/>
@@ -11476,7 +11564,7 @@
       </c>
       <c r="D293" s="7"/>
       <c t="s" r="E293" s="7">
-        <v>456</v>
+        <v>464</v>
       </c>
       <c r="F293" s="7">
         <v>321</v>
@@ -11488,7 +11576,7 @@
         <v>119</v>
       </c>
       <c t="s" r="I293" s="7">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c t="s" r="J293" s="7">
         <v>88</v>
@@ -11496,7 +11584,7 @@
       <c r="K293" s="7"/>
       <c r="L293" s="7"/>
       <c t="s" r="M293" s="7">
-        <v>457</v>
+        <v>465</v>
       </c>
     </row>
     <row r="294" ht="14.25" customHeight="1">
@@ -11511,7 +11599,7 @@
       </c>
       <c r="D294" s="7"/>
       <c t="s" r="E294" s="7">
-        <v>456</v>
+        <v>464</v>
       </c>
       <c r="F294" s="7">
         <v>321</v>
@@ -11523,7 +11611,7 @@
         <v>50</v>
       </c>
       <c t="s" r="I294" s="7">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c t="s" r="J294" s="7">
         <v>67</v>
@@ -11531,7 +11619,7 @@
       <c r="K294" s="7"/>
       <c r="L294" s="7"/>
       <c t="s" r="M294" s="7">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="295" ht="15" customHeight="1">
@@ -11561,7 +11649,7 @@
       </c>
       <c r="D296" s="7"/>
       <c t="s" r="E296" s="7">
-        <v>458</v>
+        <v>466</v>
       </c>
       <c r="F296" s="7">
         <v>320</v>
@@ -11570,18 +11658,18 @@
         <v>50</v>
       </c>
       <c t="s" r="H296" s="8">
-        <v>452</v>
+        <v>460</v>
       </c>
       <c t="s" r="I296" s="7">
-        <v>448</v>
+        <v>456</v>
       </c>
       <c t="s" r="J296" s="7">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="K296" s="7"/>
       <c r="L296" s="7"/>
       <c t="s" r="M296" s="7">
-        <v>459</v>
+        <v>467</v>
       </c>
     </row>
     <row r="297" ht="14.25" customHeight="1">
@@ -11596,13 +11684,13 @@
       </c>
       <c r="D297" s="7"/>
       <c t="s" r="E297" s="7">
-        <v>458</v>
+        <v>466</v>
       </c>
       <c r="F297" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G297" s="8">
-        <v>452</v>
+        <v>460</v>
       </c>
       <c t="s" r="H297" s="8">
         <v>50</v>
@@ -11616,7 +11704,7 @@
       <c r="K297" s="7"/>
       <c r="L297" s="7"/>
       <c t="s" r="M297" s="7">
-        <v>460</v>
+        <v>468</v>
       </c>
     </row>
     <row r="298" ht="14.25" customHeight="1">
@@ -11631,7 +11719,7 @@
       </c>
       <c r="D298" s="7"/>
       <c t="s" r="E298" s="7">
-        <v>458</v>
+        <v>466</v>
       </c>
       <c r="F298" s="7">
         <v>320</v>
@@ -11643,15 +11731,15 @@
         <v>113</v>
       </c>
       <c t="s" r="I298" s="7">
-        <v>438</v>
+        <v>445</v>
       </c>
       <c t="s" r="J298" s="7">
-        <v>461</v>
+        <v>469</v>
       </c>
       <c r="K298" s="7"/>
       <c r="L298" s="7"/>
       <c t="s" r="M298" s="7">
-        <v>462</v>
+        <v>470</v>
       </c>
     </row>
     <row r="299" ht="14.25" customHeight="1">
@@ -11666,7 +11754,7 @@
       </c>
       <c r="D299" s="7"/>
       <c t="s" r="E299" s="7">
-        <v>458</v>
+        <v>466</v>
       </c>
       <c r="F299" s="7">
         <v>320</v>
@@ -11678,7 +11766,7 @@
         <v>50</v>
       </c>
       <c t="s" r="I299" s="7">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c t="s" r="J299" s="7">
         <v>237</v>
@@ -11686,7 +11774,7 @@
       <c r="K299" s="7"/>
       <c r="L299" s="7"/>
       <c t="s" r="M299" s="7">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="300" ht="15" customHeight="1">
@@ -11701,7 +11789,7 @@
       </c>
       <c r="D300" s="7"/>
       <c t="s" r="E300" s="7">
-        <v>458</v>
+        <v>466</v>
       </c>
       <c r="F300" s="7">
         <v>320</v>
@@ -11710,10 +11798,10 @@
         <v>50</v>
       </c>
       <c t="s" r="H300" s="8">
-        <v>463</v>
+        <v>471</v>
       </c>
       <c t="s" r="I300" s="7">
-        <v>370</v>
+        <v>376</v>
       </c>
       <c t="s" r="J300" s="7">
         <v>215</v>
@@ -11736,22 +11824,22 @@
       </c>
       <c r="D301" s="7"/>
       <c t="s" r="E301" s="7">
-        <v>458</v>
+        <v>466</v>
       </c>
       <c r="F301" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G301" s="8">
-        <v>463</v>
+        <v>471</v>
       </c>
       <c t="s" r="H301" s="8">
         <v>50</v>
       </c>
       <c t="s" r="I301" s="7">
-        <v>373</v>
+        <v>379</v>
       </c>
       <c t="s" r="J301" s="7">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="K301" s="7"/>
       <c r="L301" s="7"/>
@@ -11784,7 +11872,7 @@
       </c>
       <c r="D303" s="7"/>
       <c t="s" r="E303" s="7">
-        <v>464</v>
+        <v>472</v>
       </c>
       <c r="F303" s="7">
         <v>321</v>
@@ -11793,18 +11881,18 @@
         <v>50</v>
       </c>
       <c t="s" r="H303" s="8">
-        <v>366</v>
+        <v>372</v>
       </c>
       <c t="s" r="I303" s="7">
         <v>18</v>
       </c>
       <c t="s" r="J303" s="7">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="K303" s="7"/>
       <c r="L303" s="7"/>
       <c t="s" r="M303" s="7">
-        <v>465</v>
+        <v>473</v>
       </c>
     </row>
     <row r="304" ht="14.25" customHeight="1">
@@ -11819,13 +11907,13 @@
       </c>
       <c r="D304" s="7"/>
       <c t="s" r="E304" s="7">
-        <v>464</v>
+        <v>472</v>
       </c>
       <c r="F304" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G304" s="8">
-        <v>366</v>
+        <v>372</v>
       </c>
       <c t="s" r="H304" s="8">
         <v>50</v>
@@ -11854,7 +11942,7 @@
       </c>
       <c r="D305" s="7"/>
       <c t="s" r="E305" s="7">
-        <v>464</v>
+        <v>472</v>
       </c>
       <c r="F305" s="7">
         <v>321</v>
@@ -11866,7 +11954,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I305" s="7">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c t="s" r="J305" s="7">
         <v>105</v>
@@ -11876,7 +11964,7 @@
       </c>
       <c r="L305" s="7"/>
       <c t="s" r="M305" s="7">
-        <v>466</v>
+        <v>474</v>
       </c>
     </row>
     <row r="306" ht="14.25" customHeight="1">
@@ -11891,7 +11979,7 @@
       </c>
       <c r="D306" s="7"/>
       <c t="s" r="E306" s="7">
-        <v>464</v>
+        <v>472</v>
       </c>
       <c r="F306" s="7">
         <v>321</v>
@@ -11909,11 +11997,11 @@
         <v>25</v>
       </c>
       <c t="s" r="K306" s="7">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="L306" s="7"/>
       <c t="s" r="M306" s="7">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="307" ht="14.25" customHeight="1">
@@ -11943,13 +12031,13 @@
       </c>
       <c r="D308" s="7"/>
       <c t="s" r="E308" s="7">
-        <v>467</v>
+        <v>475</v>
       </c>
       <c r="F308" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G308" s="8">
-        <v>468</v>
+        <v>476</v>
       </c>
       <c t="s" r="H308" s="8">
         <v>50</v>
@@ -11963,7 +12051,7 @@
       <c r="K308" s="7"/>
       <c r="L308" s="7"/>
       <c t="s" r="M308" s="7">
-        <v>469</v>
+        <v>477</v>
       </c>
     </row>
     <row r="309" ht="14.25" customHeight="1">
@@ -11978,7 +12066,7 @@
       </c>
       <c r="D309" s="7"/>
       <c t="s" r="E309" s="7">
-        <v>467</v>
+        <v>475</v>
       </c>
       <c r="F309" s="7">
         <v>321</v>
@@ -11993,12 +12081,12 @@
         <v>212</v>
       </c>
       <c t="s" r="J309" s="7">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="K309" s="7"/>
       <c r="L309" s="7"/>
       <c t="s" r="M309" s="7">
-        <v>470</v>
+        <v>478</v>
       </c>
     </row>
     <row r="310" ht="15" customHeight="1">
@@ -12013,7 +12101,7 @@
       </c>
       <c r="D310" s="7"/>
       <c t="s" r="E310" s="7">
-        <v>467</v>
+        <v>475</v>
       </c>
       <c r="F310" s="7">
         <v>321</v>
@@ -12028,11 +12116,13 @@
         <v>285</v>
       </c>
       <c t="s" r="J310" s="7">
-        <v>471</v>
+        <v>479</v>
       </c>
       <c r="K310" s="7"/>
       <c r="L310" s="7"/>
-      <c r="M310" s="7"/>
+      <c t="s" r="M310" s="7">
+        <v>480</v>
+      </c>
     </row>
     <row r="311" ht="14.25" customHeight="1">
       <c t="s" r="A311" s="6">
@@ -12046,7 +12136,7 @@
       </c>
       <c r="D311" s="7"/>
       <c t="s" r="E311" s="7">
-        <v>467</v>
+        <v>475</v>
       </c>
       <c r="F311" s="7">
         <v>321</v>
@@ -12058,7 +12148,7 @@
         <v>243</v>
       </c>
       <c t="s" r="I311" s="7">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c t="s" r="J311" s="7">
         <v>62</v>
@@ -12094,26 +12184,28 @@
       </c>
       <c r="D313" s="7"/>
       <c t="s" r="E313" s="7">
-        <v>472</v>
+        <v>481</v>
       </c>
       <c r="F313" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G313" s="8">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c t="s" r="H313" s="8">
         <v>57</v>
       </c>
       <c t="s" r="I313" s="7">
-        <v>407</v>
+        <v>413</v>
       </c>
       <c t="s" r="J313" s="7">
-        <v>473</v>
+        <v>482</v>
       </c>
       <c r="K313" s="7"/>
       <c r="L313" s="7"/>
-      <c r="M313" s="7"/>
+      <c t="s" r="M313" s="7">
+        <v>108</v>
+      </c>
     </row>
     <row r="314" ht="14.25" customHeight="1">
       <c r="A314" s="6"/>
@@ -12142,7 +12234,7 @@
       </c>
       <c r="D315" s="7"/>
       <c t="s" r="E315" s="7">
-        <v>474</v>
+        <v>483</v>
       </c>
       <c r="F315" s="7">
         <v>320</v>
@@ -12154,7 +12246,7 @@
         <v>39</v>
       </c>
       <c t="s" r="I315" s="7">
-        <v>475</v>
+        <v>484</v>
       </c>
       <c t="s" r="J315" s="7">
         <v>250</v>
@@ -12162,7 +12254,7 @@
       <c r="K315" s="7"/>
       <c r="L315" s="7"/>
       <c t="s" r="M315" s="7">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="316" ht="14.25" customHeight="1">
@@ -12177,7 +12269,7 @@
       </c>
       <c r="D316" s="7"/>
       <c t="s" r="E316" s="7">
-        <v>474</v>
+        <v>483</v>
       </c>
       <c r="F316" s="7">
         <v>320</v>
@@ -12189,15 +12281,15 @@
         <v>50</v>
       </c>
       <c t="s" r="I316" s="7">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c t="s" r="J316" s="7">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="K316" s="7"/>
       <c r="L316" s="7"/>
       <c t="s" r="M316" s="7">
-        <v>476</v>
+        <v>485</v>
       </c>
     </row>
     <row r="317" ht="14.25" customHeight="1">
@@ -12212,7 +12304,7 @@
       </c>
       <c r="D317" s="7"/>
       <c t="s" r="E317" s="7">
-        <v>474</v>
+        <v>483</v>
       </c>
       <c r="F317" s="7">
         <v>320</v>
@@ -12224,7 +12316,7 @@
         <v>39</v>
       </c>
       <c t="s" r="I317" s="7">
-        <v>405</v>
+        <v>411</v>
       </c>
       <c t="s" r="J317" s="7">
         <v>43</v>
@@ -12232,7 +12324,7 @@
       <c r="K317" s="7"/>
       <c r="L317" s="7"/>
       <c t="s" r="M317" s="7">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="318" ht="14.25" customHeight="1">
@@ -12247,7 +12339,7 @@
       </c>
       <c r="D318" s="7"/>
       <c t="s" r="E318" s="7">
-        <v>474</v>
+        <v>483</v>
       </c>
       <c r="F318" s="7">
         <v>320</v>
@@ -12266,7 +12358,9 @@
       </c>
       <c r="K318" s="7"/>
       <c r="L318" s="7"/>
-      <c r="M318" s="7"/>
+      <c t="s" r="M318" s="7">
+        <v>486</v>
+      </c>
     </row>
     <row r="319" ht="14.25" customHeight="1">
       <c r="A319" s="6"/>
@@ -12295,7 +12389,7 @@
       </c>
       <c r="D320" s="7"/>
       <c t="s" r="E320" s="7">
-        <v>477</v>
+        <v>487</v>
       </c>
       <c r="F320" s="7">
         <v>320</v>
@@ -12304,18 +12398,18 @@
         <v>17</v>
       </c>
       <c t="s" r="H320" s="8">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c t="s" r="I320" s="7">
         <v>97</v>
       </c>
       <c t="s" r="J320" s="7">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="K320" s="7"/>
       <c r="L320" s="7"/>
       <c t="s" r="M320" s="7">
-        <v>478</v>
+        <v>488</v>
       </c>
     </row>
     <row r="321" ht="14.25" customHeight="1">
@@ -12330,13 +12424,13 @@
       </c>
       <c r="D321" s="7"/>
       <c t="s" r="E321" s="7">
-        <v>477</v>
+        <v>487</v>
       </c>
       <c r="F321" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G321" s="8">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c t="s" r="H321" s="8">
         <v>17</v>
@@ -12345,12 +12439,12 @@
         <v>19</v>
       </c>
       <c t="s" r="J321" s="7">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="K321" s="7"/>
       <c r="L321" s="7"/>
       <c t="s" r="M321" s="7">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="322" ht="14.25" customHeight="1">
@@ -12365,7 +12459,7 @@
       </c>
       <c r="D322" s="7"/>
       <c t="s" r="E322" s="7">
-        <v>477</v>
+        <v>487</v>
       </c>
       <c r="F322" s="7">
         <v>320</v>
@@ -12385,7 +12479,7 @@
       <c r="K322" s="7"/>
       <c r="L322" s="7"/>
       <c t="s" r="M322" s="7">
-        <v>479</v>
+        <v>489</v>
       </c>
     </row>
     <row r="323" ht="14.25" customHeight="1">
@@ -12400,7 +12494,7 @@
       </c>
       <c r="D323" s="7"/>
       <c t="s" r="E323" s="7">
-        <v>477</v>
+        <v>487</v>
       </c>
       <c r="F323" s="7">
         <v>320</v>
@@ -12415,12 +12509,12 @@
         <v>94</v>
       </c>
       <c t="s" r="J323" s="7">
-        <v>425</v>
+        <v>431</v>
       </c>
       <c r="K323" s="7"/>
       <c r="L323" s="7"/>
       <c t="s" r="M323" s="7">
-        <v>480</v>
+        <v>490</v>
       </c>
     </row>
     <row r="324" ht="14.25" customHeight="1">
@@ -12435,7 +12529,7 @@
       </c>
       <c r="D324" s="7"/>
       <c t="s" r="E324" s="7">
-        <v>477</v>
+        <v>487</v>
       </c>
       <c r="F324" s="7">
         <v>320</v>
@@ -12444,18 +12538,18 @@
         <v>17</v>
       </c>
       <c t="s" r="H324" s="8">
-        <v>463</v>
+        <v>471</v>
       </c>
       <c t="s" r="I324" s="7">
         <v>301</v>
       </c>
       <c t="s" r="J324" s="7">
-        <v>481</v>
+        <v>491</v>
       </c>
       <c r="K324" s="7"/>
       <c r="L324" s="7"/>
       <c t="s" r="M324" s="7">
-        <v>482</v>
+        <v>492</v>
       </c>
     </row>
     <row r="325" ht="15" customHeight="1">
@@ -12470,13 +12564,13 @@
       </c>
       <c r="D325" s="7"/>
       <c t="s" r="E325" s="7">
-        <v>477</v>
+        <v>487</v>
       </c>
       <c r="F325" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G325" s="8">
-        <v>463</v>
+        <v>471</v>
       </c>
       <c t="s" r="H325" s="8">
         <v>17</v>
@@ -12485,7 +12579,7 @@
         <v>244</v>
       </c>
       <c t="s" r="J325" s="7">
-        <v>483</v>
+        <v>493</v>
       </c>
       <c r="K325" s="7"/>
       <c r="L325" s="7"/>
@@ -12518,7 +12612,7 @@
       </c>
       <c r="D327" s="7"/>
       <c t="s" r="E327" s="7">
-        <v>484</v>
+        <v>494</v>
       </c>
       <c r="F327" s="7">
         <v>321</v>
@@ -12527,7 +12621,7 @@
         <v>50</v>
       </c>
       <c t="s" r="H327" s="8">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c t="s" r="I327" s="7">
         <v>48</v>
@@ -12553,13 +12647,13 @@
       </c>
       <c r="D328" s="7"/>
       <c t="s" r="E328" s="7">
-        <v>484</v>
+        <v>494</v>
       </c>
       <c r="F328" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G328" s="8">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c t="s" r="H328" s="8">
         <v>50</v>
@@ -12573,7 +12667,7 @@
       <c r="K328" s="7"/>
       <c r="L328" s="7"/>
       <c t="s" r="M328" s="7">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="329" ht="14.25" customHeight="1">
@@ -12588,7 +12682,7 @@
       </c>
       <c r="D329" s="7"/>
       <c t="s" r="E329" s="7">
-        <v>484</v>
+        <v>494</v>
       </c>
       <c r="F329" s="7">
         <v>321</v>
@@ -12597,18 +12691,18 @@
         <v>50</v>
       </c>
       <c t="s" r="H329" s="8">
-        <v>485</v>
+        <v>495</v>
       </c>
       <c t="s" r="I329" s="7">
         <v>35</v>
       </c>
       <c t="s" r="J329" s="7">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="K329" s="7"/>
       <c r="L329" s="7"/>
       <c t="s" r="M329" s="7">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="330" ht="15" customHeight="1">
@@ -12623,13 +12717,13 @@
       </c>
       <c r="D330" s="7"/>
       <c t="s" r="E330" s="7">
-        <v>484</v>
+        <v>494</v>
       </c>
       <c r="F330" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G330" s="8">
-        <v>485</v>
+        <v>495</v>
       </c>
       <c t="s" r="H330" s="8">
         <v>50</v>
@@ -12638,12 +12732,12 @@
         <v>70</v>
       </c>
       <c t="s" r="J330" s="7">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="K330" s="7"/>
       <c r="L330" s="7"/>
       <c t="s" r="M330" s="7">
-        <v>486</v>
+        <v>496</v>
       </c>
     </row>
     <row r="331" ht="14.25" customHeight="1">
@@ -12673,7 +12767,7 @@
       </c>
       <c r="D332" s="7"/>
       <c t="s" r="E332" s="7">
-        <v>487</v>
+        <v>497</v>
       </c>
       <c r="F332" s="7">
         <v>320</v>
@@ -12693,7 +12787,7 @@
       <c r="K332" s="7"/>
       <c r="L332" s="7"/>
       <c t="s" r="M332" s="7">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="333" ht="14.25" customHeight="1">
@@ -12708,7 +12802,7 @@
       </c>
       <c r="D333" s="7"/>
       <c t="s" r="E333" s="7">
-        <v>487</v>
+        <v>497</v>
       </c>
       <c r="F333" s="7">
         <v>320</v>
@@ -12723,12 +12817,12 @@
         <v>283</v>
       </c>
       <c t="s" r="J333" s="7">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="K333" s="7"/>
       <c r="L333" s="7"/>
       <c t="s" r="M333" s="7">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="334" ht="14.25" customHeight="1">
@@ -12743,7 +12837,7 @@
       </c>
       <c r="D334" s="7"/>
       <c t="s" r="E334" s="7">
-        <v>487</v>
+        <v>497</v>
       </c>
       <c r="F334" s="7">
         <v>320</v>
@@ -12755,10 +12849,10 @@
         <v>33</v>
       </c>
       <c t="s" r="I334" s="7">
-        <v>438</v>
+        <v>445</v>
       </c>
       <c t="s" r="J334" s="7">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="K334" s="7"/>
       <c r="L334" s="7"/>
@@ -12778,7 +12872,7 @@
       </c>
       <c r="D335" s="7"/>
       <c t="s" r="E335" s="7">
-        <v>487</v>
+        <v>497</v>
       </c>
       <c r="F335" s="7">
         <v>320</v>
@@ -12793,12 +12887,12 @@
         <v>37</v>
       </c>
       <c t="s" r="J335" s="7">
-        <v>488</v>
+        <v>498</v>
       </c>
       <c r="K335" s="7"/>
       <c r="L335" s="7"/>
       <c t="s" r="M335" s="7">
-        <v>489</v>
+        <v>499</v>
       </c>
     </row>
     <row r="336" ht="14.25" customHeight="1">
@@ -12813,7 +12907,7 @@
       </c>
       <c r="D336" s="7"/>
       <c t="s" r="E336" s="7">
-        <v>487</v>
+        <v>497</v>
       </c>
       <c r="F336" s="7">
         <v>320</v>
@@ -12828,7 +12922,7 @@
         <v>286</v>
       </c>
       <c t="s" r="J336" s="7">
-        <v>490</v>
+        <v>500</v>
       </c>
       <c r="K336" s="7"/>
       <c r="L336" s="7"/>
@@ -12848,7 +12942,7 @@
       </c>
       <c r="D337" s="7"/>
       <c t="s" r="E337" s="7">
-        <v>487</v>
+        <v>497</v>
       </c>
       <c r="F337" s="7">
         <v>320</v>
@@ -12863,11 +12957,13 @@
         <v>108</v>
       </c>
       <c t="s" r="J337" s="7">
-        <v>481</v>
+        <v>491</v>
       </c>
       <c r="K337" s="7"/>
       <c r="L337" s="7"/>
-      <c r="M337" s="7"/>
+      <c t="s" r="M337" s="7">
+        <v>501</v>
+      </c>
     </row>
     <row r="338" ht="14.25" customHeight="1">
       <c t="s" r="A338" s="6">
@@ -12881,7 +12977,7 @@
       </c>
       <c r="D338" s="7"/>
       <c t="s" r="E338" s="7">
-        <v>487</v>
+        <v>497</v>
       </c>
       <c r="F338" s="7">
         <v>320</v>
@@ -12890,10 +12986,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H338" s="8">
-        <v>491</v>
+        <v>502</v>
       </c>
       <c t="s" r="I338" s="7">
-        <v>492</v>
+        <v>503</v>
       </c>
       <c t="s" r="J338" s="7">
         <v>18</v>
@@ -12929,7 +13025,7 @@
       </c>
       <c r="D340" s="7"/>
       <c t="s" r="E340" s="7">
-        <v>493</v>
+        <v>504</v>
       </c>
       <c r="F340" s="7">
         <v>321</v>
@@ -12941,7 +13037,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I340" s="7">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c t="s" r="J340" s="7">
         <v>79</v>
@@ -12949,7 +13045,7 @@
       <c r="K340" s="7"/>
       <c r="L340" s="7"/>
       <c t="s" r="M340" s="7">
-        <v>494</v>
+        <v>505</v>
       </c>
     </row>
     <row r="341" ht="14.25" customHeight="1">
@@ -12964,7 +13060,7 @@
       </c>
       <c r="D341" s="7"/>
       <c t="s" r="E341" s="7">
-        <v>493</v>
+        <v>504</v>
       </c>
       <c r="F341" s="7">
         <v>321</v>
@@ -12973,7 +13069,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H341" s="8">
-        <v>416</v>
+        <v>421</v>
       </c>
       <c t="s" r="I341" s="7">
         <v>271</v>
@@ -12984,7 +13080,7 @@
       <c r="K341" s="7"/>
       <c r="L341" s="7"/>
       <c t="s" r="M341" s="7">
-        <v>480</v>
+        <v>490</v>
       </c>
     </row>
     <row r="342" ht="14.25" customHeight="1">
@@ -12999,27 +13095,27 @@
       </c>
       <c r="D342" s="7"/>
       <c t="s" r="E342" s="7">
-        <v>493</v>
+        <v>504</v>
       </c>
       <c r="F342" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G342" s="8">
-        <v>416</v>
+        <v>421</v>
       </c>
       <c t="s" r="H342" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I342" s="7">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c t="s" r="J342" s="7">
-        <v>495</v>
+        <v>506</v>
       </c>
       <c r="K342" s="7"/>
       <c r="L342" s="7"/>
       <c t="s" r="M342" s="7">
-        <v>496</v>
+        <v>507</v>
       </c>
     </row>
     <row r="343" ht="14.25" customHeight="1">
@@ -13049,7 +13145,7 @@
       </c>
       <c r="D344" s="7"/>
       <c t="s" r="E344" s="7">
-        <v>497</v>
+        <v>508</v>
       </c>
       <c r="F344" s="7">
         <v>320</v>
@@ -13064,12 +13160,12 @@
         <v>233</v>
       </c>
       <c t="s" r="J344" s="7">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="K344" s="7"/>
       <c r="L344" s="7"/>
       <c t="s" r="M344" s="7">
-        <v>498</v>
+        <v>509</v>
       </c>
     </row>
     <row r="345" ht="15" customHeight="1">
@@ -13099,7 +13195,7 @@
       </c>
       <c r="D346" s="7"/>
       <c t="s" r="E346" s="7">
-        <v>499</v>
+        <v>510</v>
       </c>
       <c r="F346" s="7">
         <v>320</v>
@@ -13111,15 +13207,15 @@
         <v>50</v>
       </c>
       <c t="s" r="I346" s="7">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c t="s" r="J346" s="7">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="K346" s="7"/>
       <c r="L346" s="7"/>
       <c t="s" r="M346" s="7">
-        <v>500</v>
+        <v>511</v>
       </c>
     </row>
     <row r="347" ht="14.25" customHeight="1">
@@ -13134,7 +13230,7 @@
       </c>
       <c r="D347" s="7"/>
       <c t="s" r="E347" s="7">
-        <v>499</v>
+        <v>510</v>
       </c>
       <c r="F347" s="7">
         <v>320</v>
@@ -13149,12 +13245,12 @@
         <v>249</v>
       </c>
       <c t="s" r="J347" s="7">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="K347" s="7"/>
       <c r="L347" s="7"/>
       <c t="s" r="M347" s="7">
-        <v>501</v>
+        <v>512</v>
       </c>
     </row>
     <row r="348" ht="14.25" customHeight="1">
@@ -13169,7 +13265,7 @@
       </c>
       <c r="D348" s="7"/>
       <c t="s" r="E348" s="7">
-        <v>499</v>
+        <v>510</v>
       </c>
       <c r="F348" s="7">
         <v>320</v>
@@ -13178,7 +13274,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H348" s="8">
-        <v>452</v>
+        <v>460</v>
       </c>
       <c t="s" r="I348" s="7">
         <v>221</v>
@@ -13204,13 +13300,13 @@
       </c>
       <c r="D349" s="7"/>
       <c t="s" r="E349" s="7">
-        <v>499</v>
+        <v>510</v>
       </c>
       <c r="F349" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G349" s="8">
-        <v>452</v>
+        <v>460</v>
       </c>
       <c t="s" r="H349" s="8">
         <v>17</v>
@@ -13224,7 +13320,7 @@
       <c r="K349" s="7"/>
       <c r="L349" s="7"/>
       <c t="s" r="M349" s="7">
-        <v>502</v>
+        <v>513</v>
       </c>
     </row>
     <row r="350" ht="15" customHeight="1">
@@ -13239,7 +13335,7 @@
       </c>
       <c r="D350" s="7"/>
       <c t="s" r="E350" s="7">
-        <v>499</v>
+        <v>510</v>
       </c>
       <c r="F350" s="7">
         <v>320</v>
@@ -13254,12 +13350,12 @@
         <v>43</v>
       </c>
       <c t="s" r="J350" s="7">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="K350" s="7"/>
       <c r="L350" s="7"/>
       <c t="s" r="M350" s="7">
-        <v>503</v>
+        <v>514</v>
       </c>
     </row>
     <row r="351" ht="14.25" customHeight="1">
@@ -13274,7 +13370,7 @@
       </c>
       <c r="D351" s="7"/>
       <c t="s" r="E351" s="7">
-        <v>499</v>
+        <v>510</v>
       </c>
       <c r="F351" s="7">
         <v>320</v>
@@ -13293,7 +13389,9 @@
       </c>
       <c r="K351" s="7"/>
       <c r="L351" s="7"/>
-      <c r="M351" s="7"/>
+      <c t="s" r="M351" s="7">
+        <v>76</v>
+      </c>
     </row>
     <row r="352" ht="14.25" customHeight="1">
       <c r="A352" s="6"/>
@@ -13322,7 +13420,7 @@
       </c>
       <c r="D353" s="7"/>
       <c t="s" r="E353" s="7">
-        <v>504</v>
+        <v>515</v>
       </c>
       <c r="F353" s="7">
         <v>321</v>
@@ -13331,10 +13429,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H353" s="8">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c t="s" r="I353" s="7">
-        <v>505</v>
+        <v>516</v>
       </c>
       <c t="s" r="J353" s="7">
         <v>200</v>
@@ -13342,7 +13440,7 @@
       <c r="K353" s="7"/>
       <c r="L353" s="7"/>
       <c t="s" r="M353" s="7">
-        <v>506</v>
+        <v>517</v>
       </c>
     </row>
     <row r="354" ht="14.25" customHeight="1">
@@ -13357,13 +13455,13 @@
       </c>
       <c r="D354" s="7"/>
       <c t="s" r="E354" s="7">
-        <v>504</v>
+        <v>515</v>
       </c>
       <c r="F354" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G354" s="8">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c t="s" r="H354" s="8">
         <v>17</v>
@@ -13372,12 +13470,12 @@
         <v>18</v>
       </c>
       <c t="s" r="J354" s="7">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="K354" s="7"/>
       <c r="L354" s="7"/>
       <c t="s" r="M354" s="7">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="355" ht="15" customHeight="1">
@@ -13392,7 +13490,7 @@
       </c>
       <c r="D355" s="7"/>
       <c t="s" r="E355" s="7">
-        <v>504</v>
+        <v>515</v>
       </c>
       <c r="F355" s="7">
         <v>321</v>
@@ -13404,7 +13502,7 @@
         <v>33</v>
       </c>
       <c t="s" r="I355" s="7">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c t="s" r="J355" s="7">
         <v>206</v>
@@ -13412,7 +13510,7 @@
       <c r="K355" s="7"/>
       <c r="L355" s="7"/>
       <c t="s" r="M355" s="7">
-        <v>507</v>
+        <v>518</v>
       </c>
     </row>
     <row r="356" ht="14.25" customHeight="1">
@@ -13427,7 +13525,7 @@
       </c>
       <c r="D356" s="7"/>
       <c t="s" r="E356" s="7">
-        <v>504</v>
+        <v>515</v>
       </c>
       <c r="F356" s="7">
         <v>321</v>
@@ -13462,7 +13560,7 @@
       </c>
       <c r="D357" s="7"/>
       <c t="s" r="E357" s="7">
-        <v>504</v>
+        <v>515</v>
       </c>
       <c r="F357" s="7">
         <v>321</v>
@@ -13482,7 +13580,7 @@
       <c r="K357" s="7"/>
       <c r="L357" s="7"/>
       <c t="s" r="M357" s="7">
-        <v>508</v>
+        <v>519</v>
       </c>
     </row>
     <row r="358" ht="14.25" customHeight="1">
@@ -13497,7 +13595,7 @@
       </c>
       <c r="D358" s="7"/>
       <c t="s" r="E358" s="7">
-        <v>504</v>
+        <v>515</v>
       </c>
       <c r="F358" s="7">
         <v>321</v>
@@ -13512,11 +13610,13 @@
         <v>85</v>
       </c>
       <c t="s" r="J358" s="7">
-        <v>509</v>
+        <v>520</v>
       </c>
       <c r="K358" s="7"/>
       <c r="L358" s="7"/>
-      <c r="M358" s="7"/>
+      <c t="s" r="M358" s="7">
+        <v>521</v>
+      </c>
     </row>
     <row r="359" ht="14.25" customHeight="1">
       <c t="s" r="A359" s="6">
@@ -13530,7 +13630,7 @@
       </c>
       <c r="D359" s="7"/>
       <c t="s" r="E359" s="7">
-        <v>504</v>
+        <v>515</v>
       </c>
       <c r="F359" s="7">
         <v>321</v>
@@ -13539,13 +13639,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H359" s="8">
-        <v>510</v>
+        <v>522</v>
       </c>
       <c t="s" r="I359" s="7">
-        <v>511</v>
+        <v>523</v>
       </c>
       <c t="s" r="J359" s="7">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="K359" s="7"/>
       <c r="L359" s="7"/>
@@ -13578,7 +13678,7 @@
       </c>
       <c r="D361" s="7"/>
       <c t="s" r="E361" s="7">
-        <v>512</v>
+        <v>524</v>
       </c>
       <c r="F361" s="7">
         <v>320</v>
@@ -13590,15 +13690,15 @@
         <v>33</v>
       </c>
       <c t="s" r="I361" s="7">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c t="s" r="J361" s="7">
-        <v>475</v>
+        <v>484</v>
       </c>
       <c r="K361" s="7"/>
       <c r="L361" s="7"/>
       <c t="s" r="M361" s="7">
-        <v>513</v>
+        <v>525</v>
       </c>
     </row>
     <row r="362" ht="14.25" customHeight="1">
@@ -13613,7 +13713,7 @@
       </c>
       <c r="D362" s="7"/>
       <c t="s" r="E362" s="7">
-        <v>512</v>
+        <v>524</v>
       </c>
       <c r="F362" s="7">
         <v>320</v>
@@ -13625,15 +13725,15 @@
         <v>17</v>
       </c>
       <c t="s" r="I362" s="7">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c t="s" r="J362" s="7">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="K362" s="7"/>
       <c r="L362" s="7"/>
       <c t="s" r="M362" s="7">
-        <v>514</v>
+        <v>526</v>
       </c>
     </row>
     <row r="363" ht="14.25" customHeight="1">
@@ -13648,7 +13748,7 @@
       </c>
       <c r="D363" s="7"/>
       <c t="s" r="E363" s="7">
-        <v>512</v>
+        <v>524</v>
       </c>
       <c r="F363" s="7">
         <v>320</v>
@@ -13660,7 +13760,7 @@
         <v>72</v>
       </c>
       <c t="s" r="I363" s="7">
-        <v>438</v>
+        <v>445</v>
       </c>
       <c t="s" r="J363" s="7">
         <v>79</v>
@@ -13668,7 +13768,7 @@
       <c r="K363" s="7"/>
       <c r="L363" s="7"/>
       <c t="s" r="M363" s="7">
-        <v>462</v>
+        <v>470</v>
       </c>
     </row>
     <row r="364" ht="14.25" customHeight="1">
@@ -13683,7 +13783,7 @@
       </c>
       <c r="D364" s="7"/>
       <c t="s" r="E364" s="7">
-        <v>512</v>
+        <v>524</v>
       </c>
       <c r="F364" s="7">
         <v>320</v>
@@ -13703,7 +13803,7 @@
       <c r="K364" s="7"/>
       <c r="L364" s="7"/>
       <c t="s" r="M364" s="7">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="365" ht="15" customHeight="1">
@@ -13718,7 +13818,7 @@
       </c>
       <c r="D365" s="7"/>
       <c t="s" r="E365" s="7">
-        <v>512</v>
+        <v>524</v>
       </c>
       <c r="F365" s="7">
         <v>320</v>
@@ -13730,7 +13830,7 @@
         <v>72</v>
       </c>
       <c t="s" r="I365" s="7">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c t="s" r="J365" s="7">
         <v>285</v>
@@ -13738,7 +13838,7 @@
       <c r="K365" s="7"/>
       <c r="L365" s="7"/>
       <c t="s" r="M365" s="7">
-        <v>515</v>
+        <v>527</v>
       </c>
     </row>
     <row r="366" ht="14.25" customHeight="1">
@@ -13753,7 +13853,7 @@
       </c>
       <c r="D366" s="7"/>
       <c t="s" r="E366" s="7">
-        <v>512</v>
+        <v>524</v>
       </c>
       <c r="F366" s="7">
         <v>320</v>
@@ -13765,14 +13865,16 @@
         <v>17</v>
       </c>
       <c t="s" r="I366" s="7">
-        <v>393</v>
+        <v>399</v>
       </c>
       <c t="s" r="J366" s="7">
         <v>196</v>
       </c>
       <c r="K366" s="7"/>
       <c r="L366" s="7"/>
-      <c r="M366" s="7"/>
+      <c t="s" r="M366" s="7">
+        <v>528</v>
+      </c>
     </row>
     <row r="367" ht="14.25" customHeight="1">
       <c r="A367" s="6"/>
@@ -13801,7 +13903,7 @@
       </c>
       <c r="D368" s="7"/>
       <c t="s" r="E368" s="7">
-        <v>516</v>
+        <v>529</v>
       </c>
       <c r="F368" s="7">
         <v>320</v>
@@ -13810,10 +13912,10 @@
         <v>50</v>
       </c>
       <c t="s" r="H368" s="8">
-        <v>517</v>
+        <v>530</v>
       </c>
       <c t="s" r="I368" s="7">
-        <v>435</v>
+        <v>442</v>
       </c>
       <c t="s" r="J368" s="7">
         <v>111</v>
@@ -13821,7 +13923,7 @@
       <c r="K368" s="7"/>
       <c r="L368" s="7"/>
       <c t="s" r="M368" s="7">
-        <v>415</v>
+        <v>420</v>
       </c>
     </row>
     <row r="369" ht="14.25" customHeight="1">
@@ -13836,13 +13938,13 @@
       </c>
       <c r="D369" s="7"/>
       <c t="s" r="E369" s="7">
-        <v>516</v>
+        <v>529</v>
       </c>
       <c r="F369" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G369" s="8">
-        <v>517</v>
+        <v>530</v>
       </c>
       <c t="s" r="H369" s="8">
         <v>50</v>
@@ -13856,7 +13958,7 @@
       <c r="K369" s="7"/>
       <c r="L369" s="7"/>
       <c t="s" r="M369" s="7">
-        <v>518</v>
+        <v>531</v>
       </c>
     </row>
     <row r="370" ht="15" customHeight="1">
@@ -13871,7 +13973,7 @@
       </c>
       <c r="D370" s="7"/>
       <c t="s" r="E370" s="7">
-        <v>516</v>
+        <v>529</v>
       </c>
       <c r="F370" s="7">
         <v>320</v>
@@ -13880,7 +13982,7 @@
         <v>50</v>
       </c>
       <c t="s" r="H370" s="8">
-        <v>517</v>
+        <v>530</v>
       </c>
       <c t="s" r="I370" s="7">
         <v>64</v>
@@ -13906,13 +14008,13 @@
       </c>
       <c r="D371" s="7"/>
       <c t="s" r="E371" s="7">
-        <v>516</v>
+        <v>529</v>
       </c>
       <c r="F371" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G371" s="8">
-        <v>517</v>
+        <v>530</v>
       </c>
       <c t="s" r="H371" s="8">
         <v>50</v>
@@ -13926,7 +14028,7 @@
       <c r="K371" s="7"/>
       <c r="L371" s="7"/>
       <c t="s" r="M371" s="7">
-        <v>519</v>
+        <v>532</v>
       </c>
     </row>
     <row r="372" ht="14.25" customHeight="1">
@@ -13941,7 +14043,7 @@
       </c>
       <c r="D372" s="7"/>
       <c t="s" r="E372" s="7">
-        <v>516</v>
+        <v>529</v>
       </c>
       <c r="F372" s="7">
         <v>320</v>
@@ -13950,7 +14052,7 @@
         <v>50</v>
       </c>
       <c t="s" r="H372" s="8">
-        <v>517</v>
+        <v>530</v>
       </c>
       <c t="s" r="I372" s="7">
         <v>115</v>
@@ -13961,7 +14063,7 @@
       <c r="K372" s="7"/>
       <c r="L372" s="7"/>
       <c t="s" r="M372" s="7">
-        <v>520</v>
+        <v>533</v>
       </c>
     </row>
     <row r="373" ht="14.25" customHeight="1">
@@ -13976,13 +14078,13 @@
       </c>
       <c r="D373" s="7"/>
       <c t="s" r="E373" s="7">
-        <v>516</v>
+        <v>529</v>
       </c>
       <c r="F373" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G373" s="8">
-        <v>517</v>
+        <v>530</v>
       </c>
       <c t="s" r="H373" s="8">
         <v>50</v>
@@ -13991,12 +14093,12 @@
         <v>271</v>
       </c>
       <c t="s" r="J373" s="7">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K373" s="7"/>
       <c r="L373" s="7"/>
       <c t="s" r="M373" s="7">
-        <v>521</v>
+        <v>534</v>
       </c>
     </row>
     <row r="374" ht="14.25" customHeight="1">
@@ -14011,7 +14113,7 @@
       </c>
       <c r="D374" s="7"/>
       <c t="s" r="E374" s="7">
-        <v>516</v>
+        <v>529</v>
       </c>
       <c r="F374" s="7">
         <v>320</v>
@@ -14023,15 +14125,15 @@
         <v>17</v>
       </c>
       <c t="s" r="I374" s="7">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c t="s" r="J374" s="7">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="K374" s="7"/>
       <c r="L374" s="7"/>
       <c t="s" r="M374" s="7">
-        <v>471</v>
+        <v>535</v>
       </c>
     </row>
     <row r="375" ht="15" customHeight="1">
@@ -14061,7 +14163,7 @@
       </c>
       <c r="D376" s="7"/>
       <c t="s" r="E376" s="7">
-        <v>522</v>
+        <v>536</v>
       </c>
       <c r="F376" s="7">
         <v>321</v>
@@ -14070,10 +14172,10 @@
         <v>50</v>
       </c>
       <c t="s" r="H376" s="8">
-        <v>416</v>
+        <v>421</v>
       </c>
       <c t="s" r="I376" s="7">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c t="s" r="J376" s="7">
         <v>233</v>
@@ -14081,7 +14183,7 @@
       <c r="K376" s="7"/>
       <c r="L376" s="7"/>
       <c t="s" r="M376" s="7">
-        <v>523</v>
+        <v>537</v>
       </c>
     </row>
     <row r="377" ht="14.25" customHeight="1">
@@ -14096,13 +14198,13 @@
       </c>
       <c r="D377" s="7"/>
       <c t="s" r="E377" s="7">
-        <v>522</v>
+        <v>536</v>
       </c>
       <c r="F377" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G377" s="8">
-        <v>416</v>
+        <v>421</v>
       </c>
       <c t="s" r="H377" s="8">
         <v>50</v>
@@ -14111,12 +14213,12 @@
         <v>30</v>
       </c>
       <c t="s" r="J377" s="7">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="K377" s="7"/>
       <c r="L377" s="7"/>
       <c t="s" r="M377" s="7">
-        <v>524</v>
+        <v>538</v>
       </c>
     </row>
     <row r="378" ht="14.25" customHeight="1">
@@ -14131,7 +14233,7 @@
       </c>
       <c r="D378" s="7"/>
       <c t="s" r="E378" s="7">
-        <v>522</v>
+        <v>536</v>
       </c>
       <c r="F378" s="7">
         <v>321</v>
@@ -14143,15 +14245,15 @@
         <v>291</v>
       </c>
       <c t="s" r="I378" s="7">
-        <v>525</v>
+        <v>539</v>
       </c>
       <c t="s" r="J378" s="7">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="K378" s="7"/>
       <c r="L378" s="7"/>
       <c t="s" r="M378" s="7">
-        <v>526</v>
+        <v>540</v>
       </c>
     </row>
     <row r="379" ht="14.25" customHeight="1">
@@ -14166,7 +14268,7 @@
       </c>
       <c r="D379" s="7"/>
       <c t="s" r="E379" s="7">
-        <v>522</v>
+        <v>536</v>
       </c>
       <c r="F379" s="7">
         <v>321</v>
@@ -14186,7 +14288,7 @@
       <c r="K379" s="7"/>
       <c r="L379" s="7"/>
       <c t="s" r="M379" s="7">
-        <v>527</v>
+        <v>541</v>
       </c>
     </row>
     <row r="380" ht="15" customHeight="1">
@@ -14201,7 +14303,7 @@
       </c>
       <c r="D380" s="7"/>
       <c t="s" r="E380" s="7">
-        <v>522</v>
+        <v>536</v>
       </c>
       <c r="F380" s="7">
         <v>321</v>
@@ -14210,20 +14312,20 @@
         <v>50</v>
       </c>
       <c t="s" r="H380" s="8">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c t="s" r="I380" s="7">
-        <v>473</v>
+        <v>482</v>
       </c>
       <c t="s" r="J380" s="7">
-        <v>528</v>
+        <v>542</v>
       </c>
       <c t="s" r="K380" s="7">
-        <v>529</v>
+        <v>543</v>
       </c>
       <c r="L380" s="7"/>
       <c t="s" r="M380" s="7">
-        <v>530</v>
+        <v>544</v>
       </c>
     </row>
     <row r="381" ht="14.25" customHeight="1">
@@ -14238,25 +14340,25 @@
       </c>
       <c r="D381" s="7"/>
       <c t="s" r="E381" s="7">
-        <v>522</v>
+        <v>536</v>
       </c>
       <c r="F381" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G381" s="8">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c t="s" r="H381" s="8">
         <v>50</v>
       </c>
       <c t="s" r="I381" s="7">
-        <v>531</v>
+        <v>545</v>
       </c>
       <c t="s" r="J381" s="7">
-        <v>532</v>
+        <v>546</v>
       </c>
       <c t="s" r="K381" s="7">
-        <v>533</v>
+        <v>547</v>
       </c>
       <c r="L381" s="7"/>
       <c t="s" r="M381" s="7">
@@ -14290,7 +14392,7 @@
       </c>
       <c r="D383" s="7"/>
       <c t="s" r="E383" s="7">
-        <v>534</v>
+        <v>548</v>
       </c>
       <c r="F383" s="7">
         <v>320</v>
@@ -14299,18 +14401,18 @@
         <v>50</v>
       </c>
       <c t="s" r="H383" s="8">
-        <v>452</v>
+        <v>460</v>
       </c>
       <c t="s" r="I383" s="7">
         <v>77</v>
       </c>
       <c t="s" r="J383" s="7">
-        <v>505</v>
+        <v>516</v>
       </c>
       <c r="K383" s="7"/>
       <c r="L383" s="7"/>
       <c t="s" r="M383" s="7">
-        <v>535</v>
+        <v>549</v>
       </c>
     </row>
     <row r="384" ht="14.25" customHeight="1">
@@ -14325,19 +14427,19 @@
       </c>
       <c r="D384" s="7"/>
       <c t="s" r="E384" s="7">
-        <v>534</v>
+        <v>548</v>
       </c>
       <c r="F384" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G384" s="8">
-        <v>452</v>
+        <v>460</v>
       </c>
       <c t="s" r="H384" s="8">
         <v>50</v>
       </c>
       <c t="s" r="I384" s="7">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c t="s" r="J384" s="7">
         <v>248</v>
@@ -14345,7 +14447,7 @@
       <c r="K384" s="7"/>
       <c r="L384" s="7"/>
       <c t="s" r="M384" s="7">
-        <v>536</v>
+        <v>550</v>
       </c>
     </row>
     <row r="385" ht="15" customHeight="1">
@@ -14360,7 +14462,7 @@
       </c>
       <c r="D385" s="7"/>
       <c t="s" r="E385" s="7">
-        <v>534</v>
+        <v>548</v>
       </c>
       <c r="F385" s="7">
         <v>320</v>
@@ -14372,7 +14474,7 @@
         <v>225</v>
       </c>
       <c t="s" r="I385" s="7">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c t="s" r="J385" s="7">
         <v>219</v>
@@ -14380,7 +14482,7 @@
       <c r="K385" s="7"/>
       <c r="L385" s="7"/>
       <c t="s" r="M385" s="7">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="386" ht="14.25" customHeight="1">
@@ -14395,7 +14497,7 @@
       </c>
       <c r="D386" s="7"/>
       <c t="s" r="E386" s="7">
-        <v>534</v>
+        <v>548</v>
       </c>
       <c r="F386" s="7">
         <v>320</v>
@@ -14407,7 +14509,7 @@
         <v>50</v>
       </c>
       <c t="s" r="I386" s="7">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c t="s" r="J386" s="7">
         <v>67</v>
@@ -14415,7 +14517,7 @@
       <c r="K386" s="7"/>
       <c r="L386" s="7"/>
       <c t="s" r="M386" s="7">
-        <v>537</v>
+        <v>551</v>
       </c>
     </row>
     <row r="387" ht="14.25" customHeight="1">
@@ -14430,7 +14532,7 @@
       </c>
       <c r="D387" s="7"/>
       <c t="s" r="E387" s="7">
-        <v>534</v>
+        <v>548</v>
       </c>
       <c r="F387" s="7">
         <v>320</v>
@@ -14450,7 +14552,7 @@
       <c r="K387" s="7"/>
       <c r="L387" s="7"/>
       <c t="s" r="M387" s="7">
-        <v>538</v>
+        <v>552</v>
       </c>
     </row>
     <row r="388" ht="14.25" customHeight="1">
@@ -14465,7 +14567,7 @@
       </c>
       <c r="D388" s="7"/>
       <c t="s" r="E388" s="7">
-        <v>534</v>
+        <v>548</v>
       </c>
       <c r="F388" s="7">
         <v>320</v>
@@ -14480,12 +14582,12 @@
         <v>73</v>
       </c>
       <c t="s" r="J388" s="7">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="K388" s="7"/>
       <c r="L388" s="7"/>
       <c t="s" r="M388" s="7">
-        <v>539</v>
+        <v>553</v>
       </c>
     </row>
     <row r="389" ht="14.25" customHeight="1">
@@ -14500,7 +14602,7 @@
       </c>
       <c r="D389" s="7"/>
       <c t="s" r="E389" s="7">
-        <v>534</v>
+        <v>548</v>
       </c>
       <c r="F389" s="7">
         <v>320</v>
@@ -14509,18 +14611,18 @@
         <v>50</v>
       </c>
       <c t="s" r="H389" s="8">
-        <v>416</v>
+        <v>421</v>
       </c>
       <c t="s" r="I389" s="7">
-        <v>540</v>
+        <v>554</v>
       </c>
       <c t="s" r="J389" s="7">
-        <v>425</v>
+        <v>431</v>
       </c>
       <c r="K389" s="7"/>
       <c r="L389" s="7"/>
       <c t="s" r="M389" s="7">
-        <v>541</v>
+        <v>555</v>
       </c>
     </row>
     <row r="390" ht="15" customHeight="1">
@@ -14535,13 +14637,13 @@
       </c>
       <c r="D390" s="7"/>
       <c t="s" r="E390" s="7">
-        <v>534</v>
+        <v>548</v>
       </c>
       <c r="F390" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G390" s="8">
-        <v>416</v>
+        <v>421</v>
       </c>
       <c t="s" r="H390" s="8">
         <v>50</v>
@@ -14555,7 +14657,7 @@
       <c r="K390" s="7"/>
       <c r="L390" s="7"/>
       <c t="s" r="M390" s="7">
-        <v>542</v>
+        <v>556</v>
       </c>
     </row>
     <row r="391" ht="14.25" customHeight="1">
@@ -14570,7 +14672,7 @@
       </c>
       <c r="D391" s="7"/>
       <c t="s" r="E391" s="7">
-        <v>534</v>
+        <v>548</v>
       </c>
       <c r="F391" s="7">
         <v>320</v>
@@ -14582,14 +14684,16 @@
         <v>57</v>
       </c>
       <c t="s" r="I391" s="7">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c t="s" r="J391" s="7">
         <v>196</v>
       </c>
       <c r="K391" s="7"/>
       <c r="L391" s="7"/>
-      <c r="M391" s="7"/>
+      <c t="s" r="M391" s="7">
+        <v>557</v>
+      </c>
     </row>
     <row r="392" ht="14.25" customHeight="1">
       <c t="s" r="A392" s="6">
@@ -14603,7 +14707,7 @@
       </c>
       <c r="D392" s="7"/>
       <c t="s" r="E392" s="7">
-        <v>534</v>
+        <v>548</v>
       </c>
       <c r="F392" s="7">
         <v>320</v>
@@ -14615,10 +14719,10 @@
         <v>50</v>
       </c>
       <c t="s" r="I392" s="7">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c t="s" r="J392" s="7">
-        <v>481</v>
+        <v>491</v>
       </c>
       <c r="K392" s="7"/>
       <c r="L392" s="7"/>
@@ -14651,7 +14755,7 @@
       </c>
       <c r="D394" s="7"/>
       <c t="s" r="E394" s="7">
-        <v>543</v>
+        <v>558</v>
       </c>
       <c r="F394" s="7">
         <v>321</v>
@@ -14663,7 +14767,7 @@
         <v>57</v>
       </c>
       <c t="s" r="I394" s="7">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c t="s" r="J394" s="7">
         <v>249</v>
@@ -14671,7 +14775,7 @@
       <c r="K394" s="7"/>
       <c r="L394" s="7"/>
       <c t="s" r="M394" s="7">
-        <v>544</v>
+        <v>559</v>
       </c>
     </row>
     <row r="395" ht="15" customHeight="1">
@@ -14686,7 +14790,7 @@
       </c>
       <c r="D395" s="7"/>
       <c t="s" r="E395" s="7">
-        <v>543</v>
+        <v>558</v>
       </c>
       <c r="F395" s="7">
         <v>321</v>
@@ -14695,18 +14799,18 @@
         <v>57</v>
       </c>
       <c t="s" r="H395" s="8">
-        <v>485</v>
+        <v>495</v>
       </c>
       <c t="s" r="I395" s="7">
-        <v>545</v>
+        <v>560</v>
       </c>
       <c t="s" r="J395" s="7">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="K395" s="7"/>
       <c r="L395" s="7"/>
       <c t="s" r="M395" s="7">
-        <v>546</v>
+        <v>561</v>
       </c>
     </row>
     <row r="396" ht="14.25" customHeight="1">
@@ -14721,19 +14825,19 @@
       </c>
       <c r="D396" s="7"/>
       <c t="s" r="E396" s="7">
-        <v>543</v>
+        <v>558</v>
       </c>
       <c r="F396" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G396" s="8">
-        <v>485</v>
+        <v>495</v>
       </c>
       <c t="s" r="H396" s="8">
         <v>50</v>
       </c>
       <c t="s" r="I396" s="7">
-        <v>540</v>
+        <v>554</v>
       </c>
       <c t="s" r="J396" s="7">
         <v>25</v>
@@ -14741,7 +14845,7 @@
       <c r="K396" s="7"/>
       <c r="L396" s="7"/>
       <c t="s" r="M396" s="7">
-        <v>547</v>
+        <v>562</v>
       </c>
     </row>
     <row r="397" ht="14.25" customHeight="1">
@@ -14756,7 +14860,7 @@
       </c>
       <c r="D397" s="7"/>
       <c t="s" r="E397" s="7">
-        <v>543</v>
+        <v>558</v>
       </c>
       <c r="F397" s="7">
         <v>321</v>
@@ -14768,14 +14872,16 @@
         <v>57</v>
       </c>
       <c t="s" r="I397" s="7">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c t="s" r="J397" s="7">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="K397" s="7"/>
       <c r="L397" s="7"/>
-      <c r="M397" s="7"/>
+      <c t="s" r="M397" s="7">
+        <v>563</v>
+      </c>
     </row>
     <row r="398" ht="14.25" customHeight="1">
       <c t="s" r="A398" s="6">
@@ -14789,7 +14895,7 @@
       </c>
       <c r="D398" s="7"/>
       <c t="s" r="E398" s="7">
-        <v>543</v>
+        <v>558</v>
       </c>
       <c r="F398" s="7">
         <v>321</v>
@@ -14801,10 +14907,10 @@
         <v>46</v>
       </c>
       <c t="s" r="I398" s="7">
-        <v>548</v>
+        <v>564</v>
       </c>
       <c t="s" r="J398" s="7">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="K398" s="7"/>
       <c r="L398" s="7"/>
@@ -14837,7 +14943,7 @@
       </c>
       <c r="D400" s="7"/>
       <c t="s" r="E400" s="7">
-        <v>549</v>
+        <v>565</v>
       </c>
       <c r="F400" s="7">
         <v>321</v>
@@ -14849,7 +14955,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I400" s="7">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c t="s" r="J400" s="7">
         <v>20</v>
@@ -14857,7 +14963,7 @@
       <c r="K400" s="7"/>
       <c r="L400" s="7"/>
       <c t="s" r="M400" s="7">
-        <v>550</v>
+        <v>566</v>
       </c>
     </row>
     <row r="401" ht="14.25" customHeight="1">
@@ -14872,7 +14978,7 @@
       </c>
       <c r="D401" s="7"/>
       <c t="s" r="E401" s="7">
-        <v>549</v>
+        <v>565</v>
       </c>
       <c r="F401" s="7">
         <v>321</v>
@@ -14884,15 +14990,15 @@
         <v>57</v>
       </c>
       <c t="s" r="I401" s="7">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c t="s" r="J401" s="7">
-        <v>540</v>
+        <v>554</v>
       </c>
       <c r="K401" s="7"/>
       <c r="L401" s="7"/>
       <c t="s" r="M401" s="7">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="402" ht="14.25" customHeight="1">
@@ -14907,7 +15013,7 @@
       </c>
       <c r="D402" s="7"/>
       <c t="s" r="E402" s="7">
-        <v>549</v>
+        <v>565</v>
       </c>
       <c r="F402" s="7">
         <v>321</v>
@@ -14919,17 +15025,17 @@
         <v>17</v>
       </c>
       <c t="s" r="I402" s="7">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c t="s" r="J402" s="7">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c t="s" r="K402" s="7">
-        <v>425</v>
+        <v>431</v>
       </c>
       <c r="L402" s="7"/>
       <c t="s" r="M402" s="7">
-        <v>551</v>
+        <v>567</v>
       </c>
     </row>
     <row r="403" ht="14.25" customHeight="1">
@@ -14944,7 +15050,7 @@
       </c>
       <c r="D403" s="7"/>
       <c t="s" r="E403" s="7">
-        <v>549</v>
+        <v>565</v>
       </c>
       <c r="F403" s="7">
         <v>321</v>
@@ -14953,17 +15059,19 @@
         <v>17</v>
       </c>
       <c t="s" r="H403" s="8">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c t="s" r="I403" s="7">
         <v>54</v>
       </c>
       <c t="s" r="J403" s="7">
-        <v>552</v>
+        <v>568</v>
       </c>
       <c r="K403" s="7"/>
       <c r="L403" s="7"/>
-      <c r="M403" s="7"/>
+      <c t="s" r="M403" s="7">
+        <v>569</v>
+      </c>
     </row>
     <row r="404" ht="14.25" customHeight="1">
       <c t="s" r="A404" s="6">
@@ -14977,22 +15085,22 @@
       </c>
       <c r="D404" s="7"/>
       <c t="s" r="E404" s="7">
-        <v>549</v>
+        <v>565</v>
       </c>
       <c r="F404" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G404" s="8">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c t="s" r="H404" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I404" s="7">
-        <v>553</v>
+        <v>570</v>
       </c>
       <c t="s" r="J404" s="7">
-        <v>554</v>
+        <v>571</v>
       </c>
       <c r="K404" s="7"/>
       <c r="L404" s="7"/>
@@ -15025,7 +15133,7 @@
       </c>
       <c r="D406" s="7"/>
       <c t="s" r="E406" s="7">
-        <v>555</v>
+        <v>572</v>
       </c>
       <c r="F406" s="7">
         <v>320</v>
@@ -15045,7 +15153,7 @@
       <c r="K406" s="7"/>
       <c r="L406" s="7"/>
       <c t="s" r="M406" s="7">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="407" ht="14.25" customHeight="1">
@@ -15060,7 +15168,7 @@
       </c>
       <c r="D407" s="7"/>
       <c t="s" r="E407" s="7">
-        <v>555</v>
+        <v>572</v>
       </c>
       <c r="F407" s="7">
         <v>320</v>
@@ -15072,7 +15180,7 @@
         <v>50</v>
       </c>
       <c t="s" r="I407" s="7">
-        <v>525</v>
+        <v>539</v>
       </c>
       <c t="s" r="J407" s="7">
         <v>51</v>
@@ -15080,7 +15188,7 @@
       <c r="K407" s="7"/>
       <c r="L407" s="7"/>
       <c t="s" r="M407" s="7">
-        <v>556</v>
+        <v>573</v>
       </c>
     </row>
     <row r="408" ht="14.25" customHeight="1">
@@ -15095,7 +15203,7 @@
       </c>
       <c r="D408" s="7"/>
       <c t="s" r="E408" s="7">
-        <v>555</v>
+        <v>572</v>
       </c>
       <c r="F408" s="7">
         <v>320</v>
@@ -15110,12 +15218,12 @@
         <v>237</v>
       </c>
       <c t="s" r="J408" s="7">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="K408" s="7"/>
       <c r="L408" s="7"/>
       <c t="s" r="M408" s="7">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="409" ht="14.25" customHeight="1">
@@ -15130,7 +15238,7 @@
       </c>
       <c r="D409" s="7"/>
       <c t="s" r="E409" s="7">
-        <v>555</v>
+        <v>572</v>
       </c>
       <c r="F409" s="7">
         <v>320</v>
@@ -15145,12 +15253,12 @@
         <v>25</v>
       </c>
       <c t="s" r="J409" s="7">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="K409" s="7"/>
       <c r="L409" s="7"/>
       <c t="s" r="M409" s="7">
-        <v>557</v>
+        <v>574</v>
       </c>
     </row>
     <row r="410" ht="15" customHeight="1">
@@ -15180,7 +15288,7 @@
       </c>
       <c r="D411" s="7"/>
       <c t="s" r="E411" s="7">
-        <v>558</v>
+        <v>575</v>
       </c>
       <c r="F411" s="7">
         <v>320</v>
@@ -15189,18 +15297,18 @@
         <v>17</v>
       </c>
       <c t="s" r="H411" s="8">
-        <v>452</v>
+        <v>460</v>
       </c>
       <c t="s" r="I411" s="7">
-        <v>559</v>
+        <v>576</v>
       </c>
       <c t="s" r="J411" s="7">
-        <v>387</v>
+        <v>393</v>
       </c>
       <c r="K411" s="7"/>
       <c r="L411" s="7"/>
       <c t="s" r="M411" s="7">
-        <v>560</v>
+        <v>577</v>
       </c>
     </row>
     <row r="412" ht="14.25" customHeight="1">
@@ -15215,19 +15323,19 @@
       </c>
       <c r="D412" s="7"/>
       <c t="s" r="E412" s="7">
-        <v>558</v>
+        <v>575</v>
       </c>
       <c r="F412" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G412" s="8">
-        <v>452</v>
+        <v>460</v>
       </c>
       <c t="s" r="H412" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I412" s="7">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c t="s" r="J412" s="7">
         <v>88</v>
@@ -15235,7 +15343,7 @@
       <c r="K412" s="7"/>
       <c r="L412" s="7"/>
       <c t="s" r="M412" s="7">
-        <v>561</v>
+        <v>578</v>
       </c>
     </row>
     <row r="413" ht="14.25" customHeight="1">
@@ -15250,7 +15358,7 @@
       </c>
       <c r="D413" s="7"/>
       <c t="s" r="E413" s="7">
-        <v>558</v>
+        <v>575</v>
       </c>
       <c r="F413" s="7">
         <v>320</v>
@@ -15265,12 +15373,12 @@
         <v>97</v>
       </c>
       <c t="s" r="J413" s="7">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="K413" s="7"/>
       <c r="L413" s="7"/>
       <c t="s" r="M413" s="7">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="414" ht="14.25" customHeight="1">
@@ -15285,7 +15393,7 @@
       </c>
       <c r="D414" s="7"/>
       <c t="s" r="E414" s="7">
-        <v>558</v>
+        <v>575</v>
       </c>
       <c r="F414" s="7">
         <v>320</v>
@@ -15297,7 +15405,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I414" s="7">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c t="s" r="J414" s="7">
         <v>266</v>
@@ -15320,7 +15428,7 @@
       </c>
       <c r="D415" s="7"/>
       <c t="s" r="E415" s="7">
-        <v>558</v>
+        <v>575</v>
       </c>
       <c r="F415" s="7">
         <v>320</v>
@@ -15332,15 +15440,15 @@
         <v>33</v>
       </c>
       <c t="s" r="I415" s="7">
-        <v>488</v>
+        <v>498</v>
       </c>
       <c t="s" r="J415" s="7">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K415" s="7"/>
       <c r="L415" s="7"/>
       <c t="s" r="M415" s="7">
-        <v>562</v>
+        <v>579</v>
       </c>
     </row>
     <row r="416" ht="14.25" customHeight="1">
@@ -15355,7 +15463,7 @@
       </c>
       <c r="D416" s="7"/>
       <c t="s" r="E416" s="7">
-        <v>558</v>
+        <v>575</v>
       </c>
       <c r="F416" s="7">
         <v>320</v>
@@ -15367,7 +15475,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I416" s="7">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c t="s" r="J416" s="7">
         <v>226</v>
@@ -15375,7 +15483,7 @@
       <c r="K416" s="7"/>
       <c r="L416" s="7"/>
       <c t="s" r="M416" s="7">
-        <v>563</v>
+        <v>580</v>
       </c>
     </row>
     <row r="417" ht="14.25" customHeight="1">
@@ -15405,7 +15513,7 @@
       </c>
       <c r="D418" s="7"/>
       <c t="s" r="E418" s="7">
-        <v>564</v>
+        <v>581</v>
       </c>
       <c r="F418" s="7">
         <v>321</v>
@@ -15417,15 +15525,15 @@
         <v>72</v>
       </c>
       <c t="s" r="I418" s="7">
-        <v>505</v>
+        <v>516</v>
       </c>
       <c t="s" r="J418" s="7">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="K418" s="7"/>
       <c r="L418" s="7"/>
       <c t="s" r="M418" s="7">
-        <v>565</v>
+        <v>582</v>
       </c>
     </row>
     <row r="419" ht="14.25" customHeight="1">
@@ -15440,7 +15548,7 @@
       </c>
       <c r="D419" s="7"/>
       <c t="s" r="E419" s="7">
-        <v>564</v>
+        <v>581</v>
       </c>
       <c r="F419" s="7">
         <v>321</v>
@@ -15449,13 +15557,13 @@
         <v>72</v>
       </c>
       <c t="s" r="H419" s="8">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c t="s" r="I419" s="7">
         <v>282</v>
       </c>
       <c t="s" r="J419" s="7">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="K419" s="7"/>
       <c r="L419" s="7"/>
@@ -15475,22 +15583,22 @@
       </c>
       <c r="D420" s="7"/>
       <c t="s" r="E420" s="7">
-        <v>564</v>
+        <v>581</v>
       </c>
       <c r="F420" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G420" s="8">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c t="s" r="H420" s="8">
         <v>72</v>
       </c>
       <c t="s" r="I420" s="7">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c t="s" r="J420" s="7">
-        <v>390</v>
+        <v>396</v>
       </c>
       <c r="K420" s="7"/>
       <c r="L420" s="7"/>
@@ -15525,7 +15633,7 @@
       </c>
       <c r="D422" s="7"/>
       <c t="s" r="E422" s="7">
-        <v>566</v>
+        <v>583</v>
       </c>
       <c r="F422" s="7">
         <v>321</v>
@@ -15534,7 +15642,7 @@
         <v>50</v>
       </c>
       <c t="s" r="H422" s="8">
-        <v>485</v>
+        <v>495</v>
       </c>
       <c t="s" r="I422" s="7">
         <v>61</v>
@@ -15560,27 +15668,27 @@
       </c>
       <c r="D423" s="7"/>
       <c t="s" r="E423" s="7">
-        <v>566</v>
+        <v>583</v>
       </c>
       <c r="F423" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G423" s="8">
-        <v>485</v>
+        <v>495</v>
       </c>
       <c t="s" r="H423" s="8">
         <v>57</v>
       </c>
       <c t="s" r="I423" s="7">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c t="s" r="J423" s="7">
-        <v>545</v>
+        <v>560</v>
       </c>
       <c r="K423" s="7"/>
       <c r="L423" s="7"/>
       <c t="s" r="M423" s="7">
-        <v>429</v>
+        <v>436</v>
       </c>
     </row>
     <row r="424" ht="14.25" customHeight="1">
@@ -15595,7 +15703,7 @@
       </c>
       <c r="D424" s="7"/>
       <c t="s" r="E424" s="7">
-        <v>566</v>
+        <v>583</v>
       </c>
       <c r="F424" s="7">
         <v>321</v>
@@ -15604,10 +15712,10 @@
         <v>57</v>
       </c>
       <c t="s" r="H424" s="8">
-        <v>485</v>
+        <v>495</v>
       </c>
       <c t="s" r="I424" s="7">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c t="s" r="J424" s="7">
         <v>106</v>
@@ -15630,13 +15738,13 @@
       </c>
       <c r="D425" s="7"/>
       <c t="s" r="E425" s="7">
-        <v>566</v>
+        <v>583</v>
       </c>
       <c r="F425" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G425" s="8">
-        <v>485</v>
+        <v>495</v>
       </c>
       <c t="s" r="H425" s="8">
         <v>57</v>
@@ -15650,7 +15758,7 @@
       <c r="K425" s="7"/>
       <c r="L425" s="7"/>
       <c t="s" r="M425" s="7">
-        <v>567</v>
+        <v>584</v>
       </c>
     </row>
     <row r="426" ht="14.25" customHeight="1">
@@ -15680,7 +15788,7 @@
       </c>
       <c r="D427" s="7"/>
       <c t="s" r="E427" s="7">
-        <v>568</v>
+        <v>585</v>
       </c>
       <c r="F427" s="7">
         <v>321</v>
@@ -15689,10 +15797,10 @@
         <v>50</v>
       </c>
       <c t="s" r="H427" s="8">
-        <v>569</v>
+        <v>586</v>
       </c>
       <c t="s" r="I427" s="7">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c t="s" r="J427" s="7">
         <v>66</v>
@@ -15715,13 +15823,13 @@
       </c>
       <c r="D428" s="7"/>
       <c t="s" r="E428" s="7">
-        <v>568</v>
+        <v>585</v>
       </c>
       <c r="F428" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G428" s="8">
-        <v>569</v>
+        <v>586</v>
       </c>
       <c t="s" r="H428" s="8">
         <v>50</v>
@@ -15735,7 +15843,7 @@
       <c r="K428" s="7"/>
       <c r="L428" s="7"/>
       <c t="s" r="M428" s="7">
-        <v>343</v>
+        <v>347</v>
       </c>
     </row>
     <row r="429" ht="14.25" customHeight="1">
@@ -15750,7 +15858,7 @@
       </c>
       <c r="D429" s="7"/>
       <c t="s" r="E429" s="7">
-        <v>568</v>
+        <v>585</v>
       </c>
       <c r="F429" s="7">
         <v>321</v>
@@ -15759,18 +15867,18 @@
         <v>50</v>
       </c>
       <c t="s" r="H429" s="8">
-        <v>570</v>
+        <v>587</v>
       </c>
       <c t="s" r="I429" s="7">
         <v>269</v>
       </c>
       <c t="s" r="J429" s="7">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K429" s="7"/>
       <c r="L429" s="7"/>
       <c t="s" r="M429" s="7">
-        <v>571</v>
+        <v>588</v>
       </c>
     </row>
     <row r="430" ht="15" customHeight="1">
@@ -15785,13 +15893,13 @@
       </c>
       <c r="D430" s="7"/>
       <c t="s" r="E430" s="7">
-        <v>568</v>
+        <v>585</v>
       </c>
       <c r="F430" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G430" s="8">
-        <v>570</v>
+        <v>587</v>
       </c>
       <c t="s" r="H430" s="8">
         <v>50</v>
@@ -15800,12 +15908,12 @@
         <v>292</v>
       </c>
       <c t="s" r="J430" s="7">
-        <v>495</v>
+        <v>506</v>
       </c>
       <c r="K430" s="7"/>
       <c r="L430" s="7"/>
       <c t="s" r="M430" s="7">
-        <v>572</v>
+        <v>589</v>
       </c>
     </row>
     <row r="431" ht="14.25" customHeight="1">
@@ -15835,7 +15943,7 @@
       </c>
       <c r="D432" s="7"/>
       <c t="s" r="E432" s="7">
-        <v>573</v>
+        <v>590</v>
       </c>
       <c r="F432" s="7">
         <v>321</v>
@@ -15850,12 +15958,12 @@
         <v>231</v>
       </c>
       <c t="s" r="J432" s="7">
-        <v>387</v>
+        <v>393</v>
       </c>
       <c r="K432" s="7"/>
       <c r="L432" s="7"/>
       <c t="s" r="M432" s="7">
-        <v>574</v>
+        <v>591</v>
       </c>
     </row>
     <row r="433" ht="14.25" customHeight="1">
@@ -15870,7 +15978,7 @@
       </c>
       <c r="D433" s="7"/>
       <c t="s" r="E433" s="7">
-        <v>573</v>
+        <v>590</v>
       </c>
       <c r="F433" s="7">
         <v>321</v>
@@ -15882,15 +15990,15 @@
         <v>50</v>
       </c>
       <c t="s" r="I433" s="7">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c t="s" r="J433" s="7">
-        <v>525</v>
+        <v>539</v>
       </c>
       <c r="K433" s="7"/>
       <c r="L433" s="7"/>
       <c t="s" r="M433" s="7">
-        <v>575</v>
+        <v>592</v>
       </c>
     </row>
     <row r="434" ht="14.25" customHeight="1">
@@ -15905,7 +16013,7 @@
       </c>
       <c r="D434" s="7"/>
       <c t="s" r="E434" s="7">
-        <v>573</v>
+        <v>590</v>
       </c>
       <c r="F434" s="7">
         <v>321</v>
@@ -15917,7 +16025,7 @@
         <v>119</v>
       </c>
       <c t="s" r="I434" s="7">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c t="s" r="J434" s="7">
         <v>296</v>
@@ -15940,7 +16048,7 @@
       </c>
       <c r="D435" s="7"/>
       <c t="s" r="E435" s="7">
-        <v>573</v>
+        <v>590</v>
       </c>
       <c r="F435" s="7">
         <v>321</v>
@@ -15952,10 +16060,10 @@
         <v>50</v>
       </c>
       <c t="s" r="I435" s="7">
-        <v>461</v>
+        <v>469</v>
       </c>
       <c t="s" r="J435" s="7">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="K435" s="7"/>
       <c r="L435" s="7"/>
@@ -15975,7 +16083,7 @@
       </c>
       <c r="D436" s="7"/>
       <c t="s" r="E436" s="7">
-        <v>573</v>
+        <v>590</v>
       </c>
       <c r="F436" s="7">
         <v>321</v>
@@ -15987,15 +16095,15 @@
         <v>202</v>
       </c>
       <c t="s" r="I436" s="7">
-        <v>488</v>
+        <v>498</v>
       </c>
       <c t="s" r="J436" s="7">
-        <v>540</v>
+        <v>554</v>
       </c>
       <c r="K436" s="7"/>
       <c r="L436" s="7"/>
       <c t="s" r="M436" s="7">
-        <v>576</v>
+        <v>593</v>
       </c>
     </row>
     <row r="437" ht="14.25" customHeight="1">
@@ -16010,7 +16118,7 @@
       </c>
       <c r="D437" s="7"/>
       <c t="s" r="E437" s="7">
-        <v>573</v>
+        <v>590</v>
       </c>
       <c r="F437" s="7">
         <v>321</v>
@@ -16022,15 +16130,15 @@
         <v>50</v>
       </c>
       <c t="s" r="I437" s="7">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c t="s" r="J437" s="7">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="K437" s="7"/>
       <c r="L437" s="7"/>
       <c t="s" r="M437" s="7">
-        <v>577</v>
+        <v>594</v>
       </c>
     </row>
     <row r="438" ht="14.25" customHeight="1">
@@ -16060,7 +16168,7 @@
       </c>
       <c r="D439" s="7"/>
       <c t="s" r="E439" s="7">
-        <v>578</v>
+        <v>595</v>
       </c>
       <c r="F439" s="7">
         <v>321</v>
@@ -16080,7 +16188,7 @@
       <c r="K439" s="7"/>
       <c r="L439" s="7"/>
       <c t="s" r="M439" s="7">
-        <v>579</v>
+        <v>596</v>
       </c>
     </row>
     <row r="440" ht="15" customHeight="1">
@@ -16095,7 +16203,7 @@
       </c>
       <c r="D440" s="7"/>
       <c t="s" r="E440" s="7">
-        <v>578</v>
+        <v>595</v>
       </c>
       <c r="F440" s="7">
         <v>321</v>
@@ -16107,15 +16215,15 @@
         <v>50</v>
       </c>
       <c t="s" r="I440" s="7">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c t="s" r="J440" s="7">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="K440" s="7"/>
       <c r="L440" s="7"/>
       <c t="s" r="M440" s="7">
-        <v>580</v>
+        <v>597</v>
       </c>
     </row>
     <row r="441" ht="14.25" customHeight="1">
@@ -16130,7 +16238,7 @@
       </c>
       <c r="D441" s="7"/>
       <c t="s" r="E441" s="7">
-        <v>578</v>
+        <v>595</v>
       </c>
       <c r="F441" s="7">
         <v>321</v>
@@ -16142,7 +16250,7 @@
         <v>225</v>
       </c>
       <c t="s" r="I441" s="7">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c t="s" r="J441" s="7">
         <v>203</v>
@@ -16165,7 +16273,7 @@
       </c>
       <c r="D442" s="7"/>
       <c t="s" r="E442" s="7">
-        <v>578</v>
+        <v>595</v>
       </c>
       <c r="F442" s="7">
         <v>321</v>
@@ -16177,7 +16285,7 @@
         <v>50</v>
       </c>
       <c t="s" r="I442" s="7">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c t="s" r="J442" s="7">
         <v>221</v>
@@ -16185,7 +16293,7 @@
       <c r="K442" s="7"/>
       <c r="L442" s="7"/>
       <c t="s" r="M442" s="7">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="443" ht="14.25" customHeight="1">
@@ -16200,7 +16308,7 @@
       </c>
       <c r="D443" s="7"/>
       <c t="s" r="E443" s="7">
-        <v>578</v>
+        <v>595</v>
       </c>
       <c r="F443" s="7">
         <v>321</v>
@@ -16215,12 +16323,12 @@
         <v>269</v>
       </c>
       <c t="s" r="J443" s="7">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="K443" s="7"/>
       <c r="L443" s="7"/>
       <c t="s" r="M443" s="7">
-        <v>539</v>
+        <v>553</v>
       </c>
     </row>
     <row r="444" ht="14.25" customHeight="1">
@@ -16235,7 +16343,7 @@
       </c>
       <c r="D444" s="7"/>
       <c t="s" r="E444" s="7">
-        <v>578</v>
+        <v>595</v>
       </c>
       <c r="F444" s="7">
         <v>321</v>
@@ -16247,15 +16355,15 @@
         <v>50</v>
       </c>
       <c t="s" r="I444" s="7">
-        <v>581</v>
+        <v>598</v>
       </c>
       <c t="s" r="J444" s="7">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="K444" s="7"/>
       <c r="L444" s="7"/>
       <c t="s" r="M444" s="7">
-        <v>582</v>
+        <v>599</v>
       </c>
     </row>
     <row r="445" ht="15" customHeight="1">
@@ -16285,7 +16393,7 @@
       </c>
       <c r="D446" s="7"/>
       <c t="s" r="E446" s="7">
-        <v>583</v>
+        <v>600</v>
       </c>
       <c r="F446" s="7">
         <v>320</v>
@@ -16297,15 +16405,15 @@
         <v>101</v>
       </c>
       <c t="s" r="I446" s="7">
+        <v>156</v>
+      </c>
+      <c t="s" r="J446" s="7">
         <v>157</v>
-      </c>
-      <c t="s" r="J446" s="7">
-        <v>158</v>
       </c>
       <c r="K446" s="7"/>
       <c r="L446" s="7"/>
       <c t="s" r="M446" s="7">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="447" ht="14.25" customHeight="1">
@@ -16320,7 +16428,7 @@
       </c>
       <c r="D447" s="7"/>
       <c t="s" r="E447" s="7">
-        <v>583</v>
+        <v>600</v>
       </c>
       <c r="F447" s="7">
         <v>320</v>
@@ -16340,7 +16448,7 @@
       <c r="K447" s="7"/>
       <c r="L447" s="7"/>
       <c t="s" r="M447" s="7">
-        <v>584</v>
+        <v>601</v>
       </c>
     </row>
     <row r="448" ht="14.25" customHeight="1">
@@ -16355,7 +16463,7 @@
       </c>
       <c r="D448" s="7"/>
       <c t="s" r="E448" s="7">
-        <v>583</v>
+        <v>600</v>
       </c>
       <c r="F448" s="7">
         <v>320</v>
@@ -16367,7 +16475,7 @@
         <v>101</v>
       </c>
       <c t="s" r="I448" s="7">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c t="s" r="J448" s="7">
         <v>19</v>
@@ -16375,7 +16483,7 @@
       <c r="K448" s="7"/>
       <c r="L448" s="7"/>
       <c t="s" r="M448" s="7">
-        <v>585</v>
+        <v>602</v>
       </c>
     </row>
     <row r="449" ht="14.25" customHeight="1">
@@ -16390,7 +16498,7 @@
       </c>
       <c r="D449" s="7"/>
       <c t="s" r="E449" s="7">
-        <v>583</v>
+        <v>600</v>
       </c>
       <c r="F449" s="7">
         <v>320</v>
@@ -16410,7 +16518,7 @@
       <c r="K449" s="7"/>
       <c r="L449" s="7"/>
       <c t="s" r="M449" s="7">
-        <v>586</v>
+        <v>603</v>
       </c>
     </row>
     <row r="450" ht="15" customHeight="1">
@@ -16425,7 +16533,7 @@
       </c>
       <c r="D450" s="7"/>
       <c t="s" r="E450" s="7">
-        <v>583</v>
+        <v>600</v>
       </c>
       <c r="F450" s="7">
         <v>320</v>
@@ -16440,12 +16548,12 @@
         <v>301</v>
       </c>
       <c t="s" r="J450" s="7">
-        <v>473</v>
+        <v>482</v>
       </c>
       <c r="K450" s="7"/>
       <c r="L450" s="7"/>
       <c t="s" r="M450" s="7">
-        <v>587</v>
+        <v>604</v>
       </c>
     </row>
     <row r="451" ht="14.25" customHeight="1">
@@ -16460,7 +16568,7 @@
       </c>
       <c r="D451" s="7"/>
       <c t="s" r="E451" s="7">
-        <v>583</v>
+        <v>600</v>
       </c>
       <c r="F451" s="7">
         <v>320</v>
@@ -16472,14 +16580,16 @@
         <v>17</v>
       </c>
       <c t="s" r="I451" s="7">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c t="s" r="J451" s="7">
         <v>215</v>
       </c>
       <c r="K451" s="7"/>
       <c r="L451" s="7"/>
-      <c r="M451" s="7"/>
+      <c t="s" r="M451" s="7">
+        <v>605</v>
+      </c>
     </row>
     <row r="452" ht="14.25" customHeight="1">
       <c r="A452" s="6"/>
@@ -16508,7 +16618,7 @@
       </c>
       <c r="D453" s="7"/>
       <c t="s" r="E453" s="7">
-        <v>588</v>
+        <v>606</v>
       </c>
       <c r="F453" s="7">
         <v>321</v>
@@ -16523,7 +16633,7 @@
         <v>18</v>
       </c>
       <c t="s" r="J453" s="7">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="K453" s="7"/>
       <c r="L453" s="7"/>
@@ -16543,7 +16653,7 @@
       </c>
       <c r="D454" s="7"/>
       <c t="s" r="E454" s="7">
-        <v>588</v>
+        <v>606</v>
       </c>
       <c r="F454" s="7">
         <v>321</v>
@@ -16563,7 +16673,7 @@
       <c r="K454" s="7"/>
       <c r="L454" s="7"/>
       <c t="s" r="M454" s="7">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="455" ht="15" customHeight="1">
@@ -16578,7 +16688,7 @@
       </c>
       <c r="D455" s="7"/>
       <c t="s" r="E455" s="7">
-        <v>588</v>
+        <v>606</v>
       </c>
       <c r="F455" s="7">
         <v>321</v>
@@ -16598,7 +16708,7 @@
       <c r="K455" s="7"/>
       <c r="L455" s="7"/>
       <c t="s" r="M455" s="7">
-        <v>576</v>
+        <v>593</v>
       </c>
     </row>
     <row r="456" ht="14.25" customHeight="1">
@@ -16613,7 +16723,7 @@
       </c>
       <c r="D456" s="7"/>
       <c t="s" r="E456" s="7">
-        <v>588</v>
+        <v>606</v>
       </c>
       <c r="F456" s="7">
         <v>321</v>
@@ -16625,7 +16735,7 @@
         <v>225</v>
       </c>
       <c t="s" r="I456" s="7">
-        <v>370</v>
+        <v>376</v>
       </c>
       <c t="s" r="J456" s="7">
         <v>286</v>
@@ -16633,7 +16743,7 @@
       <c r="K456" s="7"/>
       <c r="L456" s="7"/>
       <c t="s" r="M456" s="7">
-        <v>589</v>
+        <v>607</v>
       </c>
     </row>
     <row r="457" ht="14.25" customHeight="1">
@@ -16648,7 +16758,7 @@
       </c>
       <c r="D457" s="7"/>
       <c t="s" r="E457" s="7">
-        <v>588</v>
+        <v>606</v>
       </c>
       <c r="F457" s="7">
         <v>321</v>
@@ -16660,17 +16770,17 @@
         <v>50</v>
       </c>
       <c t="s" r="I457" s="7">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c t="s" r="J457" s="7">
         <v>226</v>
       </c>
       <c t="s" r="K457" s="7">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="L457" s="7"/>
       <c t="s" r="M457" s="7">
-        <v>195</v>
+        <v>608</v>
       </c>
     </row>
     <row r="458" ht="14.25" customHeight="1">
@@ -16700,7 +16810,7 @@
       </c>
       <c r="D459" s="7"/>
       <c t="s" r="E459" s="7">
-        <v>590</v>
+        <v>609</v>
       </c>
       <c r="F459" s="7">
         <v>321</v>
@@ -16712,7 +16822,7 @@
         <v>33</v>
       </c>
       <c t="s" r="I459" s="7">
-        <v>591</v>
+        <v>610</v>
       </c>
       <c t="s" r="J459" s="7">
         <v>217</v>
@@ -16735,7 +16845,7 @@
       </c>
       <c r="D460" s="7"/>
       <c t="s" r="E460" s="7">
-        <v>590</v>
+        <v>609</v>
       </c>
       <c r="F460" s="7">
         <v>321</v>
@@ -16750,12 +16860,12 @@
         <v>41</v>
       </c>
       <c t="s" r="J460" s="7">
-        <v>134</v>
+        <v>328</v>
       </c>
       <c r="K460" s="7"/>
       <c r="L460" s="7"/>
       <c t="s" r="M460" s="7">
-        <v>592</v>
+        <v>611</v>
       </c>
     </row>
     <row r="461" ht="14.25" customHeight="1">
@@ -16785,7 +16895,7 @@
       </c>
       <c r="D462" s="7"/>
       <c t="s" r="E462" s="7">
-        <v>593</v>
+        <v>612</v>
       </c>
       <c r="F462" s="7">
         <v>321</v>
@@ -16797,15 +16907,15 @@
         <v>57</v>
       </c>
       <c t="s" r="I462" s="7">
-        <v>594</v>
+        <v>613</v>
       </c>
       <c t="s" r="J462" s="7">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="K462" s="7"/>
       <c r="L462" s="7"/>
       <c t="s" r="M462" s="7">
-        <v>595</v>
+        <v>614</v>
       </c>
     </row>
     <row r="463" ht="14.25" customHeight="1">
@@ -16820,7 +16930,7 @@
       </c>
       <c r="D463" s="7"/>
       <c t="s" r="E463" s="7">
-        <v>593</v>
+        <v>612</v>
       </c>
       <c r="F463" s="7">
         <v>321</v>
@@ -16832,15 +16942,15 @@
         <v>50</v>
       </c>
       <c t="s" r="I463" s="7">
-        <v>403</v>
+        <v>409</v>
       </c>
       <c t="s" r="J463" s="7">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="K463" s="7"/>
       <c r="L463" s="7"/>
       <c t="s" r="M463" s="7">
-        <v>596</v>
+        <v>615</v>
       </c>
     </row>
     <row r="464" ht="14.25" customHeight="1">
@@ -16855,7 +16965,7 @@
       </c>
       <c r="D464" s="7"/>
       <c t="s" r="E464" s="7">
-        <v>593</v>
+        <v>612</v>
       </c>
       <c r="F464" s="7">
         <v>321</v>
@@ -16867,10 +16977,10 @@
         <v>33</v>
       </c>
       <c t="s" r="I464" s="7">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c t="s" r="J464" s="7">
-        <v>525</v>
+        <v>539</v>
       </c>
       <c r="K464" s="7"/>
       <c r="L464" s="7"/>
@@ -16890,7 +17000,7 @@
       </c>
       <c r="D465" s="7"/>
       <c t="s" r="E465" s="7">
-        <v>593</v>
+        <v>612</v>
       </c>
       <c r="F465" s="7">
         <v>321</v>
@@ -16902,7 +17012,7 @@
         <v>50</v>
       </c>
       <c t="s" r="I465" s="7">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c t="s" r="J465" s="7">
         <v>203</v>
@@ -16910,7 +17020,7 @@
       <c r="K465" s="7"/>
       <c r="L465" s="7"/>
       <c t="s" r="M465" s="7">
-        <v>597</v>
+        <v>616</v>
       </c>
     </row>
     <row r="466" ht="14.25" customHeight="1">
@@ -16925,7 +17035,7 @@
       </c>
       <c r="D466" s="7"/>
       <c t="s" r="E466" s="7">
-        <v>593</v>
+        <v>612</v>
       </c>
       <c r="F466" s="7">
         <v>321</v>
@@ -16960,7 +17070,7 @@
       </c>
       <c r="D467" s="7"/>
       <c t="s" r="E467" s="7">
-        <v>593</v>
+        <v>612</v>
       </c>
       <c r="F467" s="7">
         <v>321</v>
@@ -16980,7 +17090,7 @@
       <c r="K467" s="7"/>
       <c r="L467" s="7"/>
       <c t="s" r="M467" s="7">
-        <v>496</v>
+        <v>507</v>
       </c>
     </row>
     <row r="468" ht="14.25" customHeight="1">
@@ -17010,7 +17120,7 @@
       </c>
       <c r="D469" s="7"/>
       <c t="s" r="E469" s="7">
-        <v>598</v>
+        <v>617</v>
       </c>
       <c r="F469" s="7">
         <v>320</v>
@@ -17025,14 +17135,14 @@
         <v>77</v>
       </c>
       <c t="s" r="J469" s="7">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c t="s" r="K469" s="7">
         <v>77</v>
       </c>
       <c r="L469" s="7"/>
       <c t="s" r="M469" s="7">
-        <v>535</v>
+        <v>549</v>
       </c>
     </row>
     <row r="470" ht="15" customHeight="1">
@@ -17047,7 +17157,7 @@
       </c>
       <c r="D470" s="7"/>
       <c t="s" r="E470" s="7">
-        <v>598</v>
+        <v>617</v>
       </c>
       <c r="F470" s="7">
         <v>320</v>
@@ -17056,18 +17166,18 @@
         <v>50</v>
       </c>
       <c t="s" r="H470" s="8">
-        <v>517</v>
+        <v>530</v>
       </c>
       <c t="s" r="I470" s="7">
+        <v>150</v>
+      </c>
+      <c t="s" r="J470" s="7">
         <v>151</v>
-      </c>
-      <c t="s" r="J470" s="7">
-        <v>152</v>
       </c>
       <c r="K470" s="7"/>
       <c r="L470" s="7"/>
       <c t="s" r="M470" s="7">
-        <v>599</v>
+        <v>618</v>
       </c>
     </row>
     <row r="471" ht="14.25" customHeight="1">
@@ -17082,19 +17192,19 @@
       </c>
       <c r="D471" s="7"/>
       <c t="s" r="E471" s="7">
-        <v>598</v>
+        <v>617</v>
       </c>
       <c r="F471" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G471" s="8">
-        <v>517</v>
+        <v>530</v>
       </c>
       <c t="s" r="H471" s="8">
         <v>50</v>
       </c>
       <c t="s" r="I471" s="7">
-        <v>390</v>
+        <v>396</v>
       </c>
       <c t="s" r="J471" s="7">
         <v>223</v>
@@ -17102,7 +17212,7 @@
       <c r="K471" s="7"/>
       <c r="L471" s="7"/>
       <c t="s" r="M471" s="7">
-        <v>600</v>
+        <v>619</v>
       </c>
     </row>
     <row r="472" ht="14.25" customHeight="1">
@@ -17117,7 +17227,7 @@
       </c>
       <c r="D472" s="7"/>
       <c t="s" r="E472" s="7">
-        <v>598</v>
+        <v>617</v>
       </c>
       <c r="F472" s="7">
         <v>320</v>
@@ -17126,10 +17236,10 @@
         <v>50</v>
       </c>
       <c t="s" r="H472" s="8">
-        <v>452</v>
+        <v>460</v>
       </c>
       <c t="s" r="I472" s="7">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c t="s" r="J472" s="7">
         <v>41</v>
@@ -17137,7 +17247,7 @@
       <c r="K472" s="7"/>
       <c r="L472" s="7"/>
       <c t="s" r="M472" s="7">
-        <v>601</v>
+        <v>620</v>
       </c>
     </row>
     <row r="473" ht="14.25" customHeight="1">
@@ -17152,22 +17262,22 @@
       </c>
       <c r="D473" s="7"/>
       <c t="s" r="E473" s="7">
-        <v>598</v>
+        <v>617</v>
       </c>
       <c r="F473" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G473" s="8">
-        <v>452</v>
+        <v>460</v>
       </c>
       <c t="s" r="H473" s="8">
         <v>50</v>
       </c>
       <c t="s" r="I473" s="7">
+        <v>141</v>
+      </c>
+      <c t="s" r="J473" s="7">
         <v>142</v>
-      </c>
-      <c t="s" r="J473" s="7">
-        <v>143</v>
       </c>
       <c r="K473" s="7"/>
       <c r="L473" s="7"/>
@@ -17202,7 +17312,7 @@
       </c>
       <c r="D475" s="7"/>
       <c t="s" r="E475" s="7">
-        <v>602</v>
+        <v>621</v>
       </c>
       <c r="F475" s="7">
         <v>330</v>
@@ -17211,18 +17321,18 @@
         <v>57</v>
       </c>
       <c t="s" r="H475" s="8">
-        <v>603</v>
+        <v>622</v>
       </c>
       <c t="s" r="I475" s="7">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c t="s" r="J475" s="7">
-        <v>394</v>
+        <v>400</v>
       </c>
       <c r="K475" s="7"/>
       <c r="L475" s="7"/>
       <c t="s" r="M475" s="7">
-        <v>604</v>
+        <v>623</v>
       </c>
     </row>
     <row r="476" ht="14.25" customHeight="1">
@@ -17237,22 +17347,22 @@
       </c>
       <c r="D476" s="7"/>
       <c t="s" r="E476" s="7">
-        <v>602</v>
+        <v>621</v>
       </c>
       <c r="F476" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G476" s="8">
-        <v>603</v>
+        <v>622</v>
       </c>
       <c t="s" r="H476" s="8">
         <v>57</v>
       </c>
       <c t="s" r="I476" s="7">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c t="s" r="J476" s="7">
-        <v>605</v>
+        <v>624</v>
       </c>
       <c r="K476" s="7"/>
       <c r="L476" s="7"/>
@@ -17285,7 +17395,7 @@
       </c>
       <c r="D478" s="7"/>
       <c t="s" r="E478" s="7">
-        <v>606</v>
+        <v>625</v>
       </c>
       <c r="F478" s="7">
         <v>330</v>
@@ -17297,7 +17407,7 @@
         <v>72</v>
       </c>
       <c t="s" r="I478" s="7">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c t="s" r="J478" s="7">
         <v>94</v>
@@ -17320,7 +17430,7 @@
       </c>
       <c r="D479" s="7"/>
       <c t="s" r="E479" s="7">
-        <v>606</v>
+        <v>625</v>
       </c>
       <c r="F479" s="7">
         <v>330</v>
@@ -17329,10 +17439,10 @@
         <v>72</v>
       </c>
       <c t="s" r="H479" s="8">
-        <v>607</v>
+        <v>626</v>
       </c>
       <c t="s" r="I479" s="7">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c t="s" r="J479" s="7">
         <v>259</v>
@@ -17340,7 +17450,7 @@
       <c r="K479" s="7"/>
       <c r="L479" s="7"/>
       <c t="s" r="M479" s="7">
-        <v>385</v>
+        <v>391</v>
       </c>
     </row>
     <row r="480" ht="15" customHeight="1">
@@ -17370,7 +17480,7 @@
       </c>
       <c r="D481" s="7"/>
       <c t="s" r="E481" s="7">
-        <v>608</v>
+        <v>627</v>
       </c>
       <c r="F481" s="7">
         <v>330</v>
@@ -17379,7 +17489,7 @@
         <v>72</v>
       </c>
       <c t="s" r="H481" s="8">
-        <v>609</v>
+        <v>628</v>
       </c>
       <c t="s" r="I481" s="7">
         <v>30</v>
@@ -17390,7 +17500,7 @@
       <c r="K481" s="7"/>
       <c r="L481" s="7"/>
       <c t="s" r="M481" s="7">
-        <v>610</v>
+        <v>629</v>
       </c>
     </row>
     <row r="482" ht="14.25" customHeight="1">
@@ -17405,19 +17515,19 @@
       </c>
       <c r="D482" s="7"/>
       <c t="s" r="E482" s="7">
-        <v>608</v>
+        <v>627</v>
       </c>
       <c r="F482" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G482" s="8">
-        <v>609</v>
+        <v>628</v>
       </c>
       <c t="s" r="H482" s="8">
         <v>72</v>
       </c>
       <c t="s" r="I482" s="7">
-        <v>540</v>
+        <v>554</v>
       </c>
       <c t="s" r="J482" s="7">
         <v>280</v>
@@ -17425,7 +17535,7 @@
       <c r="K482" s="7"/>
       <c r="L482" s="7"/>
       <c t="s" r="M482" s="7">
-        <v>611</v>
+        <v>630</v>
       </c>
     </row>
     <row r="483" ht="14.25" customHeight="1">
@@ -17455,7 +17565,7 @@
       </c>
       <c r="D484" s="7"/>
       <c t="s" r="E484" s="7">
-        <v>612</v>
+        <v>631</v>
       </c>
       <c r="F484" s="7">
         <v>330</v>
@@ -17477,7 +17587,7 @@
       </c>
       <c r="L484" s="7"/>
       <c t="s" r="M484" s="7">
-        <v>613</v>
+        <v>632</v>
       </c>
     </row>
     <row r="485" ht="15" customHeight="1">
@@ -17492,7 +17602,7 @@
       </c>
       <c r="D485" s="7"/>
       <c t="s" r="E485" s="7">
-        <v>612</v>
+        <v>631</v>
       </c>
       <c r="F485" s="7">
         <v>330</v>
@@ -17501,7 +17611,7 @@
         <v>50</v>
       </c>
       <c t="s" r="H485" s="8">
-        <v>614</v>
+        <v>633</v>
       </c>
       <c t="s" r="I485" s="7">
         <v>65</v>
@@ -17527,26 +17637,28 @@
       </c>
       <c r="D486" s="7"/>
       <c t="s" r="E486" s="7">
-        <v>612</v>
+        <v>631</v>
       </c>
       <c r="F486" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G486" s="8">
-        <v>614</v>
+        <v>633</v>
       </c>
       <c t="s" r="H486" s="8">
         <v>50</v>
       </c>
       <c t="s" r="I486" s="7">
-        <v>615</v>
+        <v>634</v>
       </c>
       <c t="s" r="J486" s="7">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="K486" s="7"/>
       <c r="L486" s="7"/>
-      <c r="M486" s="7"/>
+      <c t="s" r="M486" s="7">
+        <v>635</v>
+      </c>
     </row>
     <row r="487" ht="14.25" customHeight="1">
       <c r="A487" s="6"/>
@@ -17575,7 +17687,7 @@
       </c>
       <c r="D488" s="7"/>
       <c t="s" r="E488" s="7">
-        <v>616</v>
+        <v>636</v>
       </c>
       <c r="F488" s="7">
         <v>330</v>
@@ -17584,10 +17696,10 @@
         <v>72</v>
       </c>
       <c t="s" r="H488" s="8">
-        <v>617</v>
+        <v>637</v>
       </c>
       <c t="s" r="I488" s="7">
-        <v>475</v>
+        <v>484</v>
       </c>
       <c t="s" r="J488" s="7">
         <v>297</v>
@@ -17610,26 +17722,28 @@
       </c>
       <c r="D489" s="7"/>
       <c t="s" r="E489" s="7">
-        <v>616</v>
+        <v>636</v>
       </c>
       <c r="F489" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G489" s="8">
-        <v>617</v>
+        <v>637</v>
       </c>
       <c t="s" r="H489" s="8">
         <v>72</v>
       </c>
       <c t="s" r="I489" s="7">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c t="s" r="J489" s="7">
-        <v>446</v>
+        <v>454</v>
       </c>
       <c r="K489" s="7"/>
       <c r="L489" s="7"/>
-      <c r="M489" s="7"/>
+      <c t="s" r="M489" s="7">
+        <v>638</v>
+      </c>
     </row>
     <row r="490" ht="15" customHeight="1">
       <c r="A490" s="6"/>
@@ -17658,13 +17772,13 @@
       </c>
       <c r="D491" s="7"/>
       <c t="s" r="E491" s="7">
-        <v>618</v>
+        <v>639</v>
       </c>
       <c r="F491" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G491" s="8">
-        <v>619</v>
+        <v>640</v>
       </c>
       <c t="s" r="H491" s="8">
         <v>50</v>
@@ -17678,7 +17792,7 @@
       <c r="K491" s="7"/>
       <c r="L491" s="7"/>
       <c t="s" r="M491" s="7">
-        <v>620</v>
+        <v>641</v>
       </c>
     </row>
     <row r="492" ht="14.25" customHeight="1">
@@ -17693,7 +17807,7 @@
       </c>
       <c r="D492" s="7"/>
       <c t="s" r="E492" s="7">
-        <v>618</v>
+        <v>639</v>
       </c>
       <c r="F492" s="7">
         <v>330</v>
@@ -17705,7 +17819,7 @@
         <v>57</v>
       </c>
       <c t="s" r="I492" s="7">
-        <v>370</v>
+        <v>376</v>
       </c>
       <c t="s" r="J492" s="7">
         <v>52</v>
@@ -17713,7 +17827,7 @@
       <c r="K492" s="7"/>
       <c r="L492" s="7"/>
       <c t="s" r="M492" s="7">
-        <v>621</v>
+        <v>642</v>
       </c>
     </row>
     <row r="493" ht="14.25" customHeight="1">
@@ -17743,7 +17857,7 @@
       </c>
       <c r="D494" s="7"/>
       <c t="s" r="E494" s="7">
-        <v>622</v>
+        <v>643</v>
       </c>
       <c r="F494" s="7">
         <v>330</v>
@@ -17752,18 +17866,18 @@
         <v>50</v>
       </c>
       <c t="s" r="H494" s="8">
-        <v>623</v>
+        <v>644</v>
       </c>
       <c t="s" r="I494" s="7">
         <v>35</v>
       </c>
       <c t="s" r="J494" s="7">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="K494" s="7"/>
       <c r="L494" s="7"/>
       <c t="s" r="M494" s="7">
-        <v>624</v>
+        <v>645</v>
       </c>
     </row>
     <row r="495" ht="15" customHeight="1">
@@ -17778,13 +17892,13 @@
       </c>
       <c r="D495" s="7"/>
       <c t="s" r="E495" s="7">
-        <v>622</v>
+        <v>643</v>
       </c>
       <c r="F495" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G495" s="8">
-        <v>623</v>
+        <v>644</v>
       </c>
       <c t="s" r="H495" s="8">
         <v>50</v>
@@ -17793,15 +17907,17 @@
         <v>29</v>
       </c>
       <c t="s" r="J495" s="7">
-        <v>559</v>
+        <v>576</v>
       </c>
       <c r="K495" s="7"/>
       <c r="L495" s="7"/>
-      <c r="M495" s="7"/>
+      <c t="s" r="M495" s="7">
+        <v>646</v>
+      </c>
     </row>
     <row r="496" ht="15.75" customHeight="1">
       <c t="s" r="A496" s="9">
-        <v>625</v>
+        <v>647</v>
       </c>
       <c r="B496" s="9"/>
       <c r="C496" s="9"/>
@@ -17821,7 +17937,7 @@
     <row r="497" ht="65.25" customHeight="1"/>
     <row r="498" ht="16.5" customHeight="1">
       <c t="s" r="A498" s="10">
-        <v>626</v>
+        <v>648</v>
       </c>
       <c r="B498" s="10"/>
       <c r="C498" s="10"/>
@@ -17834,7 +17950,7 @@
       <c r="J498" s="10"/>
       <c r="K498" s="10"/>
       <c t="s" r="L498" s="11">
-        <v>627</v>
+        <v>649</v>
       </c>
       <c r="M498" s="11"/>
       <c r="N498" s="11"/>
